--- a/rates.xlsx
+++ b/rates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS COM\Dropbox\Rates Portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3C223E-DC0C-489A-BF97-2F10D47ED749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C9B9ED-71C3-4826-A889-08382BB0B7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8781,7 +8781,7 @@
         <v>2500</v>
       </c>
       <c r="F104" s="34">
-        <v>17500</v>
+        <v>21100</v>
       </c>
       <c r="G104" s="9" t="s">
         <v>1471</v>
@@ -8810,7 +8810,7 @@
         <v>2700</v>
       </c>
       <c r="F105" s="34">
-        <v>20000</v>
+        <v>22400</v>
       </c>
       <c r="G105" s="9" t="s">
         <v>1471</v>
@@ -8839,7 +8839,7 @@
         <v>2900</v>
       </c>
       <c r="F106" s="34">
-        <v>19500</v>
+        <v>23400</v>
       </c>
       <c r="G106" s="9" t="s">
         <v>1471</v>
@@ -8868,7 +8868,7 @@
         <v>2800</v>
       </c>
       <c r="F107" s="34">
-        <v>19500</v>
+        <v>22900</v>
       </c>
       <c r="G107" s="9" t="s">
         <v>1471</v>
@@ -8897,7 +8897,7 @@
         <v>2800</v>
       </c>
       <c r="F108" s="34">
-        <v>20000</v>
+        <v>22700</v>
       </c>
       <c r="G108" s="9" t="s">
         <v>1471</v>
@@ -8926,7 +8926,7 @@
         <v>2800</v>
       </c>
       <c r="F109" s="34">
-        <v>25500</v>
+        <v>22800</v>
       </c>
       <c r="G109" s="9" t="s">
         <v>1471</v>
@@ -8955,7 +8955,7 @@
         <v>3500</v>
       </c>
       <c r="F110" s="34">
-        <v>26000</v>
+        <v>28300</v>
       </c>
       <c r="G110" s="9" t="s">
         <v>1471</v>
@@ -8984,7 +8984,7 @@
         <v>3600</v>
       </c>
       <c r="F111" s="34">
-        <v>27000</v>
+        <v>29000</v>
       </c>
       <c r="G111" s="9" t="s">
         <v>1471</v>
@@ -9013,7 +9013,7 @@
         <v>3800</v>
       </c>
       <c r="F112" s="34">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="G112" s="9" t="s">
         <v>1471</v>
@@ -9042,7 +9042,7 @@
         <v>3600</v>
       </c>
       <c r="F113" s="34">
-        <v>26000</v>
+        <v>29000</v>
       </c>
       <c r="G113" s="9" t="s">
         <v>1471</v>
@@ -9071,7 +9071,7 @@
         <v>3700</v>
       </c>
       <c r="F114" s="34">
-        <v>27500</v>
+        <v>29400</v>
       </c>
       <c r="G114" s="9" t="s">
         <v>1471</v>
@@ -9100,7 +9100,7 @@
         <v>3800</v>
       </c>
       <c r="F115" s="34">
-        <v>35000</v>
+        <v>30500</v>
       </c>
       <c r="G115" s="9" t="s">
         <v>1471</v>
@@ -9129,7 +9129,7 @@
         <v>4300</v>
       </c>
       <c r="F116" s="34">
-        <v>35000</v>
+        <v>33600</v>
       </c>
       <c r="G116" s="9" t="s">
         <v>1471</v>
@@ -9158,7 +9158,7 @@
         <v>4600</v>
       </c>
       <c r="F117" s="34">
-        <v>35000</v>
+        <v>35800</v>
       </c>
       <c r="G117" s="9" t="s">
         <v>1471</v>
@@ -9187,7 +9187,7 @@
         <v>4600</v>
       </c>
       <c r="F118" s="34">
-        <v>37000</v>
+        <v>35800</v>
       </c>
       <c r="G118" s="9" t="s">
         <v>1471</v>
@@ -9216,7 +9216,7 @@
         <v>4800</v>
       </c>
       <c r="F119" s="34">
-        <v>35000</v>
+        <v>37500</v>
       </c>
       <c r="G119" s="9" t="s">
         <v>1471</v>
@@ -9245,7 +9245,7 @@
         <v>5000</v>
       </c>
       <c r="F120" s="34">
-        <v>33000</v>
+        <v>39000</v>
       </c>
       <c r="G120" s="9" t="s">
         <v>1471</v>
@@ -9274,7 +9274,7 @@
         <v>4500</v>
       </c>
       <c r="F121" s="34">
-        <v>33500</v>
+        <v>35100</v>
       </c>
       <c r="G121" s="9" t="s">
         <v>1471</v>
@@ -9303,7 +9303,7 @@
         <v>4700</v>
       </c>
       <c r="F122" s="34">
-        <v>33500</v>
+        <v>36300</v>
       </c>
       <c r="G122" s="9" t="s">
         <v>1471</v>
@@ -9332,7 +9332,7 @@
         <v>4600</v>
       </c>
       <c r="F123" s="34">
-        <v>33500</v>
+        <v>36000</v>
       </c>
       <c r="G123" s="9" t="s">
         <v>1471</v>
@@ -9361,7 +9361,7 @@
         <v>6400</v>
       </c>
       <c r="F124" s="34">
-        <v>47000</v>
+        <v>49000</v>
       </c>
       <c r="G124" s="9" t="s">
         <v>1471</v>
@@ -9390,7 +9390,7 @@
         <v>7000</v>
       </c>
       <c r="F125" s="34">
-        <v>53500</v>
+        <v>53000</v>
       </c>
       <c r="G125" s="9" t="s">
         <v>1471</v>
@@ -9419,7 +9419,7 @@
         <v>5900</v>
       </c>
       <c r="F126" s="34">
-        <v>46500</v>
+        <v>44800</v>
       </c>
       <c r="G126" s="9" t="s">
         <v>1471</v>
@@ -9448,7 +9448,7 @@
         <v>6200</v>
       </c>
       <c r="F127" s="34">
-        <v>50000</v>
+        <v>47600</v>
       </c>
       <c r="G127" s="9" t="s">
         <v>1471</v>
@@ -9477,7 +9477,7 @@
         <v>8000</v>
       </c>
       <c r="F128" s="34">
-        <v>60000</v>
+        <v>59900</v>
       </c>
       <c r="G128" s="9" t="s">
         <v>1471</v>
@@ -9506,7 +9506,7 @@
         <v>8600</v>
       </c>
       <c r="F129" s="34">
-        <v>65000</v>
+        <v>64400</v>
       </c>
       <c r="G129" s="9" t="s">
         <v>1471</v>
@@ -9535,7 +9535,7 @@
         <v>7500</v>
       </c>
       <c r="F130" s="34">
-        <v>52000</v>
+        <v>56400</v>
       </c>
       <c r="G130" s="9" t="s">
         <v>1471</v>
@@ -9564,7 +9564,7 @@
         <v>8500</v>
       </c>
       <c r="F131" s="34">
-        <v>64000</v>
+        <v>63400</v>
       </c>
       <c r="G131" s="9" t="s">
         <v>1471</v>
@@ -9593,7 +9593,7 @@
         <v>8700</v>
       </c>
       <c r="F132" s="34">
-        <v>68000</v>
+        <v>65400</v>
       </c>
       <c r="G132" s="9" t="s">
         <v>1471</v>
@@ -9622,7 +9622,7 @@
         <v>7700</v>
       </c>
       <c r="F133" s="34">
-        <v>55000</v>
+        <v>58000</v>
       </c>
       <c r="G133" s="9" t="s">
         <v>1471</v>
@@ -9651,7 +9651,7 @@
         <v>8200</v>
       </c>
       <c r="F134" s="34">
-        <v>63000</v>
+        <v>61600</v>
       </c>
       <c r="G134" s="9" t="s">
         <v>1471</v>
@@ -9680,7 +9680,7 @@
         <v>11700</v>
       </c>
       <c r="F135" s="34">
-        <v>87000</v>
+        <v>86400</v>
       </c>
       <c r="G135" s="9" t="s">
         <v>1471</v>
@@ -9709,7 +9709,7 @@
         <v>7400</v>
       </c>
       <c r="F136" s="34">
-        <v>55000</v>
+        <v>55900</v>
       </c>
       <c r="G136" s="9" t="s">
         <v>1471</v>
@@ -9738,7 +9738,7 @@
         <v>9000</v>
       </c>
       <c r="F137" s="34">
-        <v>68000</v>
+        <v>67100</v>
       </c>
       <c r="G137" s="9" t="s">
         <v>1471</v>
@@ -9767,7 +9767,7 @@
         <v>9100</v>
       </c>
       <c r="F138" s="34">
-        <v>68000</v>
+        <v>67700</v>
       </c>
       <c r="G138" s="9" t="s">
         <v>1471</v>
@@ -9796,7 +9796,7 @@
         <v>11800</v>
       </c>
       <c r="F139" s="34">
-        <v>90000</v>
+        <v>87400</v>
       </c>
       <c r="G139" s="9" t="s">
         <v>1471</v>
@@ -9825,7 +9825,7 @@
         <v>9400</v>
       </c>
       <c r="F140" s="34">
-        <v>67500</v>
+        <v>69800</v>
       </c>
       <c r="G140" s="9" t="s">
         <v>1471</v>
@@ -9854,7 +9854,7 @@
         <v>10100</v>
       </c>
       <c r="F141" s="34">
-        <v>75000</v>
+        <v>75300</v>
       </c>
       <c r="G141" s="9" t="s">
         <v>1471</v>
@@ -9883,7 +9883,7 @@
         <v>11400</v>
       </c>
       <c r="F142" s="34">
-        <v>85000</v>
+        <v>84400</v>
       </c>
       <c r="G142" s="9" t="s">
         <v>1471</v>
@@ -9912,7 +9912,7 @@
         <v>11100</v>
       </c>
       <c r="F143" s="34">
-        <v>81000</v>
+        <v>82500</v>
       </c>
       <c r="G143" s="9" t="s">
         <v>1471</v>
@@ -9941,7 +9941,7 @@
         <v>10600</v>
       </c>
       <c r="F144" s="34">
-        <v>77000</v>
+        <v>78900</v>
       </c>
       <c r="G144" s="9" t="s">
         <v>1471</v>
@@ -9970,7 +9970,7 @@
         <v>10300</v>
       </c>
       <c r="F145" s="34">
-        <v>85000</v>
+        <v>76500</v>
       </c>
       <c r="G145" s="9" t="s">
         <v>1471</v>
@@ -9999,7 +9999,7 @@
         <v>14100</v>
       </c>
       <c r="F146" s="34">
-        <v>105000</v>
+        <v>103500</v>
       </c>
       <c r="G146" s="9" t="s">
         <v>1471</v>
@@ -10028,7 +10028,7 @@
         <v>11200</v>
       </c>
       <c r="F147" s="34">
-        <v>85000</v>
+        <v>83300</v>
       </c>
       <c r="G147" s="9" t="s">
         <v>1471</v>
@@ -10086,7 +10086,7 @@
         <v>19600</v>
       </c>
       <c r="F149" s="34">
-        <v>142500</v>
+        <v>142800</v>
       </c>
       <c r="G149" s="9" t="s">
         <v>1471</v>
@@ -10115,7 +10115,7 @@
         <v>11300</v>
       </c>
       <c r="F150" s="34">
-        <v>82000</v>
+        <v>83500</v>
       </c>
       <c r="G150" s="9" t="s">
         <v>1471</v>
@@ -10144,7 +10144,7 @@
         <v>11700</v>
       </c>
       <c r="F151" s="34">
-        <v>85000</v>
+        <v>86200</v>
       </c>
       <c r="G151" s="9" t="s">
         <v>1471</v>
@@ -10173,7 +10173,7 @@
         <v>12200</v>
       </c>
       <c r="F152" s="34">
-        <v>88000</v>
+        <v>90200</v>
       </c>
       <c r="G152" s="9" t="s">
         <v>1471</v>
@@ -10202,7 +10202,7 @@
         <v>12500</v>
       </c>
       <c r="F153" s="34">
-        <v>90000</v>
+        <v>92200</v>
       </c>
       <c r="G153" s="9" t="s">
         <v>1471</v>
@@ -10231,7 +10231,7 @@
         <v>14300</v>
       </c>
       <c r="F154" s="34">
-        <v>105000</v>
+        <v>105400</v>
       </c>
       <c r="G154" s="9" t="s">
         <v>1471</v>
@@ -10260,7 +10260,7 @@
         <v>15700</v>
       </c>
       <c r="F155" s="34">
-        <v>115000</v>
+        <v>115300</v>
       </c>
       <c r="G155" s="9" t="s">
         <v>1471</v>
@@ -10289,7 +10289,7 @@
         <v>13700</v>
       </c>
       <c r="F156" s="34">
-        <v>105000</v>
+        <v>100800</v>
       </c>
       <c r="G156" s="9" t="s">
         <v>1471</v>
@@ -10318,7 +10318,7 @@
         <v>23900</v>
       </c>
       <c r="F157" s="34">
-        <v>173500</v>
+        <v>173600</v>
       </c>
       <c r="G157" s="9" t="s">
         <v>1471</v>
@@ -10347,7 +10347,7 @@
         <v>19600</v>
       </c>
       <c r="F158" s="34">
-        <v>140999</v>
+        <v>142800</v>
       </c>
       <c r="G158" s="9" t="s">
         <v>1471</v>
@@ -10376,7 +10376,7 @@
         <v>20400</v>
       </c>
       <c r="F159" s="34">
-        <v>145000</v>
+        <v>148500</v>
       </c>
       <c r="G159" s="9" t="s">
         <v>1471</v>
@@ -10405,7 +10405,7 @@
         <v>18900</v>
       </c>
       <c r="F160" s="34">
-        <v>143000</v>
+        <v>137900</v>
       </c>
       <c r="G160" s="9" t="s">
         <v>1471</v>
@@ -10434,7 +10434,7 @@
         <v>22300</v>
       </c>
       <c r="F161" s="34">
-        <v>165000</v>
+        <v>162500</v>
       </c>
       <c r="G161" s="9" t="s">
         <v>1471</v>
@@ -10463,7 +10463,7 @@
         <v>20300</v>
       </c>
       <c r="F162" s="34">
-        <v>145000</v>
+        <v>147700</v>
       </c>
       <c r="G162" s="9" t="s">
         <v>1471</v>
@@ -10492,7 +10492,7 @@
         <v>23600</v>
       </c>
       <c r="F163" s="34">
-        <v>169500</v>
+        <v>171200</v>
       </c>
       <c r="G163" s="9" t="s">
         <v>1471</v>
@@ -10521,7 +10521,7 @@
         <v>24400</v>
       </c>
       <c r="F164" s="34">
-        <v>175500</v>
+        <v>177500</v>
       </c>
       <c r="G164" s="9" t="s">
         <v>1471</v>
@@ -10550,7 +10550,7 @@
         <v>27500</v>
       </c>
       <c r="F165" s="34">
-        <v>196500</v>
+        <v>199700</v>
       </c>
       <c r="G165" s="9" t="s">
         <v>1471</v>
@@ -10579,7 +10579,7 @@
         <v>27800</v>
       </c>
       <c r="F166" s="34">
-        <v>198500</v>
+        <v>201700</v>
       </c>
       <c r="G166" s="9" t="s">
         <v>1471</v>
@@ -10608,7 +10608,7 @@
         <v>31700</v>
       </c>
       <c r="F167" s="34">
-        <v>226000</v>
+        <v>229200</v>
       </c>
       <c r="G167" s="9" t="s">
         <v>1471</v>
@@ -10637,7 +10637,7 @@
         <v>31200</v>
       </c>
       <c r="F168" s="34">
-        <v>225000</v>
+        <v>225500</v>
       </c>
       <c r="G168" s="9" t="s">
         <v>1471</v>
@@ -10666,7 +10666,7 @@
         <v>22100</v>
       </c>
       <c r="F169" s="34">
-        <v>225000</v>
+        <v>160500</v>
       </c>
       <c r="G169" s="9" t="s">
         <v>1471</v>
@@ -10695,7 +10695,7 @@
         <v>25500</v>
       </c>
       <c r="F170" s="34">
-        <v>176000</v>
+        <v>185300</v>
       </c>
       <c r="G170" s="9" t="s">
         <v>1471</v>
@@ -10724,7 +10724,7 @@
         <v>24500</v>
       </c>
       <c r="F171" s="34">
-        <v>210000</v>
+        <v>178300</v>
       </c>
       <c r="G171" s="9" t="s">
         <v>1471</v>
@@ -10753,7 +10753,7 @@
         <v>32300</v>
       </c>
       <c r="F172" s="34">
-        <v>232000</v>
+        <v>233500</v>
       </c>
       <c r="G172" s="9" t="s">
         <v>1471</v>
@@ -10782,7 +10782,7 @@
         <v>77100</v>
       </c>
       <c r="F173" s="34">
-        <v>555000</v>
+        <v>553600</v>
       </c>
       <c r="G173" s="9" t="s">
         <v>1471</v>
@@ -10811,7 +10811,7 @@
         <v>128900</v>
       </c>
       <c r="F174" s="34">
-        <v>924000</v>
+        <v>923800</v>
       </c>
       <c r="G174" s="9" t="s">
         <v>1471</v>
@@ -10869,7 +10869,7 @@
         <v>3000</v>
       </c>
       <c r="F176" s="34">
-        <v>24000</v>
+        <v>24500</v>
       </c>
       <c r="G176" s="9" t="s">
         <v>1471</v>
@@ -10927,7 +10927,7 @@
         <v>5400</v>
       </c>
       <c r="F178" s="34">
-        <v>41000</v>
+        <v>41700</v>
       </c>
       <c r="G178" s="9" t="s">
         <v>1471</v>
@@ -10956,7 +10956,7 @@
         <v>5600</v>
       </c>
       <c r="F179" s="34">
-        <v>43000</v>
+        <v>43300</v>
       </c>
       <c r="G179" s="9" t="s">
         <v>1471</v>
@@ -10985,7 +10985,7 @@
         <v>5800</v>
       </c>
       <c r="F180" s="34">
-        <v>44000</v>
+        <v>44100</v>
       </c>
       <c r="G180" s="9" t="s">
         <v>1471</v>
@@ -11014,7 +11014,7 @@
         <v>8000</v>
       </c>
       <c r="F181" s="34">
-        <v>60000</v>
+        <v>59900</v>
       </c>
       <c r="G181" s="9" t="s">
         <v>1471</v>
@@ -11043,7 +11043,7 @@
         <v>10300</v>
       </c>
       <c r="F182" s="34">
-        <v>76000</v>
+        <v>76600</v>
       </c>
       <c r="G182" s="9" t="s">
         <v>1471</v>
@@ -11072,7 +11072,7 @@
         <v>10400</v>
       </c>
       <c r="F183" s="34">
-        <v>77000</v>
+        <v>77300</v>
       </c>
       <c r="G183" s="9" t="s">
         <v>1471</v>
@@ -11101,7 +11101,7 @@
         <v>10800</v>
       </c>
       <c r="F184" s="34">
-        <v>80000</v>
+        <v>80300</v>
       </c>
       <c r="G184" s="9" t="s">
         <v>1471</v>
@@ -11130,7 +11130,7 @@
         <v>11000</v>
       </c>
       <c r="F185" s="34">
-        <v>81000</v>
+        <v>81300</v>
       </c>
       <c r="G185" s="9" t="s">
         <v>1471</v>
@@ -11159,7 +11159,7 @@
         <v>13600</v>
       </c>
       <c r="F186" s="34">
-        <v>100000</v>
+        <v>100300</v>
       </c>
       <c r="G186" s="9" t="s">
         <v>1471</v>
@@ -11188,7 +11188,7 @@
         <v>13800</v>
       </c>
       <c r="F187" s="34">
-        <v>101000</v>
+        <v>101500</v>
       </c>
       <c r="G187" s="9" t="s">
         <v>1471</v>
@@ -11217,7 +11217,7 @@
         <v>27400</v>
       </c>
       <c r="F188" s="34">
-        <v>197000</v>
+        <v>198500</v>
       </c>
       <c r="G188" s="9" t="s">
         <v>1471</v>

--- a/rates.xlsx
+++ b/rates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS COM\Dropbox\Rates Portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C9B9ED-71C3-4826-A889-08382BB0B7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963D465C-682B-412E-9E21-84D95562C35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8775,7 +8775,7 @@
         <v>238</v>
       </c>
       <c r="D104" s="34">
-        <v>18068</v>
+        <v>18041</v>
       </c>
       <c r="E104" s="34">
         <v>2500</v>
@@ -8804,7 +8804,7 @@
         <v>239</v>
       </c>
       <c r="D105" s="34">
-        <v>19368</v>
+        <v>19333</v>
       </c>
       <c r="E105" s="34">
         <v>2700</v>
@@ -8833,7 +8833,7 @@
         <v>240</v>
       </c>
       <c r="D106" s="34">
-        <v>20371</v>
+        <v>20330</v>
       </c>
       <c r="E106" s="34">
         <v>2900</v>
@@ -8862,7 +8862,7 @@
         <v>241</v>
       </c>
       <c r="D107" s="34">
-        <v>19870</v>
+        <v>19832</v>
       </c>
       <c r="E107" s="34">
         <v>2800</v>
@@ -8891,7 +8891,7 @@
         <v>242</v>
       </c>
       <c r="D108" s="34">
-        <v>19681</v>
+        <v>19644</v>
       </c>
       <c r="E108" s="34">
         <v>2800</v>
@@ -8920,7 +8920,7 @@
         <v>243</v>
       </c>
       <c r="D109" s="34">
-        <v>19783</v>
+        <v>19746</v>
       </c>
       <c r="E109" s="34">
         <v>2800</v>
@@ -8949,7 +8949,7 @@
         <v>244</v>
       </c>
       <c r="D110" s="34">
-        <v>25279</v>
+        <v>25209</v>
       </c>
       <c r="E110" s="34">
         <v>3500</v>
@@ -8978,7 +8978,7 @@
         <v>245</v>
       </c>
       <c r="D111" s="34">
-        <v>25979</v>
+        <v>25905</v>
       </c>
       <c r="E111" s="34">
         <v>3600</v>
@@ -9007,7 +9007,7 @@
         <v>246</v>
       </c>
       <c r="D112" s="34">
-        <v>26979</v>
+        <v>26899</v>
       </c>
       <c r="E112" s="34">
         <v>3800</v>
@@ -9036,7 +9036,7 @@
         <v>247</v>
       </c>
       <c r="D113" s="34">
-        <v>25981</v>
+        <v>25907</v>
       </c>
       <c r="E113" s="34">
         <v>3600</v>
@@ -9065,7 +9065,7 @@
         <v>248</v>
       </c>
       <c r="D114" s="34">
-        <v>26387</v>
+        <v>26310</v>
       </c>
       <c r="E114" s="34">
         <v>3700</v>
@@ -9094,7 +9094,7 @@
         <v>249</v>
       </c>
       <c r="D115" s="34">
-        <v>27486</v>
+        <v>27403</v>
       </c>
       <c r="E115" s="34">
         <v>3800</v>
@@ -9123,7 +9123,7 @@
         <v>250</v>
       </c>
       <c r="D116" s="34">
-        <v>30572</v>
+        <v>30470</v>
       </c>
       <c r="E116" s="34">
         <v>4300</v>
@@ -9152,7 +9152,7 @@
         <v>251</v>
       </c>
       <c r="D117" s="34">
-        <v>32773</v>
+        <v>32658</v>
       </c>
       <c r="E117" s="34">
         <v>4600</v>
@@ -9181,7 +9181,7 @@
         <v>252</v>
       </c>
       <c r="D118" s="34">
-        <v>32773</v>
+        <v>32658</v>
       </c>
       <c r="E118" s="34">
         <v>4600</v>
@@ -9210,7 +9210,7 @@
         <v>253</v>
       </c>
       <c r="D119" s="34">
-        <v>34475</v>
+        <v>34350</v>
       </c>
       <c r="E119" s="34">
         <v>4800</v>
@@ -9239,7 +9239,7 @@
         <v>254</v>
       </c>
       <c r="D120" s="34">
-        <v>35975</v>
+        <v>35841</v>
       </c>
       <c r="E120" s="34">
         <v>5000</v>
@@ -9268,7 +9268,7 @@
         <v>255</v>
       </c>
       <c r="D121" s="34">
-        <v>32088</v>
+        <v>31977</v>
       </c>
       <c r="E121" s="34">
         <v>4500</v>
@@ -9297,7 +9297,7 @@
         <v>256</v>
       </c>
       <c r="D122" s="34">
-        <v>33287</v>
+        <v>33169</v>
       </c>
       <c r="E122" s="34">
         <v>4700</v>
@@ -9326,7 +9326,7 @@
         <v>257</v>
       </c>
       <c r="D123" s="34">
-        <v>32987</v>
+        <v>32871</v>
       </c>
       <c r="E123" s="34">
         <v>4600</v>
@@ -9355,7 +9355,7 @@
         <v>258</v>
       </c>
       <c r="D124" s="34">
-        <v>46000</v>
+        <v>45806</v>
       </c>
       <c r="E124" s="34">
         <v>6400</v>
@@ -9384,7 +9384,7 @@
         <v>259</v>
       </c>
       <c r="D125" s="34">
-        <v>49984</v>
+        <v>49766</v>
       </c>
       <c r="E125" s="34">
         <v>7000</v>
@@ -9413,7 +9413,7 @@
         <v>1499</v>
       </c>
       <c r="D126" s="34">
-        <v>41797</v>
+        <v>41628</v>
       </c>
       <c r="E126" s="34">
         <v>5900</v>
@@ -9442,7 +9442,7 @@
         <v>1500</v>
       </c>
       <c r="D127" s="34">
-        <v>44600</v>
+        <v>44414</v>
       </c>
       <c r="E127" s="34">
         <v>6200</v>
@@ -9471,7 +9471,7 @@
         <v>260</v>
       </c>
       <c r="D128" s="34">
-        <v>56889</v>
+        <v>56630</v>
       </c>
       <c r="E128" s="34">
         <v>8000</v>
@@ -9500,7 +9500,7 @@
         <v>261</v>
       </c>
       <c r="D129" s="34">
-        <v>61393</v>
+        <v>61107</v>
       </c>
       <c r="E129" s="34">
         <v>8600</v>
@@ -9529,7 +9529,7 @@
         <v>262</v>
       </c>
       <c r="D130" s="34">
-        <v>53408</v>
+        <v>53170</v>
       </c>
       <c r="E130" s="34">
         <v>7500</v>
@@ -9558,7 +9558,7 @@
         <v>263</v>
       </c>
       <c r="D131" s="34">
-        <v>60392</v>
+        <v>60112</v>
       </c>
       <c r="E131" s="34">
         <v>8500</v>
@@ -9587,7 +9587,7 @@
         <v>264</v>
       </c>
       <c r="D132" s="34">
-        <v>62394</v>
+        <v>62102</v>
       </c>
       <c r="E132" s="34">
         <v>8700</v>
@@ -9616,7 +9616,7 @@
         <v>265</v>
       </c>
       <c r="D133" s="34">
-        <v>55012</v>
+        <v>54764</v>
       </c>
       <c r="E133" s="34">
         <v>7700</v>
@@ -9645,7 +9645,7 @@
         <v>266</v>
       </c>
       <c r="D134" s="34">
-        <v>58617</v>
+        <v>58348</v>
       </c>
       <c r="E134" s="34">
         <v>8200</v>
@@ -9674,7 +9674,7 @@
         <v>267</v>
       </c>
       <c r="D135" s="34">
-        <v>83407</v>
+        <v>82990</v>
       </c>
       <c r="E135" s="34">
         <v>11700</v>
@@ -9703,7 +9703,7 @@
         <v>268</v>
       </c>
       <c r="D136" s="34">
-        <v>52912</v>
+        <v>52677</v>
       </c>
       <c r="E136" s="34">
         <v>7400</v>
@@ -9732,7 +9732,7 @@
         <v>269</v>
       </c>
       <c r="D137" s="34">
-        <v>64117</v>
+        <v>63815</v>
       </c>
       <c r="E137" s="34">
         <v>9000</v>
@@ -9761,7 +9761,7 @@
         <v>270</v>
       </c>
       <c r="D138" s="34">
-        <v>64716</v>
+        <v>64411</v>
       </c>
       <c r="E138" s="34">
         <v>9100</v>
@@ -9790,7 +9790,7 @@
         <v>271</v>
       </c>
       <c r="D139" s="34">
-        <v>84407</v>
+        <v>83984</v>
       </c>
       <c r="E139" s="34">
         <v>11800</v>
@@ -9819,7 +9819,7 @@
         <v>272</v>
       </c>
       <c r="D140" s="34">
-        <v>66849</v>
+        <v>66531</v>
       </c>
       <c r="E140" s="34">
         <v>9400</v>
@@ -9848,7 +9848,7 @@
         <v>273</v>
       </c>
       <c r="D141" s="34">
-        <v>72251</v>
+        <v>71901</v>
       </c>
       <c r="E141" s="34">
         <v>10100</v>
@@ -9877,7 +9877,7 @@
         <v>274</v>
       </c>
       <c r="D142" s="34">
-        <v>81405</v>
+        <v>81000</v>
       </c>
       <c r="E142" s="34">
         <v>11400</v>
@@ -9906,7 +9906,7 @@
         <v>275</v>
       </c>
       <c r="D143" s="34">
-        <v>79505</v>
+        <v>79111</v>
       </c>
       <c r="E143" s="34">
         <v>11100</v>
@@ -9935,7 +9935,7 @@
         <v>276</v>
       </c>
       <c r="D144" s="34">
-        <v>75934</v>
+        <v>75562</v>
       </c>
       <c r="E144" s="34">
         <v>10600</v>
@@ -9964,7 +9964,7 @@
         <v>277</v>
       </c>
       <c r="D145" s="34">
-        <v>73479</v>
+        <v>73121</v>
       </c>
       <c r="E145" s="34">
         <v>10300</v>
@@ -9993,7 +9993,7 @@
         <v>278</v>
       </c>
       <c r="D146" s="34">
-        <v>100518</v>
+        <v>99999</v>
       </c>
       <c r="E146" s="34">
         <v>14100</v>
@@ -10022,7 +10022,7 @@
         <v>279</v>
       </c>
       <c r="D147" s="34">
-        <v>80336</v>
+        <v>79937</v>
       </c>
       <c r="E147" s="34">
         <v>11200</v>
@@ -10051,7 +10051,7 @@
         <v>280</v>
       </c>
       <c r="D148" s="34">
-        <v>88952</v>
+        <v>88502</v>
       </c>
       <c r="E148" s="34">
         <v>12500</v>
@@ -10080,7 +10080,7 @@
         <v>1501</v>
       </c>
       <c r="D149" s="34">
-        <v>139845</v>
+        <v>139091</v>
       </c>
       <c r="E149" s="34">
         <v>19600</v>
@@ -10109,7 +10109,7 @@
         <v>281</v>
       </c>
       <c r="D150" s="34">
-        <v>80534</v>
+        <v>80134</v>
       </c>
       <c r="E150" s="34">
         <v>11300</v>
@@ -10138,7 +10138,7 @@
         <v>282</v>
       </c>
       <c r="D151" s="34">
-        <v>83242</v>
+        <v>82826</v>
       </c>
       <c r="E151" s="34">
         <v>11700</v>
@@ -10167,7 +10167,7 @@
         <v>283</v>
       </c>
       <c r="D152" s="34">
-        <v>87245</v>
+        <v>86805</v>
       </c>
       <c r="E152" s="34">
         <v>12200</v>
@@ -10196,7 +10196,7 @@
         <v>284</v>
       </c>
       <c r="D153" s="34">
-        <v>89247</v>
+        <v>88795</v>
       </c>
       <c r="E153" s="34">
         <v>12500</v>
@@ -10225,7 +10225,7 @@
         <v>285</v>
       </c>
       <c r="D154" s="34">
-        <v>102359</v>
+        <v>101829</v>
       </c>
       <c r="E154" s="34">
         <v>14300</v>
@@ -10254,7 +10254,7 @@
         <v>286</v>
       </c>
       <c r="D155" s="34">
-        <v>112326</v>
+        <v>111737</v>
       </c>
       <c r="E155" s="34">
         <v>15700</v>
@@ -10283,7 +10283,7 @@
         <v>287</v>
       </c>
       <c r="D156" s="34">
-        <v>97754</v>
+        <v>97251</v>
       </c>
       <c r="E156" s="34">
         <v>13700</v>
@@ -10312,7 +10312,7 @@
         <v>1502</v>
       </c>
       <c r="D157" s="34">
-        <v>170565</v>
+        <v>169628</v>
       </c>
       <c r="E157" s="34">
         <v>23900</v>
@@ -10341,7 +10341,7 @@
         <v>288</v>
       </c>
       <c r="D158" s="34">
-        <v>139825</v>
+        <v>139072</v>
       </c>
       <c r="E158" s="34">
         <v>19600</v>
@@ -10370,7 +10370,7 @@
         <v>303</v>
       </c>
       <c r="D159" s="34">
-        <v>145504</v>
+        <v>144717</v>
       </c>
       <c r="E159" s="34">
         <v>20400</v>
@@ -10399,7 +10399,7 @@
         <v>289</v>
       </c>
       <c r="D160" s="34">
-        <v>134922</v>
+        <v>134198</v>
       </c>
       <c r="E160" s="34">
         <v>18900</v>
@@ -10428,7 +10428,7 @@
         <v>290</v>
       </c>
       <c r="D161" s="34">
-        <v>159510</v>
+        <v>158639</v>
       </c>
       <c r="E161" s="34">
         <v>22300</v>
@@ -10457,7 +10457,7 @@
         <v>291</v>
       </c>
       <c r="D162" s="34">
-        <v>144727</v>
+        <v>143944</v>
       </c>
       <c r="E162" s="34">
         <v>20300</v>
@@ -10486,7 +10486,7 @@
         <v>292</v>
       </c>
       <c r="D163" s="34">
-        <v>168238</v>
+        <v>167315</v>
       </c>
       <c r="E163" s="34">
         <v>23600</v>
@@ -10515,7 +10515,7 @@
         <v>293</v>
       </c>
       <c r="D164" s="34">
-        <v>174516</v>
+        <v>173556</v>
       </c>
       <c r="E164" s="34">
         <v>24400</v>
@@ -10544,7 +10544,7 @@
         <v>294</v>
       </c>
       <c r="D165" s="34">
-        <v>196742</v>
+        <v>195649</v>
       </c>
       <c r="E165" s="34">
         <v>27500</v>
@@ -10573,7 +10573,7 @@
         <v>295</v>
       </c>
       <c r="D166" s="34">
-        <v>198654</v>
+        <v>197550</v>
       </c>
       <c r="E166" s="34">
         <v>27800</v>
@@ -10602,7 +10602,7 @@
         <v>296</v>
       </c>
       <c r="D167" s="34">
-        <v>226156</v>
+        <v>224888</v>
       </c>
       <c r="E167" s="34">
         <v>31700</v>
@@ -10631,7 +10631,7 @@
         <v>297</v>
       </c>
       <c r="D168" s="34">
-        <v>222535</v>
+        <v>221288</v>
       </c>
       <c r="E168" s="34">
         <v>31200</v>
@@ -10660,7 +10660,7 @@
         <v>298</v>
       </c>
       <c r="D169" s="34">
-        <v>157532</v>
+        <v>156673</v>
       </c>
       <c r="E169" s="34">
         <v>22100</v>
@@ -10689,7 +10689,7 @@
         <v>299</v>
       </c>
       <c r="D170" s="34">
-        <v>182318</v>
+        <v>181311</v>
       </c>
       <c r="E170" s="34">
         <v>25500</v>
@@ -10718,7 +10718,7 @@
         <v>300</v>
       </c>
       <c r="D171" s="34">
-        <v>175339</v>
+        <v>174374</v>
       </c>
       <c r="E171" s="34">
         <v>24500</v>
@@ -10747,7 +10747,7 @@
         <v>300</v>
       </c>
       <c r="D172" s="34">
-        <v>230520</v>
+        <v>229226</v>
       </c>
       <c r="E172" s="34">
         <v>32300</v>
@@ -10776,7 +10776,7 @@
         <v>301</v>
       </c>
       <c r="D173" s="34">
-        <v>550639</v>
+        <v>547435</v>
       </c>
       <c r="E173" s="34">
         <v>77100</v>
@@ -10805,7 +10805,7 @@
         <v>302</v>
       </c>
       <c r="D174" s="34">
-        <v>920767</v>
+        <v>915356</v>
       </c>
       <c r="E174" s="34">
         <v>128900</v>
@@ -10834,7 +10834,7 @@
         <v>304</v>
       </c>
       <c r="D175" s="34">
-        <v>20966</v>
+        <v>20921</v>
       </c>
       <c r="E175" s="34">
         <v>2900</v>
@@ -10863,7 +10863,7 @@
         <v>305</v>
       </c>
       <c r="D176" s="34">
-        <v>21466</v>
+        <v>21418</v>
       </c>
       <c r="E176" s="34">
         <v>3000</v>
@@ -10892,7 +10892,7 @@
         <v>306</v>
       </c>
       <c r="D177" s="34">
-        <v>21966</v>
+        <v>21915</v>
       </c>
       <c r="E177" s="34">
         <v>3100</v>
@@ -10921,7 +10921,7 @@
         <v>307</v>
       </c>
       <c r="D178" s="34">
-        <v>38676</v>
+        <v>38526</v>
       </c>
       <c r="E178" s="34">
         <v>5400</v>
@@ -10950,7 +10950,7 @@
         <v>308</v>
       </c>
       <c r="D179" s="34">
-        <v>40278</v>
+        <v>40118</v>
       </c>
       <c r="E179" s="34">
         <v>5600</v>
@@ -10979,7 +10979,7 @@
         <v>309</v>
       </c>
       <c r="D180" s="34">
-        <v>41079</v>
+        <v>40914</v>
       </c>
       <c r="E180" s="34">
         <v>5800</v>
@@ -11008,7 +11008,7 @@
         <v>310</v>
       </c>
       <c r="D181" s="34">
-        <v>56889</v>
+        <v>56630</v>
       </c>
       <c r="E181" s="34">
         <v>8000</v>
@@ -11037,7 +11037,7 @@
         <v>311</v>
       </c>
       <c r="D182" s="34">
-        <v>73600</v>
+        <v>73242</v>
       </c>
       <c r="E182" s="34">
         <v>10300</v>
@@ -11066,7 +11066,7 @@
         <v>312</v>
       </c>
       <c r="D183" s="34">
-        <v>74301</v>
+        <v>73938</v>
       </c>
       <c r="E183" s="34">
         <v>10400</v>
@@ -11095,7 +11095,7 @@
         <v>313</v>
       </c>
       <c r="D184" s="34">
-        <v>77303</v>
+        <v>76922</v>
       </c>
       <c r="E184" s="34">
         <v>10800</v>
@@ -11124,7 +11124,7 @@
         <v>314</v>
       </c>
       <c r="D185" s="34">
-        <v>78303</v>
+        <v>77916</v>
       </c>
       <c r="E185" s="34">
         <v>11000</v>
@@ -11153,7 +11153,7 @@
         <v>315</v>
       </c>
       <c r="D186" s="34">
-        <v>97317</v>
+        <v>96817</v>
       </c>
       <c r="E186" s="34">
         <v>13600</v>
@@ -11182,7 +11182,7 @@
         <v>316</v>
       </c>
       <c r="D187" s="34">
-        <v>98517</v>
+        <v>98010</v>
       </c>
       <c r="E187" s="34">
         <v>13800</v>
@@ -11211,7 +11211,7 @@
         <v>317</v>
       </c>
       <c r="D188" s="34">
-        <v>195521</v>
+        <v>194435</v>
       </c>
       <c r="E188" s="34">
         <v>27400</v>

--- a/rates.xlsx
+++ b/rates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS COM\Dropbox\Rates Portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87BDB2C7-897C-484E-B501-CF856DC2B2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1C4377-EC18-48B4-919D-8FFE6DA1D797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45897,7 +45897,7 @@
         <v>1262</v>
       </c>
       <c r="B1460" s="4" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="C1460" s="7" t="s">
         <v>1666</v>

--- a/rates.xlsx
+++ b/rates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS COM\Dropbox\Rates Portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DECD5C8-7183-4DC9-89CE-FA5FB9B5BCEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8034B539-564B-4C48-A79B-5C66BE2FE68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5162,7 +5162,7 @@
     <t>DEURON DN-813</t>
   </si>
   <si>
-    <t>11 Month Plan</t>
+    <t>10Month Plan</t>
   </si>
 </sst>
 </file>

--- a/rates.xlsx
+++ b/rates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS COM\Dropbox\Rates Portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8034B539-564B-4C48-A79B-5C66BE2FE68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3BC216-211A-4E25-B40A-4A655EB28080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$I$1633</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$I$1653</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8169" uniqueCount="1702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8269" uniqueCount="1730">
   <si>
     <t>PRLP-1100</t>
   </si>
@@ -5164,6 +5164,90 @@
   <si>
     <t>10Month Plan</t>
   </si>
+  <si>
+    <t>RIMCO</t>
+  </si>
+  <si>
+    <t>ELECTRIC WATER HEATER EH-15</t>
+  </si>
+  <si>
+    <t>ELECTRIC WATER HEATER SEH-15</t>
+  </si>
+  <si>
+    <t>ELECTRIC WATER HEATER EH-30</t>
+  </si>
+  <si>
+    <t>SmartTemp™ + WattControl™</t>
+  </si>
+  <si>
+    <t>ELECTRIC WATER HEATER CEH-40</t>
+  </si>
+  <si>
+    <t>ELECTRIC WATER HEATER CEH-50</t>
+  </si>
+  <si>
+    <t>ELECTRIC WATER HEATER CEH-60</t>
+  </si>
+  <si>
+    <t>ELECTRIC WATER HEATER CEH-70</t>
+  </si>
+  <si>
+    <t>ELECTRIC WATER HEATER CEH-80</t>
+  </si>
+  <si>
+    <t>11 Month Plan</t>
+  </si>
+  <si>
+    <t>12 Month Plan</t>
+  </si>
+  <si>
+    <t>13 Month Plan</t>
+  </si>
+  <si>
+    <t>DigitalTemp™ + WattControl™</t>
+  </si>
+  <si>
+    <t>ELECTRIC WATER HEATER CEH-15 D</t>
+  </si>
+  <si>
+    <t>ELECTRIC WATER HEATER CEH-30 D</t>
+  </si>
+  <si>
+    <t>ELECTRIC WATER HEATER CEH-40 D</t>
+  </si>
+  <si>
+    <t>ELECTRIC WATER HEATER CEH-50 D</t>
+  </si>
+  <si>
+    <t>ELECTRIC WATER HEATER CEH-60 D</t>
+  </si>
+  <si>
+    <t>ELECTRIC WATER HEATER CEH-70 D</t>
+  </si>
+  <si>
+    <t>ELECTRIC WATER HEATER CEH-80 D</t>
+  </si>
+  <si>
+    <t>Hybrid Electric + Gas Water Heater</t>
+  </si>
+  <si>
+    <t>GAS &amp; ELECTRIC WATER HEATER GEH-25</t>
+  </si>
+  <si>
+    <t>GAS &amp; ELECTRIC WATER HEATER GEH-35</t>
+  </si>
+  <si>
+    <t>GAS &amp; ELECTRIC WATER HEATER GEH-55</t>
+  </si>
+  <si>
+    <t>INSTANT GAS WATER HEATER CIH-6L</t>
+  </si>
+  <si>
+    <t>INSTANT GAS WATER HEATER CIH-8L</t>
+  </si>
+  <si>
+    <t>Instant Gas Water Heater (LPG &amp; NG)</t>
+  </si>
 </sst>
 </file>
 
@@ -5173,7 +5257,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5251,6 +5335,12 @@
       <sz val="11"/>
       <name val="Jameel Noori Nastaleeq"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -5302,7 +5392,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -5468,6 +5558,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -5476,7 +5581,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5606,6 +5711,12 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5899,7 +6010,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6FE0007-86B3-4D5F-9CBC-37B22BC3E091}">
-  <dimension ref="A1:I1633"/>
+  <dimension ref="A1:I1653"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -5908,7 +6019,7 @@
     <col min="4" max="4" width="13.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="9.140625" style="1"/>
     <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16" bestFit="1" customWidth="1"/>
@@ -43810,23 +43921,23 @@
     </row>
     <row r="1382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1382" s="4" t="s">
-        <v>168</v>
+        <v>1702</v>
       </c>
       <c r="B1382" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1382" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="D1382" s="11">
-        <v>64000</v>
-      </c>
-      <c r="E1382" s="9">
-        <v>6400</v>
+        <v>1670</v>
+      </c>
+      <c r="C1382" s="7" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D1382" s="3">
+        <v>20980</v>
+      </c>
+      <c r="E1382" s="4">
+        <v>2900</v>
       </c>
       <c r="F1382" s="4"/>
       <c r="G1382" s="4" t="s">
-        <v>1459</v>
+        <v>1712</v>
       </c>
       <c r="H1382" s="4" t="s">
         <v>1455</v>
@@ -43837,23 +43948,23 @@
     </row>
     <row r="1383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1383" s="4" t="s">
-        <v>168</v>
+        <v>1702</v>
       </c>
       <c r="B1383" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1383" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="D1383" s="11">
-        <v>80000</v>
-      </c>
-      <c r="E1383" s="9">
-        <v>8000</v>
+        <v>1670</v>
+      </c>
+      <c r="C1383" s="7" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D1383" s="3">
+        <v>20980</v>
+      </c>
+      <c r="E1383" s="4">
+        <v>2900</v>
       </c>
       <c r="F1383" s="4"/>
       <c r="G1383" s="4" t="s">
-        <v>1459</v>
+        <v>1713</v>
       </c>
       <c r="H1383" s="4" t="s">
         <v>1455</v>
@@ -43864,23 +43975,23 @@
     </row>
     <row r="1384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1384" s="4" t="s">
-        <v>168</v>
+        <v>1702</v>
       </c>
       <c r="B1384" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1384" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="D1384" s="11">
-        <v>96000</v>
-      </c>
-      <c r="E1384" s="9">
-        <v>9600</v>
+        <v>1670</v>
+      </c>
+      <c r="C1384" s="7" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D1384" s="3">
+        <v>23480</v>
+      </c>
+      <c r="E1384" s="4">
+        <v>3300</v>
       </c>
       <c r="F1384" s="4"/>
       <c r="G1384" s="4" t="s">
-        <v>1459</v>
+        <v>1714</v>
       </c>
       <c r="H1384" s="4" t="s">
         <v>1455</v>
@@ -43891,23 +44002,23 @@
     </row>
     <row r="1385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1385" s="4" t="s">
-        <v>168</v>
+        <v>1702</v>
       </c>
       <c r="B1385" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1385" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="D1385" s="11">
-        <v>102000</v>
-      </c>
-      <c r="E1385" s="9">
-        <v>10200</v>
-      </c>
-      <c r="F1385" s="4"/>
+        <v>1670</v>
+      </c>
+      <c r="C1385" s="7" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D1385" s="3">
+        <v>21480</v>
+      </c>
+      <c r="E1385" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F1385" s="7"/>
       <c r="G1385" s="4" t="s">
-        <v>1459</v>
+        <v>1706</v>
       </c>
       <c r="H1385" s="4" t="s">
         <v>1455</v>
@@ -43918,23 +44029,23 @@
     </row>
     <row r="1386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1386" s="4" t="s">
-        <v>168</v>
+        <v>1702</v>
       </c>
       <c r="B1386" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1386" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="D1386" s="11">
-        <v>133000</v>
-      </c>
-      <c r="E1386" s="9">
-        <v>13300</v>
-      </c>
-      <c r="F1386" s="4"/>
+        <v>1670</v>
+      </c>
+      <c r="C1386" s="7" t="s">
+        <v>1708</v>
+      </c>
+      <c r="D1386" s="3">
+        <v>22480</v>
+      </c>
+      <c r="E1386" s="4">
+        <v>3100</v>
+      </c>
+      <c r="F1386" s="7"/>
       <c r="G1386" s="4" t="s">
-        <v>1459</v>
+        <v>1706</v>
       </c>
       <c r="H1386" s="4" t="s">
         <v>1455</v>
@@ -43945,23 +44056,23 @@
     </row>
     <row r="1387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1387" s="4" t="s">
-        <v>168</v>
+        <v>1702</v>
       </c>
       <c r="B1387" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1387" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="D1387" s="11">
-        <v>140000</v>
-      </c>
-      <c r="E1387" s="9">
-        <v>14000</v>
-      </c>
-      <c r="F1387" s="4"/>
+        <v>1670</v>
+      </c>
+      <c r="C1387" s="7" t="s">
+        <v>1709</v>
+      </c>
+      <c r="D1387" s="3">
+        <v>23480</v>
+      </c>
+      <c r="E1387" s="4">
+        <v>3300</v>
+      </c>
+      <c r="F1387" s="7"/>
       <c r="G1387" s="4" t="s">
-        <v>1459</v>
+        <v>1706</v>
       </c>
       <c r="H1387" s="4" t="s">
         <v>1455</v>
@@ -43972,23 +44083,23 @@
     </row>
     <row r="1388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1388" s="4" t="s">
-        <v>168</v>
+        <v>1702</v>
       </c>
       <c r="B1388" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1388" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="D1388" s="11">
-        <v>133000</v>
-      </c>
-      <c r="E1388" s="9">
-        <v>13300</v>
-      </c>
-      <c r="F1388" s="4"/>
+        <v>1670</v>
+      </c>
+      <c r="C1388" s="7" t="s">
+        <v>1710</v>
+      </c>
+      <c r="D1388" s="3">
+        <v>24480</v>
+      </c>
+      <c r="E1388" s="4">
+        <v>3400</v>
+      </c>
+      <c r="F1388" s="7"/>
       <c r="G1388" s="4" t="s">
-        <v>1459</v>
+        <v>1706</v>
       </c>
       <c r="H1388" s="4" t="s">
         <v>1455</v>
@@ -43999,23 +44110,23 @@
     </row>
     <row r="1389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1389" s="4" t="s">
-        <v>168</v>
+        <v>1702</v>
       </c>
       <c r="B1389" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1389" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="D1389" s="11">
-        <v>187000</v>
-      </c>
-      <c r="E1389" s="9">
-        <v>18700</v>
-      </c>
-      <c r="F1389" s="4"/>
+        <v>1670</v>
+      </c>
+      <c r="C1389" s="7" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D1389" s="3">
+        <v>25480</v>
+      </c>
+      <c r="E1389" s="4">
+        <v>3600</v>
+      </c>
+      <c r="F1389" s="7"/>
       <c r="G1389" s="4" t="s">
-        <v>1459</v>
+        <v>1706</v>
       </c>
       <c r="H1389" s="4" t="s">
         <v>1455</v>
@@ -44024,25 +44135,25 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="1390" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1390" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1390" s="4" t="s">
-        <v>168</v>
+        <v>1702</v>
       </c>
       <c r="B1390" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1390" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="D1390" s="11">
-        <v>231000</v>
-      </c>
-      <c r="E1390" s="9">
-        <v>23100</v>
-      </c>
-      <c r="F1390" s="4"/>
+        <v>1670</v>
+      </c>
+      <c r="C1390" s="7" t="s">
+        <v>1716</v>
+      </c>
+      <c r="D1390" s="3">
+        <v>20980</v>
+      </c>
+      <c r="E1390" s="46">
+        <v>2900</v>
+      </c>
+      <c r="F1390" s="47"/>
       <c r="G1390" s="4" t="s">
-        <v>1459</v>
+        <v>1715</v>
       </c>
       <c r="H1390" s="4" t="s">
         <v>1455</v>
@@ -44051,25 +44162,25 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="1391" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1391" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1391" s="4" t="s">
-        <v>168</v>
+        <v>1702</v>
       </c>
       <c r="B1391" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1391" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="D1391" s="11">
-        <v>256000</v>
-      </c>
-      <c r="E1391" s="9">
-        <v>25600</v>
-      </c>
-      <c r="F1391" s="4"/>
+        <v>1670</v>
+      </c>
+      <c r="C1391" s="7" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D1391" s="3">
+        <v>23480</v>
+      </c>
+      <c r="E1391" s="46">
+        <v>3300</v>
+      </c>
+      <c r="F1391" s="47"/>
       <c r="G1391" s="4" t="s">
-        <v>1459</v>
+        <v>1715</v>
       </c>
       <c r="H1391" s="4" t="s">
         <v>1455</v>
@@ -44078,25 +44189,25 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="1392" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1392" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1392" s="4" t="s">
-        <v>168</v>
+        <v>1702</v>
       </c>
       <c r="B1392" s="4" t="s">
-        <v>207</v>
+        <v>1670</v>
       </c>
       <c r="C1392" s="7" t="s">
-        <v>158</v>
+        <v>1718</v>
       </c>
       <c r="D1392" s="3">
-        <v>287000</v>
-      </c>
-      <c r="E1392" s="4">
-        <v>28700</v>
-      </c>
-      <c r="F1392" s="4"/>
+        <v>21980</v>
+      </c>
+      <c r="E1392" s="46">
+        <v>3100</v>
+      </c>
+      <c r="F1392" s="47"/>
       <c r="G1392" s="4" t="s">
-        <v>1459</v>
+        <v>1715</v>
       </c>
       <c r="H1392" s="4" t="s">
         <v>1455</v>
@@ -44105,25 +44216,25 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="1393" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1393" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1393" s="4" t="s">
-        <v>168</v>
+        <v>1702</v>
       </c>
       <c r="B1393" s="4" t="s">
-        <v>207</v>
+        <v>1670</v>
       </c>
       <c r="C1393" s="7" t="s">
-        <v>159</v>
+        <v>1719</v>
       </c>
       <c r="D1393" s="3">
-        <v>315000</v>
-      </c>
-      <c r="E1393" s="4">
-        <v>31500</v>
-      </c>
-      <c r="F1393" s="4"/>
+        <v>22980</v>
+      </c>
+      <c r="E1393" s="46">
+        <v>3200</v>
+      </c>
+      <c r="F1393" s="47"/>
       <c r="G1393" s="4" t="s">
-        <v>1459</v>
+        <v>1715</v>
       </c>
       <c r="H1393" s="4" t="s">
         <v>1455</v>
@@ -44132,25 +44243,25 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="1394" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1394" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1394" s="4" t="s">
-        <v>168</v>
+        <v>1702</v>
       </c>
       <c r="B1394" s="4" t="s">
-        <v>207</v>
+        <v>1670</v>
       </c>
       <c r="C1394" s="7" t="s">
-        <v>160</v>
+        <v>1720</v>
       </c>
       <c r="D1394" s="3">
-        <v>308000</v>
-      </c>
-      <c r="E1394" s="4">
-        <v>30800</v>
-      </c>
-      <c r="F1394" s="4"/>
+        <v>23980</v>
+      </c>
+      <c r="E1394" s="46">
+        <v>3400</v>
+      </c>
+      <c r="F1394" s="47"/>
       <c r="G1394" s="4" t="s">
-        <v>1459</v>
+        <v>1715</v>
       </c>
       <c r="H1394" s="4" t="s">
         <v>1455</v>
@@ -44159,25 +44270,25 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="1395" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1395" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1395" s="4" t="s">
-        <v>168</v>
+        <v>1702</v>
       </c>
       <c r="B1395" s="4" t="s">
-        <v>207</v>
+        <v>1670</v>
       </c>
       <c r="C1395" s="7" t="s">
-        <v>161</v>
+        <v>1721</v>
       </c>
       <c r="D1395" s="3">
-        <v>357000</v>
-      </c>
-      <c r="E1395" s="4">
-        <v>35700</v>
-      </c>
-      <c r="F1395" s="4"/>
+        <v>24980</v>
+      </c>
+      <c r="E1395" s="46">
+        <v>3500</v>
+      </c>
+      <c r="F1395" s="47"/>
       <c r="G1395" s="4" t="s">
-        <v>1459</v>
+        <v>1715</v>
       </c>
       <c r="H1395" s="4" t="s">
         <v>1455</v>
@@ -44186,25 +44297,25 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="1396" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1396" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1396" s="4" t="s">
-        <v>168</v>
+        <v>1702</v>
       </c>
       <c r="B1396" s="4" t="s">
-        <v>207</v>
+        <v>1670</v>
       </c>
       <c r="C1396" s="7" t="s">
-        <v>162</v>
+        <v>1722</v>
       </c>
       <c r="D1396" s="3">
-        <v>448000</v>
-      </c>
-      <c r="E1396" s="4">
-        <v>44800</v>
-      </c>
-      <c r="F1396" s="4"/>
+        <v>25980</v>
+      </c>
+      <c r="E1396" s="46">
+        <v>3600</v>
+      </c>
+      <c r="F1396" s="47"/>
       <c r="G1396" s="4" t="s">
-        <v>1459</v>
+        <v>1715</v>
       </c>
       <c r="H1396" s="4" t="s">
         <v>1455</v>
@@ -44213,25 +44324,25 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="1397" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1397" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1397" s="4" t="s">
-        <v>168</v>
+        <v>1702</v>
       </c>
       <c r="B1397" s="4" t="s">
-        <v>207</v>
+        <v>1670</v>
       </c>
       <c r="C1397" s="7" t="s">
-        <v>163</v>
+        <v>1724</v>
       </c>
       <c r="D1397" s="3">
-        <v>532000</v>
-      </c>
-      <c r="E1397" s="4">
-        <v>53200</v>
-      </c>
-      <c r="F1397" s="4"/>
+        <v>42280</v>
+      </c>
+      <c r="E1397" s="46">
+        <v>5900</v>
+      </c>
+      <c r="F1397" s="47"/>
       <c r="G1397" s="4" t="s">
-        <v>1459</v>
+        <v>1723</v>
       </c>
       <c r="H1397" s="4" t="s">
         <v>1455</v>
@@ -44240,25 +44351,25 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="1398" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1398" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1398" s="4" t="s">
-        <v>168</v>
+        <v>1702</v>
       </c>
       <c r="B1398" s="4" t="s">
-        <v>207</v>
+        <v>1670</v>
       </c>
       <c r="C1398" s="7" t="s">
-        <v>164</v>
+        <v>1725</v>
       </c>
       <c r="D1398" s="3">
-        <v>539000</v>
-      </c>
-      <c r="E1398" s="4">
-        <v>53900</v>
-      </c>
-      <c r="F1398" s="4"/>
+        <v>47280</v>
+      </c>
+      <c r="E1398" s="46">
+        <v>6600</v>
+      </c>
+      <c r="F1398" s="47"/>
       <c r="G1398" s="4" t="s">
-        <v>1459</v>
+        <v>1723</v>
       </c>
       <c r="H1398" s="4" t="s">
         <v>1455</v>
@@ -44267,25 +44378,25 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="1399" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1399" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1399" s="4" t="s">
-        <v>168</v>
+        <v>1702</v>
       </c>
       <c r="B1399" s="4" t="s">
-        <v>207</v>
+        <v>1670</v>
       </c>
       <c r="C1399" s="7" t="s">
-        <v>165</v>
+        <v>1726</v>
       </c>
       <c r="D1399" s="3">
-        <v>623000</v>
-      </c>
-      <c r="E1399" s="4">
-        <v>62300</v>
-      </c>
-      <c r="F1399" s="4"/>
+        <v>52280</v>
+      </c>
+      <c r="E1399" s="46">
+        <v>7300</v>
+      </c>
+      <c r="F1399" s="47"/>
       <c r="G1399" s="4" t="s">
-        <v>1459</v>
+        <v>1723</v>
       </c>
       <c r="H1399" s="4" t="s">
         <v>1455</v>
@@ -44294,25 +44405,25 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="1400" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1400" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1400" s="4" t="s">
-        <v>168</v>
+        <v>1702</v>
       </c>
       <c r="B1400" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1400" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D1400" s="3">
-        <v>630000</v>
+        <v>1670</v>
+      </c>
+      <c r="C1400" s="46" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D1400" s="47">
+        <v>21080</v>
       </c>
       <c r="E1400" s="4">
-        <v>63000</v>
-      </c>
-      <c r="F1400" s="4"/>
-      <c r="G1400" s="4" t="s">
-        <v>1459</v>
+        <v>3000</v>
+      </c>
+      <c r="F1400" s="46"/>
+      <c r="G1400" s="47" t="s">
+        <v>1729</v>
       </c>
       <c r="H1400" s="4" t="s">
         <v>1455</v>
@@ -44321,25 +44432,25 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="1401" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1401" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1401" s="4" t="s">
-        <v>168</v>
+        <v>1702</v>
       </c>
       <c r="B1401" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1401" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="D1401" s="3">
-        <v>728000</v>
+        <v>1670</v>
+      </c>
+      <c r="C1401" s="46" t="s">
+        <v>1728</v>
+      </c>
+      <c r="D1401" s="47">
+        <v>27180</v>
       </c>
       <c r="E1401" s="4">
-        <v>72800</v>
-      </c>
-      <c r="F1401" s="4"/>
-      <c r="G1401" s="4" t="s">
-        <v>1459</v>
+        <v>3800</v>
+      </c>
+      <c r="F1401" s="46"/>
+      <c r="G1401" s="47" t="s">
+        <v>1729</v>
       </c>
       <c r="H1401" s="4" t="s">
         <v>1455</v>
@@ -44350,19 +44461,19 @@
     </row>
     <row r="1402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1402" s="4" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1402" s="4" t="s">
-        <v>956</v>
-      </c>
-      <c r="C1402" s="7" t="s">
-        <v>1606</v>
-      </c>
-      <c r="D1402" s="3">
-        <v>8534</v>
-      </c>
-      <c r="E1402" s="4">
-        <v>1300</v>
+        <v>207</v>
+      </c>
+      <c r="C1402" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1402" s="11">
+        <v>64000</v>
+      </c>
+      <c r="E1402" s="9">
+        <v>6400</v>
       </c>
       <c r="F1402" s="4"/>
       <c r="G1402" s="4" t="s">
@@ -44377,19 +44488,19 @@
     </row>
     <row r="1403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1403" s="4" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1403" s="4" t="s">
-        <v>956</v>
-      </c>
-      <c r="C1403" s="7" t="s">
-        <v>1351</v>
-      </c>
-      <c r="D1403" s="3">
-        <v>12530</v>
-      </c>
-      <c r="E1403" s="4">
-        <v>1900</v>
+        <v>207</v>
+      </c>
+      <c r="C1403" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1403" s="11">
+        <v>80000</v>
+      </c>
+      <c r="E1403" s="9">
+        <v>8000</v>
       </c>
       <c r="F1403" s="4"/>
       <c r="G1403" s="4" t="s">
@@ -44404,19 +44515,19 @@
     </row>
     <row r="1404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1404" s="4" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1404" s="4" t="s">
-        <v>956</v>
-      </c>
-      <c r="C1404" s="7" t="s">
-        <v>1607</v>
-      </c>
-      <c r="D1404" s="3">
-        <v>12530</v>
-      </c>
-      <c r="E1404" s="4">
-        <v>1900</v>
+        <v>207</v>
+      </c>
+      <c r="C1404" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1404" s="11">
+        <v>96000</v>
+      </c>
+      <c r="E1404" s="9">
+        <v>9600</v>
       </c>
       <c r="F1404" s="4"/>
       <c r="G1404" s="4" t="s">
@@ -44431,19 +44542,19 @@
     </row>
     <row r="1405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1405" s="4" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1405" s="4" t="s">
-        <v>956</v>
-      </c>
-      <c r="C1405" s="7" t="s">
-        <v>1608</v>
-      </c>
-      <c r="D1405" s="3">
-        <v>15030</v>
-      </c>
-      <c r="E1405" s="4">
-        <v>2300</v>
+        <v>207</v>
+      </c>
+      <c r="C1405" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1405" s="11">
+        <v>102000</v>
+      </c>
+      <c r="E1405" s="9">
+        <v>10200</v>
       </c>
       <c r="F1405" s="4"/>
       <c r="G1405" s="4" t="s">
@@ -44458,19 +44569,19 @@
     </row>
     <row r="1406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1406" s="4" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1406" s="4" t="s">
-        <v>956</v>
-      </c>
-      <c r="C1406" s="7" t="s">
-        <v>1609</v>
-      </c>
-      <c r="D1406" s="3">
-        <v>12290</v>
-      </c>
-      <c r="E1406" s="4">
-        <v>1900</v>
+        <v>207</v>
+      </c>
+      <c r="C1406" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1406" s="11">
+        <v>133000</v>
+      </c>
+      <c r="E1406" s="9">
+        <v>13300</v>
       </c>
       <c r="F1406" s="4"/>
       <c r="G1406" s="4" t="s">
@@ -44485,19 +44596,19 @@
     </row>
     <row r="1407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1407" s="4" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1407" s="4" t="s">
-        <v>956</v>
-      </c>
-      <c r="C1407" s="7" t="s">
-        <v>1610</v>
-      </c>
-      <c r="D1407" s="3">
-        <v>6330</v>
-      </c>
-      <c r="E1407" s="4">
-        <v>1000</v>
+        <v>207</v>
+      </c>
+      <c r="C1407" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="D1407" s="11">
+        <v>140000</v>
+      </c>
+      <c r="E1407" s="9">
+        <v>14000</v>
       </c>
       <c r="F1407" s="4"/>
       <c r="G1407" s="4" t="s">
@@ -44512,19 +44623,19 @@
     </row>
     <row r="1408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1408" s="4" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1408" s="4" t="s">
-        <v>956</v>
-      </c>
-      <c r="C1408" s="7" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D1408" s="3">
-        <v>7530</v>
-      </c>
-      <c r="E1408" s="4">
-        <v>1200</v>
+        <v>207</v>
+      </c>
+      <c r="C1408" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1408" s="11">
+        <v>133000</v>
+      </c>
+      <c r="E1408" s="9">
+        <v>13300</v>
       </c>
       <c r="F1408" s="4"/>
       <c r="G1408" s="4" t="s">
@@ -44539,19 +44650,19 @@
     </row>
     <row r="1409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1409" s="4" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1409" s="4" t="s">
-        <v>956</v>
-      </c>
-      <c r="C1409" s="7" t="s">
-        <v>1349</v>
-      </c>
-      <c r="D1409" s="3">
-        <v>11530</v>
-      </c>
-      <c r="E1409" s="4">
-        <v>1800</v>
+        <v>207</v>
+      </c>
+      <c r="C1409" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1409" s="11">
+        <v>187000</v>
+      </c>
+      <c r="E1409" s="9">
+        <v>18700</v>
       </c>
       <c r="F1409" s="4"/>
       <c r="G1409" s="4" t="s">
@@ -44566,19 +44677,19 @@
     </row>
     <row r="1410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1410" s="4" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1410" s="4" t="s">
-        <v>956</v>
-      </c>
-      <c r="C1410" s="7" t="s">
-        <v>1350</v>
-      </c>
-      <c r="D1410" s="3">
-        <v>12130</v>
-      </c>
-      <c r="E1410" s="4">
-        <v>1900</v>
+        <v>207</v>
+      </c>
+      <c r="C1410" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1410" s="11">
+        <v>231000</v>
+      </c>
+      <c r="E1410" s="9">
+        <v>23100</v>
       </c>
       <c r="F1410" s="4"/>
       <c r="G1410" s="4" t="s">
@@ -44593,19 +44704,19 @@
     </row>
     <row r="1411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1411" s="4" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1411" s="4" t="s">
-        <v>956</v>
-      </c>
-      <c r="C1411" s="7" t="s">
-        <v>1612</v>
-      </c>
-      <c r="D1411" s="3">
-        <v>5830</v>
-      </c>
-      <c r="E1411" s="4">
-        <v>900</v>
+        <v>207</v>
+      </c>
+      <c r="C1411" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1411" s="11">
+        <v>256000</v>
+      </c>
+      <c r="E1411" s="9">
+        <v>25600</v>
       </c>
       <c r="F1411" s="4"/>
       <c r="G1411" s="4" t="s">
@@ -44620,19 +44731,19 @@
     </row>
     <row r="1412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1412" s="4" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1412" s="4" t="s">
-        <v>956</v>
+        <v>207</v>
       </c>
       <c r="C1412" s="7" t="s">
-        <v>1613</v>
+        <v>158</v>
       </c>
       <c r="D1412" s="3">
-        <v>8730</v>
+        <v>287000</v>
       </c>
       <c r="E1412" s="4">
-        <v>1400</v>
+        <v>28700</v>
       </c>
       <c r="F1412" s="4"/>
       <c r="G1412" s="4" t="s">
@@ -44647,19 +44758,19 @@
     </row>
     <row r="1413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1413" s="4" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1413" s="4" t="s">
-        <v>956</v>
+        <v>207</v>
       </c>
       <c r="C1413" s="7" t="s">
-        <v>1614</v>
+        <v>159</v>
       </c>
       <c r="D1413" s="3">
-        <v>15530</v>
+        <v>315000</v>
       </c>
       <c r="E1413" s="4">
-        <v>2400</v>
+        <v>31500</v>
       </c>
       <c r="F1413" s="4"/>
       <c r="G1413" s="4" t="s">
@@ -44674,19 +44785,19 @@
     </row>
     <row r="1414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1414" s="4" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1414" s="4" t="s">
-        <v>956</v>
+        <v>207</v>
       </c>
       <c r="C1414" s="7" t="s">
-        <v>1615</v>
+        <v>160</v>
       </c>
       <c r="D1414" s="3">
-        <v>11530</v>
+        <v>308000</v>
       </c>
       <c r="E1414" s="4">
-        <v>1800</v>
+        <v>30800</v>
       </c>
       <c r="F1414" s="4"/>
       <c r="G1414" s="4" t="s">
@@ -44701,19 +44812,19 @@
     </row>
     <row r="1415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1415" s="4" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1415" s="4" t="s">
-        <v>956</v>
+        <v>207</v>
       </c>
       <c r="C1415" s="7" t="s">
-        <v>1616</v>
+        <v>161</v>
       </c>
       <c r="D1415" s="3">
-        <v>13530</v>
+        <v>357000</v>
       </c>
       <c r="E1415" s="4">
-        <v>2100</v>
+        <v>35700</v>
       </c>
       <c r="F1415" s="4"/>
       <c r="G1415" s="4" t="s">
@@ -44728,19 +44839,19 @@
     </row>
     <row r="1416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1416" s="4" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1416" s="4" t="s">
-        <v>956</v>
+        <v>207</v>
       </c>
       <c r="C1416" s="7" t="s">
-        <v>1617</v>
+        <v>162</v>
       </c>
       <c r="D1416" s="3">
-        <v>15530</v>
+        <v>448000</v>
       </c>
       <c r="E1416" s="4">
-        <v>2400</v>
+        <v>44800</v>
       </c>
       <c r="F1416" s="4"/>
       <c r="G1416" s="4" t="s">
@@ -44755,19 +44866,19 @@
     </row>
     <row r="1417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1417" s="4" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1417" s="4" t="s">
-        <v>956</v>
+        <v>207</v>
       </c>
       <c r="C1417" s="7" t="s">
-        <v>1618</v>
+        <v>163</v>
       </c>
       <c r="D1417" s="3">
-        <v>17530</v>
+        <v>532000</v>
       </c>
       <c r="E1417" s="4">
-        <v>2700</v>
+        <v>53200</v>
       </c>
       <c r="F1417" s="4"/>
       <c r="G1417" s="4" t="s">
@@ -44782,19 +44893,19 @@
     </row>
     <row r="1418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1418" s="4" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1418" s="4" t="s">
-        <v>956</v>
+        <v>207</v>
       </c>
       <c r="C1418" s="7" t="s">
-        <v>1619</v>
+        <v>164</v>
       </c>
       <c r="D1418" s="3">
-        <v>22030</v>
+        <v>539000</v>
       </c>
       <c r="E1418" s="4">
-        <v>3400</v>
+        <v>53900</v>
       </c>
       <c r="F1418" s="4"/>
       <c r="G1418" s="4" t="s">
@@ -44809,19 +44920,19 @@
     </row>
     <row r="1419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1419" s="4" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1419" s="4" t="s">
-        <v>956</v>
+        <v>207</v>
       </c>
       <c r="C1419" s="7" t="s">
-        <v>1620</v>
+        <v>165</v>
       </c>
       <c r="D1419" s="3">
-        <v>6730</v>
+        <v>623000</v>
       </c>
       <c r="E1419" s="4">
-        <v>1000</v>
+        <v>62300</v>
       </c>
       <c r="F1419" s="4"/>
       <c r="G1419" s="4" t="s">
@@ -44836,19 +44947,19 @@
     </row>
     <row r="1420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1420" s="4" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1420" s="4" t="s">
-        <v>956</v>
+        <v>207</v>
       </c>
       <c r="C1420" s="7" t="s">
-        <v>1621</v>
+        <v>166</v>
       </c>
       <c r="D1420" s="3">
-        <v>7030</v>
+        <v>630000</v>
       </c>
       <c r="E1420" s="4">
-        <v>1100</v>
+        <v>63000</v>
       </c>
       <c r="F1420" s="4"/>
       <c r="G1420" s="4" t="s">
@@ -44863,19 +44974,19 @@
     </row>
     <row r="1421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1421" s="4" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1421" s="4" t="s">
-        <v>956</v>
+        <v>207</v>
       </c>
       <c r="C1421" s="7" t="s">
-        <v>1622</v>
+        <v>167</v>
       </c>
       <c r="D1421" s="3">
-        <v>6030</v>
+        <v>728000</v>
       </c>
       <c r="E1421" s="4">
-        <v>900</v>
+        <v>72800</v>
       </c>
       <c r="F1421" s="4"/>
       <c r="G1421" s="4" t="s">
@@ -44896,13 +45007,13 @@
         <v>956</v>
       </c>
       <c r="C1422" s="7" t="s">
-        <v>1623</v>
+        <v>1606</v>
       </c>
       <c r="D1422" s="3">
-        <v>6830</v>
+        <v>8534</v>
       </c>
       <c r="E1422" s="4">
-        <v>1100</v>
+        <v>1300</v>
       </c>
       <c r="F1422" s="4"/>
       <c r="G1422" s="4" t="s">
@@ -44923,13 +45034,13 @@
         <v>956</v>
       </c>
       <c r="C1423" s="7" t="s">
-        <v>1624</v>
+        <v>1351</v>
       </c>
       <c r="D1423" s="3">
-        <v>6930</v>
+        <v>12530</v>
       </c>
       <c r="E1423" s="4">
-        <v>1100</v>
+        <v>1900</v>
       </c>
       <c r="F1423" s="4"/>
       <c r="G1423" s="4" t="s">
@@ -44950,13 +45061,13 @@
         <v>956</v>
       </c>
       <c r="C1424" s="7" t="s">
-        <v>1352</v>
+        <v>1607</v>
       </c>
       <c r="D1424" s="3">
-        <v>14030</v>
+        <v>12530</v>
       </c>
       <c r="E1424" s="4">
-        <v>2200</v>
+        <v>1900</v>
       </c>
       <c r="F1424" s="4"/>
       <c r="G1424" s="4" t="s">
@@ -44977,13 +45088,13 @@
         <v>956</v>
       </c>
       <c r="C1425" s="7" t="s">
-        <v>1625</v>
+        <v>1608</v>
       </c>
       <c r="D1425" s="3">
-        <v>3780</v>
+        <v>15030</v>
       </c>
       <c r="E1425" s="4">
-        <v>600</v>
+        <v>2300</v>
       </c>
       <c r="F1425" s="4"/>
       <c r="G1425" s="4" t="s">
@@ -45004,13 +45115,13 @@
         <v>956</v>
       </c>
       <c r="C1426" s="7" t="s">
-        <v>1626</v>
+        <v>1609</v>
       </c>
       <c r="D1426" s="3">
-        <v>15530</v>
+        <v>12290</v>
       </c>
       <c r="E1426" s="4">
-        <v>2400</v>
+        <v>1900</v>
       </c>
       <c r="F1426" s="4"/>
       <c r="G1426" s="4" t="s">
@@ -45031,13 +45142,13 @@
         <v>956</v>
       </c>
       <c r="C1427" s="7" t="s">
-        <v>1627</v>
+        <v>1610</v>
       </c>
       <c r="D1427" s="3">
-        <v>11030</v>
+        <v>6330</v>
       </c>
       <c r="E1427" s="4">
-        <v>1700</v>
+        <v>1000</v>
       </c>
       <c r="F1427" s="4"/>
       <c r="G1427" s="4" t="s">
@@ -45058,13 +45169,13 @@
         <v>956</v>
       </c>
       <c r="C1428" s="7" t="s">
-        <v>1628</v>
+        <v>1611</v>
       </c>
       <c r="D1428" s="3">
-        <v>8530</v>
+        <v>7530</v>
       </c>
       <c r="E1428" s="4">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F1428" s="4"/>
       <c r="G1428" s="4" t="s">
@@ -45085,13 +45196,13 @@
         <v>956</v>
       </c>
       <c r="C1429" s="7" t="s">
-        <v>1629</v>
+        <v>1349</v>
       </c>
       <c r="D1429" s="3">
-        <v>12130</v>
+        <v>11530</v>
       </c>
       <c r="E1429" s="4">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="F1429" s="4"/>
       <c r="G1429" s="4" t="s">
@@ -45112,13 +45223,13 @@
         <v>956</v>
       </c>
       <c r="C1430" s="7" t="s">
-        <v>1630</v>
+        <v>1350</v>
       </c>
       <c r="D1430" s="3">
-        <v>15030</v>
+        <v>12130</v>
       </c>
       <c r="E1430" s="4">
-        <v>2300</v>
+        <v>1900</v>
       </c>
       <c r="F1430" s="4"/>
       <c r="G1430" s="4" t="s">
@@ -45139,13 +45250,13 @@
         <v>956</v>
       </c>
       <c r="C1431" s="7" t="s">
-        <v>1631</v>
+        <v>1612</v>
       </c>
       <c r="D1431" s="3">
-        <v>7530</v>
+        <v>5830</v>
       </c>
       <c r="E1431" s="4">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="F1431" s="4"/>
       <c r="G1431" s="4" t="s">
@@ -45166,13 +45277,13 @@
         <v>956</v>
       </c>
       <c r="C1432" s="7" t="s">
-        <v>1632</v>
+        <v>1613</v>
       </c>
       <c r="D1432" s="3">
-        <v>16530</v>
+        <v>8730</v>
       </c>
       <c r="E1432" s="4">
-        <v>2600</v>
+        <v>1400</v>
       </c>
       <c r="F1432" s="4"/>
       <c r="G1432" s="4" t="s">
@@ -45193,13 +45304,13 @@
         <v>956</v>
       </c>
       <c r="C1433" s="7" t="s">
-        <v>1633</v>
+        <v>1614</v>
       </c>
       <c r="D1433" s="3">
-        <v>4580</v>
+        <v>15530</v>
       </c>
       <c r="E1433" s="4">
-        <v>700</v>
+        <v>2400</v>
       </c>
       <c r="F1433" s="4"/>
       <c r="G1433" s="4" t="s">
@@ -45220,13 +45331,13 @@
         <v>956</v>
       </c>
       <c r="C1434" s="7" t="s">
-        <v>1634</v>
+        <v>1615</v>
       </c>
       <c r="D1434" s="3">
-        <v>8730</v>
+        <v>11530</v>
       </c>
       <c r="E1434" s="4">
-        <v>1400</v>
+        <v>1800</v>
       </c>
       <c r="F1434" s="4"/>
       <c r="G1434" s="4" t="s">
@@ -45244,16 +45355,16 @@
         <v>1262</v>
       </c>
       <c r="B1435" s="4" t="s">
-        <v>1263</v>
+        <v>956</v>
       </c>
       <c r="C1435" s="7" t="s">
-        <v>1635</v>
+        <v>1616</v>
       </c>
       <c r="D1435" s="3">
-        <v>59545</v>
+        <v>13530</v>
       </c>
       <c r="E1435" s="4">
-        <v>9200</v>
+        <v>2100</v>
       </c>
       <c r="F1435" s="4"/>
       <c r="G1435" s="4" t="s">
@@ -45271,16 +45382,16 @@
         <v>1262</v>
       </c>
       <c r="B1436" s="4" t="s">
-        <v>1263</v>
+        <v>956</v>
       </c>
       <c r="C1436" s="7" t="s">
-        <v>1636</v>
+        <v>1617</v>
       </c>
       <c r="D1436" s="3">
-        <v>23030</v>
+        <v>15530</v>
       </c>
       <c r="E1436" s="4">
-        <v>3600</v>
+        <v>2400</v>
       </c>
       <c r="F1436" s="4"/>
       <c r="G1436" s="4" t="s">
@@ -45298,16 +45409,16 @@
         <v>1262</v>
       </c>
       <c r="B1437" s="4" t="s">
-        <v>1263</v>
+        <v>956</v>
       </c>
       <c r="C1437" s="7" t="s">
-        <v>1637</v>
+        <v>1618</v>
       </c>
       <c r="D1437" s="3">
-        <v>32530</v>
+        <v>17530</v>
       </c>
       <c r="E1437" s="4">
-        <v>5000</v>
+        <v>2700</v>
       </c>
       <c r="F1437" s="4"/>
       <c r="G1437" s="4" t="s">
@@ -45325,16 +45436,16 @@
         <v>1262</v>
       </c>
       <c r="B1438" s="4" t="s">
-        <v>1263</v>
+        <v>956</v>
       </c>
       <c r="C1438" s="7" t="s">
-        <v>1638</v>
+        <v>1619</v>
       </c>
       <c r="D1438" s="3">
-        <v>33530</v>
+        <v>22030</v>
       </c>
       <c r="E1438" s="4">
-        <v>5200</v>
+        <v>3400</v>
       </c>
       <c r="F1438" s="4"/>
       <c r="G1438" s="4" t="s">
@@ -45352,16 +45463,16 @@
         <v>1262</v>
       </c>
       <c r="B1439" s="4" t="s">
-        <v>1263</v>
+        <v>956</v>
       </c>
       <c r="C1439" s="7" t="s">
-        <v>1257</v>
+        <v>1620</v>
       </c>
       <c r="D1439" s="3">
-        <v>27530</v>
+        <v>6730</v>
       </c>
       <c r="E1439" s="4">
-        <v>4300</v>
+        <v>1000</v>
       </c>
       <c r="F1439" s="4"/>
       <c r="G1439" s="4" t="s">
@@ -45379,16 +45490,16 @@
         <v>1262</v>
       </c>
       <c r="B1440" s="4" t="s">
-        <v>1263</v>
+        <v>956</v>
       </c>
       <c r="C1440" s="7" t="s">
-        <v>1258</v>
+        <v>1621</v>
       </c>
       <c r="D1440" s="3">
-        <v>33530</v>
+        <v>7030</v>
       </c>
       <c r="E1440" s="4">
-        <v>5200</v>
+        <v>1100</v>
       </c>
       <c r="F1440" s="4"/>
       <c r="G1440" s="4" t="s">
@@ -45406,16 +45517,16 @@
         <v>1262</v>
       </c>
       <c r="B1441" s="4" t="s">
-        <v>1263</v>
+        <v>956</v>
       </c>
       <c r="C1441" s="7" t="s">
-        <v>1259</v>
+        <v>1622</v>
       </c>
       <c r="D1441" s="3">
-        <v>32530</v>
+        <v>6030</v>
       </c>
       <c r="E1441" s="4">
-        <v>5000</v>
+        <v>900</v>
       </c>
       <c r="F1441" s="4"/>
       <c r="G1441" s="4" t="s">
@@ -45433,16 +45544,16 @@
         <v>1262</v>
       </c>
       <c r="B1442" s="4" t="s">
-        <v>1263</v>
+        <v>956</v>
       </c>
       <c r="C1442" s="7" t="s">
-        <v>1260</v>
+        <v>1623</v>
       </c>
       <c r="D1442" s="3">
-        <v>19655</v>
+        <v>6830</v>
       </c>
       <c r="E1442" s="4">
-        <v>3000</v>
+        <v>1100</v>
       </c>
       <c r="F1442" s="4"/>
       <c r="G1442" s="4" t="s">
@@ -45460,16 +45571,16 @@
         <v>1262</v>
       </c>
       <c r="B1443" s="4" t="s">
-        <v>1263</v>
+        <v>956</v>
       </c>
       <c r="C1443" s="7" t="s">
-        <v>1261</v>
+        <v>1624</v>
       </c>
       <c r="D1443" s="3">
-        <v>22696.666666666668</v>
+        <v>6930</v>
       </c>
       <c r="E1443" s="4">
-        <v>3500</v>
+        <v>1100</v>
       </c>
       <c r="F1443" s="4"/>
       <c r="G1443" s="4" t="s">
@@ -45487,16 +45598,16 @@
         <v>1262</v>
       </c>
       <c r="B1444" s="4" t="s">
-        <v>1668</v>
+        <v>956</v>
       </c>
       <c r="C1444" s="7" t="s">
-        <v>1639</v>
+        <v>1352</v>
       </c>
       <c r="D1444" s="3">
-        <v>46530</v>
+        <v>14030</v>
       </c>
       <c r="E1444" s="4">
-        <v>7200</v>
+        <v>2200</v>
       </c>
       <c r="F1444" s="4"/>
       <c r="G1444" s="4" t="s">
@@ -45514,16 +45625,16 @@
         <v>1262</v>
       </c>
       <c r="B1445" s="4" t="s">
-        <v>1668</v>
+        <v>956</v>
       </c>
       <c r="C1445" s="7" t="s">
-        <v>1640</v>
+        <v>1625</v>
       </c>
       <c r="D1445" s="3">
-        <v>46530</v>
+        <v>3780</v>
       </c>
       <c r="E1445" s="4">
-        <v>7200</v>
+        <v>600</v>
       </c>
       <c r="F1445" s="4"/>
       <c r="G1445" s="4" t="s">
@@ -45541,16 +45652,16 @@
         <v>1262</v>
       </c>
       <c r="B1446" s="4" t="s">
-        <v>1669</v>
+        <v>956</v>
       </c>
       <c r="C1446" s="7" t="s">
-        <v>1641</v>
+        <v>1626</v>
       </c>
       <c r="D1446" s="3">
-        <v>18530</v>
+        <v>15530</v>
       </c>
       <c r="E1446" s="4">
-        <v>2900</v>
+        <v>2400</v>
       </c>
       <c r="F1446" s="4"/>
       <c r="G1446" s="4" t="s">
@@ -45568,16 +45679,16 @@
         <v>1262</v>
       </c>
       <c r="B1447" s="4" t="s">
-        <v>1669</v>
+        <v>956</v>
       </c>
       <c r="C1447" s="7" t="s">
-        <v>1642</v>
+        <v>1627</v>
       </c>
       <c r="D1447" s="3">
-        <v>19030</v>
+        <v>11030</v>
       </c>
       <c r="E1447" s="4">
-        <v>2900</v>
+        <v>1700</v>
       </c>
       <c r="F1447" s="4"/>
       <c r="G1447" s="4" t="s">
@@ -45595,16 +45706,16 @@
         <v>1262</v>
       </c>
       <c r="B1448" s="4" t="s">
-        <v>1669</v>
+        <v>956</v>
       </c>
       <c r="C1448" s="7" t="s">
-        <v>1643</v>
+        <v>1628</v>
       </c>
       <c r="D1448" s="3">
-        <v>21530</v>
+        <v>8530</v>
       </c>
       <c r="E1448" s="4">
-        <v>3300</v>
+        <v>1300</v>
       </c>
       <c r="F1448" s="4"/>
       <c r="G1448" s="4" t="s">
@@ -45622,16 +45733,16 @@
         <v>1262</v>
       </c>
       <c r="B1449" s="4" t="s">
-        <v>1669</v>
+        <v>956</v>
       </c>
       <c r="C1449" s="7" t="s">
-        <v>1644</v>
+        <v>1629</v>
       </c>
       <c r="D1449" s="3">
-        <v>20530</v>
+        <v>12130</v>
       </c>
       <c r="E1449" s="4">
-        <v>3200</v>
+        <v>1900</v>
       </c>
       <c r="F1449" s="4"/>
       <c r="G1449" s="4" t="s">
@@ -45649,16 +45760,16 @@
         <v>1262</v>
       </c>
       <c r="B1450" s="4" t="s">
-        <v>1669</v>
+        <v>956</v>
       </c>
       <c r="C1450" s="7" t="s">
-        <v>1645</v>
+        <v>1630</v>
       </c>
       <c r="D1450" s="3">
-        <v>24530</v>
+        <v>15030</v>
       </c>
       <c r="E1450" s="4">
-        <v>3800</v>
+        <v>2300</v>
       </c>
       <c r="F1450" s="4"/>
       <c r="G1450" s="4" t="s">
@@ -45676,16 +45787,16 @@
         <v>1262</v>
       </c>
       <c r="B1451" s="4" t="s">
-        <v>1669</v>
+        <v>956</v>
       </c>
       <c r="C1451" s="7" t="s">
-        <v>1646</v>
+        <v>1631</v>
       </c>
       <c r="D1451" s="3">
-        <v>35030</v>
+        <v>7530</v>
       </c>
       <c r="E1451" s="4">
-        <v>5400</v>
+        <v>1200</v>
       </c>
       <c r="F1451" s="4"/>
       <c r="G1451" s="4" t="s">
@@ -45703,16 +45814,16 @@
         <v>1262</v>
       </c>
       <c r="B1452" s="4" t="s">
-        <v>1669</v>
-      </c>
-      <c r="C1452" s="6" t="s">
-        <v>1647</v>
-      </c>
-      <c r="D1452" s="5">
-        <v>37530</v>
-      </c>
-      <c r="E1452" s="5">
-        <v>5800</v>
+        <v>956</v>
+      </c>
+      <c r="C1452" s="7" t="s">
+        <v>1632</v>
+      </c>
+      <c r="D1452" s="3">
+        <v>16530</v>
+      </c>
+      <c r="E1452" s="4">
+        <v>2600</v>
       </c>
       <c r="F1452" s="4"/>
       <c r="G1452" s="4" t="s">
@@ -45730,16 +45841,16 @@
         <v>1262</v>
       </c>
       <c r="B1453" s="4" t="s">
-        <v>1669</v>
-      </c>
-      <c r="C1453" s="6" t="s">
-        <v>1648</v>
-      </c>
-      <c r="D1453" s="5">
-        <v>21030</v>
-      </c>
-      <c r="E1453" s="5">
-        <v>3300</v>
+        <v>956</v>
+      </c>
+      <c r="C1453" s="7" t="s">
+        <v>1633</v>
+      </c>
+      <c r="D1453" s="3">
+        <v>4580</v>
+      </c>
+      <c r="E1453" s="4">
+        <v>700</v>
       </c>
       <c r="F1453" s="4"/>
       <c r="G1453" s="4" t="s">
@@ -45757,16 +45868,16 @@
         <v>1262</v>
       </c>
       <c r="B1454" s="4" t="s">
-        <v>1669</v>
-      </c>
-      <c r="C1454" s="6" t="s">
-        <v>1649</v>
-      </c>
-      <c r="D1454" s="5">
-        <v>22530</v>
-      </c>
-      <c r="E1454" s="5">
-        <v>3500</v>
+        <v>956</v>
+      </c>
+      <c r="C1454" s="7" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D1454" s="3">
+        <v>8730</v>
+      </c>
+      <c r="E1454" s="4">
+        <v>1400</v>
       </c>
       <c r="F1454" s="4"/>
       <c r="G1454" s="4" t="s">
@@ -45784,16 +45895,16 @@
         <v>1262</v>
       </c>
       <c r="B1455" s="4" t="s">
-        <v>1669</v>
-      </c>
-      <c r="C1455" s="6" t="s">
-        <v>1650</v>
-      </c>
-      <c r="D1455" s="5">
-        <v>20530</v>
-      </c>
-      <c r="E1455" s="5">
-        <v>3200</v>
+        <v>1263</v>
+      </c>
+      <c r="C1455" s="7" t="s">
+        <v>1635</v>
+      </c>
+      <c r="D1455" s="3">
+        <v>59545</v>
+      </c>
+      <c r="E1455" s="4">
+        <v>9200</v>
       </c>
       <c r="F1455" s="4"/>
       <c r="G1455" s="4" t="s">
@@ -45811,16 +45922,16 @@
         <v>1262</v>
       </c>
       <c r="B1456" s="4" t="s">
-        <v>1669</v>
-      </c>
-      <c r="C1456" s="6" t="s">
-        <v>1651</v>
-      </c>
-      <c r="D1456" s="5">
-        <v>17030</v>
-      </c>
-      <c r="E1456" s="5">
-        <v>2600</v>
+        <v>1263</v>
+      </c>
+      <c r="C1456" s="7" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D1456" s="3">
+        <v>23030</v>
+      </c>
+      <c r="E1456" s="4">
+        <v>3600</v>
       </c>
       <c r="F1456" s="4"/>
       <c r="G1456" s="4" t="s">
@@ -45838,15 +45949,15 @@
         <v>1262</v>
       </c>
       <c r="B1457" s="4" t="s">
-        <v>1669</v>
-      </c>
-      <c r="C1457" s="6" t="s">
-        <v>1652</v>
-      </c>
-      <c r="D1457" s="5">
+        <v>1263</v>
+      </c>
+      <c r="C1457" s="7" t="s">
+        <v>1637</v>
+      </c>
+      <c r="D1457" s="3">
         <v>32530</v>
       </c>
-      <c r="E1457" s="5">
+      <c r="E1457" s="4">
         <v>5000</v>
       </c>
       <c r="F1457" s="4"/>
@@ -45865,16 +45976,16 @@
         <v>1262</v>
       </c>
       <c r="B1458" s="4" t="s">
-        <v>1669</v>
-      </c>
-      <c r="C1458" s="6" t="s">
-        <v>1653</v>
-      </c>
-      <c r="D1458" s="5">
-        <v>17530</v>
-      </c>
-      <c r="E1458" s="5">
-        <v>2700</v>
+        <v>1263</v>
+      </c>
+      <c r="C1458" s="7" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D1458" s="3">
+        <v>33530</v>
+      </c>
+      <c r="E1458" s="4">
+        <v>5200</v>
       </c>
       <c r="F1458" s="4"/>
       <c r="G1458" s="4" t="s">
@@ -45892,16 +46003,16 @@
         <v>1262</v>
       </c>
       <c r="B1459" s="4" t="s">
-        <v>1670</v>
-      </c>
-      <c r="C1459" s="6" t="s">
-        <v>1654</v>
-      </c>
-      <c r="D1459" s="5">
-        <v>3830</v>
-      </c>
-      <c r="E1459" s="5">
-        <v>600</v>
+        <v>1263</v>
+      </c>
+      <c r="C1459" s="7" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D1459" s="3">
+        <v>27530</v>
+      </c>
+      <c r="E1459" s="4">
+        <v>4300</v>
       </c>
       <c r="F1459" s="4"/>
       <c r="G1459" s="4" t="s">
@@ -45919,16 +46030,16 @@
         <v>1262</v>
       </c>
       <c r="B1460" s="4" t="s">
-        <v>1670</v>
-      </c>
-      <c r="C1460" s="6" t="s">
-        <v>1655</v>
-      </c>
-      <c r="D1460" s="5">
-        <v>5030</v>
-      </c>
-      <c r="E1460" s="5">
-        <v>800</v>
+        <v>1263</v>
+      </c>
+      <c r="C1460" s="7" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D1460" s="3">
+        <v>33530</v>
+      </c>
+      <c r="E1460" s="4">
+        <v>5200</v>
       </c>
       <c r="F1460" s="4"/>
       <c r="G1460" s="4" t="s">
@@ -45946,16 +46057,16 @@
         <v>1262</v>
       </c>
       <c r="B1461" s="4" t="s">
-        <v>1669</v>
+        <v>1263</v>
       </c>
       <c r="C1461" s="7" t="s">
-        <v>1656</v>
+        <v>1259</v>
       </c>
       <c r="D1461" s="3">
-        <v>23530</v>
+        <v>32530</v>
       </c>
       <c r="E1461" s="4">
-        <v>3600</v>
+        <v>5000</v>
       </c>
       <c r="F1461" s="4"/>
       <c r="G1461" s="4" t="s">
@@ -45973,16 +46084,16 @@
         <v>1262</v>
       </c>
       <c r="B1462" s="4" t="s">
-        <v>956</v>
+        <v>1263</v>
       </c>
       <c r="C1462" s="7" t="s">
-        <v>1657</v>
+        <v>1260</v>
       </c>
       <c r="D1462" s="3">
-        <v>32530</v>
+        <v>19655</v>
       </c>
       <c r="E1462" s="4">
-        <v>4600</v>
+        <v>3000</v>
       </c>
       <c r="F1462" s="4"/>
       <c r="G1462" s="4" t="s">
@@ -46000,13 +46111,13 @@
         <v>1262</v>
       </c>
       <c r="B1463" s="4" t="s">
-        <v>956</v>
+        <v>1263</v>
       </c>
       <c r="C1463" s="7" t="s">
-        <v>1658</v>
+        <v>1261</v>
       </c>
       <c r="D1463" s="3">
-        <v>25030</v>
+        <v>22696.666666666668</v>
       </c>
       <c r="E1463" s="4">
         <v>3500</v>
@@ -46027,16 +46138,16 @@
         <v>1262</v>
       </c>
       <c r="B1464" s="4" t="s">
-        <v>956</v>
+        <v>1668</v>
       </c>
       <c r="C1464" s="7" t="s">
-        <v>1659</v>
+        <v>1639</v>
       </c>
       <c r="D1464" s="3">
-        <v>25830</v>
+        <v>46530</v>
       </c>
       <c r="E1464" s="4">
-        <v>3600</v>
+        <v>7200</v>
       </c>
       <c r="F1464" s="4"/>
       <c r="G1464" s="4" t="s">
@@ -46054,16 +46165,16 @@
         <v>1262</v>
       </c>
       <c r="B1465" s="4" t="s">
-        <v>956</v>
+        <v>1668</v>
       </c>
       <c r="C1465" s="7" t="s">
-        <v>1660</v>
+        <v>1640</v>
       </c>
       <c r="D1465" s="3">
-        <v>32530</v>
+        <v>46530</v>
       </c>
       <c r="E1465" s="4">
-        <v>4600</v>
+        <v>7200</v>
       </c>
       <c r="F1465" s="4"/>
       <c r="G1465" s="4" t="s">
@@ -46081,16 +46192,16 @@
         <v>1262</v>
       </c>
       <c r="B1466" s="4" t="s">
-        <v>956</v>
+        <v>1669</v>
       </c>
       <c r="C1466" s="7" t="s">
-        <v>1661</v>
+        <v>1641</v>
       </c>
       <c r="D1466" s="3">
-        <v>25530</v>
+        <v>18530</v>
       </c>
       <c r="E1466" s="4">
-        <v>3600</v>
+        <v>2900</v>
       </c>
       <c r="F1466" s="4"/>
       <c r="G1466" s="4" t="s">
@@ -46108,16 +46219,16 @@
         <v>1262</v>
       </c>
       <c r="B1467" s="4" t="s">
-        <v>956</v>
+        <v>1669</v>
       </c>
       <c r="C1467" s="7" t="s">
-        <v>1662</v>
+        <v>1642</v>
       </c>
       <c r="D1467" s="3">
-        <v>25530</v>
+        <v>19030</v>
       </c>
       <c r="E1467" s="4">
-        <v>3600</v>
+        <v>2900</v>
       </c>
       <c r="F1467" s="4"/>
       <c r="G1467" s="4" t="s">
@@ -46135,16 +46246,16 @@
         <v>1262</v>
       </c>
       <c r="B1468" s="4" t="s">
-        <v>956</v>
+        <v>1669</v>
       </c>
       <c r="C1468" s="7" t="s">
-        <v>1663</v>
+        <v>1643</v>
       </c>
       <c r="D1468" s="3">
-        <v>25030</v>
+        <v>21530</v>
       </c>
       <c r="E1468" s="4">
-        <v>3500</v>
+        <v>3300</v>
       </c>
       <c r="F1468" s="4"/>
       <c r="G1468" s="4" t="s">
@@ -46162,16 +46273,16 @@
         <v>1262</v>
       </c>
       <c r="B1469" s="4" t="s">
-        <v>956</v>
+        <v>1669</v>
       </c>
       <c r="C1469" s="7" t="s">
-        <v>1664</v>
+        <v>1644</v>
       </c>
       <c r="D1469" s="3">
-        <v>41530</v>
+        <v>20530</v>
       </c>
       <c r="E1469" s="4">
-        <v>5800</v>
+        <v>3200</v>
       </c>
       <c r="F1469" s="4"/>
       <c r="G1469" s="4" t="s">
@@ -46189,16 +46300,16 @@
         <v>1262</v>
       </c>
       <c r="B1470" s="4" t="s">
-        <v>956</v>
+        <v>1669</v>
       </c>
       <c r="C1470" s="7" t="s">
-        <v>1665</v>
+        <v>1645</v>
       </c>
       <c r="D1470" s="3">
-        <v>22530</v>
+        <v>24530</v>
       </c>
       <c r="E1470" s="4">
-        <v>3200</v>
+        <v>3800</v>
       </c>
       <c r="F1470" s="4"/>
       <c r="G1470" s="4" t="s">
@@ -46216,16 +46327,16 @@
         <v>1262</v>
       </c>
       <c r="B1471" s="4" t="s">
-        <v>956</v>
+        <v>1669</v>
       </c>
       <c r="C1471" s="7" t="s">
-        <v>1666</v>
+        <v>1646</v>
       </c>
       <c r="D1471" s="3">
         <v>35030</v>
       </c>
       <c r="E1471" s="4">
-        <v>4900</v>
+        <v>5400</v>
       </c>
       <c r="F1471" s="4"/>
       <c r="G1471" s="4" t="s">
@@ -46243,16 +46354,16 @@
         <v>1262</v>
       </c>
       <c r="B1472" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="C1472" s="7" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D1472" s="3">
-        <v>18530</v>
-      </c>
-      <c r="E1472" s="4">
-        <v>2900</v>
+        <v>1669</v>
+      </c>
+      <c r="C1472" s="6" t="s">
+        <v>1647</v>
+      </c>
+      <c r="D1472" s="5">
+        <v>37530</v>
+      </c>
+      <c r="E1472" s="5">
+        <v>5800</v>
       </c>
       <c r="F1472" s="4"/>
       <c r="G1472" s="4" t="s">
@@ -46266,216 +46377,216 @@
       </c>
     </row>
     <row r="1473" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1473" s="9" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B1473" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1473" s="10" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D1473" s="11">
-        <v>56000</v>
-      </c>
-      <c r="E1473" s="9">
-        <v>5900</v>
-      </c>
-      <c r="F1473" s="9"/>
-      <c r="G1473" s="9" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1473" s="9" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1473" s="9">
+      <c r="A1473" s="4" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B1473" s="4" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C1473" s="6" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D1473" s="5">
+        <v>21030</v>
+      </c>
+      <c r="E1473" s="5">
+        <v>3300</v>
+      </c>
+      <c r="F1473" s="4"/>
+      <c r="G1473" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1473" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1473" s="4">
         <v>2026</v>
       </c>
     </row>
     <row r="1474" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1474" s="9" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B1474" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1474" s="10" t="s">
-        <v>1041</v>
-      </c>
-      <c r="D1474" s="11">
-        <v>66000</v>
-      </c>
-      <c r="E1474" s="9">
-        <v>7000</v>
-      </c>
-      <c r="F1474" s="9"/>
-      <c r="G1474" s="9" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1474" s="9" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1474" s="9">
+      <c r="A1474" s="4" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B1474" s="4" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C1474" s="6" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D1474" s="5">
+        <v>22530</v>
+      </c>
+      <c r="E1474" s="5">
+        <v>3500</v>
+      </c>
+      <c r="F1474" s="4"/>
+      <c r="G1474" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1474" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1474" s="4">
         <v>2026</v>
       </c>
     </row>
     <row r="1475" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1475" s="9" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B1475" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1475" s="10" t="s">
-        <v>1042</v>
-      </c>
-      <c r="D1475" s="11">
-        <v>85000</v>
-      </c>
-      <c r="E1475" s="9">
-        <v>9100</v>
-      </c>
-      <c r="F1475" s="9"/>
-      <c r="G1475" s="9" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1475" s="9" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1475" s="9">
+      <c r="A1475" s="4" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B1475" s="4" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C1475" s="6" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D1475" s="5">
+        <v>20530</v>
+      </c>
+      <c r="E1475" s="5">
+        <v>3200</v>
+      </c>
+      <c r="F1475" s="4"/>
+      <c r="G1475" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1475" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1475" s="4">
         <v>2026</v>
       </c>
     </row>
     <row r="1476" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1476" s="9" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B1476" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1476" s="10" t="s">
-        <v>1043</v>
-      </c>
-      <c r="D1476" s="11">
-        <v>109000</v>
-      </c>
-      <c r="E1476" s="9">
-        <v>10900</v>
-      </c>
-      <c r="F1476" s="9"/>
-      <c r="G1476" s="9" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1476" s="9" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1476" s="9">
+      <c r="A1476" s="4" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B1476" s="4" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C1476" s="6" t="s">
+        <v>1651</v>
+      </c>
+      <c r="D1476" s="5">
+        <v>17030</v>
+      </c>
+      <c r="E1476" s="5">
+        <v>2600</v>
+      </c>
+      <c r="F1476" s="4"/>
+      <c r="G1476" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1476" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1476" s="4">
         <v>2026</v>
       </c>
     </row>
     <row r="1477" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1477" s="9" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B1477" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1477" s="10" t="s">
-        <v>1044</v>
-      </c>
-      <c r="D1477" s="11">
-        <v>112000</v>
-      </c>
-      <c r="E1477" s="9">
-        <v>11900</v>
-      </c>
-      <c r="F1477" s="9"/>
-      <c r="G1477" s="9" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1477" s="9" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1477" s="9">
+      <c r="A1477" s="4" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B1477" s="4" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C1477" s="6" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D1477" s="5">
+        <v>32530</v>
+      </c>
+      <c r="E1477" s="5">
+        <v>5000</v>
+      </c>
+      <c r="F1477" s="4"/>
+      <c r="G1477" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1477" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1477" s="4">
         <v>2026</v>
       </c>
     </row>
     <row r="1478" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1478" s="9" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B1478" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1478" s="10" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D1478" s="11">
-        <v>140000</v>
-      </c>
-      <c r="E1478" s="9">
-        <v>14000</v>
-      </c>
-      <c r="F1478" s="9"/>
-      <c r="G1478" s="9" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1478" s="9" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1478" s="9">
+      <c r="A1478" s="4" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B1478" s="4" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C1478" s="6" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D1478" s="5">
+        <v>17530</v>
+      </c>
+      <c r="E1478" s="5">
+        <v>2700</v>
+      </c>
+      <c r="F1478" s="4"/>
+      <c r="G1478" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1478" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1478" s="4">
         <v>2026</v>
       </c>
     </row>
     <row r="1479" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1479" s="9" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B1479" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1479" s="10" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D1479" s="11">
-        <v>154000</v>
-      </c>
-      <c r="E1479" s="9">
-        <v>15400</v>
-      </c>
-      <c r="F1479" s="9"/>
-      <c r="G1479" s="9" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1479" s="9" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1479" s="9">
+      <c r="A1479" s="4" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B1479" s="4" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C1479" s="6" t="s">
+        <v>1654</v>
+      </c>
+      <c r="D1479" s="5">
+        <v>3830</v>
+      </c>
+      <c r="E1479" s="5">
+        <v>600</v>
+      </c>
+      <c r="F1479" s="4"/>
+      <c r="G1479" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1479" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1479" s="4">
         <v>2026</v>
       </c>
     </row>
     <row r="1480" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1480" s="4" t="s">
-        <v>170</v>
+        <v>1262</v>
       </c>
       <c r="B1480" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1480" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="D1480" s="3">
-        <v>700000</v>
-      </c>
-      <c r="E1480" s="4">
-        <v>70000</v>
+        <v>1670</v>
+      </c>
+      <c r="C1480" s="6" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D1480" s="5">
+        <v>5030</v>
+      </c>
+      <c r="E1480" s="5">
+        <v>800</v>
       </c>
       <c r="F1480" s="4"/>
       <c r="G1480" s="4" t="s">
         <v>1459</v>
       </c>
       <c r="H1480" s="4" t="s">
-        <v>206</v>
+        <v>1455</v>
       </c>
       <c r="I1480" s="4">
         <v>2026</v>
@@ -46483,26 +46594,26 @@
     </row>
     <row r="1481" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1481" s="4" t="s">
-        <v>170</v>
+        <v>1262</v>
       </c>
       <c r="B1481" s="4" t="s">
-        <v>207</v>
+        <v>1669</v>
       </c>
       <c r="C1481" s="7" t="s">
-        <v>185</v>
+        <v>1656</v>
       </c>
       <c r="D1481" s="3">
-        <v>490000</v>
+        <v>23530</v>
       </c>
       <c r="E1481" s="4">
-        <v>49000</v>
+        <v>3600</v>
       </c>
       <c r="F1481" s="4"/>
       <c r="G1481" s="4" t="s">
         <v>1459</v>
       </c>
       <c r="H1481" s="4" t="s">
-        <v>206</v>
+        <v>1455</v>
       </c>
       <c r="I1481" s="4">
         <v>2026</v>
@@ -46510,26 +46621,26 @@
     </row>
     <row r="1482" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1482" s="4" t="s">
-        <v>170</v>
+        <v>1262</v>
       </c>
       <c r="B1482" s="4" t="s">
-        <v>207</v>
+        <v>956</v>
       </c>
       <c r="C1482" s="7" t="s">
-        <v>186</v>
+        <v>1657</v>
       </c>
       <c r="D1482" s="3">
-        <v>378000</v>
+        <v>32530</v>
       </c>
       <c r="E1482" s="4">
-        <v>37800</v>
+        <v>4600</v>
       </c>
       <c r="F1482" s="4"/>
       <c r="G1482" s="4" t="s">
         <v>1459</v>
       </c>
       <c r="H1482" s="4" t="s">
-        <v>206</v>
+        <v>1455</v>
       </c>
       <c r="I1482" s="4">
         <v>2026</v>
@@ -46537,26 +46648,26 @@
     </row>
     <row r="1483" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1483" s="4" t="s">
-        <v>170</v>
+        <v>1262</v>
       </c>
       <c r="B1483" s="4" t="s">
-        <v>207</v>
+        <v>956</v>
       </c>
       <c r="C1483" s="7" t="s">
-        <v>187</v>
+        <v>1658</v>
       </c>
       <c r="D1483" s="3">
-        <v>280000</v>
+        <v>25030</v>
       </c>
       <c r="E1483" s="4">
-        <v>28000</v>
+        <v>3500</v>
       </c>
       <c r="F1483" s="4"/>
       <c r="G1483" s="4" t="s">
         <v>1459</v>
       </c>
       <c r="H1483" s="4" t="s">
-        <v>206</v>
+        <v>1455</v>
       </c>
       <c r="I1483" s="4">
         <v>2026</v>
@@ -46564,26 +46675,26 @@
     </row>
     <row r="1484" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1484" s="4" t="s">
-        <v>170</v>
+        <v>1262</v>
       </c>
       <c r="B1484" s="4" t="s">
-        <v>207</v>
+        <v>956</v>
       </c>
       <c r="C1484" s="7" t="s">
-        <v>188</v>
+        <v>1659</v>
       </c>
       <c r="D1484" s="3">
-        <v>252000</v>
+        <v>25830</v>
       </c>
       <c r="E1484" s="4">
-        <v>25200</v>
+        <v>3600</v>
       </c>
       <c r="F1484" s="4"/>
       <c r="G1484" s="4" t="s">
         <v>1459</v>
       </c>
       <c r="H1484" s="4" t="s">
-        <v>206</v>
+        <v>1455</v>
       </c>
       <c r="I1484" s="4">
         <v>2026</v>
@@ -46591,26 +46702,26 @@
     </row>
     <row r="1485" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1485" s="4" t="s">
-        <v>170</v>
+        <v>1262</v>
       </c>
       <c r="B1485" s="4" t="s">
-        <v>207</v>
+        <v>956</v>
       </c>
       <c r="C1485" s="7" t="s">
-        <v>189</v>
+        <v>1660</v>
       </c>
       <c r="D1485" s="3">
-        <v>224000</v>
+        <v>32530</v>
       </c>
       <c r="E1485" s="4">
-        <v>22400</v>
+        <v>4600</v>
       </c>
       <c r="F1485" s="4"/>
       <c r="G1485" s="4" t="s">
         <v>1459</v>
       </c>
       <c r="H1485" s="4" t="s">
-        <v>206</v>
+        <v>1455</v>
       </c>
       <c r="I1485" s="4">
         <v>2026</v>
@@ -46618,26 +46729,26 @@
     </row>
     <row r="1486" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1486" s="4" t="s">
-        <v>170</v>
+        <v>1262</v>
       </c>
       <c r="B1486" s="4" t="s">
-        <v>207</v>
+        <v>956</v>
       </c>
       <c r="C1486" s="7" t="s">
-        <v>190</v>
+        <v>1661</v>
       </c>
       <c r="D1486" s="3">
-        <v>217000</v>
+        <v>25530</v>
       </c>
       <c r="E1486" s="4">
-        <v>21700</v>
+        <v>3600</v>
       </c>
       <c r="F1486" s="4"/>
       <c r="G1486" s="4" t="s">
         <v>1459</v>
       </c>
       <c r="H1486" s="4" t="s">
-        <v>206</v>
+        <v>1455</v>
       </c>
       <c r="I1486" s="4">
         <v>2026</v>
@@ -46645,26 +46756,26 @@
     </row>
     <row r="1487" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1487" s="4" t="s">
-        <v>170</v>
+        <v>1262</v>
       </c>
       <c r="B1487" s="4" t="s">
-        <v>207</v>
+        <v>956</v>
       </c>
       <c r="C1487" s="7" t="s">
-        <v>191</v>
+        <v>1662</v>
       </c>
       <c r="D1487" s="3">
-        <v>204000</v>
+        <v>25530</v>
       </c>
       <c r="E1487" s="4">
-        <v>20400</v>
+        <v>3600</v>
       </c>
       <c r="F1487" s="4"/>
       <c r="G1487" s="4" t="s">
         <v>1459</v>
       </c>
       <c r="H1487" s="4" t="s">
-        <v>206</v>
+        <v>1455</v>
       </c>
       <c r="I1487" s="4">
         <v>2026</v>
@@ -46672,26 +46783,26 @@
     </row>
     <row r="1488" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1488" s="4" t="s">
-        <v>170</v>
+        <v>1262</v>
       </c>
       <c r="B1488" s="4" t="s">
-        <v>207</v>
+        <v>956</v>
       </c>
       <c r="C1488" s="7" t="s">
-        <v>192</v>
+        <v>1663</v>
       </c>
       <c r="D1488" s="3">
-        <v>189000</v>
+        <v>25030</v>
       </c>
       <c r="E1488" s="4">
-        <v>18900</v>
+        <v>3500</v>
       </c>
       <c r="F1488" s="4"/>
       <c r="G1488" s="4" t="s">
         <v>1459</v>
       </c>
       <c r="H1488" s="4" t="s">
-        <v>206</v>
+        <v>1455</v>
       </c>
       <c r="I1488" s="4">
         <v>2026</v>
@@ -46699,26 +46810,26 @@
     </row>
     <row r="1489" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1489" s="4" t="s">
-        <v>170</v>
+        <v>1262</v>
       </c>
       <c r="B1489" s="4" t="s">
-        <v>207</v>
+        <v>956</v>
       </c>
       <c r="C1489" s="7" t="s">
-        <v>193</v>
+        <v>1664</v>
       </c>
       <c r="D1489" s="3">
-        <v>175000</v>
+        <v>41530</v>
       </c>
       <c r="E1489" s="4">
-        <v>17500</v>
+        <v>5800</v>
       </c>
       <c r="F1489" s="4"/>
       <c r="G1489" s="4" t="s">
         <v>1459</v>
       </c>
       <c r="H1489" s="4" t="s">
-        <v>206</v>
+        <v>1455</v>
       </c>
       <c r="I1489" s="4">
         <v>2026</v>
@@ -46726,26 +46837,26 @@
     </row>
     <row r="1490" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1490" s="4" t="s">
-        <v>170</v>
+        <v>1262</v>
       </c>
       <c r="B1490" s="4" t="s">
-        <v>207</v>
+        <v>956</v>
       </c>
       <c r="C1490" s="7" t="s">
-        <v>194</v>
+        <v>1665</v>
       </c>
       <c r="D1490" s="3">
-        <v>154000</v>
+        <v>22530</v>
       </c>
       <c r="E1490" s="4">
-        <v>15400</v>
+        <v>3200</v>
       </c>
       <c r="F1490" s="4"/>
       <c r="G1490" s="4" t="s">
         <v>1459</v>
       </c>
       <c r="H1490" s="4" t="s">
-        <v>206</v>
+        <v>1455</v>
       </c>
       <c r="I1490" s="4">
         <v>2026</v>
@@ -46753,26 +46864,26 @@
     </row>
     <row r="1491" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1491" s="4" t="s">
-        <v>170</v>
+        <v>1262</v>
       </c>
       <c r="B1491" s="4" t="s">
-        <v>207</v>
+        <v>956</v>
       </c>
       <c r="C1491" s="7" t="s">
-        <v>195</v>
+        <v>1666</v>
       </c>
       <c r="D1491" s="3">
-        <v>140000</v>
+        <v>35030</v>
       </c>
       <c r="E1491" s="4">
-        <v>14000</v>
+        <v>4900</v>
       </c>
       <c r="F1491" s="4"/>
       <c r="G1491" s="4" t="s">
         <v>1459</v>
       </c>
       <c r="H1491" s="4" t="s">
-        <v>206</v>
+        <v>1455</v>
       </c>
       <c r="I1491" s="4">
         <v>2026</v>
@@ -46780,217 +46891,217 @@
     </row>
     <row r="1492" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1492" s="4" t="s">
-        <v>170</v>
+        <v>1262</v>
       </c>
       <c r="B1492" s="4" t="s">
-        <v>207</v>
+        <v>398</v>
       </c>
       <c r="C1492" s="7" t="s">
-        <v>196</v>
+        <v>1667</v>
       </c>
       <c r="D1492" s="3">
-        <v>133000</v>
+        <v>18530</v>
       </c>
       <c r="E1492" s="4">
-        <v>13300</v>
+        <v>2900</v>
       </c>
       <c r="F1492" s="4"/>
       <c r="G1492" s="4" t="s">
         <v>1459</v>
       </c>
       <c r="H1492" s="4" t="s">
-        <v>206</v>
+        <v>1455</v>
       </c>
       <c r="I1492" s="4">
         <v>2026</v>
       </c>
     </row>
     <row r="1493" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1493" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1493" s="4" t="s">
+      <c r="A1493" s="9" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B1493" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="C1493" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D1493" s="3">
-        <v>123000</v>
-      </c>
-      <c r="E1493" s="4">
-        <v>12300</v>
-      </c>
-      <c r="F1493" s="4"/>
-      <c r="G1493" s="4" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1493" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="I1493" s="4">
+      <c r="C1493" s="10" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1493" s="11">
+        <v>56000</v>
+      </c>
+      <c r="E1493" s="9">
+        <v>5900</v>
+      </c>
+      <c r="F1493" s="9"/>
+      <c r="G1493" s="9" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1493" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1493" s="9">
         <v>2026</v>
       </c>
     </row>
     <row r="1494" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1494" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1494" s="4" t="s">
+      <c r="A1494" s="9" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B1494" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="C1494" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="D1494" s="3">
-        <v>116000</v>
-      </c>
-      <c r="E1494" s="4">
-        <v>11600</v>
-      </c>
-      <c r="F1494" s="4"/>
-      <c r="G1494" s="4" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1494" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="I1494" s="4">
+      <c r="C1494" s="10" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D1494" s="11">
+        <v>66000</v>
+      </c>
+      <c r="E1494" s="9">
+        <v>7000</v>
+      </c>
+      <c r="F1494" s="9"/>
+      <c r="G1494" s="9" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1494" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1494" s="9">
         <v>2026</v>
       </c>
     </row>
     <row r="1495" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1495" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1495" s="4" t="s">
+      <c r="A1495" s="9" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B1495" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="C1495" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="D1495" s="3">
-        <v>102000</v>
-      </c>
-      <c r="E1495" s="4">
-        <v>10200</v>
-      </c>
-      <c r="F1495" s="4"/>
-      <c r="G1495" s="4" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1495" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="I1495" s="4">
+      <c r="C1495" s="10" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D1495" s="11">
+        <v>85000</v>
+      </c>
+      <c r="E1495" s="9">
+        <v>9100</v>
+      </c>
+      <c r="F1495" s="9"/>
+      <c r="G1495" s="9" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1495" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1495" s="9">
         <v>2026</v>
       </c>
     </row>
     <row r="1496" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1496" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1496" s="4" t="s">
+      <c r="A1496" s="9" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B1496" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="C1496" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="D1496" s="3">
-        <v>97000</v>
-      </c>
-      <c r="E1496" s="4">
-        <v>9700</v>
-      </c>
-      <c r="F1496" s="4"/>
-      <c r="G1496" s="4" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1496" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="I1496" s="4">
+      <c r="C1496" s="10" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D1496" s="11">
+        <v>109000</v>
+      </c>
+      <c r="E1496" s="9">
+        <v>10900</v>
+      </c>
+      <c r="F1496" s="9"/>
+      <c r="G1496" s="9" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1496" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1496" s="9">
         <v>2026</v>
       </c>
     </row>
     <row r="1497" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1497" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1497" s="4" t="s">
+      <c r="A1497" s="9" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B1497" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="C1497" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="D1497" s="3">
-        <v>74000</v>
-      </c>
-      <c r="E1497" s="4">
-        <v>7400</v>
-      </c>
-      <c r="F1497" s="4"/>
-      <c r="G1497" s="4" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1497" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="I1497" s="4">
+      <c r="C1497" s="10" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D1497" s="11">
+        <v>112000</v>
+      </c>
+      <c r="E1497" s="9">
+        <v>11900</v>
+      </c>
+      <c r="F1497" s="9"/>
+      <c r="G1497" s="9" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1497" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1497" s="9">
         <v>2026</v>
       </c>
     </row>
     <row r="1498" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1498" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1498" s="4" t="s">
+      <c r="A1498" s="9" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B1498" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="C1498" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="D1498" s="3">
-        <v>71000</v>
-      </c>
-      <c r="E1498" s="4">
-        <v>7100</v>
-      </c>
-      <c r="F1498" s="4"/>
-      <c r="G1498" s="4" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1498" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="I1498" s="4">
+      <c r="C1498" s="10" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D1498" s="11">
+        <v>140000</v>
+      </c>
+      <c r="E1498" s="9">
+        <v>14000</v>
+      </c>
+      <c r="F1498" s="9"/>
+      <c r="G1498" s="9" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1498" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1498" s="9">
         <v>2026</v>
       </c>
     </row>
     <row r="1499" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1499" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1499" s="4" t="s">
+      <c r="A1499" s="9" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B1499" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="C1499" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="D1499" s="3">
-        <v>63000</v>
-      </c>
-      <c r="E1499" s="4">
-        <v>6300</v>
-      </c>
-      <c r="F1499" s="4"/>
-      <c r="G1499" s="4" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1499" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="I1499" s="4">
+      <c r="C1499" s="10" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D1499" s="11">
+        <v>154000</v>
+      </c>
+      <c r="E1499" s="9">
+        <v>15400</v>
+      </c>
+      <c r="F1499" s="9"/>
+      <c r="G1499" s="9" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1499" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1499" s="9">
         <v>2026</v>
       </c>
     </row>
@@ -47002,13 +47113,13 @@
         <v>207</v>
       </c>
       <c r="C1500" s="7" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="D1500" s="3">
-        <v>56000</v>
+        <v>700000</v>
       </c>
       <c r="E1500" s="4">
-        <v>5600</v>
+        <v>70000</v>
       </c>
       <c r="F1500" s="4"/>
       <c r="G1500" s="4" t="s">
@@ -47023,19 +47134,19 @@
     </row>
     <row r="1501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1501" s="4" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1501" s="4" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1501" s="7" t="s">
-        <v>629</v>
+        <v>185</v>
       </c>
       <c r="D1501" s="3">
-        <v>5400</v>
+        <v>490000</v>
       </c>
       <c r="E1501" s="4">
-        <v>800</v>
+        <v>49000</v>
       </c>
       <c r="F1501" s="4"/>
       <c r="G1501" s="4" t="s">
@@ -47050,19 +47161,19 @@
     </row>
     <row r="1502" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1502" s="4" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1502" s="4" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1502" s="7" t="s">
-        <v>630</v>
+        <v>186</v>
       </c>
       <c r="D1502" s="3">
-        <v>26200</v>
+        <v>378000</v>
       </c>
       <c r="E1502" s="4">
-        <v>4100</v>
+        <v>37800</v>
       </c>
       <c r="F1502" s="4"/>
       <c r="G1502" s="4" t="s">
@@ -47077,19 +47188,19 @@
     </row>
     <row r="1503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1503" s="4" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1503" s="4" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1503" s="7" t="s">
-        <v>631</v>
+        <v>187</v>
       </c>
       <c r="D1503" s="3">
-        <v>27200</v>
+        <v>280000</v>
       </c>
       <c r="E1503" s="4">
-        <v>4200</v>
+        <v>28000</v>
       </c>
       <c r="F1503" s="4"/>
       <c r="G1503" s="4" t="s">
@@ -47104,19 +47215,19 @@
     </row>
     <row r="1504" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1504" s="4" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1504" s="4" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1504" s="7" t="s">
-        <v>632</v>
+        <v>188</v>
       </c>
       <c r="D1504" s="3">
-        <v>20700</v>
+        <v>252000</v>
       </c>
       <c r="E1504" s="4">
-        <v>3200</v>
+        <v>25200</v>
       </c>
       <c r="F1504" s="4"/>
       <c r="G1504" s="4" t="s">
@@ -47131,19 +47242,19 @@
     </row>
     <row r="1505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1505" s="4" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1505" s="4" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1505" s="7" t="s">
-        <v>633</v>
+        <v>189</v>
       </c>
       <c r="D1505" s="3">
-        <v>9900</v>
+        <v>224000</v>
       </c>
       <c r="E1505" s="4">
-        <v>1500</v>
+        <v>22400</v>
       </c>
       <c r="F1505" s="4"/>
       <c r="G1505" s="4" t="s">
@@ -47158,19 +47269,19 @@
     </row>
     <row r="1506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1506" s="4" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1506" s="4" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1506" s="7" t="s">
-        <v>634</v>
+        <v>190</v>
       </c>
       <c r="D1506" s="3">
-        <v>10200</v>
+        <v>217000</v>
       </c>
       <c r="E1506" s="4">
-        <v>1600</v>
+        <v>21700</v>
       </c>
       <c r="F1506" s="4"/>
       <c r="G1506" s="4" t="s">
@@ -47185,19 +47296,19 @@
     </row>
     <row r="1507" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1507" s="4" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1507" s="4" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1507" s="7" t="s">
-        <v>635</v>
+        <v>191</v>
       </c>
       <c r="D1507" s="3">
-        <v>14300</v>
+        <v>204000</v>
       </c>
       <c r="E1507" s="4">
-        <v>2200</v>
+        <v>20400</v>
       </c>
       <c r="F1507" s="4"/>
       <c r="G1507" s="4" t="s">
@@ -47212,19 +47323,19 @@
     </row>
     <row r="1508" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1508" s="4" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1508" s="4" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1508" s="7" t="s">
-        <v>636</v>
+        <v>192</v>
       </c>
       <c r="D1508" s="3">
-        <v>8500</v>
+        <v>189000</v>
       </c>
       <c r="E1508" s="4">
-        <v>1300</v>
+        <v>18900</v>
       </c>
       <c r="F1508" s="4"/>
       <c r="G1508" s="4" t="s">
@@ -47239,19 +47350,19 @@
     </row>
     <row r="1509" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1509" s="4" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1509" s="4" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1509" s="7" t="s">
-        <v>637</v>
+        <v>193</v>
       </c>
       <c r="D1509" s="3">
-        <v>9400</v>
+        <v>175000</v>
       </c>
       <c r="E1509" s="4">
-        <v>1500</v>
+        <v>17500</v>
       </c>
       <c r="F1509" s="4"/>
       <c r="G1509" s="4" t="s">
@@ -47266,19 +47377,19 @@
     </row>
     <row r="1510" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1510" s="4" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1510" s="4" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1510" s="7" t="s">
-        <v>638</v>
+        <v>194</v>
       </c>
       <c r="D1510" s="3">
-        <v>7900</v>
+        <v>154000</v>
       </c>
       <c r="E1510" s="4">
-        <v>1200</v>
+        <v>15400</v>
       </c>
       <c r="F1510" s="4"/>
       <c r="G1510" s="4" t="s">
@@ -47293,19 +47404,19 @@
     </row>
     <row r="1511" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1511" s="4" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1511" s="4" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1511" s="7" t="s">
-        <v>639</v>
+        <v>195</v>
       </c>
       <c r="D1511" s="3">
-        <v>36900</v>
+        <v>140000</v>
       </c>
       <c r="E1511" s="4">
-        <v>5700</v>
+        <v>14000</v>
       </c>
       <c r="F1511" s="4"/>
       <c r="G1511" s="4" t="s">
@@ -47320,19 +47431,19 @@
     </row>
     <row r="1512" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1512" s="4" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1512" s="4" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1512" s="7" t="s">
-        <v>640</v>
+        <v>196</v>
       </c>
       <c r="D1512" s="3">
-        <v>26600</v>
+        <v>133000</v>
       </c>
       <c r="E1512" s="4">
-        <v>4100</v>
+        <v>13300</v>
       </c>
       <c r="F1512" s="4"/>
       <c r="G1512" s="4" t="s">
@@ -47347,19 +47458,19 @@
     </row>
     <row r="1513" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1513" s="4" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1513" s="4" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1513" s="7" t="s">
-        <v>641</v>
+        <v>197</v>
       </c>
       <c r="D1513" s="3">
-        <v>40200</v>
+        <v>123000</v>
       </c>
       <c r="E1513" s="4">
-        <v>6200</v>
+        <v>12300</v>
       </c>
       <c r="F1513" s="4"/>
       <c r="G1513" s="4" t="s">
@@ -47374,19 +47485,19 @@
     </row>
     <row r="1514" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1514" s="4" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1514" s="4" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1514" s="7" t="s">
-        <v>642</v>
+        <v>198</v>
       </c>
       <c r="D1514" s="3">
-        <v>8400</v>
+        <v>116000</v>
       </c>
       <c r="E1514" s="4">
-        <v>1300</v>
+        <v>11600</v>
       </c>
       <c r="F1514" s="4"/>
       <c r="G1514" s="4" t="s">
@@ -47401,19 +47512,19 @@
     </row>
     <row r="1515" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1515" s="4" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1515" s="4" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1515" s="7" t="s">
-        <v>643</v>
+        <v>199</v>
       </c>
       <c r="D1515" s="3">
-        <v>8300</v>
+        <v>102000</v>
       </c>
       <c r="E1515" s="4">
-        <v>1300</v>
+        <v>10200</v>
       </c>
       <c r="F1515" s="4"/>
       <c r="G1515" s="4" t="s">
@@ -47428,19 +47539,19 @@
     </row>
     <row r="1516" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1516" s="4" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1516" s="4" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1516" s="7" t="s">
-        <v>644</v>
+        <v>200</v>
       </c>
       <c r="D1516" s="3">
-        <v>8000</v>
+        <v>97000</v>
       </c>
       <c r="E1516" s="4">
-        <v>1200</v>
+        <v>9700</v>
       </c>
       <c r="F1516" s="4"/>
       <c r="G1516" s="4" t="s">
@@ -47455,19 +47566,19 @@
     </row>
     <row r="1517" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1517" s="4" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1517" s="4" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1517" s="7" t="s">
-        <v>645</v>
+        <v>201</v>
       </c>
       <c r="D1517" s="3">
-        <v>18300</v>
+        <v>74000</v>
       </c>
       <c r="E1517" s="4">
-        <v>2800</v>
+        <v>7400</v>
       </c>
       <c r="F1517" s="4"/>
       <c r="G1517" s="4" t="s">
@@ -47482,19 +47593,19 @@
     </row>
     <row r="1518" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1518" s="4" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1518" s="4" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1518" s="7" t="s">
-        <v>646</v>
+        <v>202</v>
       </c>
       <c r="D1518" s="3">
-        <v>15500</v>
+        <v>71000</v>
       </c>
       <c r="E1518" s="4">
-        <v>2400</v>
+        <v>7100</v>
       </c>
       <c r="F1518" s="4"/>
       <c r="G1518" s="4" t="s">
@@ -47509,19 +47620,19 @@
     </row>
     <row r="1519" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1519" s="4" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1519" s="4" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1519" s="7" t="s">
-        <v>647</v>
+        <v>203</v>
       </c>
       <c r="D1519" s="3">
-        <v>18300</v>
+        <v>63000</v>
       </c>
       <c r="E1519" s="4">
-        <v>2800</v>
+        <v>6300</v>
       </c>
       <c r="F1519" s="4"/>
       <c r="G1519" s="4" t="s">
@@ -47536,19 +47647,19 @@
     </row>
     <row r="1520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1520" s="4" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1520" s="4" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1520" s="7" t="s">
-        <v>648</v>
+        <v>204</v>
       </c>
       <c r="D1520" s="3">
-        <v>20600</v>
+        <v>56000</v>
       </c>
       <c r="E1520" s="4">
-        <v>3200</v>
+        <v>5600</v>
       </c>
       <c r="F1520" s="4"/>
       <c r="G1520" s="4" t="s">
@@ -47569,13 +47680,13 @@
         <v>447</v>
       </c>
       <c r="C1521" s="7" t="s">
-        <v>649</v>
+        <v>629</v>
       </c>
       <c r="D1521" s="3">
-        <v>19391</v>
+        <v>5400</v>
       </c>
       <c r="E1521" s="4">
-        <v>3000</v>
+        <v>800</v>
       </c>
       <c r="F1521" s="4"/>
       <c r="G1521" s="4" t="s">
@@ -47596,13 +47707,13 @@
         <v>447</v>
       </c>
       <c r="C1522" s="7" t="s">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="D1522" s="3">
-        <v>19391</v>
+        <v>26200</v>
       </c>
       <c r="E1522" s="4">
-        <v>3000</v>
+        <v>4100</v>
       </c>
       <c r="F1522" s="4"/>
       <c r="G1522" s="4" t="s">
@@ -47623,13 +47734,13 @@
         <v>447</v>
       </c>
       <c r="C1523" s="7" t="s">
-        <v>651</v>
+        <v>631</v>
       </c>
       <c r="D1523" s="3">
-        <v>7700</v>
+        <v>27200</v>
       </c>
       <c r="E1523" s="4">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F1523" s="4"/>
       <c r="G1523" s="4" t="s">
@@ -47650,13 +47761,13 @@
         <v>447</v>
       </c>
       <c r="C1524" s="7" t="s">
-        <v>652</v>
+        <v>632</v>
       </c>
       <c r="D1524" s="3">
-        <v>10300</v>
+        <v>20700</v>
       </c>
       <c r="E1524" s="4">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="F1524" s="4"/>
       <c r="G1524" s="4" t="s">
@@ -47677,10 +47788,10 @@
         <v>447</v>
       </c>
       <c r="C1525" s="7" t="s">
-        <v>653</v>
+        <v>633</v>
       </c>
       <c r="D1525" s="3">
-        <v>9700</v>
+        <v>9900</v>
       </c>
       <c r="E1525" s="4">
         <v>1500</v>
@@ -47704,13 +47815,13 @@
         <v>447</v>
       </c>
       <c r="C1526" s="7" t="s">
-        <v>654</v>
+        <v>634</v>
       </c>
       <c r="D1526" s="3">
-        <v>9068</v>
+        <v>10200</v>
       </c>
       <c r="E1526" s="4">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="F1526" s="4"/>
       <c r="G1526" s="4" t="s">
@@ -47731,13 +47842,13 @@
         <v>447</v>
       </c>
       <c r="C1527" s="7" t="s">
-        <v>655</v>
+        <v>635</v>
       </c>
       <c r="D1527" s="3">
-        <v>8200</v>
+        <v>14300</v>
       </c>
       <c r="E1527" s="4">
-        <v>1300</v>
+        <v>2200</v>
       </c>
       <c r="F1527" s="4"/>
       <c r="G1527" s="4" t="s">
@@ -47758,13 +47869,13 @@
         <v>447</v>
       </c>
       <c r="C1528" s="7" t="s">
-        <v>656</v>
+        <v>636</v>
       </c>
       <c r="D1528" s="3">
-        <v>11400</v>
+        <v>8500</v>
       </c>
       <c r="E1528" s="4">
-        <v>1800</v>
+        <v>1300</v>
       </c>
       <c r="F1528" s="4"/>
       <c r="G1528" s="4" t="s">
@@ -47785,13 +47896,13 @@
         <v>447</v>
       </c>
       <c r="C1529" s="7" t="s">
-        <v>657</v>
+        <v>637</v>
       </c>
       <c r="D1529" s="3">
-        <v>10000</v>
+        <v>9400</v>
       </c>
       <c r="E1529" s="4">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="F1529" s="4"/>
       <c r="G1529" s="4" t="s">
@@ -47812,13 +47923,13 @@
         <v>447</v>
       </c>
       <c r="C1530" s="7" t="s">
-        <v>658</v>
+        <v>638</v>
       </c>
       <c r="D1530" s="3">
-        <v>8510</v>
+        <v>7900</v>
       </c>
       <c r="E1530" s="4">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F1530" s="4"/>
       <c r="G1530" s="4" t="s">
@@ -47839,13 +47950,13 @@
         <v>447</v>
       </c>
       <c r="C1531" s="7" t="s">
-        <v>659</v>
+        <v>639</v>
       </c>
       <c r="D1531" s="3">
-        <v>8200</v>
+        <v>36900</v>
       </c>
       <c r="E1531" s="4">
-        <v>1300</v>
+        <v>5700</v>
       </c>
       <c r="F1531" s="4"/>
       <c r="G1531" s="4" t="s">
@@ -47866,13 +47977,13 @@
         <v>447</v>
       </c>
       <c r="C1532" s="7" t="s">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="D1532" s="3">
-        <v>8000</v>
+        <v>26600</v>
       </c>
       <c r="E1532" s="4">
-        <v>1200</v>
+        <v>4100</v>
       </c>
       <c r="F1532" s="4"/>
       <c r="G1532" s="4" t="s">
@@ -47893,13 +48004,13 @@
         <v>447</v>
       </c>
       <c r="C1533" s="7" t="s">
-        <v>661</v>
+        <v>641</v>
       </c>
       <c r="D1533" s="3">
-        <v>6929</v>
+        <v>40200</v>
       </c>
       <c r="E1533" s="4">
-        <v>1100</v>
+        <v>6200</v>
       </c>
       <c r="F1533" s="4"/>
       <c r="G1533" s="4" t="s">
@@ -47920,13 +48031,13 @@
         <v>447</v>
       </c>
       <c r="C1534" s="7" t="s">
-        <v>662</v>
+        <v>642</v>
       </c>
       <c r="D1534" s="3">
-        <v>16400</v>
+        <v>8400</v>
       </c>
       <c r="E1534" s="4">
-        <v>2500</v>
+        <v>1300</v>
       </c>
       <c r="F1534" s="4"/>
       <c r="G1534" s="4" t="s">
@@ -47947,13 +48058,13 @@
         <v>447</v>
       </c>
       <c r="C1535" s="7" t="s">
-        <v>663</v>
+        <v>643</v>
       </c>
       <c r="D1535" s="3">
-        <v>14800</v>
+        <v>8300</v>
       </c>
       <c r="E1535" s="4">
-        <v>2300</v>
+        <v>1300</v>
       </c>
       <c r="F1535" s="4"/>
       <c r="G1535" s="4" t="s">
@@ -47974,13 +48085,13 @@
         <v>447</v>
       </c>
       <c r="C1536" s="7" t="s">
-        <v>664</v>
+        <v>644</v>
       </c>
       <c r="D1536" s="3">
-        <v>14800</v>
+        <v>8000</v>
       </c>
       <c r="E1536" s="4">
-        <v>2300</v>
+        <v>1200</v>
       </c>
       <c r="F1536" s="4"/>
       <c r="G1536" s="4" t="s">
@@ -48001,13 +48112,13 @@
         <v>447</v>
       </c>
       <c r="C1537" s="7" t="s">
-        <v>665</v>
+        <v>645</v>
       </c>
       <c r="D1537" s="3">
-        <v>9000</v>
+        <v>18300</v>
       </c>
       <c r="E1537" s="4">
-        <v>1400</v>
+        <v>2800</v>
       </c>
       <c r="F1537" s="4"/>
       <c r="G1537" s="4" t="s">
@@ -48028,13 +48139,13 @@
         <v>447</v>
       </c>
       <c r="C1538" s="7" t="s">
-        <v>666</v>
+        <v>646</v>
       </c>
       <c r="D1538" s="3">
-        <v>34900</v>
+        <v>15500</v>
       </c>
       <c r="E1538" s="4">
-        <v>5400</v>
+        <v>2400</v>
       </c>
       <c r="F1538" s="4"/>
       <c r="G1538" s="4" t="s">
@@ -48055,13 +48166,13 @@
         <v>447</v>
       </c>
       <c r="C1539" s="7" t="s">
-        <v>667</v>
+        <v>647</v>
       </c>
       <c r="D1539" s="3">
-        <v>4000</v>
+        <v>18300</v>
       </c>
       <c r="E1539" s="4">
-        <v>600</v>
+        <v>2800</v>
       </c>
       <c r="F1539" s="4"/>
       <c r="G1539" s="4" t="s">
@@ -48082,13 +48193,13 @@
         <v>447</v>
       </c>
       <c r="C1540" s="7" t="s">
-        <v>668</v>
+        <v>648</v>
       </c>
       <c r="D1540" s="3">
-        <v>4200</v>
+        <v>20600</v>
       </c>
       <c r="E1540" s="4">
-        <v>700</v>
+        <v>3200</v>
       </c>
       <c r="F1540" s="4"/>
       <c r="G1540" s="4" t="s">
@@ -48109,13 +48220,13 @@
         <v>447</v>
       </c>
       <c r="C1541" s="7" t="s">
-        <v>669</v>
+        <v>649</v>
       </c>
       <c r="D1541" s="3">
-        <v>8300</v>
+        <v>19391</v>
       </c>
       <c r="E1541" s="4">
-        <v>1300</v>
+        <v>3000</v>
       </c>
       <c r="F1541" s="4"/>
       <c r="G1541" s="4" t="s">
@@ -48136,13 +48247,13 @@
         <v>447</v>
       </c>
       <c r="C1542" s="7" t="s">
-        <v>670</v>
+        <v>650</v>
       </c>
       <c r="D1542" s="3">
-        <v>7900</v>
+        <v>19391</v>
       </c>
       <c r="E1542" s="4">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="F1542" s="4"/>
       <c r="G1542" s="4" t="s">
@@ -48163,10 +48274,10 @@
         <v>447</v>
       </c>
       <c r="C1543" s="7" t="s">
-        <v>671</v>
+        <v>651</v>
       </c>
       <c r="D1543" s="3">
-        <v>7900</v>
+        <v>7700</v>
       </c>
       <c r="E1543" s="4">
         <v>1200</v>
@@ -48190,13 +48301,13 @@
         <v>447</v>
       </c>
       <c r="C1544" s="7" t="s">
-        <v>672</v>
+        <v>652</v>
       </c>
       <c r="D1544" s="3">
-        <v>9900</v>
+        <v>10300</v>
       </c>
       <c r="E1544" s="4">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="F1544" s="4"/>
       <c r="G1544" s="4" t="s">
@@ -48217,13 +48328,13 @@
         <v>447</v>
       </c>
       <c r="C1545" s="7" t="s">
-        <v>673</v>
+        <v>653</v>
       </c>
       <c r="D1545" s="3">
-        <v>12600</v>
+        <v>9700</v>
       </c>
       <c r="E1545" s="4">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="F1545" s="4"/>
       <c r="G1545" s="4" t="s">
@@ -48244,13 +48355,13 @@
         <v>447</v>
       </c>
       <c r="C1546" s="7" t="s">
-        <v>674</v>
+        <v>654</v>
       </c>
       <c r="D1546" s="3">
-        <v>33200</v>
+        <v>9068</v>
       </c>
       <c r="E1546" s="4">
-        <v>5100</v>
+        <v>1400</v>
       </c>
       <c r="F1546" s="4"/>
       <c r="G1546" s="4" t="s">
@@ -48271,13 +48382,13 @@
         <v>447</v>
       </c>
       <c r="C1547" s="7" t="s">
-        <v>675</v>
+        <v>655</v>
       </c>
       <c r="D1547" s="3">
-        <v>27600</v>
+        <v>8200</v>
       </c>
       <c r="E1547" s="4">
-        <v>4300</v>
+        <v>1300</v>
       </c>
       <c r="F1547" s="4"/>
       <c r="G1547" s="4" t="s">
@@ -48298,13 +48409,13 @@
         <v>447</v>
       </c>
       <c r="C1548" s="7" t="s">
-        <v>676</v>
+        <v>656</v>
       </c>
       <c r="D1548" s="3">
-        <v>29400</v>
+        <v>11400</v>
       </c>
       <c r="E1548" s="4">
-        <v>4600</v>
+        <v>1800</v>
       </c>
       <c r="F1548" s="4"/>
       <c r="G1548" s="4" t="s">
@@ -48325,13 +48436,13 @@
         <v>447</v>
       </c>
       <c r="C1549" s="7" t="s">
-        <v>677</v>
+        <v>657</v>
       </c>
       <c r="D1549" s="3">
-        <v>25800</v>
+        <v>10000</v>
       </c>
       <c r="E1549" s="4">
-        <v>4000</v>
+        <v>1600</v>
       </c>
       <c r="F1549" s="4"/>
       <c r="G1549" s="4" t="s">
@@ -48352,13 +48463,13 @@
         <v>447</v>
       </c>
       <c r="C1550" s="7" t="s">
-        <v>678</v>
+        <v>658</v>
       </c>
       <c r="D1550" s="3">
-        <v>19391</v>
+        <v>8510</v>
       </c>
       <c r="E1550" s="4">
-        <v>3000</v>
+        <v>1300</v>
       </c>
       <c r="F1550" s="4"/>
       <c r="G1550" s="4" t="s">
@@ -48379,13 +48490,13 @@
         <v>447</v>
       </c>
       <c r="C1551" s="7" t="s">
-        <v>679</v>
+        <v>659</v>
       </c>
       <c r="D1551" s="3">
-        <v>19391</v>
+        <v>8200</v>
       </c>
       <c r="E1551" s="4">
-        <v>3000</v>
+        <v>1300</v>
       </c>
       <c r="F1551" s="4"/>
       <c r="G1551" s="4" t="s">
@@ -48406,13 +48517,13 @@
         <v>447</v>
       </c>
       <c r="C1552" s="7" t="s">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="D1552" s="3">
-        <v>21100</v>
+        <v>8000</v>
       </c>
       <c r="E1552" s="4">
-        <v>3300</v>
+        <v>1200</v>
       </c>
       <c r="F1552" s="4"/>
       <c r="G1552" s="4" t="s">
@@ -48433,13 +48544,13 @@
         <v>447</v>
       </c>
       <c r="C1553" s="7" t="s">
-        <v>681</v>
+        <v>661</v>
       </c>
       <c r="D1553" s="3">
-        <v>7500</v>
+        <v>6929</v>
       </c>
       <c r="E1553" s="4">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="F1553" s="4"/>
       <c r="G1553" s="4" t="s">
@@ -48460,13 +48571,13 @@
         <v>447</v>
       </c>
       <c r="C1554" s="7" t="s">
-        <v>682</v>
+        <v>662</v>
       </c>
       <c r="D1554" s="3">
-        <v>8500</v>
+        <v>16400</v>
       </c>
       <c r="E1554" s="4">
-        <v>1300</v>
+        <v>2500</v>
       </c>
       <c r="F1554" s="4"/>
       <c r="G1554" s="4" t="s">
@@ -48487,13 +48598,13 @@
         <v>447</v>
       </c>
       <c r="C1555" s="7" t="s">
-        <v>683</v>
+        <v>663</v>
       </c>
       <c r="D1555" s="3">
-        <v>4300</v>
+        <v>14800</v>
       </c>
       <c r="E1555" s="4">
-        <v>700</v>
+        <v>2300</v>
       </c>
       <c r="F1555" s="4"/>
       <c r="G1555" s="4" t="s">
@@ -48514,13 +48625,13 @@
         <v>447</v>
       </c>
       <c r="C1556" s="7" t="s">
-        <v>684</v>
+        <v>664</v>
       </c>
       <c r="D1556" s="3">
-        <v>8800</v>
+        <v>14800</v>
       </c>
       <c r="E1556" s="4">
-        <v>1400</v>
+        <v>2300</v>
       </c>
       <c r="F1556" s="4"/>
       <c r="G1556" s="4" t="s">
@@ -48541,10 +48652,10 @@
         <v>447</v>
       </c>
       <c r="C1557" s="7" t="s">
-        <v>685</v>
+        <v>665</v>
       </c>
       <c r="D1557" s="3">
-        <v>8800</v>
+        <v>9000</v>
       </c>
       <c r="E1557" s="4">
         <v>1400</v>
@@ -48568,13 +48679,13 @@
         <v>447</v>
       </c>
       <c r="C1558" s="7" t="s">
-        <v>686</v>
+        <v>666</v>
       </c>
       <c r="D1558" s="3">
-        <v>7900</v>
+        <v>34900</v>
       </c>
       <c r="E1558" s="4">
-        <v>1200</v>
+        <v>5400</v>
       </c>
       <c r="F1558" s="4"/>
       <c r="G1558" s="4" t="s">
@@ -48595,13 +48706,13 @@
         <v>447</v>
       </c>
       <c r="C1559" s="7" t="s">
-        <v>687</v>
+        <v>667</v>
       </c>
       <c r="D1559" s="3">
-        <v>32900</v>
+        <v>4000</v>
       </c>
       <c r="E1559" s="4">
-        <v>5100</v>
+        <v>600</v>
       </c>
       <c r="F1559" s="4"/>
       <c r="G1559" s="4" t="s">
@@ -48622,13 +48733,13 @@
         <v>447</v>
       </c>
       <c r="C1560" s="7" t="s">
-        <v>688</v>
+        <v>668</v>
       </c>
       <c r="D1560" s="3">
-        <v>7700</v>
+        <v>4200</v>
       </c>
       <c r="E1560" s="4">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="F1560" s="4"/>
       <c r="G1560" s="4" t="s">
@@ -48649,13 +48760,13 @@
         <v>447</v>
       </c>
       <c r="C1561" s="7" t="s">
-        <v>689</v>
+        <v>669</v>
       </c>
       <c r="D1561" s="3">
-        <v>21300</v>
+        <v>8300</v>
       </c>
       <c r="E1561" s="4">
-        <v>3300</v>
+        <v>1300</v>
       </c>
       <c r="F1561" s="4"/>
       <c r="G1561" s="4" t="s">
@@ -48676,13 +48787,13 @@
         <v>447</v>
       </c>
       <c r="C1562" s="7" t="s">
-        <v>690</v>
+        <v>670</v>
       </c>
       <c r="D1562" s="3">
-        <v>16300</v>
+        <v>7900</v>
       </c>
       <c r="E1562" s="4">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="F1562" s="4"/>
       <c r="G1562" s="4" t="s">
@@ -48703,13 +48814,13 @@
         <v>447</v>
       </c>
       <c r="C1563" s="7" t="s">
-        <v>691</v>
+        <v>671</v>
       </c>
       <c r="D1563" s="3">
-        <v>12200</v>
+        <v>7900</v>
       </c>
       <c r="E1563" s="4">
-        <v>1900</v>
+        <v>1200</v>
       </c>
       <c r="F1563" s="4"/>
       <c r="G1563" s="4" t="s">
@@ -48730,10 +48841,10 @@
         <v>447</v>
       </c>
       <c r="C1564" s="7" t="s">
-        <v>692</v>
+        <v>672</v>
       </c>
       <c r="D1564" s="3">
-        <v>9400</v>
+        <v>9900</v>
       </c>
       <c r="E1564" s="4">
         <v>1500</v>
@@ -48757,13 +48868,13 @@
         <v>447</v>
       </c>
       <c r="C1565" s="7" t="s">
-        <v>693</v>
+        <v>673</v>
       </c>
       <c r="D1565" s="3">
-        <v>10300</v>
+        <v>12600</v>
       </c>
       <c r="E1565" s="4">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="F1565" s="4"/>
       <c r="G1565" s="4" t="s">
@@ -48784,13 +48895,13 @@
         <v>447</v>
       </c>
       <c r="C1566" s="7" t="s">
-        <v>694</v>
+        <v>674</v>
       </c>
       <c r="D1566" s="3">
-        <v>14300</v>
+        <v>33200</v>
       </c>
       <c r="E1566" s="4">
-        <v>2200</v>
+        <v>5100</v>
       </c>
       <c r="F1566" s="4"/>
       <c r="G1566" s="4" t="s">
@@ -48811,13 +48922,13 @@
         <v>447</v>
       </c>
       <c r="C1567" s="7" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
       <c r="D1567" s="3">
-        <v>8510</v>
+        <v>27600</v>
       </c>
       <c r="E1567" s="4">
-        <v>1300</v>
+        <v>4300</v>
       </c>
       <c r="F1567" s="4"/>
       <c r="G1567" s="4" t="s">
@@ -48838,13 +48949,13 @@
         <v>447</v>
       </c>
       <c r="C1568" s="7" t="s">
-        <v>696</v>
+        <v>676</v>
       </c>
       <c r="D1568" s="3">
-        <v>9600</v>
+        <v>29400</v>
       </c>
       <c r="E1568" s="4">
-        <v>1500</v>
+        <v>4600</v>
       </c>
       <c r="F1568" s="4"/>
       <c r="G1568" s="4" t="s">
@@ -48865,13 +48976,13 @@
         <v>447</v>
       </c>
       <c r="C1569" s="7" t="s">
-        <v>697</v>
+        <v>677</v>
       </c>
       <c r="D1569" s="3">
-        <v>9400</v>
+        <v>25800</v>
       </c>
       <c r="E1569" s="4">
-        <v>1500</v>
+        <v>4000</v>
       </c>
       <c r="F1569" s="4"/>
       <c r="G1569" s="4" t="s">
@@ -48892,13 +49003,13 @@
         <v>447</v>
       </c>
       <c r="C1570" s="7" t="s">
-        <v>698</v>
+        <v>678</v>
       </c>
       <c r="D1570" s="3">
-        <v>7700</v>
+        <v>19391</v>
       </c>
       <c r="E1570" s="4">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="F1570" s="4"/>
       <c r="G1570" s="4" t="s">
@@ -48919,13 +49030,13 @@
         <v>447</v>
       </c>
       <c r="C1571" s="7" t="s">
-        <v>699</v>
+        <v>679</v>
       </c>
       <c r="D1571" s="3">
-        <v>5900</v>
+        <v>19391</v>
       </c>
       <c r="E1571" s="4">
-        <v>900</v>
+        <v>3000</v>
       </c>
       <c r="F1571" s="4"/>
       <c r="G1571" s="4" t="s">
@@ -48946,13 +49057,13 @@
         <v>447</v>
       </c>
       <c r="C1572" s="7" t="s">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="D1572" s="3">
-        <v>5900</v>
+        <v>21100</v>
       </c>
       <c r="E1572" s="4">
-        <v>900</v>
+        <v>3300</v>
       </c>
       <c r="F1572" s="4"/>
       <c r="G1572" s="4" t="s">
@@ -48973,10 +49084,10 @@
         <v>447</v>
       </c>
       <c r="C1573" s="7" t="s">
-        <v>701</v>
+        <v>681</v>
       </c>
       <c r="D1573" s="3">
-        <v>7952</v>
+        <v>7500</v>
       </c>
       <c r="E1573" s="4">
         <v>1200</v>
@@ -49000,13 +49111,13 @@
         <v>447</v>
       </c>
       <c r="C1574" s="7" t="s">
-        <v>702</v>
+        <v>682</v>
       </c>
       <c r="D1574" s="3">
-        <v>44035</v>
+        <v>8500</v>
       </c>
       <c r="E1574" s="4">
-        <v>6800</v>
+        <v>1300</v>
       </c>
       <c r="F1574" s="4"/>
       <c r="G1574" s="4" t="s">
@@ -49027,13 +49138,13 @@
         <v>447</v>
       </c>
       <c r="C1575" s="7" t="s">
-        <v>703</v>
+        <v>683</v>
       </c>
       <c r="D1575" s="3">
-        <v>8045</v>
+        <v>4300</v>
       </c>
       <c r="E1575" s="4">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="F1575" s="4"/>
       <c r="G1575" s="4" t="s">
@@ -49054,13 +49165,13 @@
         <v>447</v>
       </c>
       <c r="C1576" s="7" t="s">
-        <v>704</v>
+        <v>684</v>
       </c>
       <c r="D1576" s="3">
-        <v>15857</v>
+        <v>8800</v>
       </c>
       <c r="E1576" s="4">
-        <v>2500</v>
+        <v>1400</v>
       </c>
       <c r="F1576" s="4"/>
       <c r="G1576" s="4" t="s">
@@ -49081,13 +49192,13 @@
         <v>447</v>
       </c>
       <c r="C1577" s="7" t="s">
-        <v>705</v>
+        <v>685</v>
       </c>
       <c r="D1577" s="3">
-        <v>16415</v>
+        <v>8800</v>
       </c>
       <c r="E1577" s="4">
-        <v>2500</v>
+        <v>1400</v>
       </c>
       <c r="F1577" s="4"/>
       <c r="G1577" s="4" t="s">
@@ -49108,13 +49219,13 @@
         <v>447</v>
       </c>
       <c r="C1578" s="7" t="s">
-        <v>675</v>
+        <v>686</v>
       </c>
       <c r="D1578" s="3">
-        <v>27854</v>
+        <v>7900</v>
       </c>
       <c r="E1578" s="4">
-        <v>3900</v>
+        <v>1200</v>
       </c>
       <c r="F1578" s="4"/>
       <c r="G1578" s="4" t="s">
@@ -49135,13 +49246,13 @@
         <v>447</v>
       </c>
       <c r="C1579" s="7" t="s">
-        <v>706</v>
+        <v>687</v>
       </c>
       <c r="D1579" s="3">
-        <v>6929</v>
+        <v>32900</v>
       </c>
       <c r="E1579" s="4">
-        <v>1000</v>
+        <v>5100</v>
       </c>
       <c r="F1579" s="4"/>
       <c r="G1579" s="4" t="s">
@@ -49162,13 +49273,13 @@
         <v>447</v>
       </c>
       <c r="C1580" s="7" t="s">
-        <v>707</v>
+        <v>688</v>
       </c>
       <c r="D1580" s="3">
-        <v>7855</v>
+        <v>7700</v>
       </c>
       <c r="E1580" s="4">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="F1580" s="4"/>
       <c r="G1580" s="4" t="s">
@@ -49189,13 +49300,13 @@
         <v>447</v>
       </c>
       <c r="C1581" s="7" t="s">
-        <v>708</v>
+        <v>689</v>
       </c>
       <c r="D1581" s="3">
-        <v>21158</v>
+        <v>21300</v>
       </c>
       <c r="E1581" s="4">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="F1581" s="4"/>
       <c r="G1581" s="4" t="s">
@@ -49216,13 +49327,13 @@
         <v>447</v>
       </c>
       <c r="C1582" s="7" t="s">
-        <v>709</v>
+        <v>690</v>
       </c>
       <c r="D1582" s="3">
-        <v>19949</v>
+        <v>16300</v>
       </c>
       <c r="E1582" s="4">
-        <v>2800</v>
+        <v>2500</v>
       </c>
       <c r="F1582" s="4"/>
       <c r="G1582" s="4" t="s">
@@ -49243,13 +49354,13 @@
         <v>447</v>
       </c>
       <c r="C1583" s="7" t="s">
-        <v>710</v>
+        <v>691</v>
       </c>
       <c r="D1583" s="3">
-        <v>9626</v>
+        <v>12200</v>
       </c>
       <c r="E1583" s="4">
-        <v>1300</v>
+        <v>1900</v>
       </c>
       <c r="F1583" s="4"/>
       <c r="G1583" s="4" t="s">
@@ -49270,13 +49381,13 @@
         <v>447</v>
       </c>
       <c r="C1584" s="7" t="s">
-        <v>711</v>
+        <v>692</v>
       </c>
       <c r="D1584" s="3">
-        <v>9719</v>
+        <v>9400</v>
       </c>
       <c r="E1584" s="4">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="F1584" s="4"/>
       <c r="G1584" s="4" t="s">
@@ -49297,13 +49408,13 @@
         <v>447</v>
       </c>
       <c r="C1585" s="7" t="s">
-        <v>712</v>
+        <v>693</v>
       </c>
       <c r="D1585" s="3">
-        <v>12974</v>
+        <v>10300</v>
       </c>
       <c r="E1585" s="4">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="F1585" s="4"/>
       <c r="G1585" s="4" t="s">
@@ -49324,13 +49435,13 @@
         <v>447</v>
       </c>
       <c r="C1586" s="7" t="s">
-        <v>1467</v>
+        <v>694</v>
       </c>
       <c r="D1586" s="3">
-        <v>21344</v>
+        <v>14300</v>
       </c>
       <c r="E1586" s="4">
-        <v>3000</v>
+        <v>2200</v>
       </c>
       <c r="F1586" s="4"/>
       <c r="G1586" s="4" t="s">
@@ -49351,13 +49462,13 @@
         <v>447</v>
       </c>
       <c r="C1587" s="7" t="s">
-        <v>713</v>
+        <v>695</v>
       </c>
       <c r="D1587" s="3">
-        <v>14276</v>
+        <v>8510</v>
       </c>
       <c r="E1587" s="4">
-        <v>2000</v>
+        <v>1300</v>
       </c>
       <c r="F1587" s="4"/>
       <c r="G1587" s="4" t="s">
@@ -49378,13 +49489,13 @@
         <v>447</v>
       </c>
       <c r="C1588" s="7" t="s">
-        <v>714</v>
+        <v>696</v>
       </c>
       <c r="D1588" s="3">
-        <v>14276</v>
+        <v>9600</v>
       </c>
       <c r="E1588" s="4">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="F1588" s="4"/>
       <c r="G1588" s="4" t="s">
@@ -49405,13 +49516,13 @@
         <v>447</v>
       </c>
       <c r="C1589" s="7" t="s">
-        <v>715</v>
+        <v>697</v>
       </c>
       <c r="D1589" s="3">
-        <v>15950</v>
+        <v>9400</v>
       </c>
       <c r="E1589" s="4">
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="F1589" s="4"/>
       <c r="G1589" s="4" t="s">
@@ -49432,13 +49543,13 @@
         <v>447</v>
       </c>
       <c r="C1590" s="7" t="s">
-        <v>716</v>
+        <v>698</v>
       </c>
       <c r="D1590" s="3">
-        <v>28970</v>
+        <v>7700</v>
       </c>
       <c r="E1590" s="4">
-        <v>4100</v>
+        <v>1200</v>
       </c>
       <c r="F1590" s="4"/>
       <c r="G1590" s="4" t="s">
@@ -49453,19 +49564,19 @@
     </row>
     <row r="1591" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1591" s="4" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1591" s="4" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1591" s="7" t="s">
-        <v>1061</v>
+        <v>699</v>
       </c>
       <c r="D1591" s="3">
-        <v>41000</v>
+        <v>5900</v>
       </c>
       <c r="E1591" s="4">
-        <v>4100</v>
+        <v>900</v>
       </c>
       <c r="F1591" s="4"/>
       <c r="G1591" s="4" t="s">
@@ -49480,19 +49591,19 @@
     </row>
     <row r="1592" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1592" s="4" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1592" s="4" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1592" s="7" t="s">
-        <v>1062</v>
+        <v>700</v>
       </c>
       <c r="D1592" s="3">
-        <v>55000</v>
+        <v>5900</v>
       </c>
       <c r="E1592" s="4">
-        <v>5500</v>
+        <v>900</v>
       </c>
       <c r="F1592" s="4"/>
       <c r="G1592" s="4" t="s">
@@ -49507,19 +49618,19 @@
     </row>
     <row r="1593" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1593" s="4" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1593" s="4" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1593" s="7" t="s">
-        <v>1063</v>
+        <v>701</v>
       </c>
       <c r="D1593" s="3">
-        <v>45000</v>
+        <v>7952</v>
       </c>
       <c r="E1593" s="4">
-        <v>4500</v>
+        <v>1200</v>
       </c>
       <c r="F1593" s="4"/>
       <c r="G1593" s="4" t="s">
@@ -49534,19 +49645,19 @@
     </row>
     <row r="1594" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1594" s="4" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1594" s="4" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1594" s="7" t="s">
-        <v>1064</v>
+        <v>702</v>
       </c>
       <c r="D1594" s="3">
-        <v>63000</v>
+        <v>44035</v>
       </c>
       <c r="E1594" s="4">
-        <v>6300</v>
+        <v>6800</v>
       </c>
       <c r="F1594" s="4"/>
       <c r="G1594" s="4" t="s">
@@ -49561,19 +49672,19 @@
     </row>
     <row r="1595" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1595" s="4" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1595" s="4" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1595" s="7" t="s">
-        <v>1065</v>
+        <v>703</v>
       </c>
       <c r="D1595" s="3">
-        <v>60000</v>
+        <v>8045</v>
       </c>
       <c r="E1595" s="4">
-        <v>6000</v>
+        <v>1200</v>
       </c>
       <c r="F1595" s="4"/>
       <c r="G1595" s="4" t="s">
@@ -49588,19 +49699,19 @@
     </row>
     <row r="1596" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1596" s="4" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1596" s="4" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1596" s="7" t="s">
-        <v>1066</v>
+        <v>704</v>
       </c>
       <c r="D1596" s="3">
-        <v>42000</v>
+        <v>15857</v>
       </c>
       <c r="E1596" s="4">
-        <v>4200</v>
+        <v>2500</v>
       </c>
       <c r="F1596" s="4"/>
       <c r="G1596" s="4" t="s">
@@ -49615,19 +49726,19 @@
     </row>
     <row r="1597" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1597" s="4" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1597" s="4" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1597" s="7" t="s">
-        <v>1067</v>
+        <v>705</v>
       </c>
       <c r="D1597" s="3">
-        <v>64000</v>
+        <v>16415</v>
       </c>
       <c r="E1597" s="4">
-        <v>6400</v>
+        <v>2500</v>
       </c>
       <c r="F1597" s="4"/>
       <c r="G1597" s="4" t="s">
@@ -49642,19 +49753,19 @@
     </row>
     <row r="1598" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1598" s="4" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1598" s="4" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1598" s="7" t="s">
-        <v>1068</v>
+        <v>675</v>
       </c>
       <c r="D1598" s="3">
-        <v>78000</v>
+        <v>27854</v>
       </c>
       <c r="E1598" s="4">
-        <v>7800</v>
+        <v>3900</v>
       </c>
       <c r="F1598" s="4"/>
       <c r="G1598" s="4" t="s">
@@ -49669,19 +49780,19 @@
     </row>
     <row r="1599" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1599" s="4" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1599" s="4" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1599" s="7" t="s">
-        <v>1069</v>
+        <v>706</v>
       </c>
       <c r="D1599" s="3">
-        <v>83000</v>
+        <v>6929</v>
       </c>
       <c r="E1599" s="4">
-        <v>8300</v>
+        <v>1000</v>
       </c>
       <c r="F1599" s="4"/>
       <c r="G1599" s="4" t="s">
@@ -49696,19 +49807,19 @@
     </row>
     <row r="1600" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1600" s="4" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1600" s="4" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1600" s="7" t="s">
-        <v>1070</v>
+        <v>707</v>
       </c>
       <c r="D1600" s="3">
-        <v>106000</v>
+        <v>7855</v>
       </c>
       <c r="E1600" s="4">
-        <v>10600</v>
+        <v>1100</v>
       </c>
       <c r="F1600" s="4"/>
       <c r="G1600" s="4" t="s">
@@ -49723,19 +49834,19 @@
     </row>
     <row r="1601" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1601" s="4" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1601" s="4" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1601" s="7" t="s">
-        <v>1071</v>
+        <v>708</v>
       </c>
       <c r="D1601" s="3">
-        <v>81000</v>
+        <v>21158</v>
       </c>
       <c r="E1601" s="4">
-        <v>8100</v>
+        <v>3000</v>
       </c>
       <c r="F1601" s="4"/>
       <c r="G1601" s="4" t="s">
@@ -49750,19 +49861,19 @@
     </row>
     <row r="1602" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1602" s="4" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1602" s="4" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1602" s="7" t="s">
-        <v>1072</v>
+        <v>709</v>
       </c>
       <c r="D1602" s="3">
-        <v>84000</v>
+        <v>19949</v>
       </c>
       <c r="E1602" s="4">
-        <v>8400</v>
+        <v>2800</v>
       </c>
       <c r="F1602" s="4"/>
       <c r="G1602" s="4" t="s">
@@ -49777,19 +49888,19 @@
     </row>
     <row r="1603" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1603" s="4" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1603" s="4" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1603" s="7" t="s">
-        <v>1073</v>
+        <v>710</v>
       </c>
       <c r="D1603" s="3">
-        <v>120000</v>
+        <v>9626</v>
       </c>
       <c r="E1603" s="4">
-        <v>12000</v>
+        <v>1300</v>
       </c>
       <c r="F1603" s="4"/>
       <c r="G1603" s="4" t="s">
@@ -49804,19 +49915,19 @@
     </row>
     <row r="1604" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1604" s="4" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1604" s="4" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1604" s="7" t="s">
-        <v>1074</v>
+        <v>711</v>
       </c>
       <c r="D1604" s="3">
-        <v>113000</v>
+        <v>9719</v>
       </c>
       <c r="E1604" s="4">
-        <v>11300</v>
+        <v>1400</v>
       </c>
       <c r="F1604" s="4"/>
       <c r="G1604" s="4" t="s">
@@ -49831,19 +49942,19 @@
     </row>
     <row r="1605" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1605" s="4" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1605" s="4" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1605" s="7" t="s">
-        <v>1075</v>
+        <v>712</v>
       </c>
       <c r="D1605" s="3">
-        <v>141000</v>
+        <v>12974</v>
       </c>
       <c r="E1605" s="4">
-        <v>14100</v>
+        <v>1800</v>
       </c>
       <c r="F1605" s="4"/>
       <c r="G1605" s="4" t="s">
@@ -49858,19 +49969,19 @@
     </row>
     <row r="1606" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1606" s="4" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1606" s="4" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1606" s="7" t="s">
-        <v>1076</v>
+        <v>1467</v>
       </c>
       <c r="D1606" s="3">
-        <v>141000</v>
+        <v>21344</v>
       </c>
       <c r="E1606" s="4">
-        <v>14100</v>
+        <v>3000</v>
       </c>
       <c r="F1606" s="4"/>
       <c r="G1606" s="4" t="s">
@@ -49885,19 +49996,19 @@
     </row>
     <row r="1607" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1607" s="4" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1607" s="4" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1607" s="7" t="s">
-        <v>1077</v>
+        <v>713</v>
       </c>
       <c r="D1607" s="3">
-        <v>169000</v>
+        <v>14276</v>
       </c>
       <c r="E1607" s="4">
-        <v>16900</v>
+        <v>2000</v>
       </c>
       <c r="F1607" s="4"/>
       <c r="G1607" s="4" t="s">
@@ -49912,19 +50023,19 @@
     </row>
     <row r="1608" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1608" s="4" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1608" s="4" t="s">
-        <v>401</v>
+        <v>447</v>
       </c>
       <c r="C1608" s="7" t="s">
-        <v>1249</v>
+        <v>714</v>
       </c>
       <c r="D1608" s="3">
-        <v>47240</v>
+        <v>14276</v>
       </c>
       <c r="E1608" s="4">
-        <v>6400</v>
+        <v>2000</v>
       </c>
       <c r="F1608" s="4"/>
       <c r="G1608" s="4" t="s">
@@ -49939,19 +50050,19 @@
     </row>
     <row r="1609" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1609" s="4" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1609" s="4" t="s">
-        <v>401</v>
+        <v>447</v>
       </c>
       <c r="C1609" s="7" t="s">
-        <v>1250</v>
+        <v>715</v>
       </c>
       <c r="D1609" s="3">
-        <v>71600</v>
+        <v>15950</v>
       </c>
       <c r="E1609" s="4">
-        <v>9700</v>
+        <v>2200</v>
       </c>
       <c r="F1609" s="4"/>
       <c r="G1609" s="4" t="s">
@@ -49966,19 +50077,19 @@
     </row>
     <row r="1610" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1610" s="4" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1610" s="4" t="s">
-        <v>401</v>
+        <v>447</v>
       </c>
       <c r="C1610" s="7" t="s">
-        <v>1251</v>
+        <v>716</v>
       </c>
       <c r="D1610" s="3">
-        <v>87720</v>
+        <v>28970</v>
       </c>
       <c r="E1610" s="4">
-        <v>11800</v>
+        <v>4100</v>
       </c>
       <c r="F1610" s="4"/>
       <c r="G1610" s="4" t="s">
@@ -49996,16 +50107,16 @@
         <v>1080</v>
       </c>
       <c r="B1611" s="4" t="s">
-        <v>401</v>
+        <v>207</v>
       </c>
       <c r="C1611" s="7" t="s">
-        <v>1252</v>
+        <v>1061</v>
       </c>
       <c r="D1611" s="3">
-        <v>124360</v>
+        <v>41000</v>
       </c>
       <c r="E1611" s="4">
-        <v>16800</v>
+        <v>4100</v>
       </c>
       <c r="F1611" s="4"/>
       <c r="G1611" s="4" t="s">
@@ -50023,16 +50134,16 @@
         <v>1080</v>
       </c>
       <c r="B1612" s="4" t="s">
-        <v>401</v>
+        <v>207</v>
       </c>
       <c r="C1612" s="7" t="s">
-        <v>1253</v>
+        <v>1062</v>
       </c>
       <c r="D1612" s="3">
-        <v>178440</v>
+        <v>55000</v>
       </c>
       <c r="E1612" s="4">
-        <v>24100</v>
+        <v>5500</v>
       </c>
       <c r="F1612" s="4"/>
       <c r="G1612" s="4" t="s">
@@ -50050,16 +50161,16 @@
         <v>1080</v>
       </c>
       <c r="B1613" s="4" t="s">
-        <v>401</v>
+        <v>207</v>
       </c>
       <c r="C1613" s="7" t="s">
-        <v>1254</v>
+        <v>1063</v>
       </c>
       <c r="D1613" s="3">
-        <v>258920</v>
+        <v>45000</v>
       </c>
       <c r="E1613" s="4">
-        <v>35000</v>
+        <v>4500</v>
       </c>
       <c r="F1613" s="4"/>
       <c r="G1613" s="4" t="s">
@@ -50077,16 +50188,16 @@
         <v>1080</v>
       </c>
       <c r="B1614" s="4" t="s">
-        <v>401</v>
+        <v>207</v>
       </c>
       <c r="C1614" s="7" t="s">
-        <v>1255</v>
+        <v>1064</v>
       </c>
       <c r="D1614" s="3">
-        <v>236130</v>
+        <v>63000</v>
       </c>
       <c r="E1614" s="4">
-        <v>31900</v>
+        <v>6300</v>
       </c>
       <c r="F1614" s="4"/>
       <c r="G1614" s="4" t="s">
@@ -50104,16 +50215,16 @@
         <v>1080</v>
       </c>
       <c r="B1615" s="4" t="s">
-        <v>401</v>
+        <v>207</v>
       </c>
       <c r="C1615" s="7" t="s">
-        <v>1256</v>
+        <v>1065</v>
       </c>
       <c r="D1615" s="3">
-        <v>329950</v>
+        <v>60000</v>
       </c>
       <c r="E1615" s="4">
-        <v>44500</v>
+        <v>6000</v>
       </c>
       <c r="F1615" s="4"/>
       <c r="G1615" s="4" t="s">
@@ -50128,27 +50239,26 @@
     </row>
     <row r="1616" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1616" s="4" t="s">
-        <v>1438</v>
+        <v>1080</v>
       </c>
       <c r="B1616" s="4" t="s">
-        <v>1442</v>
+        <v>207</v>
       </c>
       <c r="C1616" s="7" t="s">
-        <v>1681</v>
+        <v>1066</v>
       </c>
       <c r="D1616" s="3">
-        <f>E1616*10</f>
-        <v>256000</v>
+        <v>42000</v>
       </c>
       <c r="E1616" s="4">
-        <v>25600</v>
+        <v>4200</v>
       </c>
       <c r="F1616" s="4"/>
       <c r="G1616" s="4" t="s">
-        <v>1691</v>
+        <v>1459</v>
       </c>
       <c r="H1616" s="4" t="s">
-        <v>1455</v>
+        <v>206</v>
       </c>
       <c r="I1616" s="4">
         <v>2026</v>
@@ -50156,27 +50266,26 @@
     </row>
     <row r="1617" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1617" s="4" t="s">
-        <v>1438</v>
+        <v>1080</v>
       </c>
       <c r="B1617" s="4" t="s">
-        <v>1442</v>
+        <v>207</v>
       </c>
       <c r="C1617" s="7" t="s">
-        <v>1682</v>
+        <v>1067</v>
       </c>
       <c r="D1617" s="3">
-        <f t="shared" ref="D1617:D1626" si="0">E1617*10</f>
-        <v>324000</v>
+        <v>64000</v>
       </c>
       <c r="E1617" s="4">
-        <v>32400</v>
+        <v>6400</v>
       </c>
       <c r="F1617" s="4"/>
       <c r="G1617" s="4" t="s">
-        <v>1692</v>
+        <v>1459</v>
       </c>
       <c r="H1617" s="4" t="s">
-        <v>1455</v>
+        <v>206</v>
       </c>
       <c r="I1617" s="4">
         <v>2026</v>
@@ -50184,447 +50293,989 @@
     </row>
     <row r="1618" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1618" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1618" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1618" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D1618" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E1618" s="4">
+        <v>7800</v>
+      </c>
+      <c r="F1618" s="4"/>
+      <c r="G1618" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1618" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1618" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1619" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1619" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1619" s="7" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D1619" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E1619" s="4">
+        <v>8300</v>
+      </c>
+      <c r="F1619" s="4"/>
+      <c r="G1619" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1619" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1619" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1620" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1620" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1620" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D1620" s="3">
+        <v>106000</v>
+      </c>
+      <c r="E1620" s="4">
+        <v>10600</v>
+      </c>
+      <c r="F1620" s="4"/>
+      <c r="G1620" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1620" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1620" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1621" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1621" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1621" s="7" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D1621" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E1621" s="4">
+        <v>8100</v>
+      </c>
+      <c r="F1621" s="4"/>
+      <c r="G1621" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1621" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1621" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1622" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1622" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1622" s="7" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D1622" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E1622" s="4">
+        <v>8400</v>
+      </c>
+      <c r="F1622" s="4"/>
+      <c r="G1622" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1622" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1622" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1623" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1623" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1623" s="7" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D1623" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E1623" s="4">
+        <v>12000</v>
+      </c>
+      <c r="F1623" s="4"/>
+      <c r="G1623" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1623" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1623" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1624" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1624" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1624" s="7" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D1624" s="3">
+        <v>113000</v>
+      </c>
+      <c r="E1624" s="4">
+        <v>11300</v>
+      </c>
+      <c r="F1624" s="4"/>
+      <c r="G1624" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1624" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1624" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1625" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1625" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1625" s="7" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D1625" s="3">
+        <v>141000</v>
+      </c>
+      <c r="E1625" s="4">
+        <v>14100</v>
+      </c>
+      <c r="F1625" s="4"/>
+      <c r="G1625" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1625" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1625" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1626" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1626" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1626" s="7" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D1626" s="3">
+        <v>141000</v>
+      </c>
+      <c r="E1626" s="4">
+        <v>14100</v>
+      </c>
+      <c r="F1626" s="4"/>
+      <c r="G1626" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1626" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1626" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1627" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1627" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1627" s="7" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D1627" s="3">
+        <v>169000</v>
+      </c>
+      <c r="E1627" s="4">
+        <v>16900</v>
+      </c>
+      <c r="F1627" s="4"/>
+      <c r="G1627" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1627" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1627" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1628" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1628" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C1628" s="7" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D1628" s="3">
+        <v>47240</v>
+      </c>
+      <c r="E1628" s="4">
+        <v>6400</v>
+      </c>
+      <c r="F1628" s="4"/>
+      <c r="G1628" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1628" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1628" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1629" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1629" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C1629" s="7" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D1629" s="3">
+        <v>71600</v>
+      </c>
+      <c r="E1629" s="4">
+        <v>9700</v>
+      </c>
+      <c r="F1629" s="4"/>
+      <c r="G1629" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1629" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1629" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1630" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1630" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C1630" s="7" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D1630" s="3">
+        <v>87720</v>
+      </c>
+      <c r="E1630" s="4">
+        <v>11800</v>
+      </c>
+      <c r="F1630" s="4"/>
+      <c r="G1630" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1630" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1630" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1631" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1631" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C1631" s="7" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D1631" s="3">
+        <v>124360</v>
+      </c>
+      <c r="E1631" s="4">
+        <v>16800</v>
+      </c>
+      <c r="F1631" s="4"/>
+      <c r="G1631" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1631" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1631" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1632" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1632" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C1632" s="7" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D1632" s="3">
+        <v>178440</v>
+      </c>
+      <c r="E1632" s="4">
+        <v>24100</v>
+      </c>
+      <c r="F1632" s="4"/>
+      <c r="G1632" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1632" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1632" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1633" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1633" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C1633" s="7" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D1633" s="3">
+        <v>258920</v>
+      </c>
+      <c r="E1633" s="4">
+        <v>35000</v>
+      </c>
+      <c r="F1633" s="4"/>
+      <c r="G1633" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1633" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1633" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1634" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1634" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C1634" s="7" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D1634" s="3">
+        <v>236130</v>
+      </c>
+      <c r="E1634" s="4">
+        <v>31900</v>
+      </c>
+      <c r="F1634" s="4"/>
+      <c r="G1634" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1634" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1634" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1635" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1635" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C1635" s="7" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D1635" s="3">
+        <v>329950</v>
+      </c>
+      <c r="E1635" s="4">
+        <v>44500</v>
+      </c>
+      <c r="F1635" s="4"/>
+      <c r="G1635" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1635" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1635" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1636" s="4" t="s">
         <v>1438</v>
       </c>
-      <c r="B1618" s="4" t="s">
+      <c r="B1636" s="4" t="s">
         <v>1442</v>
       </c>
-      <c r="C1618" s="7" t="s">
+      <c r="C1636" s="7" t="s">
+        <v>1681</v>
+      </c>
+      <c r="D1636" s="3">
+        <f>E1636*10</f>
+        <v>256000</v>
+      </c>
+      <c r="E1636" s="4">
+        <v>25600</v>
+      </c>
+      <c r="F1636" s="4"/>
+      <c r="G1636" s="4" t="s">
+        <v>1691</v>
+      </c>
+      <c r="H1636" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1636" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1637" s="4" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B1637" s="4" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C1637" s="7" t="s">
+        <v>1682</v>
+      </c>
+      <c r="D1637" s="3">
+        <f t="shared" ref="D1637:D1646" si="0">E1637*10</f>
+        <v>324000</v>
+      </c>
+      <c r="E1637" s="4">
+        <v>32400</v>
+      </c>
+      <c r="F1637" s="4"/>
+      <c r="G1637" s="4" t="s">
+        <v>1692</v>
+      </c>
+      <c r="H1637" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1637" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1638" s="4" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B1638" s="4" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C1638" s="7" t="s">
         <v>1683</v>
       </c>
-      <c r="D1618" s="3">
+      <c r="D1638" s="3">
         <f t="shared" si="0"/>
         <v>404000</v>
       </c>
-      <c r="E1618" s="4">
+      <c r="E1638" s="4">
         <v>40400</v>
       </c>
-      <c r="F1618" s="4"/>
-      <c r="G1618" s="4" t="s">
+      <c r="F1638" s="4"/>
+      <c r="G1638" s="4" t="s">
         <v>1693</v>
       </c>
-      <c r="H1618" s="4" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1618" s="4">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="1619" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1619" s="4" t="s">
+      <c r="H1638" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1638" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1639" s="4" t="s">
         <v>1438</v>
       </c>
-      <c r="B1619" s="4" t="s">
+      <c r="B1639" s="4" t="s">
         <v>1442</v>
       </c>
-      <c r="C1619" s="7" t="s">
+      <c r="C1639" s="7" t="s">
         <v>1684</v>
       </c>
-      <c r="D1619" s="3">
+      <c r="D1639" s="3">
         <f t="shared" si="0"/>
         <v>297000</v>
       </c>
-      <c r="E1619" s="4">
+      <c r="E1639" s="4">
         <v>29700</v>
       </c>
-      <c r="F1619" s="4"/>
-      <c r="G1619" s="4" t="s">
+      <c r="F1639" s="4"/>
+      <c r="G1639" s="4" t="s">
         <v>1694</v>
       </c>
-      <c r="H1619" s="4" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1619" s="4">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="1620" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1620" s="4" t="s">
+      <c r="H1639" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1639" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1640" s="4" t="s">
         <v>1438</v>
       </c>
-      <c r="B1620" s="4" t="s">
+      <c r="B1640" s="4" t="s">
         <v>1442</v>
       </c>
-      <c r="C1620" s="7" t="s">
+      <c r="C1640" s="7" t="s">
         <v>1685</v>
       </c>
-      <c r="D1620" s="3">
+      <c r="D1640" s="3">
         <f t="shared" si="0"/>
         <v>310000</v>
       </c>
-      <c r="E1620" s="4">
+      <c r="E1640" s="4">
         <v>31000</v>
       </c>
-      <c r="F1620" s="4"/>
-      <c r="G1620" s="4" t="s">
+      <c r="F1640" s="4"/>
+      <c r="G1640" s="4" t="s">
         <v>1695</v>
       </c>
-      <c r="H1620" s="4" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1620" s="4">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="1621" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1621" s="4" t="s">
+      <c r="H1640" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1640" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1641" s="4" t="s">
         <v>1438</v>
       </c>
-      <c r="B1621" s="4" t="s">
+      <c r="B1641" s="4" t="s">
         <v>1442</v>
       </c>
-      <c r="C1621" s="7" t="s">
+      <c r="C1641" s="7" t="s">
         <v>1686</v>
       </c>
-      <c r="D1621" s="3">
+      <c r="D1641" s="3">
         <f t="shared" si="0"/>
         <v>337000</v>
       </c>
-      <c r="E1621" s="4">
+      <c r="E1641" s="4">
         <v>33700</v>
       </c>
-      <c r="F1621" s="4"/>
-      <c r="G1621" s="4" t="s">
+      <c r="F1641" s="4"/>
+      <c r="G1641" s="4" t="s">
         <v>1696</v>
       </c>
-      <c r="H1621" s="4" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1621" s="4">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="1622" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1622" s="4" t="s">
+      <c r="H1641" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1641" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1642" s="4" t="s">
         <v>1438</v>
       </c>
-      <c r="B1622" s="4" t="s">
+      <c r="B1642" s="4" t="s">
         <v>1442</v>
       </c>
-      <c r="C1622" s="7" t="s">
+      <c r="C1642" s="7" t="s">
         <v>1687</v>
       </c>
-      <c r="D1622" s="3">
+      <c r="D1642" s="3">
         <f t="shared" si="0"/>
         <v>351000</v>
       </c>
-      <c r="E1622" s="4">
+      <c r="E1642" s="4">
         <v>35100</v>
       </c>
-      <c r="F1622" s="4"/>
-      <c r="G1622" s="4" t="s">
+      <c r="F1642" s="4"/>
+      <c r="G1642" s="4" t="s">
         <v>1696</v>
       </c>
-      <c r="H1622" s="4" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1622" s="4">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="1623" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1623" s="4" t="s">
+      <c r="H1642" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1642" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1643" s="4" t="s">
         <v>1438</v>
       </c>
-      <c r="B1623" s="4" t="s">
+      <c r="B1643" s="4" t="s">
         <v>1442</v>
       </c>
-      <c r="C1623" s="7" t="s">
+      <c r="C1643" s="7" t="s">
         <v>1688</v>
       </c>
-      <c r="D1623" s="3">
+      <c r="D1643" s="3">
         <f t="shared" si="0"/>
         <v>378000</v>
       </c>
-      <c r="E1623" s="4">
+      <c r="E1643" s="4">
         <v>37800</v>
       </c>
-      <c r="F1623" s="4"/>
-      <c r="G1623" s="4" t="s">
+      <c r="F1643" s="4"/>
+      <c r="G1643" s="4" t="s">
         <v>1697</v>
       </c>
-      <c r="H1623" s="4" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1623" s="4">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="1624" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1624" s="4" t="s">
+      <c r="H1643" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1643" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1644" s="4" t="s">
         <v>1438</v>
       </c>
-      <c r="B1624" s="4" t="s">
+      <c r="B1644" s="4" t="s">
         <v>1442</v>
       </c>
-      <c r="C1624" s="7" t="s">
+      <c r="C1644" s="7" t="s">
         <v>1689</v>
       </c>
-      <c r="D1624" s="3">
+      <c r="D1644" s="3">
         <f t="shared" si="0"/>
         <v>526000</v>
       </c>
-      <c r="E1624" s="4">
+      <c r="E1644" s="4">
         <v>52600</v>
       </c>
-      <c r="F1624" s="4"/>
-      <c r="G1624" s="4" t="s">
+      <c r="F1644" s="4"/>
+      <c r="G1644" s="4" t="s">
         <v>1698</v>
       </c>
-      <c r="H1624" s="4" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1624" s="4">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="1625" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1625" s="4" t="s">
+      <c r="H1644" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1644" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1645" s="4" t="s">
         <v>1438</v>
       </c>
-      <c r="B1625" s="4" t="s">
+      <c r="B1645" s="4" t="s">
         <v>1442</v>
       </c>
-      <c r="C1625" s="7" t="s">
+      <c r="C1645" s="7" t="s">
         <v>1690</v>
       </c>
-      <c r="D1625" s="3">
+      <c r="D1645" s="3">
         <f t="shared" si="0"/>
         <v>742000</v>
       </c>
-      <c r="E1625" s="4">
+      <c r="E1645" s="4">
         <v>74200</v>
       </c>
-      <c r="F1625" s="4"/>
-      <c r="G1625" s="4" t="s">
+      <c r="F1645" s="4"/>
+      <c r="G1645" s="4" t="s">
         <v>1699</v>
       </c>
-      <c r="H1625" s="4" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1625" s="4">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="1626" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1626" s="4" t="s">
+      <c r="H1645" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1645" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1646" s="4" t="s">
         <v>1439</v>
       </c>
-      <c r="B1626" s="4" t="s">
+      <c r="B1646" s="4" t="s">
         <v>1442</v>
       </c>
-      <c r="C1626" s="7" t="s">
+      <c r="C1646" s="7" t="s">
         <v>1440</v>
       </c>
-      <c r="D1626" s="3">
+      <c r="D1646" s="3">
         <f t="shared" si="0"/>
         <v>567000</v>
       </c>
-      <c r="E1626" s="4">
+      <c r="E1646" s="4">
         <v>56700</v>
       </c>
-      <c r="F1626" s="4"/>
-      <c r="G1626" s="4" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1626" s="4" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1626" s="4">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="1627" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1627" s="4" t="s">
+      <c r="F1646" s="4"/>
+      <c r="G1646" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1646" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1646" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1647" s="4" t="s">
         <v>1441</v>
       </c>
-      <c r="B1627" s="4" t="s">
+      <c r="B1647" s="4" t="s">
         <v>1442</v>
       </c>
-      <c r="C1627" s="7" t="s">
+      <c r="C1647" s="7" t="s">
         <v>1443</v>
       </c>
-      <c r="D1627" s="3">
+      <c r="D1647" s="3">
         <v>250000</v>
       </c>
-      <c r="E1627" s="4">
+      <c r="E1647" s="4">
         <v>25000</v>
       </c>
-      <c r="F1627" s="4"/>
-      <c r="G1627" s="4" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1627" s="4" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1627" s="4">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="1628" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1628" s="4" t="s">
+      <c r="F1647" s="4"/>
+      <c r="G1647" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1647" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1647" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1648" s="4" t="s">
         <v>1441</v>
       </c>
-      <c r="B1628" s="4" t="s">
+      <c r="B1648" s="4" t="s">
         <v>1442</v>
       </c>
-      <c r="C1628" s="7" t="s">
+      <c r="C1648" s="7" t="s">
         <v>1444</v>
       </c>
-      <c r="D1628" s="3">
+      <c r="D1648" s="3">
         <v>236000</v>
       </c>
-      <c r="E1628" s="4">
+      <c r="E1648" s="4">
         <v>23600</v>
       </c>
-      <c r="F1628" s="4"/>
-      <c r="G1628" s="4" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1628" s="4" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1628" s="4">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="1629" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1629" s="4" t="s">
+      <c r="F1648" s="4"/>
+      <c r="G1648" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1648" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1648" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1649" s="4" t="s">
         <v>1445</v>
       </c>
-      <c r="B1629" s="4" t="s">
+      <c r="B1649" s="4" t="s">
         <v>1442</v>
       </c>
-      <c r="C1629" s="7" t="s">
+      <c r="C1649" s="7" t="s">
         <v>1446</v>
       </c>
-      <c r="D1629" s="3">
+      <c r="D1649" s="3">
         <v>312000</v>
       </c>
-      <c r="E1629" s="4">
+      <c r="E1649" s="4">
         <v>31200</v>
       </c>
-      <c r="F1629" s="4"/>
-      <c r="G1629" s="4" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1629" s="4" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1629" s="4">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="1630" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1630" s="4" t="s">
+      <c r="F1649" s="4"/>
+      <c r="G1649" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1649" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1649" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1650" s="4" t="s">
         <v>1445</v>
       </c>
-      <c r="B1630" s="4" t="s">
+      <c r="B1650" s="4" t="s">
         <v>1447</v>
       </c>
-      <c r="C1630" s="7" t="s">
+      <c r="C1650" s="7" t="s">
         <v>1448</v>
       </c>
-      <c r="D1630" s="3">
+      <c r="D1650" s="3">
         <v>156000</v>
       </c>
-      <c r="E1630" s="4">
+      <c r="E1650" s="4">
         <v>15600</v>
       </c>
-      <c r="F1630" s="4"/>
-      <c r="G1630" s="4" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1630" s="4" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1630" s="4">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="1631" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1631" s="4" t="s">
+      <c r="F1650" s="4"/>
+      <c r="G1650" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1650" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1650" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1651" s="4" t="s">
         <v>1449</v>
       </c>
-      <c r="B1631" s="4" t="s">
+      <c r="B1651" s="4" t="s">
         <v>1447</v>
       </c>
-      <c r="C1631" s="7" t="s">
+      <c r="C1651" s="7" t="s">
         <v>1450</v>
       </c>
-      <c r="D1631" s="3">
+      <c r="D1651" s="3">
         <v>153000</v>
       </c>
-      <c r="E1631" s="4">
+      <c r="E1651" s="4">
         <v>15300</v>
       </c>
-      <c r="F1631" s="4"/>
-      <c r="G1631" s="4" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1631" s="4" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1631" s="4">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="1632" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1632" s="4" t="s">
+      <c r="F1651" s="4"/>
+      <c r="G1651" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1651" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1651" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1652" s="4" t="s">
         <v>1451</v>
       </c>
-      <c r="B1632" s="4" t="s">
+      <c r="B1652" s="4" t="s">
         <v>1447</v>
       </c>
-      <c r="C1632" s="7" t="s">
+      <c r="C1652" s="7" t="s">
         <v>1452</v>
       </c>
-      <c r="D1632" s="3">
+      <c r="D1652" s="3">
         <v>153000</v>
       </c>
-      <c r="E1632" s="4">
+      <c r="E1652" s="4">
         <v>15300</v>
       </c>
-      <c r="F1632" s="4"/>
-      <c r="G1632" s="4" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1632" s="4" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1632" s="4">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="1633" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1633" s="4" t="s">
+      <c r="F1652" s="4"/>
+      <c r="G1652" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1652" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1652" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1653" s="4" t="s">
         <v>1453</v>
       </c>
-      <c r="B1633" s="4" t="s">
+      <c r="B1653" s="4" t="s">
         <v>1447</v>
       </c>
-      <c r="C1633" s="7" t="s">
+      <c r="C1653" s="7" t="s">
         <v>1454</v>
       </c>
-      <c r="D1633" s="3">
+      <c r="D1653" s="3">
         <v>153000</v>
       </c>
-      <c r="E1633" s="4">
+      <c r="E1653" s="4">
         <v>15300</v>
       </c>
-      <c r="F1633" s="4"/>
-      <c r="G1633" s="4" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1633" s="4" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1633" s="4">
+      <c r="F1653" s="4"/>
+      <c r="G1653" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1653" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1653" s="4">
         <v>2026</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1633" xr:uid="{B6FE0007-86B3-4D5F-9CBC-37B22BC3E091}"/>
+  <autoFilter ref="A1:I1653" xr:uid="{B6FE0007-86B3-4D5F-9CBC-37B22BC3E091}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/rates.xlsx
+++ b/rates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS COM\Dropbox\Rates Portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3BC216-211A-4E25-B40A-4A655EB28080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43FD5441-8875-40F1-BC7E-3CE18BB1F683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8269" uniqueCount="1730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8269" uniqueCount="1727">
   <si>
     <t>PRLP-1100</t>
   </si>
@@ -5193,15 +5193,6 @@
   </si>
   <si>
     <t>ELECTRIC WATER HEATER CEH-80</t>
-  </si>
-  <si>
-    <t>11 Month Plan</t>
-  </si>
-  <si>
-    <t>12 Month Plan</t>
-  </si>
-  <si>
-    <t>13 Month Plan</t>
   </si>
   <si>
     <t>DigitalTemp™ + WattControl™</t>
@@ -43937,7 +43928,7 @@
       </c>
       <c r="F1382" s="4"/>
       <c r="G1382" s="4" t="s">
-        <v>1712</v>
+        <v>1459</v>
       </c>
       <c r="H1382" s="4" t="s">
         <v>1455</v>
@@ -43964,7 +43955,7 @@
       </c>
       <c r="F1383" s="4"/>
       <c r="G1383" s="4" t="s">
-        <v>1713</v>
+        <v>1459</v>
       </c>
       <c r="H1383" s="4" t="s">
         <v>1455</v>
@@ -43991,7 +43982,7 @@
       </c>
       <c r="F1384" s="4"/>
       <c r="G1384" s="4" t="s">
-        <v>1714</v>
+        <v>1459</v>
       </c>
       <c r="H1384" s="4" t="s">
         <v>1455</v>
@@ -44143,7 +44134,7 @@
         <v>1670</v>
       </c>
       <c r="C1390" s="7" t="s">
-        <v>1716</v>
+        <v>1713</v>
       </c>
       <c r="D1390" s="3">
         <v>20980</v>
@@ -44153,7 +44144,7 @@
       </c>
       <c r="F1390" s="47"/>
       <c r="G1390" s="4" t="s">
-        <v>1715</v>
+        <v>1712</v>
       </c>
       <c r="H1390" s="4" t="s">
         <v>1455</v>
@@ -44170,7 +44161,7 @@
         <v>1670</v>
       </c>
       <c r="C1391" s="7" t="s">
-        <v>1717</v>
+        <v>1714</v>
       </c>
       <c r="D1391" s="3">
         <v>23480</v>
@@ -44180,7 +44171,7 @@
       </c>
       <c r="F1391" s="47"/>
       <c r="G1391" s="4" t="s">
-        <v>1715</v>
+        <v>1712</v>
       </c>
       <c r="H1391" s="4" t="s">
         <v>1455</v>
@@ -44197,7 +44188,7 @@
         <v>1670</v>
       </c>
       <c r="C1392" s="7" t="s">
-        <v>1718</v>
+        <v>1715</v>
       </c>
       <c r="D1392" s="3">
         <v>21980</v>
@@ -44207,7 +44198,7 @@
       </c>
       <c r="F1392" s="47"/>
       <c r="G1392" s="4" t="s">
-        <v>1715</v>
+        <v>1712</v>
       </c>
       <c r="H1392" s="4" t="s">
         <v>1455</v>
@@ -44224,7 +44215,7 @@
         <v>1670</v>
       </c>
       <c r="C1393" s="7" t="s">
-        <v>1719</v>
+        <v>1716</v>
       </c>
       <c r="D1393" s="3">
         <v>22980</v>
@@ -44234,7 +44225,7 @@
       </c>
       <c r="F1393" s="47"/>
       <c r="G1393" s="4" t="s">
-        <v>1715</v>
+        <v>1712</v>
       </c>
       <c r="H1393" s="4" t="s">
         <v>1455</v>
@@ -44251,7 +44242,7 @@
         <v>1670</v>
       </c>
       <c r="C1394" s="7" t="s">
-        <v>1720</v>
+        <v>1717</v>
       </c>
       <c r="D1394" s="3">
         <v>23980</v>
@@ -44261,7 +44252,7 @@
       </c>
       <c r="F1394" s="47"/>
       <c r="G1394" s="4" t="s">
-        <v>1715</v>
+        <v>1712</v>
       </c>
       <c r="H1394" s="4" t="s">
         <v>1455</v>
@@ -44278,7 +44269,7 @@
         <v>1670</v>
       </c>
       <c r="C1395" s="7" t="s">
-        <v>1721</v>
+        <v>1718</v>
       </c>
       <c r="D1395" s="3">
         <v>24980</v>
@@ -44288,7 +44279,7 @@
       </c>
       <c r="F1395" s="47"/>
       <c r="G1395" s="4" t="s">
-        <v>1715</v>
+        <v>1712</v>
       </c>
       <c r="H1395" s="4" t="s">
         <v>1455</v>
@@ -44305,7 +44296,7 @@
         <v>1670</v>
       </c>
       <c r="C1396" s="7" t="s">
-        <v>1722</v>
+        <v>1719</v>
       </c>
       <c r="D1396" s="3">
         <v>25980</v>
@@ -44315,7 +44306,7 @@
       </c>
       <c r="F1396" s="47"/>
       <c r="G1396" s="4" t="s">
-        <v>1715</v>
+        <v>1712</v>
       </c>
       <c r="H1396" s="4" t="s">
         <v>1455</v>
@@ -44332,7 +44323,7 @@
         <v>1670</v>
       </c>
       <c r="C1397" s="7" t="s">
-        <v>1724</v>
+        <v>1721</v>
       </c>
       <c r="D1397" s="3">
         <v>42280</v>
@@ -44342,7 +44333,7 @@
       </c>
       <c r="F1397" s="47"/>
       <c r="G1397" s="4" t="s">
-        <v>1723</v>
+        <v>1720</v>
       </c>
       <c r="H1397" s="4" t="s">
         <v>1455</v>
@@ -44359,7 +44350,7 @@
         <v>1670</v>
       </c>
       <c r="C1398" s="7" t="s">
-        <v>1725</v>
+        <v>1722</v>
       </c>
       <c r="D1398" s="3">
         <v>47280</v>
@@ -44369,7 +44360,7 @@
       </c>
       <c r="F1398" s="47"/>
       <c r="G1398" s="4" t="s">
-        <v>1723</v>
+        <v>1720</v>
       </c>
       <c r="H1398" s="4" t="s">
         <v>1455</v>
@@ -44386,7 +44377,7 @@
         <v>1670</v>
       </c>
       <c r="C1399" s="7" t="s">
-        <v>1726</v>
+        <v>1723</v>
       </c>
       <c r="D1399" s="3">
         <v>52280</v>
@@ -44396,7 +44387,7 @@
       </c>
       <c r="F1399" s="47"/>
       <c r="G1399" s="4" t="s">
-        <v>1723</v>
+        <v>1720</v>
       </c>
       <c r="H1399" s="4" t="s">
         <v>1455</v>
@@ -44413,7 +44404,7 @@
         <v>1670</v>
       </c>
       <c r="C1400" s="46" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
       <c r="D1400" s="47">
         <v>21080</v>
@@ -44423,7 +44414,7 @@
       </c>
       <c r="F1400" s="46"/>
       <c r="G1400" s="47" t="s">
-        <v>1729</v>
+        <v>1726</v>
       </c>
       <c r="H1400" s="4" t="s">
         <v>1455</v>
@@ -44440,7 +44431,7 @@
         <v>1670</v>
       </c>
       <c r="C1401" s="46" t="s">
-        <v>1728</v>
+        <v>1725</v>
       </c>
       <c r="D1401" s="47">
         <v>27180</v>
@@ -44450,7 +44441,7 @@
       </c>
       <c r="F1401" s="46"/>
       <c r="G1401" s="47" t="s">
-        <v>1729</v>
+        <v>1726</v>
       </c>
       <c r="H1401" s="4" t="s">
         <v>1455</v>

--- a/rates.xlsx
+++ b/rates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS COM\Dropbox\Rates Portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC20B3AE-3C37-448B-B409-418FA5F23A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A718EFB4-29DB-4E33-B21E-3654AFF62397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43664,7 +43664,7 @@
         <v>1700</v>
       </c>
       <c r="B1382" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1382" s="19" t="s">
         <v>1701</v>
@@ -43691,7 +43691,7 @@
         <v>1700</v>
       </c>
       <c r="B1383" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1383" s="19" t="s">
         <v>1702</v>
@@ -43718,7 +43718,7 @@
         <v>1700</v>
       </c>
       <c r="B1384" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1384" s="19" t="s">
         <v>1703</v>
@@ -43745,7 +43745,7 @@
         <v>1700</v>
       </c>
       <c r="B1385" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1385" s="19" t="s">
         <v>1705</v>
@@ -43772,7 +43772,7 @@
         <v>1700</v>
       </c>
       <c r="B1386" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1386" s="19" t="s">
         <v>1706</v>
@@ -43799,7 +43799,7 @@
         <v>1700</v>
       </c>
       <c r="B1387" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1387" s="19" t="s">
         <v>1707</v>
@@ -43826,7 +43826,7 @@
         <v>1700</v>
       </c>
       <c r="B1388" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1388" s="19" t="s">
         <v>1708</v>
@@ -43853,7 +43853,7 @@
         <v>1700</v>
       </c>
       <c r="B1389" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1389" s="19" t="s">
         <v>1709</v>
@@ -43880,7 +43880,7 @@
         <v>1700</v>
       </c>
       <c r="B1390" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1390" s="19" t="s">
         <v>1711</v>
@@ -43907,7 +43907,7 @@
         <v>1700</v>
       </c>
       <c r="B1391" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1391" s="19" t="s">
         <v>1712</v>
@@ -43934,7 +43934,7 @@
         <v>1700</v>
       </c>
       <c r="B1392" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1392" s="19" t="s">
         <v>1713</v>
@@ -43961,7 +43961,7 @@
         <v>1700</v>
       </c>
       <c r="B1393" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1393" s="19" t="s">
         <v>1714</v>
@@ -43988,7 +43988,7 @@
         <v>1700</v>
       </c>
       <c r="B1394" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1394" s="19" t="s">
         <v>1715</v>
@@ -44015,7 +44015,7 @@
         <v>1700</v>
       </c>
       <c r="B1395" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1395" s="19" t="s">
         <v>1716</v>
@@ -44042,7 +44042,7 @@
         <v>1700</v>
       </c>
       <c r="B1396" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1396" s="19" t="s">
         <v>1717</v>
@@ -44069,7 +44069,7 @@
         <v>1700</v>
       </c>
       <c r="B1397" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1397" s="19" t="s">
         <v>1719</v>
@@ -44096,7 +44096,7 @@
         <v>1700</v>
       </c>
       <c r="B1398" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1398" s="19" t="s">
         <v>1720</v>
@@ -44123,7 +44123,7 @@
         <v>1700</v>
       </c>
       <c r="B1399" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1399" s="19" t="s">
         <v>1721</v>
@@ -44150,7 +44150,7 @@
         <v>1700</v>
       </c>
       <c r="B1400" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1400" s="19" t="s">
         <v>1722</v>
@@ -44177,7 +44177,7 @@
         <v>1700</v>
       </c>
       <c r="B1401" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1401" s="19" t="s">
         <v>1723</v>

--- a/rates.xlsx
+++ b/rates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS COM\Dropbox\Rates Portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A718EFB4-29DB-4E33-B21E-3654AFF62397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58037BF5-97DF-4E62-B0CB-EC873D65DE9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5149,9 +5149,6 @@
     <t>DEURON DN-813</t>
   </si>
   <si>
-    <t>RIMCO</t>
-  </si>
-  <si>
     <t>ELECTRIC WATER HEATER EH-15</t>
   </si>
   <si>
@@ -5225,6 +5222,9 @@
   </si>
   <si>
     <t>HGL-30100 چرغہ ماذل</t>
+  </si>
+  <si>
+    <t>Cherry</t>
   </si>
 </sst>
 </file>
@@ -13370,7 +13370,7 @@
         <v>403</v>
       </c>
       <c r="C263" s="17" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="D263" s="6">
         <v>41155</v>
@@ -43661,13 +43661,13 @@
     </row>
     <row r="1382" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1382" s="6" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="B1382" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1382" s="19" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="D1382" s="7">
         <v>20980</v>
@@ -43688,13 +43688,13 @@
     </row>
     <row r="1383" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1383" s="6" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="B1383" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1383" s="19" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="D1383" s="7">
         <v>20980</v>
@@ -43715,13 +43715,13 @@
     </row>
     <row r="1384" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1384" s="6" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="B1384" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1384" s="19" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="D1384" s="7">
         <v>23480</v>
@@ -43742,13 +43742,13 @@
     </row>
     <row r="1385" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1385" s="6" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="B1385" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1385" s="19" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="D1385" s="7">
         <v>21480</v>
@@ -43758,7 +43758,7 @@
       </c>
       <c r="F1385" s="6"/>
       <c r="G1385" s="6" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H1385" s="6" t="s">
         <v>1455</v>
@@ -43769,13 +43769,13 @@
     </row>
     <row r="1386" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1386" s="6" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="B1386" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1386" s="19" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="D1386" s="7">
         <v>22480</v>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="F1386" s="6"/>
       <c r="G1386" s="6" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H1386" s="6" t="s">
         <v>1455</v>
@@ -43796,13 +43796,13 @@
     </row>
     <row r="1387" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1387" s="6" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="B1387" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1387" s="19" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="D1387" s="7">
         <v>23480</v>
@@ -43812,7 +43812,7 @@
       </c>
       <c r="F1387" s="6"/>
       <c r="G1387" s="6" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H1387" s="6" t="s">
         <v>1455</v>
@@ -43823,13 +43823,13 @@
     </row>
     <row r="1388" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1388" s="6" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="B1388" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1388" s="19" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="D1388" s="7">
         <v>24480</v>
@@ -43839,7 +43839,7 @@
       </c>
       <c r="F1388" s="6"/>
       <c r="G1388" s="6" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H1388" s="6" t="s">
         <v>1455</v>
@@ -43850,13 +43850,13 @@
     </row>
     <row r="1389" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1389" s="6" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="B1389" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1389" s="19" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="D1389" s="7">
         <v>25480</v>
@@ -43866,7 +43866,7 @@
       </c>
       <c r="F1389" s="6"/>
       <c r="G1389" s="6" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H1389" s="6" t="s">
         <v>1455</v>
@@ -43877,13 +43877,13 @@
     </row>
     <row r="1390" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1390" s="6" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="B1390" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1390" s="19" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="D1390" s="7">
         <v>20980</v>
@@ -43893,7 +43893,7 @@
       </c>
       <c r="F1390" s="6"/>
       <c r="G1390" s="6" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H1390" s="6" t="s">
         <v>1455</v>
@@ -43904,13 +43904,13 @@
     </row>
     <row r="1391" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1391" s="6" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="B1391" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1391" s="19" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="D1391" s="7">
         <v>23480</v>
@@ -43920,7 +43920,7 @@
       </c>
       <c r="F1391" s="6"/>
       <c r="G1391" s="6" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H1391" s="6" t="s">
         <v>1455</v>
@@ -43931,13 +43931,13 @@
     </row>
     <row r="1392" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1392" s="6" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="B1392" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1392" s="19" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="D1392" s="7">
         <v>21980</v>
@@ -43947,7 +43947,7 @@
       </c>
       <c r="F1392" s="6"/>
       <c r="G1392" s="6" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H1392" s="6" t="s">
         <v>1455</v>
@@ -43958,13 +43958,13 @@
     </row>
     <row r="1393" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1393" s="6" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="B1393" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1393" s="19" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="D1393" s="7">
         <v>22980</v>
@@ -43974,7 +43974,7 @@
       </c>
       <c r="F1393" s="6"/>
       <c r="G1393" s="6" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H1393" s="6" t="s">
         <v>1455</v>
@@ -43985,13 +43985,13 @@
     </row>
     <row r="1394" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1394" s="6" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="B1394" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1394" s="19" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="D1394" s="7">
         <v>23980</v>
@@ -44001,7 +44001,7 @@
       </c>
       <c r="F1394" s="6"/>
       <c r="G1394" s="6" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H1394" s="6" t="s">
         <v>1455</v>
@@ -44012,13 +44012,13 @@
     </row>
     <row r="1395" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1395" s="6" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="B1395" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1395" s="19" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="D1395" s="7">
         <v>24980</v>
@@ -44028,7 +44028,7 @@
       </c>
       <c r="F1395" s="6"/>
       <c r="G1395" s="6" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H1395" s="6" t="s">
         <v>1455</v>
@@ -44039,13 +44039,13 @@
     </row>
     <row r="1396" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1396" s="6" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="B1396" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1396" s="19" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="D1396" s="7">
         <v>25980</v>
@@ -44055,7 +44055,7 @@
       </c>
       <c r="F1396" s="6"/>
       <c r="G1396" s="6" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H1396" s="6" t="s">
         <v>1455</v>
@@ -44066,13 +44066,13 @@
     </row>
     <row r="1397" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1397" s="6" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="B1397" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1397" s="19" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="D1397" s="7">
         <v>42280</v>
@@ -44082,7 +44082,7 @@
       </c>
       <c r="F1397" s="6"/>
       <c r="G1397" s="6" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="H1397" s="6" t="s">
         <v>1455</v>
@@ -44093,13 +44093,13 @@
     </row>
     <row r="1398" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1398" s="6" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="B1398" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1398" s="19" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="D1398" s="7">
         <v>47280</v>
@@ -44109,7 +44109,7 @@
       </c>
       <c r="F1398" s="6"/>
       <c r="G1398" s="6" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="H1398" s="6" t="s">
         <v>1455</v>
@@ -44120,13 +44120,13 @@
     </row>
     <row r="1399" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1399" s="6" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="B1399" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1399" s="19" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="D1399" s="7">
         <v>52280</v>
@@ -44136,7 +44136,7 @@
       </c>
       <c r="F1399" s="6"/>
       <c r="G1399" s="6" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="H1399" s="6" t="s">
         <v>1455</v>
@@ -44147,13 +44147,13 @@
     </row>
     <row r="1400" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1400" s="6" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="B1400" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1400" s="19" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="D1400" s="6">
         <v>21080</v>
@@ -44163,7 +44163,7 @@
       </c>
       <c r="F1400" s="6"/>
       <c r="G1400" s="6" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H1400" s="6" t="s">
         <v>1455</v>
@@ -44174,13 +44174,13 @@
     </row>
     <row r="1401" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1401" s="6" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="B1401" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1401" s="19" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="D1401" s="6">
         <v>27180</v>
@@ -44190,7 +44190,7 @@
       </c>
       <c r="F1401" s="6"/>
       <c r="G1401" s="6" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H1401" s="6" t="s">
         <v>1455</v>

--- a/rates.xlsx
+++ b/rates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS COM\Dropbox\Rates Portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58037BF5-97DF-4E62-B0CB-EC873D65DE9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FF9690-8921-4E85-9470-251B7AD9B049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5224,7 +5224,7 @@
     <t>HGL-30100 چرغہ ماذل</t>
   </si>
   <si>
-    <t>Cherry</t>
+    <t>CHERRY</t>
   </si>
 </sst>
 </file>

--- a/rates.xlsx
+++ b/rates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS COM\Dropbox\Rates Portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FF9690-8921-4E85-9470-251B7AD9B049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCBC1E3-95B7-4379-9C14-52A2672FF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$I$1653</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$I$1659</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8269" uniqueCount="1726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8299" uniqueCount="1737">
   <si>
     <t>PRLP-1100</t>
   </si>
@@ -5149,6 +5149,9 @@
     <t>DEURON DN-813</t>
   </si>
   <si>
+    <t>RIMCO</t>
+  </si>
+  <si>
     <t>ELECTRIC WATER HEATER EH-15</t>
   </si>
   <si>
@@ -5225,6 +5228,36 @@
   </si>
   <si>
     <t>CHERRY</t>
+  </si>
+  <si>
+    <t>EH-25L White Aquator</t>
+  </si>
+  <si>
+    <t>EH-25L Jewel Jewel</t>
+  </si>
+  <si>
+    <t>EH-40L Magma</t>
+  </si>
+  <si>
+    <t>EH-60L Magma</t>
+  </si>
+  <si>
+    <t>EH-50L WattPro</t>
+  </si>
+  <si>
+    <t>EH-70L WattPro</t>
+  </si>
+  <si>
+    <t>1500W Italy element; Heavy gauge water tank</t>
+  </si>
+  <si>
+    <t>1500W Italy element; Heavy gauge water tank; Digital temperature display (shown on poster)</t>
+  </si>
+  <si>
+    <t>Digital temperature display; 1500W Italy element; Heavy gauge water tank</t>
+  </si>
+  <si>
+    <t>Digital temperature display; 2000W Italy element; Watt control; Inverter technology; Heavy gauge water tank</t>
   </si>
 </sst>
 </file>
@@ -5375,7 +5408,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5457,6 +5490,9 @@
     </xf>
     <xf numFmtId="3" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5750,7 +5786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6FE0007-86B3-4D5F-9CBC-37B22BC3E091}">
-  <dimension ref="A1:I1654"/>
+  <dimension ref="A1:I1660"/>
   <sheetFormatPr defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -13370,7 +13406,7 @@
         <v>403</v>
       </c>
       <c r="C263" s="17" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="D263" s="6">
         <v>41155</v>
@@ -43661,23 +43697,23 @@
     </row>
     <row r="1382" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1382" s="6" t="s">
-        <v>1725</v>
+        <v>1700</v>
       </c>
       <c r="B1382" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1382" s="19" t="s">
-        <v>1700</v>
+        <v>1727</v>
       </c>
       <c r="D1382" s="7">
-        <v>20980</v>
+        <v>19180</v>
       </c>
       <c r="E1382" s="6">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="F1382" s="6"/>
-      <c r="G1382" s="6" t="s">
-        <v>1459</v>
+      <c r="G1382" s="30" t="s">
+        <v>1733</v>
       </c>
       <c r="H1382" s="6" t="s">
         <v>1455</v>
@@ -43688,23 +43724,23 @@
     </row>
     <row r="1383" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1383" s="6" t="s">
-        <v>1725</v>
+        <v>1700</v>
       </c>
       <c r="B1383" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1383" s="19" t="s">
-        <v>1701</v>
+        <v>1728</v>
       </c>
       <c r="D1383" s="7">
-        <v>20980</v>
+        <v>19680</v>
       </c>
       <c r="E1383" s="6">
-        <v>2900</v>
+        <v>3100</v>
       </c>
       <c r="F1383" s="6"/>
-      <c r="G1383" s="6" t="s">
-        <v>1459</v>
+      <c r="G1383" s="30" t="s">
+        <v>1734</v>
       </c>
       <c r="H1383" s="6" t="s">
         <v>1455</v>
@@ -43715,23 +43751,23 @@
     </row>
     <row r="1384" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1384" s="6" t="s">
-        <v>1725</v>
+        <v>1700</v>
       </c>
       <c r="B1384" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1384" s="19" t="s">
-        <v>1702</v>
+        <v>1729</v>
       </c>
       <c r="D1384" s="7">
-        <v>23480</v>
+        <v>20680</v>
       </c>
       <c r="E1384" s="6">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="F1384" s="6"/>
-      <c r="G1384" s="6" t="s">
-        <v>1459</v>
+      <c r="G1384" s="30" t="s">
+        <v>1735</v>
       </c>
       <c r="H1384" s="6" t="s">
         <v>1455</v>
@@ -43742,23 +43778,23 @@
     </row>
     <row r="1385" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1385" s="6" t="s">
-        <v>1725</v>
+        <v>1700</v>
       </c>
       <c r="B1385" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1385" s="19" t="s">
-        <v>1704</v>
+        <v>1730</v>
       </c>
       <c r="D1385" s="7">
-        <v>21480</v>
+        <v>22280</v>
       </c>
       <c r="E1385" s="6">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="F1385" s="6"/>
-      <c r="G1385" s="6" t="s">
-        <v>1703</v>
+      <c r="G1385" s="30" t="s">
+        <v>1735</v>
       </c>
       <c r="H1385" s="6" t="s">
         <v>1455</v>
@@ -43769,23 +43805,23 @@
     </row>
     <row r="1386" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1386" s="6" t="s">
-        <v>1725</v>
+        <v>1700</v>
       </c>
       <c r="B1386" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1386" s="19" t="s">
-        <v>1705</v>
+        <v>1731</v>
       </c>
       <c r="D1386" s="7">
-        <v>22480</v>
+        <v>23780</v>
       </c>
       <c r="E1386" s="6">
-        <v>3100</v>
+        <v>3700</v>
       </c>
       <c r="F1386" s="6"/>
-      <c r="G1386" s="6" t="s">
-        <v>1703</v>
+      <c r="G1386" s="30" t="s">
+        <v>1736</v>
       </c>
       <c r="H1386" s="6" t="s">
         <v>1455</v>
@@ -43796,23 +43832,23 @@
     </row>
     <row r="1387" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1387" s="6" t="s">
-        <v>1725</v>
+        <v>1700</v>
       </c>
       <c r="B1387" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1387" s="19" t="s">
-        <v>1706</v>
+        <v>1732</v>
       </c>
       <c r="D1387" s="7">
-        <v>23480</v>
+        <v>24780</v>
       </c>
       <c r="E1387" s="6">
-        <v>3300</v>
+        <v>3800</v>
       </c>
       <c r="F1387" s="6"/>
-      <c r="G1387" s="6" t="s">
-        <v>1703</v>
+      <c r="G1387" s="30" t="s">
+        <v>1736</v>
       </c>
       <c r="H1387" s="6" t="s">
         <v>1455</v>
@@ -43823,23 +43859,23 @@
     </row>
     <row r="1388" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1388" s="6" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1388" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1388" s="19" t="s">
-        <v>1707</v>
+        <v>1701</v>
       </c>
       <c r="D1388" s="7">
-        <v>24480</v>
+        <v>20980</v>
       </c>
       <c r="E1388" s="6">
-        <v>3400</v>
+        <v>2900</v>
       </c>
       <c r="F1388" s="6"/>
       <c r="G1388" s="6" t="s">
-        <v>1703</v>
+        <v>1459</v>
       </c>
       <c r="H1388" s="6" t="s">
         <v>1455</v>
@@ -43850,23 +43886,23 @@
     </row>
     <row r="1389" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1389" s="6" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1389" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1389" s="19" t="s">
-        <v>1708</v>
+        <v>1702</v>
       </c>
       <c r="D1389" s="7">
-        <v>25480</v>
+        <v>20980</v>
       </c>
       <c r="E1389" s="6">
-        <v>3600</v>
+        <v>2900</v>
       </c>
       <c r="F1389" s="6"/>
       <c r="G1389" s="6" t="s">
-        <v>1703</v>
+        <v>1459</v>
       </c>
       <c r="H1389" s="6" t="s">
         <v>1455</v>
@@ -43877,23 +43913,23 @@
     </row>
     <row r="1390" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1390" s="6" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1390" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1390" s="19" t="s">
-        <v>1710</v>
+        <v>1703</v>
       </c>
       <c r="D1390" s="7">
-        <v>20980</v>
+        <v>23480</v>
       </c>
       <c r="E1390" s="6">
-        <v>2900</v>
+        <v>3300</v>
       </c>
       <c r="F1390" s="6"/>
       <c r="G1390" s="6" t="s">
-        <v>1709</v>
+        <v>1459</v>
       </c>
       <c r="H1390" s="6" t="s">
         <v>1455</v>
@@ -43904,23 +43940,23 @@
     </row>
     <row r="1391" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1391" s="6" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1391" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1391" s="19" t="s">
-        <v>1711</v>
+        <v>1705</v>
       </c>
       <c r="D1391" s="7">
-        <v>23480</v>
+        <v>21480</v>
       </c>
       <c r="E1391" s="6">
-        <v>3300</v>
+        <v>3000</v>
       </c>
       <c r="F1391" s="6"/>
       <c r="G1391" s="6" t="s">
-        <v>1709</v>
+        <v>1704</v>
       </c>
       <c r="H1391" s="6" t="s">
         <v>1455</v>
@@ -43931,23 +43967,23 @@
     </row>
     <row r="1392" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1392" s="6" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1392" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1392" s="19" t="s">
-        <v>1712</v>
+        <v>1706</v>
       </c>
       <c r="D1392" s="7">
-        <v>21980</v>
+        <v>22480</v>
       </c>
       <c r="E1392" s="6">
         <v>3100</v>
       </c>
       <c r="F1392" s="6"/>
       <c r="G1392" s="6" t="s">
-        <v>1709</v>
+        <v>1704</v>
       </c>
       <c r="H1392" s="6" t="s">
         <v>1455</v>
@@ -43958,23 +43994,23 @@
     </row>
     <row r="1393" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1393" s="6" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1393" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1393" s="19" t="s">
-        <v>1713</v>
+        <v>1707</v>
       </c>
       <c r="D1393" s="7">
-        <v>22980</v>
+        <v>23480</v>
       </c>
       <c r="E1393" s="6">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="F1393" s="6"/>
       <c r="G1393" s="6" t="s">
-        <v>1709</v>
+        <v>1704</v>
       </c>
       <c r="H1393" s="6" t="s">
         <v>1455</v>
@@ -43985,23 +44021,23 @@
     </row>
     <row r="1394" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1394" s="6" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1394" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1394" s="19" t="s">
-        <v>1714</v>
+        <v>1708</v>
       </c>
       <c r="D1394" s="7">
-        <v>23980</v>
+        <v>24480</v>
       </c>
       <c r="E1394" s="6">
         <v>3400</v>
       </c>
       <c r="F1394" s="6"/>
       <c r="G1394" s="6" t="s">
-        <v>1709</v>
+        <v>1704</v>
       </c>
       <c r="H1394" s="6" t="s">
         <v>1455</v>
@@ -44012,23 +44048,23 @@
     </row>
     <row r="1395" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1395" s="6" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1395" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1395" s="19" t="s">
-        <v>1715</v>
+        <v>1709</v>
       </c>
       <c r="D1395" s="7">
-        <v>24980</v>
+        <v>25480</v>
       </c>
       <c r="E1395" s="6">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="F1395" s="6"/>
       <c r="G1395" s="6" t="s">
-        <v>1709</v>
+        <v>1704</v>
       </c>
       <c r="H1395" s="6" t="s">
         <v>1455</v>
@@ -44039,23 +44075,23 @@
     </row>
     <row r="1396" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1396" s="6" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1396" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1396" s="19" t="s">
-        <v>1716</v>
+        <v>1711</v>
       </c>
       <c r="D1396" s="7">
-        <v>25980</v>
+        <v>20980</v>
       </c>
       <c r="E1396" s="6">
-        <v>3600</v>
+        <v>2900</v>
       </c>
       <c r="F1396" s="6"/>
       <c r="G1396" s="6" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="H1396" s="6" t="s">
         <v>1455</v>
@@ -44066,23 +44102,23 @@
     </row>
     <row r="1397" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1397" s="6" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1397" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1397" s="19" t="s">
-        <v>1718</v>
+        <v>1712</v>
       </c>
       <c r="D1397" s="7">
-        <v>42280</v>
+        <v>23480</v>
       </c>
       <c r="E1397" s="6">
-        <v>5900</v>
+        <v>3300</v>
       </c>
       <c r="F1397" s="6"/>
       <c r="G1397" s="6" t="s">
-        <v>1717</v>
+        <v>1710</v>
       </c>
       <c r="H1397" s="6" t="s">
         <v>1455</v>
@@ -44093,23 +44129,23 @@
     </row>
     <row r="1398" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1398" s="6" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1398" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1398" s="19" t="s">
-        <v>1719</v>
+        <v>1713</v>
       </c>
       <c r="D1398" s="7">
-        <v>47280</v>
+        <v>21980</v>
       </c>
       <c r="E1398" s="6">
-        <v>6600</v>
+        <v>3100</v>
       </c>
       <c r="F1398" s="6"/>
       <c r="G1398" s="6" t="s">
-        <v>1717</v>
+        <v>1710</v>
       </c>
       <c r="H1398" s="6" t="s">
         <v>1455</v>
@@ -44120,23 +44156,23 @@
     </row>
     <row r="1399" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1399" s="6" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1399" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1399" s="19" t="s">
-        <v>1720</v>
+        <v>1714</v>
       </c>
       <c r="D1399" s="7">
-        <v>52280</v>
+        <v>22980</v>
       </c>
       <c r="E1399" s="6">
-        <v>7300</v>
+        <v>3200</v>
       </c>
       <c r="F1399" s="6"/>
       <c r="G1399" s="6" t="s">
-        <v>1717</v>
+        <v>1710</v>
       </c>
       <c r="H1399" s="6" t="s">
         <v>1455</v>
@@ -44147,23 +44183,23 @@
     </row>
     <row r="1400" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1400" s="6" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1400" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1400" s="19" t="s">
-        <v>1721</v>
-      </c>
-      <c r="D1400" s="6">
-        <v>21080</v>
+        <v>1715</v>
+      </c>
+      <c r="D1400" s="7">
+        <v>23980</v>
       </c>
       <c r="E1400" s="6">
-        <v>3000</v>
+        <v>3400</v>
       </c>
       <c r="F1400" s="6"/>
       <c r="G1400" s="6" t="s">
-        <v>1723</v>
+        <v>1710</v>
       </c>
       <c r="H1400" s="6" t="s">
         <v>1455</v>
@@ -44174,23 +44210,23 @@
     </row>
     <row r="1401" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1401" s="6" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1401" s="6" t="s">
         <v>1669</v>
       </c>
       <c r="C1401" s="19" t="s">
-        <v>1722</v>
-      </c>
-      <c r="D1401" s="6">
-        <v>27180</v>
+        <v>1716</v>
+      </c>
+      <c r="D1401" s="7">
+        <v>24980</v>
       </c>
       <c r="E1401" s="6">
-        <v>3800</v>
+        <v>3500</v>
       </c>
       <c r="F1401" s="6"/>
       <c r="G1401" s="6" t="s">
-        <v>1723</v>
+        <v>1710</v>
       </c>
       <c r="H1401" s="6" t="s">
         <v>1455</v>
@@ -44201,23 +44237,23 @@
     </row>
     <row r="1402" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1402" s="6" t="s">
-        <v>168</v>
+        <v>1726</v>
       </c>
       <c r="B1402" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1402" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="D1402" s="15">
-        <v>64000</v>
-      </c>
-      <c r="E1402" s="5">
-        <v>6400</v>
+        <v>1669</v>
+      </c>
+      <c r="C1402" s="19" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D1402" s="7">
+        <v>25980</v>
+      </c>
+      <c r="E1402" s="6">
+        <v>3600</v>
       </c>
       <c r="F1402" s="6"/>
       <c r="G1402" s="6" t="s">
-        <v>1459</v>
+        <v>1710</v>
       </c>
       <c r="H1402" s="6" t="s">
         <v>1455</v>
@@ -44228,23 +44264,23 @@
     </row>
     <row r="1403" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1403" s="6" t="s">
-        <v>168</v>
+        <v>1726</v>
       </c>
       <c r="B1403" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1403" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="D1403" s="15">
-        <v>80000</v>
-      </c>
-      <c r="E1403" s="5">
-        <v>8000</v>
+        <v>1669</v>
+      </c>
+      <c r="C1403" s="19" t="s">
+        <v>1719</v>
+      </c>
+      <c r="D1403" s="7">
+        <v>42280</v>
+      </c>
+      <c r="E1403" s="6">
+        <v>5900</v>
       </c>
       <c r="F1403" s="6"/>
       <c r="G1403" s="6" t="s">
-        <v>1459</v>
+        <v>1718</v>
       </c>
       <c r="H1403" s="6" t="s">
         <v>1455</v>
@@ -44255,23 +44291,23 @@
     </row>
     <row r="1404" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1404" s="6" t="s">
-        <v>168</v>
+        <v>1726</v>
       </c>
       <c r="B1404" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1404" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="D1404" s="15">
-        <v>96000</v>
-      </c>
-      <c r="E1404" s="5">
-        <v>9600</v>
+        <v>1669</v>
+      </c>
+      <c r="C1404" s="19" t="s">
+        <v>1720</v>
+      </c>
+      <c r="D1404" s="7">
+        <v>47280</v>
+      </c>
+      <c r="E1404" s="6">
+        <v>6600</v>
       </c>
       <c r="F1404" s="6"/>
       <c r="G1404" s="6" t="s">
-        <v>1459</v>
+        <v>1718</v>
       </c>
       <c r="H1404" s="6" t="s">
         <v>1455</v>
@@ -44282,23 +44318,23 @@
     </row>
     <row r="1405" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1405" s="6" t="s">
-        <v>168</v>
+        <v>1726</v>
       </c>
       <c r="B1405" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1405" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="D1405" s="15">
-        <v>102000</v>
-      </c>
-      <c r="E1405" s="5">
-        <v>10200</v>
+        <v>1669</v>
+      </c>
+      <c r="C1405" s="19" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D1405" s="7">
+        <v>52280</v>
+      </c>
+      <c r="E1405" s="6">
+        <v>7300</v>
       </c>
       <c r="F1405" s="6"/>
       <c r="G1405" s="6" t="s">
-        <v>1459</v>
+        <v>1718</v>
       </c>
       <c r="H1405" s="6" t="s">
         <v>1455</v>
@@ -44309,23 +44345,23 @@
     </row>
     <row r="1406" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1406" s="6" t="s">
-        <v>168</v>
+        <v>1726</v>
       </c>
       <c r="B1406" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1406" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="D1406" s="15">
-        <v>133000</v>
-      </c>
-      <c r="E1406" s="5">
-        <v>13300</v>
+        <v>1669</v>
+      </c>
+      <c r="C1406" s="19" t="s">
+        <v>1722</v>
+      </c>
+      <c r="D1406" s="6">
+        <v>21080</v>
+      </c>
+      <c r="E1406" s="6">
+        <v>3000</v>
       </c>
       <c r="F1406" s="6"/>
       <c r="G1406" s="6" t="s">
-        <v>1459</v>
+        <v>1724</v>
       </c>
       <c r="H1406" s="6" t="s">
         <v>1455</v>
@@ -44336,23 +44372,23 @@
     </row>
     <row r="1407" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1407" s="6" t="s">
-        <v>168</v>
+        <v>1726</v>
       </c>
       <c r="B1407" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1407" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="D1407" s="15">
-        <v>140000</v>
-      </c>
-      <c r="E1407" s="5">
-        <v>14000</v>
+        <v>1669</v>
+      </c>
+      <c r="C1407" s="19" t="s">
+        <v>1723</v>
+      </c>
+      <c r="D1407" s="6">
+        <v>27180</v>
+      </c>
+      <c r="E1407" s="6">
+        <v>3800</v>
       </c>
       <c r="F1407" s="6"/>
       <c r="G1407" s="6" t="s">
-        <v>1459</v>
+        <v>1724</v>
       </c>
       <c r="H1407" s="6" t="s">
         <v>1455</v>
@@ -44369,13 +44405,13 @@
         <v>207</v>
       </c>
       <c r="C1408" s="22" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D1408" s="15">
-        <v>133000</v>
+        <v>64000</v>
       </c>
       <c r="E1408" s="5">
-        <v>13300</v>
+        <v>6400</v>
       </c>
       <c r="F1408" s="6"/>
       <c r="G1408" s="6" t="s">
@@ -44396,13 +44432,13 @@
         <v>207</v>
       </c>
       <c r="C1409" s="22" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D1409" s="15">
-        <v>187000</v>
+        <v>80000</v>
       </c>
       <c r="E1409" s="5">
-        <v>18700</v>
+        <v>8000</v>
       </c>
       <c r="F1409" s="6"/>
       <c r="G1409" s="6" t="s">
@@ -44423,13 +44459,13 @@
         <v>207</v>
       </c>
       <c r="C1410" s="22" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D1410" s="15">
-        <v>231000</v>
+        <v>96000</v>
       </c>
       <c r="E1410" s="5">
-        <v>23100</v>
+        <v>9600</v>
       </c>
       <c r="F1410" s="6"/>
       <c r="G1410" s="6" t="s">
@@ -44450,13 +44486,13 @@
         <v>207</v>
       </c>
       <c r="C1411" s="22" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D1411" s="15">
-        <v>256000</v>
+        <v>102000</v>
       </c>
       <c r="E1411" s="5">
-        <v>25600</v>
+        <v>10200</v>
       </c>
       <c r="F1411" s="6"/>
       <c r="G1411" s="6" t="s">
@@ -44476,14 +44512,14 @@
       <c r="B1412" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="C1412" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="D1412" s="7">
-        <v>287000</v>
-      </c>
-      <c r="E1412" s="6">
-        <v>28700</v>
+      <c r="C1412" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1412" s="15">
+        <v>133000</v>
+      </c>
+      <c r="E1412" s="5">
+        <v>13300</v>
       </c>
       <c r="F1412" s="6"/>
       <c r="G1412" s="6" t="s">
@@ -44503,14 +44539,14 @@
       <c r="B1413" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="C1413" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="D1413" s="7">
-        <v>315000</v>
-      </c>
-      <c r="E1413" s="6">
-        <v>31500</v>
+      <c r="C1413" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="D1413" s="15">
+        <v>140000</v>
+      </c>
+      <c r="E1413" s="5">
+        <v>14000</v>
       </c>
       <c r="F1413" s="6"/>
       <c r="G1413" s="6" t="s">
@@ -44530,14 +44566,14 @@
       <c r="B1414" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="C1414" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="D1414" s="7">
-        <v>308000</v>
-      </c>
-      <c r="E1414" s="6">
-        <v>30800</v>
+      <c r="C1414" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1414" s="15">
+        <v>133000</v>
+      </c>
+      <c r="E1414" s="5">
+        <v>13300</v>
       </c>
       <c r="F1414" s="6"/>
       <c r="G1414" s="6" t="s">
@@ -44557,14 +44593,14 @@
       <c r="B1415" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="C1415" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="D1415" s="7">
-        <v>357000</v>
-      </c>
-      <c r="E1415" s="6">
-        <v>35700</v>
+      <c r="C1415" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1415" s="15">
+        <v>187000</v>
+      </c>
+      <c r="E1415" s="5">
+        <v>18700</v>
       </c>
       <c r="F1415" s="6"/>
       <c r="G1415" s="6" t="s">
@@ -44584,14 +44620,14 @@
       <c r="B1416" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="C1416" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="D1416" s="7">
-        <v>448000</v>
-      </c>
-      <c r="E1416" s="6">
-        <v>44800</v>
+      <c r="C1416" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1416" s="15">
+        <v>231000</v>
+      </c>
+      <c r="E1416" s="5">
+        <v>23100</v>
       </c>
       <c r="F1416" s="6"/>
       <c r="G1416" s="6" t="s">
@@ -44611,14 +44647,14 @@
       <c r="B1417" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="C1417" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="D1417" s="7">
-        <v>532000</v>
-      </c>
-      <c r="E1417" s="6">
-        <v>53200</v>
+      <c r="C1417" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1417" s="15">
+        <v>256000</v>
+      </c>
+      <c r="E1417" s="5">
+        <v>25600</v>
       </c>
       <c r="F1417" s="6"/>
       <c r="G1417" s="6" t="s">
@@ -44639,13 +44675,13 @@
         <v>207</v>
       </c>
       <c r="C1418" s="19" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D1418" s="7">
-        <v>539000</v>
+        <v>287000</v>
       </c>
       <c r="E1418" s="6">
-        <v>53900</v>
+        <v>28700</v>
       </c>
       <c r="F1418" s="6"/>
       <c r="G1418" s="6" t="s">
@@ -44666,13 +44702,13 @@
         <v>207</v>
       </c>
       <c r="C1419" s="19" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D1419" s="7">
-        <v>623000</v>
+        <v>315000</v>
       </c>
       <c r="E1419" s="6">
-        <v>62300</v>
+        <v>31500</v>
       </c>
       <c r="F1419" s="6"/>
       <c r="G1419" s="6" t="s">
@@ -44693,13 +44729,13 @@
         <v>207</v>
       </c>
       <c r="C1420" s="19" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D1420" s="7">
-        <v>630000</v>
+        <v>308000</v>
       </c>
       <c r="E1420" s="6">
-        <v>63000</v>
+        <v>30800</v>
       </c>
       <c r="F1420" s="6"/>
       <c r="G1420" s="6" t="s">
@@ -44720,13 +44756,13 @@
         <v>207</v>
       </c>
       <c r="C1421" s="19" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D1421" s="7">
-        <v>728000</v>
+        <v>357000</v>
       </c>
       <c r="E1421" s="6">
-        <v>72800</v>
+        <v>35700</v>
       </c>
       <c r="F1421" s="6"/>
       <c r="G1421" s="6" t="s">
@@ -44741,19 +44777,19 @@
     </row>
     <row r="1422" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1422" s="6" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1422" s="6" t="s">
-        <v>956</v>
+        <v>207</v>
       </c>
       <c r="C1422" s="19" t="s">
-        <v>1606</v>
+        <v>162</v>
       </c>
       <c r="D1422" s="7">
-        <v>8534</v>
+        <v>448000</v>
       </c>
       <c r="E1422" s="6">
-        <v>1300</v>
+        <v>44800</v>
       </c>
       <c r="F1422" s="6"/>
       <c r="G1422" s="6" t="s">
@@ -44768,19 +44804,19 @@
     </row>
     <row r="1423" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1423" s="6" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1423" s="6" t="s">
-        <v>956</v>
+        <v>207</v>
       </c>
       <c r="C1423" s="19" t="s">
-        <v>1351</v>
+        <v>163</v>
       </c>
       <c r="D1423" s="7">
-        <v>12530</v>
+        <v>532000</v>
       </c>
       <c r="E1423" s="6">
-        <v>1900</v>
+        <v>53200</v>
       </c>
       <c r="F1423" s="6"/>
       <c r="G1423" s="6" t="s">
@@ -44795,19 +44831,19 @@
     </row>
     <row r="1424" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1424" s="6" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1424" s="6" t="s">
-        <v>956</v>
+        <v>207</v>
       </c>
       <c r="C1424" s="19" t="s">
-        <v>1607</v>
+        <v>164</v>
       </c>
       <c r="D1424" s="7">
-        <v>12530</v>
+        <v>539000</v>
       </c>
       <c r="E1424" s="6">
-        <v>1900</v>
+        <v>53900</v>
       </c>
       <c r="F1424" s="6"/>
       <c r="G1424" s="6" t="s">
@@ -44822,19 +44858,19 @@
     </row>
     <row r="1425" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1425" s="6" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1425" s="6" t="s">
-        <v>956</v>
+        <v>207</v>
       </c>
       <c r="C1425" s="19" t="s">
-        <v>1608</v>
+        <v>165</v>
       </c>
       <c r="D1425" s="7">
-        <v>15030</v>
+        <v>623000</v>
       </c>
       <c r="E1425" s="6">
-        <v>2300</v>
+        <v>62300</v>
       </c>
       <c r="F1425" s="6"/>
       <c r="G1425" s="6" t="s">
@@ -44849,19 +44885,19 @@
     </row>
     <row r="1426" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1426" s="6" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1426" s="6" t="s">
-        <v>956</v>
+        <v>207</v>
       </c>
       <c r="C1426" s="19" t="s">
-        <v>1609</v>
+        <v>166</v>
       </c>
       <c r="D1426" s="7">
-        <v>12290</v>
+        <v>630000</v>
       </c>
       <c r="E1426" s="6">
-        <v>1900</v>
+        <v>63000</v>
       </c>
       <c r="F1426" s="6"/>
       <c r="G1426" s="6" t="s">
@@ -44876,19 +44912,19 @@
     </row>
     <row r="1427" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1427" s="6" t="s">
-        <v>1262</v>
+        <v>168</v>
       </c>
       <c r="B1427" s="6" t="s">
-        <v>956</v>
+        <v>207</v>
       </c>
       <c r="C1427" s="19" t="s">
-        <v>1610</v>
+        <v>167</v>
       </c>
       <c r="D1427" s="7">
-        <v>6330</v>
+        <v>728000</v>
       </c>
       <c r="E1427" s="6">
-        <v>1000</v>
+        <v>72800</v>
       </c>
       <c r="F1427" s="6"/>
       <c r="G1427" s="6" t="s">
@@ -44909,13 +44945,13 @@
         <v>956</v>
       </c>
       <c r="C1428" s="19" t="s">
-        <v>1611</v>
+        <v>1606</v>
       </c>
       <c r="D1428" s="7">
-        <v>7530</v>
+        <v>8534</v>
       </c>
       <c r="E1428" s="6">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="F1428" s="6"/>
       <c r="G1428" s="6" t="s">
@@ -44936,13 +44972,13 @@
         <v>956</v>
       </c>
       <c r="C1429" s="19" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="D1429" s="7">
-        <v>11530</v>
+        <v>12530</v>
       </c>
       <c r="E1429" s="6">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="F1429" s="6"/>
       <c r="G1429" s="6" t="s">
@@ -44963,10 +44999,10 @@
         <v>956</v>
       </c>
       <c r="C1430" s="19" t="s">
-        <v>1350</v>
+        <v>1607</v>
       </c>
       <c r="D1430" s="7">
-        <v>12130</v>
+        <v>12530</v>
       </c>
       <c r="E1430" s="6">
         <v>1900</v>
@@ -44990,13 +45026,13 @@
         <v>956</v>
       </c>
       <c r="C1431" s="19" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
       <c r="D1431" s="7">
-        <v>5830</v>
+        <v>15030</v>
       </c>
       <c r="E1431" s="6">
-        <v>900</v>
+        <v>2300</v>
       </c>
       <c r="F1431" s="6"/>
       <c r="G1431" s="6" t="s">
@@ -45017,13 +45053,13 @@
         <v>956</v>
       </c>
       <c r="C1432" s="19" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="D1432" s="7">
-        <v>8730</v>
+        <v>12290</v>
       </c>
       <c r="E1432" s="6">
-        <v>1400</v>
+        <v>1900</v>
       </c>
       <c r="F1432" s="6"/>
       <c r="G1432" s="6" t="s">
@@ -45044,13 +45080,13 @@
         <v>956</v>
       </c>
       <c r="C1433" s="19" t="s">
-        <v>1614</v>
+        <v>1610</v>
       </c>
       <c r="D1433" s="7">
-        <v>15530</v>
+        <v>6330</v>
       </c>
       <c r="E1433" s="6">
-        <v>2400</v>
+        <v>1000</v>
       </c>
       <c r="F1433" s="6"/>
       <c r="G1433" s="6" t="s">
@@ -45071,13 +45107,13 @@
         <v>956</v>
       </c>
       <c r="C1434" s="19" t="s">
-        <v>1615</v>
+        <v>1611</v>
       </c>
       <c r="D1434" s="7">
-        <v>11530</v>
+        <v>7530</v>
       </c>
       <c r="E1434" s="6">
-        <v>1800</v>
+        <v>1200</v>
       </c>
       <c r="F1434" s="6"/>
       <c r="G1434" s="6" t="s">
@@ -45098,13 +45134,13 @@
         <v>956</v>
       </c>
       <c r="C1435" s="19" t="s">
-        <v>1616</v>
+        <v>1349</v>
       </c>
       <c r="D1435" s="7">
-        <v>13530</v>
+        <v>11530</v>
       </c>
       <c r="E1435" s="6">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="F1435" s="6"/>
       <c r="G1435" s="6" t="s">
@@ -45125,13 +45161,13 @@
         <v>956</v>
       </c>
       <c r="C1436" s="19" t="s">
-        <v>1617</v>
+        <v>1350</v>
       </c>
       <c r="D1436" s="7">
-        <v>15530</v>
+        <v>12130</v>
       </c>
       <c r="E1436" s="6">
-        <v>2400</v>
+        <v>1900</v>
       </c>
       <c r="F1436" s="6"/>
       <c r="G1436" s="6" t="s">
@@ -45152,13 +45188,13 @@
         <v>956</v>
       </c>
       <c r="C1437" s="19" t="s">
-        <v>1618</v>
+        <v>1612</v>
       </c>
       <c r="D1437" s="7">
-        <v>17530</v>
+        <v>5830</v>
       </c>
       <c r="E1437" s="6">
-        <v>2700</v>
+        <v>900</v>
       </c>
       <c r="F1437" s="6"/>
       <c r="G1437" s="6" t="s">
@@ -45179,13 +45215,13 @@
         <v>956</v>
       </c>
       <c r="C1438" s="19" t="s">
-        <v>1619</v>
+        <v>1613</v>
       </c>
       <c r="D1438" s="7">
-        <v>22030</v>
+        <v>8730</v>
       </c>
       <c r="E1438" s="6">
-        <v>3400</v>
+        <v>1400</v>
       </c>
       <c r="F1438" s="6"/>
       <c r="G1438" s="6" t="s">
@@ -45206,13 +45242,13 @@
         <v>956</v>
       </c>
       <c r="C1439" s="19" t="s">
-        <v>1620</v>
+        <v>1614</v>
       </c>
       <c r="D1439" s="7">
-        <v>6730</v>
+        <v>15530</v>
       </c>
       <c r="E1439" s="6">
-        <v>1000</v>
+        <v>2400</v>
       </c>
       <c r="F1439" s="6"/>
       <c r="G1439" s="6" t="s">
@@ -45233,13 +45269,13 @@
         <v>956</v>
       </c>
       <c r="C1440" s="19" t="s">
-        <v>1621</v>
+        <v>1615</v>
       </c>
       <c r="D1440" s="7">
-        <v>7030</v>
+        <v>11530</v>
       </c>
       <c r="E1440" s="6">
-        <v>1100</v>
+        <v>1800</v>
       </c>
       <c r="F1440" s="6"/>
       <c r="G1440" s="6" t="s">
@@ -45260,13 +45296,13 @@
         <v>956</v>
       </c>
       <c r="C1441" s="19" t="s">
-        <v>1622</v>
+        <v>1616</v>
       </c>
       <c r="D1441" s="7">
-        <v>6030</v>
+        <v>13530</v>
       </c>
       <c r="E1441" s="6">
-        <v>900</v>
+        <v>2100</v>
       </c>
       <c r="F1441" s="6"/>
       <c r="G1441" s="6" t="s">
@@ -45287,13 +45323,13 @@
         <v>956</v>
       </c>
       <c r="C1442" s="19" t="s">
-        <v>1623</v>
+        <v>1617</v>
       </c>
       <c r="D1442" s="7">
-        <v>6830</v>
+        <v>15530</v>
       </c>
       <c r="E1442" s="6">
-        <v>1100</v>
+        <v>2400</v>
       </c>
       <c r="F1442" s="6"/>
       <c r="G1442" s="6" t="s">
@@ -45314,13 +45350,13 @@
         <v>956</v>
       </c>
       <c r="C1443" s="19" t="s">
-        <v>1624</v>
+        <v>1618</v>
       </c>
       <c r="D1443" s="7">
-        <v>6930</v>
+        <v>17530</v>
       </c>
       <c r="E1443" s="6">
-        <v>1100</v>
+        <v>2700</v>
       </c>
       <c r="F1443" s="6"/>
       <c r="G1443" s="6" t="s">
@@ -45341,13 +45377,13 @@
         <v>956</v>
       </c>
       <c r="C1444" s="19" t="s">
-        <v>1352</v>
+        <v>1619</v>
       </c>
       <c r="D1444" s="7">
-        <v>14030</v>
+        <v>22030</v>
       </c>
       <c r="E1444" s="6">
-        <v>2200</v>
+        <v>3400</v>
       </c>
       <c r="F1444" s="6"/>
       <c r="G1444" s="6" t="s">
@@ -45368,13 +45404,13 @@
         <v>956</v>
       </c>
       <c r="C1445" s="19" t="s">
-        <v>1625</v>
+        <v>1620</v>
       </c>
       <c r="D1445" s="7">
-        <v>3780</v>
+        <v>6730</v>
       </c>
       <c r="E1445" s="6">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="F1445" s="6"/>
       <c r="G1445" s="6" t="s">
@@ -45395,13 +45431,13 @@
         <v>956</v>
       </c>
       <c r="C1446" s="19" t="s">
-        <v>1626</v>
+        <v>1621</v>
       </c>
       <c r="D1446" s="7">
-        <v>15530</v>
+        <v>7030</v>
       </c>
       <c r="E1446" s="6">
-        <v>2400</v>
+        <v>1100</v>
       </c>
       <c r="F1446" s="6"/>
       <c r="G1446" s="6" t="s">
@@ -45422,13 +45458,13 @@
         <v>956</v>
       </c>
       <c r="C1447" s="19" t="s">
-        <v>1627</v>
+        <v>1622</v>
       </c>
       <c r="D1447" s="7">
-        <v>11030</v>
+        <v>6030</v>
       </c>
       <c r="E1447" s="6">
-        <v>1700</v>
+        <v>900</v>
       </c>
       <c r="F1447" s="6"/>
       <c r="G1447" s="6" t="s">
@@ -45449,13 +45485,13 @@
         <v>956</v>
       </c>
       <c r="C1448" s="19" t="s">
-        <v>1628</v>
+        <v>1623</v>
       </c>
       <c r="D1448" s="7">
-        <v>8530</v>
+        <v>6830</v>
       </c>
       <c r="E1448" s="6">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="F1448" s="6"/>
       <c r="G1448" s="6" t="s">
@@ -45476,13 +45512,13 @@
         <v>956</v>
       </c>
       <c r="C1449" s="19" t="s">
-        <v>1629</v>
+        <v>1624</v>
       </c>
       <c r="D1449" s="7">
-        <v>12130</v>
+        <v>6930</v>
       </c>
       <c r="E1449" s="6">
-        <v>1900</v>
+        <v>1100</v>
       </c>
       <c r="F1449" s="6"/>
       <c r="G1449" s="6" t="s">
@@ -45503,13 +45539,13 @@
         <v>956</v>
       </c>
       <c r="C1450" s="19" t="s">
-        <v>1630</v>
+        <v>1352</v>
       </c>
       <c r="D1450" s="7">
-        <v>15030</v>
+        <v>14030</v>
       </c>
       <c r="E1450" s="6">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="F1450" s="6"/>
       <c r="G1450" s="6" t="s">
@@ -45530,13 +45566,13 @@
         <v>956</v>
       </c>
       <c r="C1451" s="19" t="s">
-        <v>1631</v>
+        <v>1625</v>
       </c>
       <c r="D1451" s="7">
-        <v>7530</v>
+        <v>3780</v>
       </c>
       <c r="E1451" s="6">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="F1451" s="6"/>
       <c r="G1451" s="6" t="s">
@@ -45557,13 +45593,13 @@
         <v>956</v>
       </c>
       <c r="C1452" s="19" t="s">
-        <v>1632</v>
+        <v>1626</v>
       </c>
       <c r="D1452" s="7">
-        <v>16530</v>
+        <v>15530</v>
       </c>
       <c r="E1452" s="6">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="F1452" s="6"/>
       <c r="G1452" s="6" t="s">
@@ -45584,13 +45620,13 @@
         <v>956</v>
       </c>
       <c r="C1453" s="19" t="s">
-        <v>1633</v>
+        <v>1627</v>
       </c>
       <c r="D1453" s="7">
-        <v>4580</v>
+        <v>11030</v>
       </c>
       <c r="E1453" s="6">
-        <v>700</v>
+        <v>1700</v>
       </c>
       <c r="F1453" s="6"/>
       <c r="G1453" s="6" t="s">
@@ -45611,13 +45647,13 @@
         <v>956</v>
       </c>
       <c r="C1454" s="19" t="s">
-        <v>1634</v>
+        <v>1628</v>
       </c>
       <c r="D1454" s="7">
-        <v>8730</v>
+        <v>8530</v>
       </c>
       <c r="E1454" s="6">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="F1454" s="6"/>
       <c r="G1454" s="6" t="s">
@@ -45635,16 +45671,16 @@
         <v>1262</v>
       </c>
       <c r="B1455" s="6" t="s">
-        <v>1263</v>
+        <v>956</v>
       </c>
       <c r="C1455" s="19" t="s">
-        <v>1635</v>
+        <v>1629</v>
       </c>
       <c r="D1455" s="7">
-        <v>59545</v>
+        <v>12130</v>
       </c>
       <c r="E1455" s="6">
-        <v>9200</v>
+        <v>1900</v>
       </c>
       <c r="F1455" s="6"/>
       <c r="G1455" s="6" t="s">
@@ -45662,16 +45698,16 @@
         <v>1262</v>
       </c>
       <c r="B1456" s="6" t="s">
-        <v>1263</v>
+        <v>956</v>
       </c>
       <c r="C1456" s="19" t="s">
-        <v>1636</v>
+        <v>1630</v>
       </c>
       <c r="D1456" s="7">
-        <v>23030</v>
+        <v>15030</v>
       </c>
       <c r="E1456" s="6">
-        <v>3600</v>
+        <v>2300</v>
       </c>
       <c r="F1456" s="6"/>
       <c r="G1456" s="6" t="s">
@@ -45689,16 +45725,16 @@
         <v>1262</v>
       </c>
       <c r="B1457" s="6" t="s">
-        <v>1263</v>
+        <v>956</v>
       </c>
       <c r="C1457" s="19" t="s">
-        <v>1637</v>
+        <v>1631</v>
       </c>
       <c r="D1457" s="7">
-        <v>32530</v>
+        <v>7530</v>
       </c>
       <c r="E1457" s="6">
-        <v>5000</v>
+        <v>1200</v>
       </c>
       <c r="F1457" s="6"/>
       <c r="G1457" s="6" t="s">
@@ -45716,16 +45752,16 @@
         <v>1262</v>
       </c>
       <c r="B1458" s="6" t="s">
-        <v>1263</v>
+        <v>956</v>
       </c>
       <c r="C1458" s="19" t="s">
-        <v>1638</v>
+        <v>1632</v>
       </c>
       <c r="D1458" s="7">
-        <v>33530</v>
+        <v>16530</v>
       </c>
       <c r="E1458" s="6">
-        <v>5200</v>
+        <v>2600</v>
       </c>
       <c r="F1458" s="6"/>
       <c r="G1458" s="6" t="s">
@@ -45743,16 +45779,16 @@
         <v>1262</v>
       </c>
       <c r="B1459" s="6" t="s">
-        <v>1263</v>
+        <v>956</v>
       </c>
       <c r="C1459" s="19" t="s">
-        <v>1257</v>
+        <v>1633</v>
       </c>
       <c r="D1459" s="7">
-        <v>27530</v>
+        <v>4580</v>
       </c>
       <c r="E1459" s="6">
-        <v>4300</v>
+        <v>700</v>
       </c>
       <c r="F1459" s="6"/>
       <c r="G1459" s="6" t="s">
@@ -45770,16 +45806,16 @@
         <v>1262</v>
       </c>
       <c r="B1460" s="6" t="s">
-        <v>1263</v>
+        <v>956</v>
       </c>
       <c r="C1460" s="19" t="s">
-        <v>1258</v>
+        <v>1634</v>
       </c>
       <c r="D1460" s="7">
-        <v>33530</v>
+        <v>8730</v>
       </c>
       <c r="E1460" s="6">
-        <v>5200</v>
+        <v>1400</v>
       </c>
       <c r="F1460" s="6"/>
       <c r="G1460" s="6" t="s">
@@ -45800,13 +45836,13 @@
         <v>1263</v>
       </c>
       <c r="C1461" s="19" t="s">
-        <v>1259</v>
+        <v>1635</v>
       </c>
       <c r="D1461" s="7">
-        <v>32530</v>
+        <v>59545</v>
       </c>
       <c r="E1461" s="6">
-        <v>5000</v>
+        <v>9200</v>
       </c>
       <c r="F1461" s="6"/>
       <c r="G1461" s="6" t="s">
@@ -45827,13 +45863,13 @@
         <v>1263</v>
       </c>
       <c r="C1462" s="19" t="s">
-        <v>1260</v>
+        <v>1636</v>
       </c>
       <c r="D1462" s="7">
-        <v>19655</v>
+        <v>23030</v>
       </c>
       <c r="E1462" s="6">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="F1462" s="6"/>
       <c r="G1462" s="6" t="s">
@@ -45854,13 +45890,13 @@
         <v>1263</v>
       </c>
       <c r="C1463" s="19" t="s">
-        <v>1261</v>
+        <v>1637</v>
       </c>
       <c r="D1463" s="7">
-        <v>22696.666666666668</v>
+        <v>32530</v>
       </c>
       <c r="E1463" s="6">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="F1463" s="6"/>
       <c r="G1463" s="6" t="s">
@@ -45878,16 +45914,16 @@
         <v>1262</v>
       </c>
       <c r="B1464" s="6" t="s">
-        <v>1668</v>
+        <v>1263</v>
       </c>
       <c r="C1464" s="19" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="D1464" s="7">
-        <v>46530</v>
+        <v>33530</v>
       </c>
       <c r="E1464" s="6">
-        <v>7200</v>
+        <v>5200</v>
       </c>
       <c r="F1464" s="6"/>
       <c r="G1464" s="6" t="s">
@@ -45905,16 +45941,16 @@
         <v>1262</v>
       </c>
       <c r="B1465" s="6" t="s">
-        <v>1668</v>
+        <v>1263</v>
       </c>
       <c r="C1465" s="19" t="s">
-        <v>1640</v>
+        <v>1257</v>
       </c>
       <c r="D1465" s="7">
-        <v>46530</v>
+        <v>27530</v>
       </c>
       <c r="E1465" s="6">
-        <v>7200</v>
+        <v>4300</v>
       </c>
       <c r="F1465" s="6"/>
       <c r="G1465" s="6" t="s">
@@ -45932,16 +45968,16 @@
         <v>1262</v>
       </c>
       <c r="B1466" s="6" t="s">
-        <v>1669</v>
+        <v>1263</v>
       </c>
       <c r="C1466" s="19" t="s">
-        <v>1641</v>
+        <v>1258</v>
       </c>
       <c r="D1466" s="7">
-        <v>18530</v>
+        <v>33530</v>
       </c>
       <c r="E1466" s="6">
-        <v>2900</v>
+        <v>5200</v>
       </c>
       <c r="F1466" s="6"/>
       <c r="G1466" s="6" t="s">
@@ -45959,16 +45995,16 @@
         <v>1262</v>
       </c>
       <c r="B1467" s="6" t="s">
-        <v>1669</v>
+        <v>1263</v>
       </c>
       <c r="C1467" s="19" t="s">
-        <v>1642</v>
+        <v>1259</v>
       </c>
       <c r="D1467" s="7">
-        <v>19030</v>
+        <v>32530</v>
       </c>
       <c r="E1467" s="6">
-        <v>2900</v>
+        <v>5000</v>
       </c>
       <c r="F1467" s="6"/>
       <c r="G1467" s="6" t="s">
@@ -45986,16 +46022,16 @@
         <v>1262</v>
       </c>
       <c r="B1468" s="6" t="s">
-        <v>1669</v>
+        <v>1263</v>
       </c>
       <c r="C1468" s="19" t="s">
-        <v>1643</v>
+        <v>1260</v>
       </c>
       <c r="D1468" s="7">
-        <v>21530</v>
+        <v>19655</v>
       </c>
       <c r="E1468" s="6">
-        <v>3300</v>
+        <v>3000</v>
       </c>
       <c r="F1468" s="6"/>
       <c r="G1468" s="6" t="s">
@@ -46013,16 +46049,16 @@
         <v>1262</v>
       </c>
       <c r="B1469" s="6" t="s">
-        <v>1669</v>
+        <v>1263</v>
       </c>
       <c r="C1469" s="19" t="s">
-        <v>1644</v>
+        <v>1261</v>
       </c>
       <c r="D1469" s="7">
-        <v>20530</v>
+        <v>22696.666666666668</v>
       </c>
       <c r="E1469" s="6">
-        <v>3200</v>
+        <v>3500</v>
       </c>
       <c r="F1469" s="6"/>
       <c r="G1469" s="6" t="s">
@@ -46040,16 +46076,16 @@
         <v>1262</v>
       </c>
       <c r="B1470" s="6" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="C1470" s="19" t="s">
-        <v>1645</v>
+        <v>1639</v>
       </c>
       <c r="D1470" s="7">
-        <v>24530</v>
+        <v>46530</v>
       </c>
       <c r="E1470" s="6">
-        <v>3800</v>
+        <v>7200</v>
       </c>
       <c r="F1470" s="6"/>
       <c r="G1470" s="6" t="s">
@@ -46067,16 +46103,16 @@
         <v>1262</v>
       </c>
       <c r="B1471" s="6" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="C1471" s="19" t="s">
-        <v>1646</v>
+        <v>1640</v>
       </c>
       <c r="D1471" s="7">
-        <v>35030</v>
+        <v>46530</v>
       </c>
       <c r="E1471" s="6">
-        <v>5400</v>
+        <v>7200</v>
       </c>
       <c r="F1471" s="6"/>
       <c r="G1471" s="6" t="s">
@@ -46096,14 +46132,14 @@
       <c r="B1472" s="6" t="s">
         <v>1669</v>
       </c>
-      <c r="C1472" s="18" t="s">
-        <v>1647</v>
-      </c>
-      <c r="D1472" s="16">
-        <v>37530</v>
-      </c>
-      <c r="E1472" s="16">
-        <v>5800</v>
+      <c r="C1472" s="19" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D1472" s="7">
+        <v>18530</v>
+      </c>
+      <c r="E1472" s="6">
+        <v>2900</v>
       </c>
       <c r="F1472" s="6"/>
       <c r="G1472" s="6" t="s">
@@ -46123,14 +46159,14 @@
       <c r="B1473" s="6" t="s">
         <v>1669</v>
       </c>
-      <c r="C1473" s="18" t="s">
-        <v>1648</v>
-      </c>
-      <c r="D1473" s="16">
-        <v>21030</v>
-      </c>
-      <c r="E1473" s="16">
-        <v>3300</v>
+      <c r="C1473" s="19" t="s">
+        <v>1642</v>
+      </c>
+      <c r="D1473" s="7">
+        <v>19030</v>
+      </c>
+      <c r="E1473" s="6">
+        <v>2900</v>
       </c>
       <c r="F1473" s="6"/>
       <c r="G1473" s="6" t="s">
@@ -46150,14 +46186,14 @@
       <c r="B1474" s="6" t="s">
         <v>1669</v>
       </c>
-      <c r="C1474" s="18" t="s">
-        <v>1649</v>
-      </c>
-      <c r="D1474" s="16">
-        <v>22530</v>
-      </c>
-      <c r="E1474" s="16">
-        <v>3500</v>
+      <c r="C1474" s="19" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D1474" s="7">
+        <v>21530</v>
+      </c>
+      <c r="E1474" s="6">
+        <v>3300</v>
       </c>
       <c r="F1474" s="6"/>
       <c r="G1474" s="6" t="s">
@@ -46177,13 +46213,13 @@
       <c r="B1475" s="6" t="s">
         <v>1669</v>
       </c>
-      <c r="C1475" s="18" t="s">
-        <v>1650</v>
-      </c>
-      <c r="D1475" s="16">
+      <c r="C1475" s="19" t="s">
+        <v>1644</v>
+      </c>
+      <c r="D1475" s="7">
         <v>20530</v>
       </c>
-      <c r="E1475" s="16">
+      <c r="E1475" s="6">
         <v>3200</v>
       </c>
       <c r="F1475" s="6"/>
@@ -46204,14 +46240,14 @@
       <c r="B1476" s="6" t="s">
         <v>1669</v>
       </c>
-      <c r="C1476" s="18" t="s">
-        <v>1651</v>
-      </c>
-      <c r="D1476" s="16">
-        <v>17030</v>
-      </c>
-      <c r="E1476" s="16">
-        <v>2600</v>
+      <c r="C1476" s="19" t="s">
+        <v>1645</v>
+      </c>
+      <c r="D1476" s="7">
+        <v>24530</v>
+      </c>
+      <c r="E1476" s="6">
+        <v>3800</v>
       </c>
       <c r="F1476" s="6"/>
       <c r="G1476" s="6" t="s">
@@ -46231,14 +46267,14 @@
       <c r="B1477" s="6" t="s">
         <v>1669</v>
       </c>
-      <c r="C1477" s="18" t="s">
-        <v>1652</v>
-      </c>
-      <c r="D1477" s="16">
-        <v>32530</v>
-      </c>
-      <c r="E1477" s="16">
-        <v>5000</v>
+      <c r="C1477" s="19" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D1477" s="7">
+        <v>35030</v>
+      </c>
+      <c r="E1477" s="6">
+        <v>5400</v>
       </c>
       <c r="F1477" s="6"/>
       <c r="G1477" s="6" t="s">
@@ -46259,13 +46295,13 @@
         <v>1669</v>
       </c>
       <c r="C1478" s="18" t="s">
-        <v>1653</v>
+        <v>1647</v>
       </c>
       <c r="D1478" s="16">
-        <v>17530</v>
+        <v>37530</v>
       </c>
       <c r="E1478" s="16">
-        <v>2700</v>
+        <v>5800</v>
       </c>
       <c r="F1478" s="6"/>
       <c r="G1478" s="6" t="s">
@@ -46283,16 +46319,16 @@
         <v>1262</v>
       </c>
       <c r="B1479" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1479" s="18" t="s">
-        <v>1654</v>
+        <v>1648</v>
       </c>
       <c r="D1479" s="16">
-        <v>3830</v>
+        <v>21030</v>
       </c>
       <c r="E1479" s="16">
-        <v>600</v>
+        <v>3300</v>
       </c>
       <c r="F1479" s="6"/>
       <c r="G1479" s="6" t="s">
@@ -46310,16 +46346,16 @@
         <v>1262</v>
       </c>
       <c r="B1480" s="6" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C1480" s="18" t="s">
-        <v>1655</v>
+        <v>1649</v>
       </c>
       <c r="D1480" s="16">
-        <v>5030</v>
+        <v>22530</v>
       </c>
       <c r="E1480" s="16">
-        <v>800</v>
+        <v>3500</v>
       </c>
       <c r="F1480" s="6"/>
       <c r="G1480" s="6" t="s">
@@ -46339,14 +46375,14 @@
       <c r="B1481" s="6" t="s">
         <v>1669</v>
       </c>
-      <c r="C1481" s="19" t="s">
-        <v>1656</v>
-      </c>
-      <c r="D1481" s="7">
-        <v>23530</v>
-      </c>
-      <c r="E1481" s="6">
-        <v>3600</v>
+      <c r="C1481" s="18" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D1481" s="16">
+        <v>20530</v>
+      </c>
+      <c r="E1481" s="16">
+        <v>3200</v>
       </c>
       <c r="F1481" s="6"/>
       <c r="G1481" s="6" t="s">
@@ -46364,16 +46400,16 @@
         <v>1262</v>
       </c>
       <c r="B1482" s="6" t="s">
-        <v>956</v>
-      </c>
-      <c r="C1482" s="19" t="s">
-        <v>1657</v>
-      </c>
-      <c r="D1482" s="7">
-        <v>32530</v>
-      </c>
-      <c r="E1482" s="6">
-        <v>4600</v>
+        <v>1669</v>
+      </c>
+      <c r="C1482" s="18" t="s">
+        <v>1651</v>
+      </c>
+      <c r="D1482" s="16">
+        <v>17030</v>
+      </c>
+      <c r="E1482" s="16">
+        <v>2600</v>
       </c>
       <c r="F1482" s="6"/>
       <c r="G1482" s="6" t="s">
@@ -46391,16 +46427,16 @@
         <v>1262</v>
       </c>
       <c r="B1483" s="6" t="s">
-        <v>956</v>
-      </c>
-      <c r="C1483" s="19" t="s">
-        <v>1658</v>
-      </c>
-      <c r="D1483" s="7">
-        <v>25030</v>
-      </c>
-      <c r="E1483" s="6">
-        <v>3500</v>
+        <v>1669</v>
+      </c>
+      <c r="C1483" s="18" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D1483" s="16">
+        <v>32530</v>
+      </c>
+      <c r="E1483" s="16">
+        <v>5000</v>
       </c>
       <c r="F1483" s="6"/>
       <c r="G1483" s="6" t="s">
@@ -46418,16 +46454,16 @@
         <v>1262</v>
       </c>
       <c r="B1484" s="6" t="s">
-        <v>956</v>
-      </c>
-      <c r="C1484" s="19" t="s">
-        <v>1659</v>
-      </c>
-      <c r="D1484" s="7">
-        <v>25830</v>
-      </c>
-      <c r="E1484" s="6">
-        <v>3600</v>
+        <v>1669</v>
+      </c>
+      <c r="C1484" s="18" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D1484" s="16">
+        <v>17530</v>
+      </c>
+      <c r="E1484" s="16">
+        <v>2700</v>
       </c>
       <c r="F1484" s="6"/>
       <c r="G1484" s="6" t="s">
@@ -46445,16 +46481,16 @@
         <v>1262</v>
       </c>
       <c r="B1485" s="6" t="s">
-        <v>956</v>
-      </c>
-      <c r="C1485" s="19" t="s">
-        <v>1660</v>
-      </c>
-      <c r="D1485" s="7">
-        <v>32530</v>
-      </c>
-      <c r="E1485" s="6">
-        <v>4600</v>
+        <v>1670</v>
+      </c>
+      <c r="C1485" s="18" t="s">
+        <v>1654</v>
+      </c>
+      <c r="D1485" s="16">
+        <v>3830</v>
+      </c>
+      <c r="E1485" s="16">
+        <v>600</v>
       </c>
       <c r="F1485" s="6"/>
       <c r="G1485" s="6" t="s">
@@ -46472,16 +46508,16 @@
         <v>1262</v>
       </c>
       <c r="B1486" s="6" t="s">
-        <v>956</v>
-      </c>
-      <c r="C1486" s="19" t="s">
-        <v>1661</v>
-      </c>
-      <c r="D1486" s="7">
-        <v>25530</v>
-      </c>
-      <c r="E1486" s="6">
-        <v>3600</v>
+        <v>1670</v>
+      </c>
+      <c r="C1486" s="18" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D1486" s="16">
+        <v>5030</v>
+      </c>
+      <c r="E1486" s="16">
+        <v>800</v>
       </c>
       <c r="F1486" s="6"/>
       <c r="G1486" s="6" t="s">
@@ -46499,13 +46535,13 @@
         <v>1262</v>
       </c>
       <c r="B1487" s="6" t="s">
-        <v>956</v>
+        <v>1669</v>
       </c>
       <c r="C1487" s="19" t="s">
-        <v>1662</v>
+        <v>1656</v>
       </c>
       <c r="D1487" s="7">
-        <v>25530</v>
+        <v>23530</v>
       </c>
       <c r="E1487" s="6">
         <v>3600</v>
@@ -46529,13 +46565,13 @@
         <v>956</v>
       </c>
       <c r="C1488" s="19" t="s">
-        <v>1663</v>
+        <v>1657</v>
       </c>
       <c r="D1488" s="7">
-        <v>25030</v>
+        <v>32530</v>
       </c>
       <c r="E1488" s="6">
-        <v>3500</v>
+        <v>4600</v>
       </c>
       <c r="F1488" s="6"/>
       <c r="G1488" s="6" t="s">
@@ -46556,13 +46592,13 @@
         <v>956</v>
       </c>
       <c r="C1489" s="19" t="s">
-        <v>1664</v>
+        <v>1658</v>
       </c>
       <c r="D1489" s="7">
-        <v>41530</v>
+        <v>25030</v>
       </c>
       <c r="E1489" s="6">
-        <v>5800</v>
+        <v>3500</v>
       </c>
       <c r="F1489" s="6"/>
       <c r="G1489" s="6" t="s">
@@ -46583,13 +46619,13 @@
         <v>956</v>
       </c>
       <c r="C1490" s="19" t="s">
-        <v>1665</v>
+        <v>1659</v>
       </c>
       <c r="D1490" s="7">
-        <v>22530</v>
+        <v>25830</v>
       </c>
       <c r="E1490" s="6">
-        <v>3200</v>
+        <v>3600</v>
       </c>
       <c r="F1490" s="6"/>
       <c r="G1490" s="6" t="s">
@@ -46610,13 +46646,13 @@
         <v>956</v>
       </c>
       <c r="C1491" s="19" t="s">
-        <v>1666</v>
+        <v>1660</v>
       </c>
       <c r="D1491" s="7">
-        <v>35030</v>
+        <v>32530</v>
       </c>
       <c r="E1491" s="6">
-        <v>4900</v>
+        <v>4600</v>
       </c>
       <c r="F1491" s="6"/>
       <c r="G1491" s="6" t="s">
@@ -46634,16 +46670,16 @@
         <v>1262</v>
       </c>
       <c r="B1492" s="6" t="s">
-        <v>398</v>
+        <v>956</v>
       </c>
       <c r="C1492" s="19" t="s">
-        <v>1667</v>
+        <v>1661</v>
       </c>
       <c r="D1492" s="7">
-        <v>18530</v>
+        <v>25530</v>
       </c>
       <c r="E1492" s="6">
-        <v>2900</v>
+        <v>3600</v>
       </c>
       <c r="F1492" s="6"/>
       <c r="G1492" s="6" t="s">
@@ -46657,164 +46693,164 @@
       </c>
     </row>
     <row r="1493" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1493" s="5" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B1493" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1493" s="22" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D1493" s="15">
-        <v>56000</v>
-      </c>
-      <c r="E1493" s="5">
-        <v>5900</v>
-      </c>
-      <c r="F1493" s="5"/>
-      <c r="G1493" s="5" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1493" s="5" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1493" s="5">
+      <c r="A1493" s="6" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B1493" s="6" t="s">
+        <v>956</v>
+      </c>
+      <c r="C1493" s="19" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D1493" s="7">
+        <v>25530</v>
+      </c>
+      <c r="E1493" s="6">
+        <v>3600</v>
+      </c>
+      <c r="F1493" s="6"/>
+      <c r="G1493" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1493" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1493" s="6">
         <v>2026</v>
       </c>
     </row>
     <row r="1494" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1494" s="5" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B1494" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1494" s="22" t="s">
-        <v>1041</v>
-      </c>
-      <c r="D1494" s="15">
-        <v>66000</v>
-      </c>
-      <c r="E1494" s="5">
-        <v>7000</v>
-      </c>
-      <c r="F1494" s="5"/>
-      <c r="G1494" s="5" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1494" s="5" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1494" s="5">
+      <c r="A1494" s="6" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B1494" s="6" t="s">
+        <v>956</v>
+      </c>
+      <c r="C1494" s="19" t="s">
+        <v>1663</v>
+      </c>
+      <c r="D1494" s="7">
+        <v>25030</v>
+      </c>
+      <c r="E1494" s="6">
+        <v>3500</v>
+      </c>
+      <c r="F1494" s="6"/>
+      <c r="G1494" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1494" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1494" s="6">
         <v>2026</v>
       </c>
     </row>
     <row r="1495" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1495" s="5" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B1495" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1495" s="22" t="s">
-        <v>1042</v>
-      </c>
-      <c r="D1495" s="15">
-        <v>85000</v>
-      </c>
-      <c r="E1495" s="5">
-        <v>9100</v>
-      </c>
-      <c r="F1495" s="5"/>
-      <c r="G1495" s="5" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1495" s="5" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1495" s="5">
+      <c r="A1495" s="6" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B1495" s="6" t="s">
+        <v>956</v>
+      </c>
+      <c r="C1495" s="19" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D1495" s="7">
+        <v>41530</v>
+      </c>
+      <c r="E1495" s="6">
+        <v>5800</v>
+      </c>
+      <c r="F1495" s="6"/>
+      <c r="G1495" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1495" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1495" s="6">
         <v>2026</v>
       </c>
     </row>
     <row r="1496" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1496" s="5" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B1496" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1496" s="22" t="s">
-        <v>1043</v>
-      </c>
-      <c r="D1496" s="15">
-        <v>109000</v>
-      </c>
-      <c r="E1496" s="5">
-        <v>10900</v>
-      </c>
-      <c r="F1496" s="5"/>
-      <c r="G1496" s="5" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1496" s="5" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1496" s="5">
+      <c r="A1496" s="6" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B1496" s="6" t="s">
+        <v>956</v>
+      </c>
+      <c r="C1496" s="19" t="s">
+        <v>1665</v>
+      </c>
+      <c r="D1496" s="7">
+        <v>22530</v>
+      </c>
+      <c r="E1496" s="6">
+        <v>3200</v>
+      </c>
+      <c r="F1496" s="6"/>
+      <c r="G1496" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1496" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1496" s="6">
         <v>2026</v>
       </c>
     </row>
     <row r="1497" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1497" s="5" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B1497" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1497" s="22" t="s">
-        <v>1044</v>
-      </c>
-      <c r="D1497" s="15">
-        <v>112000</v>
-      </c>
-      <c r="E1497" s="5">
-        <v>11900</v>
-      </c>
-      <c r="F1497" s="5"/>
-      <c r="G1497" s="5" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1497" s="5" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1497" s="5">
+      <c r="A1497" s="6" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B1497" s="6" t="s">
+        <v>956</v>
+      </c>
+      <c r="C1497" s="19" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D1497" s="7">
+        <v>35030</v>
+      </c>
+      <c r="E1497" s="6">
+        <v>4900</v>
+      </c>
+      <c r="F1497" s="6"/>
+      <c r="G1497" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1497" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1497" s="6">
         <v>2026</v>
       </c>
     </row>
     <row r="1498" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1498" s="5" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B1498" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1498" s="22" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D1498" s="15">
-        <v>140000</v>
-      </c>
-      <c r="E1498" s="5">
-        <v>14000</v>
-      </c>
-      <c r="F1498" s="5"/>
-      <c r="G1498" s="5" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1498" s="5" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1498" s="5">
+      <c r="A1498" s="6" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B1498" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="C1498" s="19" t="s">
+        <v>1667</v>
+      </c>
+      <c r="D1498" s="7">
+        <v>18530</v>
+      </c>
+      <c r="E1498" s="6">
+        <v>2900</v>
+      </c>
+      <c r="F1498" s="6"/>
+      <c r="G1498" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1498" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1498" s="6">
         <v>2026</v>
       </c>
     </row>
@@ -46826,13 +46862,13 @@
         <v>207</v>
       </c>
       <c r="C1499" s="22" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="D1499" s="15">
-        <v>154000</v>
+        <v>56000</v>
       </c>
       <c r="E1499" s="5">
-        <v>15400</v>
+        <v>5900</v>
       </c>
       <c r="F1499" s="5"/>
       <c r="G1499" s="5" t="s">
@@ -46846,164 +46882,164 @@
       </c>
     </row>
     <row r="1500" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1500" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1500" s="6" t="s">
+      <c r="A1500" s="5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B1500" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C1500" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="D1500" s="7">
-        <v>700000</v>
-      </c>
-      <c r="E1500" s="6">
-        <v>70000</v>
-      </c>
-      <c r="F1500" s="6"/>
-      <c r="G1500" s="6" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1500" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="I1500" s="6">
+      <c r="C1500" s="22" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D1500" s="15">
+        <v>66000</v>
+      </c>
+      <c r="E1500" s="5">
+        <v>7000</v>
+      </c>
+      <c r="F1500" s="5"/>
+      <c r="G1500" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1500" s="5" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1500" s="5">
         <v>2026</v>
       </c>
     </row>
     <row r="1501" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1501" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1501" s="6" t="s">
+      <c r="A1501" s="5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B1501" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C1501" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="D1501" s="7">
-        <v>490000</v>
-      </c>
-      <c r="E1501" s="6">
-        <v>49000</v>
-      </c>
-      <c r="F1501" s="6"/>
-      <c r="G1501" s="6" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1501" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="I1501" s="6">
+      <c r="C1501" s="22" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D1501" s="15">
+        <v>85000</v>
+      </c>
+      <c r="E1501" s="5">
+        <v>9100</v>
+      </c>
+      <c r="F1501" s="5"/>
+      <c r="G1501" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1501" s="5" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1501" s="5">
         <v>2026</v>
       </c>
     </row>
     <row r="1502" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1502" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1502" s="6" t="s">
+      <c r="A1502" s="5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B1502" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C1502" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="D1502" s="7">
-        <v>378000</v>
-      </c>
-      <c r="E1502" s="6">
-        <v>37800</v>
-      </c>
-      <c r="F1502" s="6"/>
-      <c r="G1502" s="6" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1502" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="I1502" s="6">
+      <c r="C1502" s="22" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D1502" s="15">
+        <v>109000</v>
+      </c>
+      <c r="E1502" s="5">
+        <v>10900</v>
+      </c>
+      <c r="F1502" s="5"/>
+      <c r="G1502" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1502" s="5" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1502" s="5">
         <v>2026</v>
       </c>
     </row>
     <row r="1503" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1503" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1503" s="6" t="s">
+      <c r="A1503" s="5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B1503" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C1503" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D1503" s="7">
-        <v>280000</v>
-      </c>
-      <c r="E1503" s="6">
-        <v>28000</v>
-      </c>
-      <c r="F1503" s="6"/>
-      <c r="G1503" s="6" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1503" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="I1503" s="6">
+      <c r="C1503" s="22" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D1503" s="15">
+        <v>112000</v>
+      </c>
+      <c r="E1503" s="5">
+        <v>11900</v>
+      </c>
+      <c r="F1503" s="5"/>
+      <c r="G1503" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1503" s="5" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1503" s="5">
         <v>2026</v>
       </c>
     </row>
     <row r="1504" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1504" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1504" s="6" t="s">
+      <c r="A1504" s="5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B1504" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C1504" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="D1504" s="7">
-        <v>252000</v>
-      </c>
-      <c r="E1504" s="6">
-        <v>25200</v>
-      </c>
-      <c r="F1504" s="6"/>
-      <c r="G1504" s="6" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1504" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="I1504" s="6">
+      <c r="C1504" s="22" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D1504" s="15">
+        <v>140000</v>
+      </c>
+      <c r="E1504" s="5">
+        <v>14000</v>
+      </c>
+      <c r="F1504" s="5"/>
+      <c r="G1504" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1504" s="5" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1504" s="5">
         <v>2026</v>
       </c>
     </row>
     <row r="1505" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1505" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1505" s="6" t="s">
+      <c r="A1505" s="5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B1505" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C1505" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="D1505" s="7">
-        <v>224000</v>
-      </c>
-      <c r="E1505" s="6">
-        <v>22400</v>
-      </c>
-      <c r="F1505" s="6"/>
-      <c r="G1505" s="6" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1505" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="I1505" s="6">
+      <c r="C1505" s="22" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D1505" s="15">
+        <v>154000</v>
+      </c>
+      <c r="E1505" s="5">
+        <v>15400</v>
+      </c>
+      <c r="F1505" s="5"/>
+      <c r="G1505" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1505" s="5" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1505" s="5">
         <v>2026</v>
       </c>
     </row>
@@ -47015,13 +47051,13 @@
         <v>207</v>
       </c>
       <c r="C1506" s="19" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D1506" s="7">
-        <v>217000</v>
+        <v>700000</v>
       </c>
       <c r="E1506" s="6">
-        <v>21700</v>
+        <v>70000</v>
       </c>
       <c r="F1506" s="6"/>
       <c r="G1506" s="6" t="s">
@@ -47042,13 +47078,13 @@
         <v>207</v>
       </c>
       <c r="C1507" s="19" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D1507" s="7">
-        <v>204000</v>
+        <v>490000</v>
       </c>
       <c r="E1507" s="6">
-        <v>20400</v>
+        <v>49000</v>
       </c>
       <c r="F1507" s="6"/>
       <c r="G1507" s="6" t="s">
@@ -47069,13 +47105,13 @@
         <v>207</v>
       </c>
       <c r="C1508" s="19" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D1508" s="7">
-        <v>189000</v>
+        <v>378000</v>
       </c>
       <c r="E1508" s="6">
-        <v>18900</v>
+        <v>37800</v>
       </c>
       <c r="F1508" s="6"/>
       <c r="G1508" s="6" t="s">
@@ -47096,13 +47132,13 @@
         <v>207</v>
       </c>
       <c r="C1509" s="19" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D1509" s="7">
-        <v>175000</v>
+        <v>280000</v>
       </c>
       <c r="E1509" s="6">
-        <v>17500</v>
+        <v>28000</v>
       </c>
       <c r="F1509" s="6"/>
       <c r="G1509" s="6" t="s">
@@ -47123,13 +47159,13 @@
         <v>207</v>
       </c>
       <c r="C1510" s="19" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D1510" s="7">
-        <v>154000</v>
+        <v>252000</v>
       </c>
       <c r="E1510" s="6">
-        <v>15400</v>
+        <v>25200</v>
       </c>
       <c r="F1510" s="6"/>
       <c r="G1510" s="6" t="s">
@@ -47150,13 +47186,13 @@
         <v>207</v>
       </c>
       <c r="C1511" s="19" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D1511" s="7">
-        <v>140000</v>
+        <v>224000</v>
       </c>
       <c r="E1511" s="6">
-        <v>14000</v>
+        <v>22400</v>
       </c>
       <c r="F1511" s="6"/>
       <c r="G1511" s="6" t="s">
@@ -47177,13 +47213,13 @@
         <v>207</v>
       </c>
       <c r="C1512" s="19" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D1512" s="7">
-        <v>133000</v>
+        <v>217000</v>
       </c>
       <c r="E1512" s="6">
-        <v>13300</v>
+        <v>21700</v>
       </c>
       <c r="F1512" s="6"/>
       <c r="G1512" s="6" t="s">
@@ -47204,13 +47240,13 @@
         <v>207</v>
       </c>
       <c r="C1513" s="19" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D1513" s="7">
-        <v>123000</v>
+        <v>204000</v>
       </c>
       <c r="E1513" s="6">
-        <v>12300</v>
+        <v>20400</v>
       </c>
       <c r="F1513" s="6"/>
       <c r="G1513" s="6" t="s">
@@ -47231,13 +47267,13 @@
         <v>207</v>
       </c>
       <c r="C1514" s="19" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D1514" s="7">
-        <v>116000</v>
+        <v>189000</v>
       </c>
       <c r="E1514" s="6">
-        <v>11600</v>
+        <v>18900</v>
       </c>
       <c r="F1514" s="6"/>
       <c r="G1514" s="6" t="s">
@@ -47258,13 +47294,13 @@
         <v>207</v>
       </c>
       <c r="C1515" s="19" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D1515" s="7">
-        <v>102000</v>
+        <v>175000</v>
       </c>
       <c r="E1515" s="6">
-        <v>10200</v>
+        <v>17500</v>
       </c>
       <c r="F1515" s="6"/>
       <c r="G1515" s="6" t="s">
@@ -47285,13 +47321,13 @@
         <v>207</v>
       </c>
       <c r="C1516" s="19" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D1516" s="7">
-        <v>97000</v>
+        <v>154000</v>
       </c>
       <c r="E1516" s="6">
-        <v>9700</v>
+        <v>15400</v>
       </c>
       <c r="F1516" s="6"/>
       <c r="G1516" s="6" t="s">
@@ -47312,13 +47348,13 @@
         <v>207</v>
       </c>
       <c r="C1517" s="19" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D1517" s="7">
-        <v>74000</v>
+        <v>140000</v>
       </c>
       <c r="E1517" s="6">
-        <v>7400</v>
+        <v>14000</v>
       </c>
       <c r="F1517" s="6"/>
       <c r="G1517" s="6" t="s">
@@ -47339,13 +47375,13 @@
         <v>207</v>
       </c>
       <c r="C1518" s="19" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D1518" s="7">
-        <v>71000</v>
+        <v>133000</v>
       </c>
       <c r="E1518" s="6">
-        <v>7100</v>
+        <v>13300</v>
       </c>
       <c r="F1518" s="6"/>
       <c r="G1518" s="6" t="s">
@@ -47366,13 +47402,13 @@
         <v>207</v>
       </c>
       <c r="C1519" s="19" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D1519" s="7">
-        <v>63000</v>
+        <v>123000</v>
       </c>
       <c r="E1519" s="6">
-        <v>6300</v>
+        <v>12300</v>
       </c>
       <c r="F1519" s="6"/>
       <c r="G1519" s="6" t="s">
@@ -47393,13 +47429,13 @@
         <v>207</v>
       </c>
       <c r="C1520" s="19" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D1520" s="7">
-        <v>56000</v>
+        <v>116000</v>
       </c>
       <c r="E1520" s="6">
-        <v>5600</v>
+        <v>11600</v>
       </c>
       <c r="F1520" s="6"/>
       <c r="G1520" s="6" t="s">
@@ -47414,19 +47450,19 @@
     </row>
     <row r="1521" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1521" s="6" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1521" s="6" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1521" s="19" t="s">
-        <v>629</v>
+        <v>199</v>
       </c>
       <c r="D1521" s="7">
-        <v>5400</v>
+        <v>102000</v>
       </c>
       <c r="E1521" s="6">
-        <v>800</v>
+        <v>10200</v>
       </c>
       <c r="F1521" s="6"/>
       <c r="G1521" s="6" t="s">
@@ -47441,19 +47477,19 @@
     </row>
     <row r="1522" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1522" s="6" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1522" s="6" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1522" s="19" t="s">
-        <v>630</v>
+        <v>200</v>
       </c>
       <c r="D1522" s="7">
-        <v>26200</v>
+        <v>97000</v>
       </c>
       <c r="E1522" s="6">
-        <v>4100</v>
+        <v>9700</v>
       </c>
       <c r="F1522" s="6"/>
       <c r="G1522" s="6" t="s">
@@ -47468,19 +47504,19 @@
     </row>
     <row r="1523" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1523" s="6" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1523" s="6" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1523" s="19" t="s">
-        <v>631</v>
+        <v>201</v>
       </c>
       <c r="D1523" s="7">
-        <v>27200</v>
+        <v>74000</v>
       </c>
       <c r="E1523" s="6">
-        <v>4200</v>
+        <v>7400</v>
       </c>
       <c r="F1523" s="6"/>
       <c r="G1523" s="6" t="s">
@@ -47495,19 +47531,19 @@
     </row>
     <row r="1524" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1524" s="6" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1524" s="6" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1524" s="19" t="s">
-        <v>632</v>
+        <v>202</v>
       </c>
       <c r="D1524" s="7">
-        <v>20700</v>
+        <v>71000</v>
       </c>
       <c r="E1524" s="6">
-        <v>3200</v>
+        <v>7100</v>
       </c>
       <c r="F1524" s="6"/>
       <c r="G1524" s="6" t="s">
@@ -47522,19 +47558,19 @@
     </row>
     <row r="1525" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1525" s="6" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1525" s="6" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1525" s="19" t="s">
-        <v>633</v>
+        <v>203</v>
       </c>
       <c r="D1525" s="7">
-        <v>9900</v>
+        <v>63000</v>
       </c>
       <c r="E1525" s="6">
-        <v>1500</v>
+        <v>6300</v>
       </c>
       <c r="F1525" s="6"/>
       <c r="G1525" s="6" t="s">
@@ -47549,19 +47585,19 @@
     </row>
     <row r="1526" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1526" s="6" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1526" s="6" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1526" s="19" t="s">
-        <v>634</v>
+        <v>204</v>
       </c>
       <c r="D1526" s="7">
-        <v>10200</v>
+        <v>56000</v>
       </c>
       <c r="E1526" s="6">
-        <v>1600</v>
+        <v>5600</v>
       </c>
       <c r="F1526" s="6"/>
       <c r="G1526" s="6" t="s">
@@ -47582,13 +47618,13 @@
         <v>447</v>
       </c>
       <c r="C1527" s="19" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="D1527" s="7">
-        <v>14300</v>
+        <v>5400</v>
       </c>
       <c r="E1527" s="6">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="F1527" s="6"/>
       <c r="G1527" s="6" t="s">
@@ -47609,13 +47645,13 @@
         <v>447</v>
       </c>
       <c r="C1528" s="19" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="D1528" s="7">
-        <v>8500</v>
+        <v>26200</v>
       </c>
       <c r="E1528" s="6">
-        <v>1300</v>
+        <v>4100</v>
       </c>
       <c r="F1528" s="6"/>
       <c r="G1528" s="6" t="s">
@@ -47636,13 +47672,13 @@
         <v>447</v>
       </c>
       <c r="C1529" s="19" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="D1529" s="7">
-        <v>9400</v>
+        <v>27200</v>
       </c>
       <c r="E1529" s="6">
-        <v>1500</v>
+        <v>4200</v>
       </c>
       <c r="F1529" s="6"/>
       <c r="G1529" s="6" t="s">
@@ -47663,13 +47699,13 @@
         <v>447</v>
       </c>
       <c r="C1530" s="19" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="D1530" s="7">
-        <v>7900</v>
+        <v>20700</v>
       </c>
       <c r="E1530" s="6">
-        <v>1200</v>
+        <v>3200</v>
       </c>
       <c r="F1530" s="6"/>
       <c r="G1530" s="6" t="s">
@@ -47690,13 +47726,13 @@
         <v>447</v>
       </c>
       <c r="C1531" s="19" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="D1531" s="7">
-        <v>36900</v>
+        <v>9900</v>
       </c>
       <c r="E1531" s="6">
-        <v>5700</v>
+        <v>1500</v>
       </c>
       <c r="F1531" s="6"/>
       <c r="G1531" s="6" t="s">
@@ -47717,13 +47753,13 @@
         <v>447</v>
       </c>
       <c r="C1532" s="19" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="D1532" s="7">
-        <v>26600</v>
+        <v>10200</v>
       </c>
       <c r="E1532" s="6">
-        <v>4100</v>
+        <v>1600</v>
       </c>
       <c r="F1532" s="6"/>
       <c r="G1532" s="6" t="s">
@@ -47744,13 +47780,13 @@
         <v>447</v>
       </c>
       <c r="C1533" s="19" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="D1533" s="7">
-        <v>40200</v>
+        <v>14300</v>
       </c>
       <c r="E1533" s="6">
-        <v>6200</v>
+        <v>2200</v>
       </c>
       <c r="F1533" s="6"/>
       <c r="G1533" s="6" t="s">
@@ -47771,10 +47807,10 @@
         <v>447</v>
       </c>
       <c r="C1534" s="19" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="D1534" s="7">
-        <v>8400</v>
+        <v>8500</v>
       </c>
       <c r="E1534" s="6">
         <v>1300</v>
@@ -47798,13 +47834,13 @@
         <v>447</v>
       </c>
       <c r="C1535" s="19" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="D1535" s="7">
-        <v>8300</v>
+        <v>9400</v>
       </c>
       <c r="E1535" s="6">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="F1535" s="6"/>
       <c r="G1535" s="6" t="s">
@@ -47825,10 +47861,10 @@
         <v>447</v>
       </c>
       <c r="C1536" s="19" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="D1536" s="7">
-        <v>8000</v>
+        <v>7900</v>
       </c>
       <c r="E1536" s="6">
         <v>1200</v>
@@ -47852,13 +47888,13 @@
         <v>447</v>
       </c>
       <c r="C1537" s="19" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="D1537" s="7">
-        <v>18300</v>
+        <v>36900</v>
       </c>
       <c r="E1537" s="6">
-        <v>2800</v>
+        <v>5700</v>
       </c>
       <c r="F1537" s="6"/>
       <c r="G1537" s="6" t="s">
@@ -47879,13 +47915,13 @@
         <v>447</v>
       </c>
       <c r="C1538" s="19" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="D1538" s="7">
-        <v>15500</v>
+        <v>26600</v>
       </c>
       <c r="E1538" s="6">
-        <v>2400</v>
+        <v>4100</v>
       </c>
       <c r="F1538" s="6"/>
       <c r="G1538" s="6" t="s">
@@ -47906,13 +47942,13 @@
         <v>447</v>
       </c>
       <c r="C1539" s="19" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="D1539" s="7">
-        <v>18300</v>
+        <v>40200</v>
       </c>
       <c r="E1539" s="6">
-        <v>2800</v>
+        <v>6200</v>
       </c>
       <c r="F1539" s="6"/>
       <c r="G1539" s="6" t="s">
@@ -47933,13 +47969,13 @@
         <v>447</v>
       </c>
       <c r="C1540" s="19" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="D1540" s="7">
-        <v>20600</v>
+        <v>8400</v>
       </c>
       <c r="E1540" s="6">
-        <v>3200</v>
+        <v>1300</v>
       </c>
       <c r="F1540" s="6"/>
       <c r="G1540" s="6" t="s">
@@ -47960,13 +47996,13 @@
         <v>447</v>
       </c>
       <c r="C1541" s="19" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="D1541" s="7">
-        <v>19391</v>
+        <v>8300</v>
       </c>
       <c r="E1541" s="6">
-        <v>3000</v>
+        <v>1300</v>
       </c>
       <c r="F1541" s="6"/>
       <c r="G1541" s="6" t="s">
@@ -47987,13 +48023,13 @@
         <v>447</v>
       </c>
       <c r="C1542" s="19" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="D1542" s="7">
-        <v>19391</v>
+        <v>8000</v>
       </c>
       <c r="E1542" s="6">
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="F1542" s="6"/>
       <c r="G1542" s="6" t="s">
@@ -48014,13 +48050,13 @@
         <v>447</v>
       </c>
       <c r="C1543" s="19" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="D1543" s="7">
-        <v>7700</v>
+        <v>18300</v>
       </c>
       <c r="E1543" s="6">
-        <v>1200</v>
+        <v>2800</v>
       </c>
       <c r="F1543" s="6"/>
       <c r="G1543" s="6" t="s">
@@ -48041,13 +48077,13 @@
         <v>447</v>
       </c>
       <c r="C1544" s="19" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="D1544" s="7">
-        <v>10300</v>
+        <v>15500</v>
       </c>
       <c r="E1544" s="6">
-        <v>1600</v>
+        <v>2400</v>
       </c>
       <c r="F1544" s="6"/>
       <c r="G1544" s="6" t="s">
@@ -48068,13 +48104,13 @@
         <v>447</v>
       </c>
       <c r="C1545" s="19" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="D1545" s="7">
-        <v>9700</v>
+        <v>18300</v>
       </c>
       <c r="E1545" s="6">
-        <v>1500</v>
+        <v>2800</v>
       </c>
       <c r="F1545" s="6"/>
       <c r="G1545" s="6" t="s">
@@ -48095,13 +48131,13 @@
         <v>447</v>
       </c>
       <c r="C1546" s="19" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="D1546" s="7">
-        <v>9068</v>
+        <v>20600</v>
       </c>
       <c r="E1546" s="6">
-        <v>1400</v>
+        <v>3200</v>
       </c>
       <c r="F1546" s="6"/>
       <c r="G1546" s="6" t="s">
@@ -48122,13 +48158,13 @@
         <v>447</v>
       </c>
       <c r="C1547" s="19" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="D1547" s="7">
-        <v>8200</v>
+        <v>19391</v>
       </c>
       <c r="E1547" s="6">
-        <v>1300</v>
+        <v>3000</v>
       </c>
       <c r="F1547" s="6"/>
       <c r="G1547" s="6" t="s">
@@ -48149,13 +48185,13 @@
         <v>447</v>
       </c>
       <c r="C1548" s="19" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="D1548" s="7">
-        <v>11400</v>
+        <v>19391</v>
       </c>
       <c r="E1548" s="6">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="F1548" s="6"/>
       <c r="G1548" s="6" t="s">
@@ -48176,13 +48212,13 @@
         <v>447</v>
       </c>
       <c r="C1549" s="19" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="D1549" s="7">
-        <v>10000</v>
+        <v>7700</v>
       </c>
       <c r="E1549" s="6">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="F1549" s="6"/>
       <c r="G1549" s="6" t="s">
@@ -48203,13 +48239,13 @@
         <v>447</v>
       </c>
       <c r="C1550" s="19" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="D1550" s="7">
-        <v>8510</v>
+        <v>10300</v>
       </c>
       <c r="E1550" s="6">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="F1550" s="6"/>
       <c r="G1550" s="6" t="s">
@@ -48230,13 +48266,13 @@
         <v>447</v>
       </c>
       <c r="C1551" s="19" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="D1551" s="7">
-        <v>8200</v>
+        <v>9700</v>
       </c>
       <c r="E1551" s="6">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="F1551" s="6"/>
       <c r="G1551" s="6" t="s">
@@ -48257,13 +48293,13 @@
         <v>447</v>
       </c>
       <c r="C1552" s="19" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="D1552" s="7">
-        <v>8000</v>
+        <v>9068</v>
       </c>
       <c r="E1552" s="6">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="F1552" s="6"/>
       <c r="G1552" s="6" t="s">
@@ -48284,13 +48320,13 @@
         <v>447</v>
       </c>
       <c r="C1553" s="19" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="D1553" s="7">
-        <v>6929</v>
+        <v>8200</v>
       </c>
       <c r="E1553" s="6">
-        <v>1100</v>
+        <v>1300</v>
       </c>
       <c r="F1553" s="6"/>
       <c r="G1553" s="6" t="s">
@@ -48311,13 +48347,13 @@
         <v>447</v>
       </c>
       <c r="C1554" s="19" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="D1554" s="7">
-        <v>16400</v>
+        <v>11400</v>
       </c>
       <c r="E1554" s="6">
-        <v>2500</v>
+        <v>1800</v>
       </c>
       <c r="F1554" s="6"/>
       <c r="G1554" s="6" t="s">
@@ -48338,13 +48374,13 @@
         <v>447</v>
       </c>
       <c r="C1555" s="19" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="D1555" s="7">
-        <v>14800</v>
+        <v>10000</v>
       </c>
       <c r="E1555" s="6">
-        <v>2300</v>
+        <v>1600</v>
       </c>
       <c r="F1555" s="6"/>
       <c r="G1555" s="6" t="s">
@@ -48365,13 +48401,13 @@
         <v>447</v>
       </c>
       <c r="C1556" s="19" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="D1556" s="7">
-        <v>14800</v>
+        <v>8510</v>
       </c>
       <c r="E1556" s="6">
-        <v>2300</v>
+        <v>1300</v>
       </c>
       <c r="F1556" s="6"/>
       <c r="G1556" s="6" t="s">
@@ -48392,13 +48428,13 @@
         <v>447</v>
       </c>
       <c r="C1557" s="19" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="D1557" s="7">
-        <v>9000</v>
+        <v>8200</v>
       </c>
       <c r="E1557" s="6">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="F1557" s="6"/>
       <c r="G1557" s="6" t="s">
@@ -48419,13 +48455,13 @@
         <v>447</v>
       </c>
       <c r="C1558" s="19" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D1558" s="7">
-        <v>34900</v>
+        <v>8000</v>
       </c>
       <c r="E1558" s="6">
-        <v>5400</v>
+        <v>1200</v>
       </c>
       <c r="F1558" s="6"/>
       <c r="G1558" s="6" t="s">
@@ -48446,13 +48482,13 @@
         <v>447</v>
       </c>
       <c r="C1559" s="19" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="D1559" s="7">
-        <v>4000</v>
+        <v>6929</v>
       </c>
       <c r="E1559" s="6">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="F1559" s="6"/>
       <c r="G1559" s="6" t="s">
@@ -48473,13 +48509,13 @@
         <v>447</v>
       </c>
       <c r="C1560" s="19" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="D1560" s="7">
-        <v>4200</v>
+        <v>16400</v>
       </c>
       <c r="E1560" s="6">
-        <v>700</v>
+        <v>2500</v>
       </c>
       <c r="F1560" s="6"/>
       <c r="G1560" s="6" t="s">
@@ -48500,13 +48536,13 @@
         <v>447</v>
       </c>
       <c r="C1561" s="19" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="D1561" s="7">
-        <v>8300</v>
+        <v>14800</v>
       </c>
       <c r="E1561" s="6">
-        <v>1300</v>
+        <v>2300</v>
       </c>
       <c r="F1561" s="6"/>
       <c r="G1561" s="6" t="s">
@@ -48527,13 +48563,13 @@
         <v>447</v>
       </c>
       <c r="C1562" s="19" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="D1562" s="7">
-        <v>7900</v>
+        <v>14800</v>
       </c>
       <c r="E1562" s="6">
-        <v>1200</v>
+        <v>2300</v>
       </c>
       <c r="F1562" s="6"/>
       <c r="G1562" s="6" t="s">
@@ -48554,13 +48590,13 @@
         <v>447</v>
       </c>
       <c r="C1563" s="19" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="D1563" s="7">
-        <v>7900</v>
+        <v>9000</v>
       </c>
       <c r="E1563" s="6">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="F1563" s="6"/>
       <c r="G1563" s="6" t="s">
@@ -48581,13 +48617,13 @@
         <v>447</v>
       </c>
       <c r="C1564" s="19" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="D1564" s="7">
-        <v>9900</v>
+        <v>34900</v>
       </c>
       <c r="E1564" s="6">
-        <v>1500</v>
+        <v>5400</v>
       </c>
       <c r="F1564" s="6"/>
       <c r="G1564" s="6" t="s">
@@ -48608,13 +48644,13 @@
         <v>447</v>
       </c>
       <c r="C1565" s="19" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="D1565" s="7">
-        <v>12600</v>
+        <v>4000</v>
       </c>
       <c r="E1565" s="6">
-        <v>2000</v>
+        <v>600</v>
       </c>
       <c r="F1565" s="6"/>
       <c r="G1565" s="6" t="s">
@@ -48635,13 +48671,13 @@
         <v>447</v>
       </c>
       <c r="C1566" s="19" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D1566" s="7">
-        <v>33200</v>
+        <v>4200</v>
       </c>
       <c r="E1566" s="6">
-        <v>5100</v>
+        <v>700</v>
       </c>
       <c r="F1566" s="6"/>
       <c r="G1566" s="6" t="s">
@@ -48662,13 +48698,13 @@
         <v>447</v>
       </c>
       <c r="C1567" s="19" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D1567" s="7">
-        <v>27600</v>
+        <v>8300</v>
       </c>
       <c r="E1567" s="6">
-        <v>4300</v>
+        <v>1300</v>
       </c>
       <c r="F1567" s="6"/>
       <c r="G1567" s="6" t="s">
@@ -48689,13 +48725,13 @@
         <v>447</v>
       </c>
       <c r="C1568" s="19" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="D1568" s="7">
-        <v>29400</v>
+        <v>7900</v>
       </c>
       <c r="E1568" s="6">
-        <v>4600</v>
+        <v>1200</v>
       </c>
       <c r="F1568" s="6"/>
       <c r="G1568" s="6" t="s">
@@ -48716,13 +48752,13 @@
         <v>447</v>
       </c>
       <c r="C1569" s="19" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="D1569" s="7">
-        <v>25800</v>
+        <v>7900</v>
       </c>
       <c r="E1569" s="6">
-        <v>4000</v>
+        <v>1200</v>
       </c>
       <c r="F1569" s="6"/>
       <c r="G1569" s="6" t="s">
@@ -48743,13 +48779,13 @@
         <v>447</v>
       </c>
       <c r="C1570" s="19" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="D1570" s="7">
-        <v>19391</v>
+        <v>9900</v>
       </c>
       <c r="E1570" s="6">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="F1570" s="6"/>
       <c r="G1570" s="6" t="s">
@@ -48770,13 +48806,13 @@
         <v>447</v>
       </c>
       <c r="C1571" s="19" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="D1571" s="7">
-        <v>19391</v>
+        <v>12600</v>
       </c>
       <c r="E1571" s="6">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="F1571" s="6"/>
       <c r="G1571" s="6" t="s">
@@ -48797,13 +48833,13 @@
         <v>447</v>
       </c>
       <c r="C1572" s="19" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="D1572" s="7">
-        <v>21100</v>
+        <v>33200</v>
       </c>
       <c r="E1572" s="6">
-        <v>3300</v>
+        <v>5100</v>
       </c>
       <c r="F1572" s="6"/>
       <c r="G1572" s="6" t="s">
@@ -48824,13 +48860,13 @@
         <v>447</v>
       </c>
       <c r="C1573" s="19" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="D1573" s="7">
-        <v>7500</v>
+        <v>27600</v>
       </c>
       <c r="E1573" s="6">
-        <v>1200</v>
+        <v>4300</v>
       </c>
       <c r="F1573" s="6"/>
       <c r="G1573" s="6" t="s">
@@ -48851,13 +48887,13 @@
         <v>447</v>
       </c>
       <c r="C1574" s="19" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="D1574" s="7">
-        <v>8500</v>
+        <v>29400</v>
       </c>
       <c r="E1574" s="6">
-        <v>1300</v>
+        <v>4600</v>
       </c>
       <c r="F1574" s="6"/>
       <c r="G1574" s="6" t="s">
@@ -48878,13 +48914,13 @@
         <v>447</v>
       </c>
       <c r="C1575" s="19" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="D1575" s="7">
-        <v>4300</v>
+        <v>25800</v>
       </c>
       <c r="E1575" s="6">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="F1575" s="6"/>
       <c r="G1575" s="6" t="s">
@@ -48905,13 +48941,13 @@
         <v>447</v>
       </c>
       <c r="C1576" s="19" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="D1576" s="7">
-        <v>8800</v>
+        <v>19391</v>
       </c>
       <c r="E1576" s="6">
-        <v>1400</v>
+        <v>3000</v>
       </c>
       <c r="F1576" s="6"/>
       <c r="G1576" s="6" t="s">
@@ -48932,13 +48968,13 @@
         <v>447</v>
       </c>
       <c r="C1577" s="19" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="D1577" s="7">
-        <v>8800</v>
+        <v>19391</v>
       </c>
       <c r="E1577" s="6">
-        <v>1400</v>
+        <v>3000</v>
       </c>
       <c r="F1577" s="6"/>
       <c r="G1577" s="6" t="s">
@@ -48959,13 +48995,13 @@
         <v>447</v>
       </c>
       <c r="C1578" s="19" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="D1578" s="7">
-        <v>7900</v>
+        <v>21100</v>
       </c>
       <c r="E1578" s="6">
-        <v>1200</v>
+        <v>3300</v>
       </c>
       <c r="F1578" s="6"/>
       <c r="G1578" s="6" t="s">
@@ -48986,13 +49022,13 @@
         <v>447</v>
       </c>
       <c r="C1579" s="19" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="D1579" s="7">
-        <v>32900</v>
+        <v>7500</v>
       </c>
       <c r="E1579" s="6">
-        <v>5100</v>
+        <v>1200</v>
       </c>
       <c r="F1579" s="6"/>
       <c r="G1579" s="6" t="s">
@@ -49013,13 +49049,13 @@
         <v>447</v>
       </c>
       <c r="C1580" s="19" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="D1580" s="7">
-        <v>7700</v>
+        <v>8500</v>
       </c>
       <c r="E1580" s="6">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="F1580" s="6"/>
       <c r="G1580" s="6" t="s">
@@ -49040,13 +49076,13 @@
         <v>447</v>
       </c>
       <c r="C1581" s="19" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="D1581" s="7">
-        <v>21300</v>
+        <v>4300</v>
       </c>
       <c r="E1581" s="6">
-        <v>3300</v>
+        <v>700</v>
       </c>
       <c r="F1581" s="6"/>
       <c r="G1581" s="6" t="s">
@@ -49067,13 +49103,13 @@
         <v>447</v>
       </c>
       <c r="C1582" s="19" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="D1582" s="7">
-        <v>16300</v>
+        <v>8800</v>
       </c>
       <c r="E1582" s="6">
-        <v>2500</v>
+        <v>1400</v>
       </c>
       <c r="F1582" s="6"/>
       <c r="G1582" s="6" t="s">
@@ -49094,13 +49130,13 @@
         <v>447</v>
       </c>
       <c r="C1583" s="19" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="D1583" s="7">
-        <v>12200</v>
+        <v>8800</v>
       </c>
       <c r="E1583" s="6">
-        <v>1900</v>
+        <v>1400</v>
       </c>
       <c r="F1583" s="6"/>
       <c r="G1583" s="6" t="s">
@@ -49121,13 +49157,13 @@
         <v>447</v>
       </c>
       <c r="C1584" s="19" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="D1584" s="7">
-        <v>9400</v>
+        <v>7900</v>
       </c>
       <c r="E1584" s="6">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="F1584" s="6"/>
       <c r="G1584" s="6" t="s">
@@ -49148,13 +49184,13 @@
         <v>447</v>
       </c>
       <c r="C1585" s="19" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="D1585" s="7">
-        <v>10300</v>
+        <v>32900</v>
       </c>
       <c r="E1585" s="6">
-        <v>1600</v>
+        <v>5100</v>
       </c>
       <c r="F1585" s="6"/>
       <c r="G1585" s="6" t="s">
@@ -49175,13 +49211,13 @@
         <v>447</v>
       </c>
       <c r="C1586" s="19" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="D1586" s="7">
-        <v>14300</v>
+        <v>7700</v>
       </c>
       <c r="E1586" s="6">
-        <v>2200</v>
+        <v>1200</v>
       </c>
       <c r="F1586" s="6"/>
       <c r="G1586" s="6" t="s">
@@ -49202,13 +49238,13 @@
         <v>447</v>
       </c>
       <c r="C1587" s="19" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="D1587" s="7">
-        <v>8510</v>
+        <v>21300</v>
       </c>
       <c r="E1587" s="6">
-        <v>1300</v>
+        <v>3300</v>
       </c>
       <c r="F1587" s="6"/>
       <c r="G1587" s="6" t="s">
@@ -49229,13 +49265,13 @@
         <v>447</v>
       </c>
       <c r="C1588" s="19" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="D1588" s="7">
-        <v>9600</v>
+        <v>16300</v>
       </c>
       <c r="E1588" s="6">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="F1588" s="6"/>
       <c r="G1588" s="6" t="s">
@@ -49256,13 +49292,13 @@
         <v>447</v>
       </c>
       <c r="C1589" s="19" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="D1589" s="7">
-        <v>9400</v>
+        <v>12200</v>
       </c>
       <c r="E1589" s="6">
-        <v>1500</v>
+        <v>1900</v>
       </c>
       <c r="F1589" s="6"/>
       <c r="G1589" s="6" t="s">
@@ -49283,13 +49319,13 @@
         <v>447</v>
       </c>
       <c r="C1590" s="19" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="D1590" s="7">
-        <v>7700</v>
+        <v>9400</v>
       </c>
       <c r="E1590" s="6">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="F1590" s="6"/>
       <c r="G1590" s="6" t="s">
@@ -49310,13 +49346,13 @@
         <v>447</v>
       </c>
       <c r="C1591" s="19" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D1591" s="7">
-        <v>5900</v>
+        <v>10300</v>
       </c>
       <c r="E1591" s="6">
-        <v>900</v>
+        <v>1600</v>
       </c>
       <c r="F1591" s="6"/>
       <c r="G1591" s="6" t="s">
@@ -49337,13 +49373,13 @@
         <v>447</v>
       </c>
       <c r="C1592" s="19" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="D1592" s="7">
-        <v>5900</v>
+        <v>14300</v>
       </c>
       <c r="E1592" s="6">
-        <v>900</v>
+        <v>2200</v>
       </c>
       <c r="F1592" s="6"/>
       <c r="G1592" s="6" t="s">
@@ -49364,13 +49400,13 @@
         <v>447</v>
       </c>
       <c r="C1593" s="19" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="D1593" s="7">
-        <v>7952</v>
+        <v>8510</v>
       </c>
       <c r="E1593" s="6">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="F1593" s="6"/>
       <c r="G1593" s="6" t="s">
@@ -49391,13 +49427,13 @@
         <v>447</v>
       </c>
       <c r="C1594" s="19" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="D1594" s="7">
-        <v>44035</v>
+        <v>9600</v>
       </c>
       <c r="E1594" s="6">
-        <v>6800</v>
+        <v>1500</v>
       </c>
       <c r="F1594" s="6"/>
       <c r="G1594" s="6" t="s">
@@ -49418,13 +49454,13 @@
         <v>447</v>
       </c>
       <c r="C1595" s="19" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="D1595" s="7">
-        <v>8045</v>
+        <v>9400</v>
       </c>
       <c r="E1595" s="6">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="F1595" s="6"/>
       <c r="G1595" s="6" t="s">
@@ -49445,13 +49481,13 @@
         <v>447</v>
       </c>
       <c r="C1596" s="19" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="D1596" s="7">
-        <v>15857</v>
+        <v>7700</v>
       </c>
       <c r="E1596" s="6">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="F1596" s="6"/>
       <c r="G1596" s="6" t="s">
@@ -49472,13 +49508,13 @@
         <v>447</v>
       </c>
       <c r="C1597" s="19" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="D1597" s="7">
-        <v>16415</v>
+        <v>5900</v>
       </c>
       <c r="E1597" s="6">
-        <v>2500</v>
+        <v>900</v>
       </c>
       <c r="F1597" s="6"/>
       <c r="G1597" s="6" t="s">
@@ -49499,13 +49535,13 @@
         <v>447</v>
       </c>
       <c r="C1598" s="19" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="D1598" s="7">
-        <v>27854</v>
+        <v>5900</v>
       </c>
       <c r="E1598" s="6">
-        <v>3900</v>
+        <v>900</v>
       </c>
       <c r="F1598" s="6"/>
       <c r="G1598" s="6" t="s">
@@ -49526,13 +49562,13 @@
         <v>447</v>
       </c>
       <c r="C1599" s="19" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="D1599" s="7">
-        <v>6929</v>
+        <v>7952</v>
       </c>
       <c r="E1599" s="6">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="F1599" s="6"/>
       <c r="G1599" s="6" t="s">
@@ -49553,13 +49589,13 @@
         <v>447</v>
       </c>
       <c r="C1600" s="19" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="D1600" s="7">
-        <v>7855</v>
+        <v>44035</v>
       </c>
       <c r="E1600" s="6">
-        <v>1100</v>
+        <v>6800</v>
       </c>
       <c r="F1600" s="6"/>
       <c r="G1600" s="6" t="s">
@@ -49580,13 +49616,13 @@
         <v>447</v>
       </c>
       <c r="C1601" s="19" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="D1601" s="7">
-        <v>21158</v>
+        <v>8045</v>
       </c>
       <c r="E1601" s="6">
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="F1601" s="6"/>
       <c r="G1601" s="6" t="s">
@@ -49607,13 +49643,13 @@
         <v>447</v>
       </c>
       <c r="C1602" s="19" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="D1602" s="7">
-        <v>19949</v>
+        <v>15857</v>
       </c>
       <c r="E1602" s="6">
-        <v>2800</v>
+        <v>2500</v>
       </c>
       <c r="F1602" s="6"/>
       <c r="G1602" s="6" t="s">
@@ -49634,13 +49670,13 @@
         <v>447</v>
       </c>
       <c r="C1603" s="19" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="D1603" s="7">
-        <v>9626</v>
+        <v>16415</v>
       </c>
       <c r="E1603" s="6">
-        <v>1300</v>
+        <v>2500</v>
       </c>
       <c r="F1603" s="6"/>
       <c r="G1603" s="6" t="s">
@@ -49661,13 +49697,13 @@
         <v>447</v>
       </c>
       <c r="C1604" s="19" t="s">
-        <v>711</v>
+        <v>675</v>
       </c>
       <c r="D1604" s="7">
-        <v>9719</v>
+        <v>27854</v>
       </c>
       <c r="E1604" s="6">
-        <v>1400</v>
+        <v>3900</v>
       </c>
       <c r="F1604" s="6"/>
       <c r="G1604" s="6" t="s">
@@ -49688,13 +49724,13 @@
         <v>447</v>
       </c>
       <c r="C1605" s="19" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="D1605" s="7">
-        <v>12974</v>
+        <v>6929</v>
       </c>
       <c r="E1605" s="6">
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="F1605" s="6"/>
       <c r="G1605" s="6" t="s">
@@ -49715,13 +49751,13 @@
         <v>447</v>
       </c>
       <c r="C1606" s="19" t="s">
-        <v>1467</v>
+        <v>707</v>
       </c>
       <c r="D1606" s="7">
-        <v>21344</v>
+        <v>7855</v>
       </c>
       <c r="E1606" s="6">
-        <v>3000</v>
+        <v>1100</v>
       </c>
       <c r="F1606" s="6"/>
       <c r="G1606" s="6" t="s">
@@ -49742,13 +49778,13 @@
         <v>447</v>
       </c>
       <c r="C1607" s="19" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="D1607" s="7">
-        <v>14276</v>
+        <v>21158</v>
       </c>
       <c r="E1607" s="6">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F1607" s="6"/>
       <c r="G1607" s="6" t="s">
@@ -49769,13 +49805,13 @@
         <v>447</v>
       </c>
       <c r="C1608" s="19" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="D1608" s="7">
-        <v>14276</v>
+        <v>19949</v>
       </c>
       <c r="E1608" s="6">
-        <v>2000</v>
+        <v>2800</v>
       </c>
       <c r="F1608" s="6"/>
       <c r="G1608" s="6" t="s">
@@ -49796,13 +49832,13 @@
         <v>447</v>
       </c>
       <c r="C1609" s="19" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="D1609" s="7">
-        <v>15950</v>
+        <v>9626</v>
       </c>
       <c r="E1609" s="6">
-        <v>2200</v>
+        <v>1300</v>
       </c>
       <c r="F1609" s="6"/>
       <c r="G1609" s="6" t="s">
@@ -49823,13 +49859,13 @@
         <v>447</v>
       </c>
       <c r="C1610" s="19" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="D1610" s="7">
-        <v>28970</v>
+        <v>9719</v>
       </c>
       <c r="E1610" s="6">
-        <v>4100</v>
+        <v>1400</v>
       </c>
       <c r="F1610" s="6"/>
       <c r="G1610" s="6" t="s">
@@ -49844,19 +49880,19 @@
     </row>
     <row r="1611" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1611" s="6" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1611" s="6" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1611" s="19" t="s">
-        <v>1061</v>
+        <v>712</v>
       </c>
       <c r="D1611" s="7">
-        <v>41000</v>
+        <v>12974</v>
       </c>
       <c r="E1611" s="6">
-        <v>4100</v>
+        <v>1800</v>
       </c>
       <c r="F1611" s="6"/>
       <c r="G1611" s="6" t="s">
@@ -49871,19 +49907,19 @@
     </row>
     <row r="1612" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1612" s="6" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1612" s="6" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1612" s="19" t="s">
-        <v>1062</v>
+        <v>1467</v>
       </c>
       <c r="D1612" s="7">
-        <v>55000</v>
+        <v>21344</v>
       </c>
       <c r="E1612" s="6">
-        <v>5500</v>
+        <v>3000</v>
       </c>
       <c r="F1612" s="6"/>
       <c r="G1612" s="6" t="s">
@@ -49898,19 +49934,19 @@
     </row>
     <row r="1613" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1613" s="6" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1613" s="6" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1613" s="19" t="s">
-        <v>1063</v>
+        <v>713</v>
       </c>
       <c r="D1613" s="7">
-        <v>45000</v>
+        <v>14276</v>
       </c>
       <c r="E1613" s="6">
-        <v>4500</v>
+        <v>2000</v>
       </c>
       <c r="F1613" s="6"/>
       <c r="G1613" s="6" t="s">
@@ -49925,19 +49961,19 @@
     </row>
     <row r="1614" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1614" s="6" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1614" s="6" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1614" s="19" t="s">
-        <v>1064</v>
+        <v>714</v>
       </c>
       <c r="D1614" s="7">
-        <v>63000</v>
+        <v>14276</v>
       </c>
       <c r="E1614" s="6">
-        <v>6300</v>
+        <v>2000</v>
       </c>
       <c r="F1614" s="6"/>
       <c r="G1614" s="6" t="s">
@@ -49952,19 +49988,19 @@
     </row>
     <row r="1615" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1615" s="6" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1615" s="6" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1615" s="19" t="s">
-        <v>1065</v>
+        <v>715</v>
       </c>
       <c r="D1615" s="7">
-        <v>60000</v>
+        <v>15950</v>
       </c>
       <c r="E1615" s="6">
-        <v>6000</v>
+        <v>2200</v>
       </c>
       <c r="F1615" s="6"/>
       <c r="G1615" s="6" t="s">
@@ -49979,19 +50015,19 @@
     </row>
     <row r="1616" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1616" s="6" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1616" s="6" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1616" s="19" t="s">
-        <v>1066</v>
+        <v>716</v>
       </c>
       <c r="D1616" s="7">
-        <v>42000</v>
+        <v>28970</v>
       </c>
       <c r="E1616" s="6">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="F1616" s="6"/>
       <c r="G1616" s="6" t="s">
@@ -50012,13 +50048,13 @@
         <v>207</v>
       </c>
       <c r="C1617" s="19" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="D1617" s="7">
-        <v>64000</v>
+        <v>41000</v>
       </c>
       <c r="E1617" s="6">
-        <v>6400</v>
+        <v>4100</v>
       </c>
       <c r="F1617" s="6"/>
       <c r="G1617" s="6" t="s">
@@ -50039,13 +50075,13 @@
         <v>207</v>
       </c>
       <c r="C1618" s="19" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="D1618" s="7">
-        <v>78000</v>
+        <v>55000</v>
       </c>
       <c r="E1618" s="6">
-        <v>7800</v>
+        <v>5500</v>
       </c>
       <c r="F1618" s="6"/>
       <c r="G1618" s="6" t="s">
@@ -50066,13 +50102,13 @@
         <v>207</v>
       </c>
       <c r="C1619" s="19" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
       <c r="D1619" s="7">
-        <v>83000</v>
+        <v>45000</v>
       </c>
       <c r="E1619" s="6">
-        <v>8300</v>
+        <v>4500</v>
       </c>
       <c r="F1619" s="6"/>
       <c r="G1619" s="6" t="s">
@@ -50093,13 +50129,13 @@
         <v>207</v>
       </c>
       <c r="C1620" s="19" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
       <c r="D1620" s="7">
-        <v>106000</v>
+        <v>63000</v>
       </c>
       <c r="E1620" s="6">
-        <v>10600</v>
+        <v>6300</v>
       </c>
       <c r="F1620" s="6"/>
       <c r="G1620" s="6" t="s">
@@ -50120,13 +50156,13 @@
         <v>207</v>
       </c>
       <c r="C1621" s="19" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="D1621" s="7">
-        <v>81000</v>
+        <v>60000</v>
       </c>
       <c r="E1621" s="6">
-        <v>8100</v>
+        <v>6000</v>
       </c>
       <c r="F1621" s="6"/>
       <c r="G1621" s="6" t="s">
@@ -50147,13 +50183,13 @@
         <v>207</v>
       </c>
       <c r="C1622" s="19" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="D1622" s="7">
-        <v>84000</v>
+        <v>42000</v>
       </c>
       <c r="E1622" s="6">
-        <v>8400</v>
+        <v>4200</v>
       </c>
       <c r="F1622" s="6"/>
       <c r="G1622" s="6" t="s">
@@ -50174,13 +50210,13 @@
         <v>207</v>
       </c>
       <c r="C1623" s="19" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="D1623" s="7">
-        <v>120000</v>
+        <v>64000</v>
       </c>
       <c r="E1623" s="6">
-        <v>12000</v>
+        <v>6400</v>
       </c>
       <c r="F1623" s="6"/>
       <c r="G1623" s="6" t="s">
@@ -50201,13 +50237,13 @@
         <v>207</v>
       </c>
       <c r="C1624" s="19" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="D1624" s="7">
-        <v>113000</v>
+        <v>78000</v>
       </c>
       <c r="E1624" s="6">
-        <v>11300</v>
+        <v>7800</v>
       </c>
       <c r="F1624" s="6"/>
       <c r="G1624" s="6" t="s">
@@ -50228,13 +50264,13 @@
         <v>207</v>
       </c>
       <c r="C1625" s="19" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="D1625" s="7">
-        <v>141000</v>
+        <v>83000</v>
       </c>
       <c r="E1625" s="6">
-        <v>14100</v>
+        <v>8300</v>
       </c>
       <c r="F1625" s="6"/>
       <c r="G1625" s="6" t="s">
@@ -50255,13 +50291,13 @@
         <v>207</v>
       </c>
       <c r="C1626" s="19" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="D1626" s="7">
-        <v>141000</v>
+        <v>106000</v>
       </c>
       <c r="E1626" s="6">
-        <v>14100</v>
+        <v>10600</v>
       </c>
       <c r="F1626" s="6"/>
       <c r="G1626" s="6" t="s">
@@ -50282,13 +50318,13 @@
         <v>207</v>
       </c>
       <c r="C1627" s="19" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="D1627" s="7">
-        <v>169000</v>
+        <v>81000</v>
       </c>
       <c r="E1627" s="6">
-        <v>16900</v>
+        <v>8100</v>
       </c>
       <c r="F1627" s="6"/>
       <c r="G1627" s="6" t="s">
@@ -50306,16 +50342,16 @@
         <v>1080</v>
       </c>
       <c r="B1628" s="6" t="s">
-        <v>401</v>
+        <v>207</v>
       </c>
       <c r="C1628" s="19" t="s">
-        <v>1249</v>
+        <v>1072</v>
       </c>
       <c r="D1628" s="7">
-        <v>47240</v>
+        <v>84000</v>
       </c>
       <c r="E1628" s="6">
-        <v>6400</v>
+        <v>8400</v>
       </c>
       <c r="F1628" s="6"/>
       <c r="G1628" s="6" t="s">
@@ -50333,16 +50369,16 @@
         <v>1080</v>
       </c>
       <c r="B1629" s="6" t="s">
-        <v>401</v>
+        <v>207</v>
       </c>
       <c r="C1629" s="19" t="s">
-        <v>1250</v>
+        <v>1073</v>
       </c>
       <c r="D1629" s="7">
-        <v>71600</v>
+        <v>120000</v>
       </c>
       <c r="E1629" s="6">
-        <v>9700</v>
+        <v>12000</v>
       </c>
       <c r="F1629" s="6"/>
       <c r="G1629" s="6" t="s">
@@ -50360,16 +50396,16 @@
         <v>1080</v>
       </c>
       <c r="B1630" s="6" t="s">
-        <v>401</v>
+        <v>207</v>
       </c>
       <c r="C1630" s="19" t="s">
-        <v>1251</v>
+        <v>1074</v>
       </c>
       <c r="D1630" s="7">
-        <v>87720</v>
+        <v>113000</v>
       </c>
       <c r="E1630" s="6">
-        <v>11800</v>
+        <v>11300</v>
       </c>
       <c r="F1630" s="6"/>
       <c r="G1630" s="6" t="s">
@@ -50387,16 +50423,16 @@
         <v>1080</v>
       </c>
       <c r="B1631" s="6" t="s">
-        <v>401</v>
+        <v>207</v>
       </c>
       <c r="C1631" s="19" t="s">
-        <v>1252</v>
+        <v>1075</v>
       </c>
       <c r="D1631" s="7">
-        <v>124360</v>
+        <v>141000</v>
       </c>
       <c r="E1631" s="6">
-        <v>16800</v>
+        <v>14100</v>
       </c>
       <c r="F1631" s="6"/>
       <c r="G1631" s="6" t="s">
@@ -50414,16 +50450,16 @@
         <v>1080</v>
       </c>
       <c r="B1632" s="6" t="s">
-        <v>401</v>
+        <v>207</v>
       </c>
       <c r="C1632" s="19" t="s">
-        <v>1253</v>
+        <v>1076</v>
       </c>
       <c r="D1632" s="7">
-        <v>178440</v>
+        <v>141000</v>
       </c>
       <c r="E1632" s="6">
-        <v>24100</v>
+        <v>14100</v>
       </c>
       <c r="F1632" s="6"/>
       <c r="G1632" s="6" t="s">
@@ -50441,16 +50477,16 @@
         <v>1080</v>
       </c>
       <c r="B1633" s="6" t="s">
-        <v>401</v>
+        <v>207</v>
       </c>
       <c r="C1633" s="19" t="s">
-        <v>1254</v>
+        <v>1077</v>
       </c>
       <c r="D1633" s="7">
-        <v>258920</v>
+        <v>169000</v>
       </c>
       <c r="E1633" s="6">
-        <v>35000</v>
+        <v>16900</v>
       </c>
       <c r="F1633" s="6"/>
       <c r="G1633" s="6" t="s">
@@ -50471,13 +50507,13 @@
         <v>401</v>
       </c>
       <c r="C1634" s="19" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
       <c r="D1634" s="7">
-        <v>236130</v>
+        <v>47240</v>
       </c>
       <c r="E1634" s="6">
-        <v>31900</v>
+        <v>6400</v>
       </c>
       <c r="F1634" s="6"/>
       <c r="G1634" s="6" t="s">
@@ -50498,13 +50534,13 @@
         <v>401</v>
       </c>
       <c r="C1635" s="19" t="s">
-        <v>1256</v>
+        <v>1250</v>
       </c>
       <c r="D1635" s="7">
-        <v>329950</v>
+        <v>71600</v>
       </c>
       <c r="E1635" s="6">
-        <v>44500</v>
+        <v>9700</v>
       </c>
       <c r="F1635" s="6"/>
       <c r="G1635" s="6" t="s">
@@ -50519,27 +50555,26 @@
     </row>
     <row r="1636" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1636" s="6" t="s">
-        <v>1438</v>
+        <v>1080</v>
       </c>
       <c r="B1636" s="6" t="s">
-        <v>1442</v>
+        <v>401</v>
       </c>
       <c r="C1636" s="19" t="s">
-        <v>1680</v>
+        <v>1251</v>
       </c>
       <c r="D1636" s="7">
-        <f>E1636*10</f>
-        <v>256000</v>
+        <v>87720</v>
       </c>
       <c r="E1636" s="6">
-        <v>25600</v>
+        <v>11800</v>
       </c>
       <c r="F1636" s="6"/>
       <c r="G1636" s="6" t="s">
-        <v>1690</v>
+        <v>1459</v>
       </c>
       <c r="H1636" s="6" t="s">
-        <v>1455</v>
+        <v>206</v>
       </c>
       <c r="I1636" s="6">
         <v>2026</v>
@@ -50547,27 +50582,26 @@
     </row>
     <row r="1637" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1637" s="6" t="s">
-        <v>1438</v>
+        <v>1080</v>
       </c>
       <c r="B1637" s="6" t="s">
-        <v>1442</v>
+        <v>401</v>
       </c>
       <c r="C1637" s="19" t="s">
-        <v>1681</v>
+        <v>1252</v>
       </c>
       <c r="D1637" s="7">
-        <f t="shared" ref="D1637:D1646" si="0">E1637*10</f>
-        <v>324000</v>
+        <v>124360</v>
       </c>
       <c r="E1637" s="6">
-        <v>32400</v>
+        <v>16800</v>
       </c>
       <c r="F1637" s="6"/>
       <c r="G1637" s="6" t="s">
-        <v>1691</v>
+        <v>1459</v>
       </c>
       <c r="H1637" s="6" t="s">
-        <v>1455</v>
+        <v>206</v>
       </c>
       <c r="I1637" s="6">
         <v>2026</v>
@@ -50575,27 +50609,26 @@
     </row>
     <row r="1638" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1638" s="6" t="s">
-        <v>1438</v>
+        <v>1080</v>
       </c>
       <c r="B1638" s="6" t="s">
-        <v>1442</v>
+        <v>401</v>
       </c>
       <c r="C1638" s="19" t="s">
-        <v>1682</v>
+        <v>1253</v>
       </c>
       <c r="D1638" s="7">
-        <f t="shared" si="0"/>
-        <v>404000</v>
+        <v>178440</v>
       </c>
       <c r="E1638" s="6">
-        <v>40400</v>
+        <v>24100</v>
       </c>
       <c r="F1638" s="6"/>
       <c r="G1638" s="6" t="s">
-        <v>1692</v>
+        <v>1459</v>
       </c>
       <c r="H1638" s="6" t="s">
-        <v>1455</v>
+        <v>206</v>
       </c>
       <c r="I1638" s="6">
         <v>2026</v>
@@ -50603,27 +50636,26 @@
     </row>
     <row r="1639" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1639" s="6" t="s">
-        <v>1438</v>
+        <v>1080</v>
       </c>
       <c r="B1639" s="6" t="s">
-        <v>1442</v>
+        <v>401</v>
       </c>
       <c r="C1639" s="19" t="s">
-        <v>1683</v>
+        <v>1254</v>
       </c>
       <c r="D1639" s="7">
-        <f t="shared" si="0"/>
-        <v>297000</v>
+        <v>258920</v>
       </c>
       <c r="E1639" s="6">
-        <v>29700</v>
+        <v>35000</v>
       </c>
       <c r="F1639" s="6"/>
       <c r="G1639" s="6" t="s">
-        <v>1693</v>
+        <v>1459</v>
       </c>
       <c r="H1639" s="6" t="s">
-        <v>1455</v>
+        <v>206</v>
       </c>
       <c r="I1639" s="6">
         <v>2026</v>
@@ -50631,27 +50663,26 @@
     </row>
     <row r="1640" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1640" s="6" t="s">
-        <v>1438</v>
+        <v>1080</v>
       </c>
       <c r="B1640" s="6" t="s">
-        <v>1442</v>
+        <v>401</v>
       </c>
       <c r="C1640" s="19" t="s">
-        <v>1684</v>
+        <v>1255</v>
       </c>
       <c r="D1640" s="7">
-        <f t="shared" si="0"/>
-        <v>310000</v>
+        <v>236130</v>
       </c>
       <c r="E1640" s="6">
-        <v>31000</v>
+        <v>31900</v>
       </c>
       <c r="F1640" s="6"/>
       <c r="G1640" s="6" t="s">
-        <v>1694</v>
+        <v>1459</v>
       </c>
       <c r="H1640" s="6" t="s">
-        <v>1455</v>
+        <v>206</v>
       </c>
       <c r="I1640" s="6">
         <v>2026</v>
@@ -50659,27 +50690,26 @@
     </row>
     <row r="1641" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1641" s="6" t="s">
-        <v>1438</v>
+        <v>1080</v>
       </c>
       <c r="B1641" s="6" t="s">
-        <v>1442</v>
+        <v>401</v>
       </c>
       <c r="C1641" s="19" t="s">
-        <v>1685</v>
+        <v>1256</v>
       </c>
       <c r="D1641" s="7">
-        <f t="shared" si="0"/>
-        <v>337000</v>
+        <v>329950</v>
       </c>
       <c r="E1641" s="6">
-        <v>33700</v>
+        <v>44500</v>
       </c>
       <c r="F1641" s="6"/>
       <c r="G1641" s="6" t="s">
-        <v>1695</v>
+        <v>1459</v>
       </c>
       <c r="H1641" s="6" t="s">
-        <v>1455</v>
+        <v>206</v>
       </c>
       <c r="I1641" s="6">
         <v>2026</v>
@@ -50693,18 +50723,18 @@
         <v>1442</v>
       </c>
       <c r="C1642" s="19" t="s">
-        <v>1686</v>
+        <v>1680</v>
       </c>
       <c r="D1642" s="7">
-        <f t="shared" si="0"/>
-        <v>351000</v>
+        <f>E1642*10</f>
+        <v>256000</v>
       </c>
       <c r="E1642" s="6">
-        <v>35100</v>
+        <v>25600</v>
       </c>
       <c r="F1642" s="6"/>
       <c r="G1642" s="6" t="s">
-        <v>1695</v>
+        <v>1690</v>
       </c>
       <c r="H1642" s="6" t="s">
         <v>1455</v>
@@ -50721,18 +50751,18 @@
         <v>1442</v>
       </c>
       <c r="C1643" s="19" t="s">
-        <v>1687</v>
+        <v>1681</v>
       </c>
       <c r="D1643" s="7">
-        <f t="shared" si="0"/>
-        <v>378000</v>
+        <f t="shared" ref="D1643:D1652" si="0">E1643*10</f>
+        <v>324000</v>
       </c>
       <c r="E1643" s="6">
-        <v>37800</v>
+        <v>32400</v>
       </c>
       <c r="F1643" s="6"/>
       <c r="G1643" s="6" t="s">
-        <v>1696</v>
+        <v>1691</v>
       </c>
       <c r="H1643" s="6" t="s">
         <v>1455</v>
@@ -50749,18 +50779,18 @@
         <v>1442</v>
       </c>
       <c r="C1644" s="19" t="s">
-        <v>1688</v>
+        <v>1682</v>
       </c>
       <c r="D1644" s="7">
         <f t="shared" si="0"/>
-        <v>526000</v>
+        <v>404000</v>
       </c>
       <c r="E1644" s="6">
-        <v>52600</v>
+        <v>40400</v>
       </c>
       <c r="F1644" s="6"/>
       <c r="G1644" s="6" t="s">
-        <v>1697</v>
+        <v>1692</v>
       </c>
       <c r="H1644" s="6" t="s">
         <v>1455</v>
@@ -50777,18 +50807,18 @@
         <v>1442</v>
       </c>
       <c r="C1645" s="19" t="s">
-        <v>1689</v>
+        <v>1683</v>
       </c>
       <c r="D1645" s="7">
         <f t="shared" si="0"/>
-        <v>742000</v>
+        <v>297000</v>
       </c>
       <c r="E1645" s="6">
-        <v>74200</v>
+        <v>29700</v>
       </c>
       <c r="F1645" s="6"/>
       <c r="G1645" s="6" t="s">
-        <v>1698</v>
+        <v>1693</v>
       </c>
       <c r="H1645" s="6" t="s">
         <v>1455</v>
@@ -50799,24 +50829,24 @@
     </row>
     <row r="1646" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1646" s="6" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B1646" s="6" t="s">
         <v>1442</v>
       </c>
       <c r="C1646" s="19" t="s">
-        <v>1440</v>
+        <v>1684</v>
       </c>
       <c r="D1646" s="7">
         <f t="shared" si="0"/>
-        <v>567000</v>
+        <v>310000</v>
       </c>
       <c r="E1646" s="6">
-        <v>56700</v>
+        <v>31000</v>
       </c>
       <c r="F1646" s="6"/>
       <c r="G1646" s="6" t="s">
-        <v>1459</v>
+        <v>1694</v>
       </c>
       <c r="H1646" s="6" t="s">
         <v>1455</v>
@@ -50827,23 +50857,24 @@
     </row>
     <row r="1647" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1647" s="6" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="B1647" s="6" t="s">
         <v>1442</v>
       </c>
       <c r="C1647" s="19" t="s">
-        <v>1443</v>
+        <v>1685</v>
       </c>
       <c r="D1647" s="7">
-        <v>250000</v>
+        <f t="shared" si="0"/>
+        <v>337000</v>
       </c>
       <c r="E1647" s="6">
-        <v>25000</v>
+        <v>33700</v>
       </c>
       <c r="F1647" s="6"/>
       <c r="G1647" s="6" t="s">
-        <v>1459</v>
+        <v>1695</v>
       </c>
       <c r="H1647" s="6" t="s">
         <v>1455</v>
@@ -50854,23 +50885,24 @@
     </row>
     <row r="1648" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1648" s="6" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="B1648" s="6" t="s">
         <v>1442</v>
       </c>
       <c r="C1648" s="19" t="s">
-        <v>1444</v>
+        <v>1686</v>
       </c>
       <c r="D1648" s="7">
-        <v>236000</v>
+        <f t="shared" si="0"/>
+        <v>351000</v>
       </c>
       <c r="E1648" s="6">
-        <v>23600</v>
+        <v>35100</v>
       </c>
       <c r="F1648" s="6"/>
       <c r="G1648" s="6" t="s">
-        <v>1459</v>
+        <v>1695</v>
       </c>
       <c r="H1648" s="6" t="s">
         <v>1455</v>
@@ -50881,23 +50913,24 @@
     </row>
     <row r="1649" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1649" s="6" t="s">
-        <v>1445</v>
+        <v>1438</v>
       </c>
       <c r="B1649" s="6" t="s">
         <v>1442</v>
       </c>
       <c r="C1649" s="19" t="s">
-        <v>1446</v>
+        <v>1687</v>
       </c>
       <c r="D1649" s="7">
-        <v>312000</v>
+        <f t="shared" si="0"/>
+        <v>378000</v>
       </c>
       <c r="E1649" s="6">
-        <v>31200</v>
+        <v>37800</v>
       </c>
       <c r="F1649" s="6"/>
       <c r="G1649" s="6" t="s">
-        <v>1459</v>
+        <v>1696</v>
       </c>
       <c r="H1649" s="6" t="s">
         <v>1455</v>
@@ -50908,23 +50941,24 @@
     </row>
     <row r="1650" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1650" s="6" t="s">
-        <v>1445</v>
+        <v>1438</v>
       </c>
       <c r="B1650" s="6" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="C1650" s="19" t="s">
-        <v>1448</v>
+        <v>1688</v>
       </c>
       <c r="D1650" s="7">
-        <v>156000</v>
+        <f t="shared" si="0"/>
+        <v>526000</v>
       </c>
       <c r="E1650" s="6">
-        <v>15600</v>
+        <v>52600</v>
       </c>
       <c r="F1650" s="6"/>
       <c r="G1650" s="6" t="s">
-        <v>1459</v>
+        <v>1697</v>
       </c>
       <c r="H1650" s="6" t="s">
         <v>1455</v>
@@ -50935,23 +50969,24 @@
     </row>
     <row r="1651" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1651" s="6" t="s">
-        <v>1449</v>
+        <v>1438</v>
       </c>
       <c r="B1651" s="6" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="C1651" s="19" t="s">
-        <v>1450</v>
+        <v>1689</v>
       </c>
       <c r="D1651" s="7">
-        <v>153000</v>
+        <f t="shared" si="0"/>
+        <v>742000</v>
       </c>
       <c r="E1651" s="6">
-        <v>15300</v>
+        <v>74200</v>
       </c>
       <c r="F1651" s="6"/>
       <c r="G1651" s="6" t="s">
-        <v>1459</v>
+        <v>1698</v>
       </c>
       <c r="H1651" s="6" t="s">
         <v>1455</v>
@@ -50962,19 +50997,20 @@
     </row>
     <row r="1652" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1652" s="6" t="s">
-        <v>1451</v>
+        <v>1439</v>
       </c>
       <c r="B1652" s="6" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="C1652" s="19" t="s">
-        <v>1452</v>
+        <v>1440</v>
       </c>
       <c r="D1652" s="7">
-        <v>153000</v>
+        <f t="shared" si="0"/>
+        <v>567000</v>
       </c>
       <c r="E1652" s="6">
-        <v>15300</v>
+        <v>56700</v>
       </c>
       <c r="F1652" s="6"/>
       <c r="G1652" s="6" t="s">
@@ -50989,19 +51025,19 @@
     </row>
     <row r="1653" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1653" s="6" t="s">
-        <v>1453</v>
+        <v>1441</v>
       </c>
       <c r="B1653" s="6" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="C1653" s="19" t="s">
-        <v>1454</v>
+        <v>1443</v>
       </c>
       <c r="D1653" s="7">
-        <v>153000</v>
+        <v>250000</v>
       </c>
       <c r="E1653" s="6">
-        <v>15300</v>
+        <v>25000</v>
       </c>
       <c r="F1653" s="6"/>
       <c r="G1653" s="6" t="s">
@@ -51014,9 +51050,171 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="1654" spans="1:9" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="1654" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1654" s="6" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B1654" s="6" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C1654" s="19" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D1654" s="7">
+        <v>236000</v>
+      </c>
+      <c r="E1654" s="6">
+        <v>23600</v>
+      </c>
+      <c r="F1654" s="6"/>
+      <c r="G1654" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1654" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1654" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1655" s="6" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B1655" s="6" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C1655" s="19" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D1655" s="7">
+        <v>312000</v>
+      </c>
+      <c r="E1655" s="6">
+        <v>31200</v>
+      </c>
+      <c r="F1655" s="6"/>
+      <c r="G1655" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1655" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1655" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1656" s="6" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B1656" s="6" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C1656" s="19" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D1656" s="7">
+        <v>156000</v>
+      </c>
+      <c r="E1656" s="6">
+        <v>15600</v>
+      </c>
+      <c r="F1656" s="6"/>
+      <c r="G1656" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1656" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1656" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1657" s="6" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B1657" s="6" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C1657" s="19" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D1657" s="7">
+        <v>153000</v>
+      </c>
+      <c r="E1657" s="6">
+        <v>15300</v>
+      </c>
+      <c r="F1657" s="6"/>
+      <c r="G1657" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1657" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1657" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1658" s="6" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B1658" s="6" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C1658" s="19" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D1658" s="7">
+        <v>153000</v>
+      </c>
+      <c r="E1658" s="6">
+        <v>15300</v>
+      </c>
+      <c r="F1658" s="6"/>
+      <c r="G1658" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1658" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1658" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1659" s="6" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B1659" s="6" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C1659" s="19" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1659" s="7">
+        <v>153000</v>
+      </c>
+      <c r="E1659" s="6">
+        <v>15300</v>
+      </c>
+      <c r="F1659" s="6"/>
+      <c r="G1659" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1659" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1659" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:9" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:I1653" xr:uid="{B6FE0007-86B3-4D5F-9CBC-37B22BC3E091}"/>
+  <autoFilter ref="A1:I1659" xr:uid="{B6FE0007-86B3-4D5F-9CBC-37B22BC3E091}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/rates.xlsx
+++ b/rates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS COM\Dropbox\Rates Portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCBC1E3-95B7-4379-9C14-52A2672FF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FE7038-061E-4B82-AA39-86EC9AAE0E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12307,13 +12307,13 @@
         <v>1494</v>
       </c>
       <c r="D225" s="6">
-        <v>50280</v>
+        <v>48756</v>
       </c>
       <c r="E225" s="6">
-        <v>7000</v>
+        <v>6800</v>
       </c>
       <c r="F225" s="6">
-        <v>53000</v>
+        <v>52000</v>
       </c>
       <c r="G225" s="5" t="s">
         <v>1459</v>
@@ -12336,13 +12336,13 @@
         <v>351</v>
       </c>
       <c r="D226" s="6">
-        <v>73073</v>
+        <v>71067</v>
       </c>
       <c r="E226" s="6">
-        <v>10200</v>
+        <v>9900</v>
       </c>
       <c r="F226" s="6">
-        <v>76000</v>
+        <v>74000</v>
       </c>
       <c r="G226" s="5" t="s">
         <v>1459</v>
@@ -12365,13 +12365,13 @@
         <v>352</v>
       </c>
       <c r="D227" s="6">
-        <v>74741</v>
+        <v>72466</v>
       </c>
       <c r="E227" s="6">
-        <v>10500</v>
+        <v>10100</v>
       </c>
       <c r="F227" s="6">
-        <v>78000</v>
+        <v>75000</v>
       </c>
       <c r="G227" s="5" t="s">
         <v>1459</v>
@@ -12394,13 +12394,13 @@
         <v>353</v>
       </c>
       <c r="D228" s="6">
-        <v>113830</v>
+        <v>110421</v>
       </c>
       <c r="E228" s="6">
-        <v>15900</v>
+        <v>15500</v>
       </c>
       <c r="F228" s="6">
-        <v>117000</v>
+        <v>113000</v>
       </c>
       <c r="G228" s="5" t="s">
         <v>1459</v>
@@ -12423,13 +12423,13 @@
         <v>354</v>
       </c>
       <c r="D229" s="6">
-        <v>180071</v>
+        <v>174715</v>
       </c>
       <c r="E229" s="6">
-        <v>25200</v>
+        <v>24500</v>
       </c>
       <c r="F229" s="6">
-        <v>183000</v>
+        <v>178000</v>
       </c>
       <c r="G229" s="5" t="s">
         <v>1459</v>
@@ -12452,13 +12452,13 @@
         <v>355</v>
       </c>
       <c r="D230" s="6">
-        <v>50905</v>
+        <v>49252</v>
       </c>
       <c r="E230" s="6">
-        <v>7100</v>
+        <v>6900</v>
       </c>
       <c r="F230" s="6">
-        <v>54000</v>
+        <v>52000</v>
       </c>
       <c r="G230" s="5" t="s">
         <v>1459</v>
@@ -12481,13 +12481,13 @@
         <v>1495</v>
       </c>
       <c r="D231" s="6">
-        <v>68072</v>
+        <v>66065</v>
       </c>
       <c r="E231" s="6">
-        <v>9500</v>
+        <v>9200</v>
       </c>
       <c r="F231" s="6">
-        <v>71000</v>
+        <v>69000</v>
       </c>
       <c r="G231" s="5" t="s">
         <v>1459</v>
@@ -12510,13 +12510,13 @@
         <v>356</v>
       </c>
       <c r="D232" s="6">
-        <v>95951</v>
+        <v>93271</v>
       </c>
       <c r="E232" s="6">
-        <v>13400</v>
+        <v>13100</v>
       </c>
       <c r="F232" s="6">
-        <v>99000</v>
+        <v>96000</v>
       </c>
       <c r="G232" s="5" t="s">
         <v>1459</v>
@@ -12539,13 +12539,13 @@
         <v>1496</v>
       </c>
       <c r="D233" s="6">
-        <v>89480</v>
+        <v>86900</v>
       </c>
       <c r="E233" s="6">
-        <v>12500</v>
+        <v>12200</v>
       </c>
       <c r="F233" s="6">
-        <v>92000</v>
+        <v>90000</v>
       </c>
       <c r="G233" s="5" t="s">
         <v>1459</v>
@@ -12568,13 +12568,13 @@
         <v>357</v>
       </c>
       <c r="D234" s="6">
-        <v>105255</v>
+        <v>102002</v>
       </c>
       <c r="E234" s="6">
-        <v>14700</v>
+        <v>14300</v>
       </c>
       <c r="F234" s="6">
-        <v>108000</v>
+        <v>105000</v>
       </c>
       <c r="G234" s="5" t="s">
         <v>1459</v>
@@ -12597,13 +12597,13 @@
         <v>358</v>
       </c>
       <c r="D235" s="6">
-        <v>122660</v>
+        <v>118895</v>
       </c>
       <c r="E235" s="6">
-        <v>17200</v>
+        <v>16600</v>
       </c>
       <c r="F235" s="6">
-        <v>126000</v>
+        <v>122000</v>
       </c>
       <c r="G235" s="5" t="s">
         <v>1459</v>
@@ -12626,13 +12626,13 @@
         <v>359</v>
       </c>
       <c r="D236" s="6">
-        <v>185934</v>
+        <v>180417</v>
       </c>
       <c r="E236" s="6">
-        <v>26000</v>
+        <v>25300</v>
       </c>
       <c r="F236" s="6">
-        <v>189000</v>
+        <v>183000</v>
       </c>
       <c r="G236" s="5" t="s">
         <v>1459</v>
@@ -12655,13 +12655,13 @@
         <v>1497</v>
       </c>
       <c r="D237" s="6">
-        <v>262479</v>
+        <v>254560</v>
       </c>
       <c r="E237" s="6">
-        <v>36700</v>
+        <v>35600</v>
       </c>
       <c r="F237" s="6">
-        <v>265000</v>
+        <v>258000</v>
       </c>
       <c r="G237" s="5" t="s">
         <v>1459</v>
@@ -12684,13 +12684,13 @@
         <v>360</v>
       </c>
       <c r="D238" s="6">
-        <v>139060</v>
+        <v>134752</v>
       </c>
       <c r="E238" s="6">
-        <v>19500</v>
+        <v>18900</v>
       </c>
       <c r="F238" s="6">
-        <v>142000</v>
+        <v>138000</v>
       </c>
       <c r="G238" s="5" t="s">
         <v>1459</v>
@@ -12713,13 +12713,13 @@
         <v>361</v>
       </c>
       <c r="D239" s="6">
-        <v>200361</v>
+        <v>193897</v>
       </c>
       <c r="E239" s="6">
-        <v>28100</v>
+        <v>27100</v>
       </c>
       <c r="F239" s="6">
-        <v>203000</v>
+        <v>197000</v>
       </c>
       <c r="G239" s="5" t="s">
         <v>1459</v>
@@ -12742,13 +12742,13 @@
         <v>1498</v>
       </c>
       <c r="D240" s="6">
-        <v>139060</v>
+        <v>134755</v>
       </c>
       <c r="E240" s="6">
-        <v>19500</v>
+        <v>18900</v>
       </c>
       <c r="F240" s="6">
-        <v>142000</v>
+        <v>138000</v>
       </c>
       <c r="G240" s="5" t="s">
         <v>1459</v>
@@ -12771,13 +12771,13 @@
         <v>362</v>
       </c>
       <c r="D241" s="6">
-        <v>200361</v>
+        <v>193903</v>
       </c>
       <c r="E241" s="6">
-        <v>28100</v>
+        <v>27100</v>
       </c>
       <c r="F241" s="6">
-        <v>203000</v>
+        <v>197000</v>
       </c>
       <c r="G241" s="5" t="s">
         <v>1459</v>
@@ -12800,13 +12800,13 @@
         <v>363</v>
       </c>
       <c r="D242" s="6">
-        <v>292185</v>
+        <v>283762</v>
       </c>
       <c r="E242" s="6">
-        <v>40900</v>
+        <v>39700</v>
       </c>
       <c r="F242" s="6">
-        <v>295000</v>
+        <v>287000</v>
       </c>
       <c r="G242" s="5" t="s">
         <v>1459</v>
@@ -12829,13 +12829,13 @@
         <v>364</v>
       </c>
       <c r="D243" s="6">
-        <v>426063</v>
+        <v>411875</v>
       </c>
       <c r="E243" s="6">
-        <v>59600</v>
+        <v>57700</v>
       </c>
       <c r="F243" s="6">
-        <v>429000</v>
+        <v>415000</v>
       </c>
       <c r="G243" s="5" t="s">
         <v>1459</v>
@@ -12858,13 +12858,13 @@
         <v>365</v>
       </c>
       <c r="D244" s="6">
-        <v>162025</v>
+        <v>157026</v>
       </c>
       <c r="E244" s="6">
-        <v>22700</v>
+        <v>22000</v>
       </c>
       <c r="F244" s="6">
-        <v>165000</v>
+        <v>160000</v>
       </c>
       <c r="G244" s="5" t="s">
         <v>1459</v>
@@ -12887,13 +12887,13 @@
         <v>1499</v>
       </c>
       <c r="D245" s="6">
-        <v>222483</v>
+        <v>215114</v>
       </c>
       <c r="E245" s="6">
-        <v>31100</v>
+        <v>30100</v>
       </c>
       <c r="F245" s="6">
-        <v>225000</v>
+        <v>218000</v>
       </c>
       <c r="G245" s="5" t="s">
         <v>1459</v>
@@ -12916,13 +12916,13 @@
         <v>1500</v>
       </c>
       <c r="D246" s="6">
-        <v>316338</v>
+        <v>306050</v>
       </c>
       <c r="E246" s="6">
-        <v>44300</v>
+        <v>42800</v>
       </c>
       <c r="F246" s="6">
-        <v>319000</v>
+        <v>309000</v>
       </c>
       <c r="G246" s="5" t="s">
         <v>1459</v>
@@ -12945,13 +12945,13 @@
         <v>366</v>
       </c>
       <c r="D247" s="6">
-        <v>466135</v>
+        <v>450232</v>
       </c>
       <c r="E247" s="6">
-        <v>65300</v>
+        <v>63000</v>
       </c>
       <c r="F247" s="6">
-        <v>469000</v>
+        <v>453000</v>
       </c>
       <c r="G247" s="5" t="s">
         <v>1459</v>
@@ -12974,13 +12974,13 @@
         <v>367</v>
       </c>
       <c r="D248" s="6">
-        <v>821029</v>
+        <v>797309</v>
       </c>
       <c r="E248" s="6">
-        <v>114900</v>
+        <v>111600</v>
       </c>
       <c r="F248" s="6">
-        <v>824000</v>
+        <v>800000</v>
       </c>
       <c r="G248" s="5" t="s">
         <v>1459</v>

--- a/rates.xlsx
+++ b/rates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS COM\Dropbox\Rates Portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FE7038-061E-4B82-AA39-86EC9AAE0E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BD1B11-1B69-497B-B165-3A3DDE90053C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12336,13 +12336,13 @@
         <v>351</v>
       </c>
       <c r="D226" s="6">
-        <v>71067</v>
+        <v>64882</v>
       </c>
       <c r="E226" s="6">
-        <v>9900</v>
+        <v>9100</v>
       </c>
       <c r="F226" s="6">
-        <v>74000</v>
+        <v>68000</v>
       </c>
       <c r="G226" s="5" t="s">
         <v>1459</v>
@@ -12481,13 +12481,13 @@
         <v>1495</v>
       </c>
       <c r="D231" s="6">
-        <v>66065</v>
+        <v>64882</v>
       </c>
       <c r="E231" s="6">
-        <v>9200</v>
+        <v>9100</v>
       </c>
       <c r="F231" s="6">
-        <v>69000</v>
+        <v>68000</v>
       </c>
       <c r="G231" s="5" t="s">
         <v>1459</v>
@@ -12510,13 +12510,13 @@
         <v>356</v>
       </c>
       <c r="D232" s="6">
-        <v>93271</v>
+        <v>85500</v>
       </c>
       <c r="E232" s="6">
-        <v>13100</v>
+        <v>12000</v>
       </c>
       <c r="F232" s="6">
-        <v>96000</v>
+        <v>89000</v>
       </c>
       <c r="G232" s="5" t="s">
         <v>1459</v>

--- a/rates.xlsx
+++ b/rates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS COM\Dropbox\Rates Portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BD1B11-1B69-497B-B165-3A3DDE90053C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D87086BB-035D-4CC2-AB6B-3FC4FB1AFFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$I$1659</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$I$1663</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8299" uniqueCount="1737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8319" uniqueCount="1742">
   <si>
     <t>PRLP-1100</t>
   </si>
@@ -5258,6 +5258,21 @@
   </si>
   <si>
     <t>Digital temperature display; 2000W Italy element; Watt control; Inverter technology; Heavy gauge water tank</t>
+  </si>
+  <si>
+    <t>SUPER ACTION</t>
+  </si>
+  <si>
+    <t>Dual  Geezer  15 Gallon</t>
+  </si>
+  <si>
+    <t>Dual Geezer 25 Gallon</t>
+  </si>
+  <si>
+    <t>Duel Geezer  25 Gallon</t>
+  </si>
+  <si>
+    <t>Duel  Geezer  35 Gallon</t>
   </si>
 </sst>
 </file>
@@ -5786,10 +5801,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6FE0007-86B3-4D5F-9CBC-37B22BC3E091}">
-  <dimension ref="A1:I1660"/>
+  <dimension ref="A1:I1664"/>
   <sheetFormatPr defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="75.7109375" style="23" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" style="2" bestFit="1" customWidth="1"/>
@@ -46855,110 +46870,110 @@
       </c>
     </row>
     <row r="1499" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1499" s="5" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B1499" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1499" s="22" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D1499" s="15">
-        <v>56000</v>
-      </c>
-      <c r="E1499" s="5">
+      <c r="A1499" s="6" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B1499" s="6" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C1499" s="19" t="s">
+        <v>1738</v>
+      </c>
+      <c r="D1499" s="7">
+        <v>37780</v>
+      </c>
+      <c r="E1499" s="6">
+        <v>5400</v>
+      </c>
+      <c r="F1499" s="6"/>
+      <c r="G1499" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1499" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1499" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1500" s="6" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B1500" s="6" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C1500" s="19" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D1500" s="7">
+        <v>40780</v>
+      </c>
+      <c r="E1500" s="6">
         <v>5900</v>
       </c>
-      <c r="F1499" s="5"/>
-      <c r="G1499" s="5" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1499" s="5" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1499" s="5">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="1500" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1500" s="5" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B1500" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1500" s="22" t="s">
-        <v>1041</v>
-      </c>
-      <c r="D1500" s="15">
-        <v>66000</v>
-      </c>
-      <c r="E1500" s="5">
-        <v>7000</v>
-      </c>
-      <c r="F1500" s="5"/>
-      <c r="G1500" s="5" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1500" s="5" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1500" s="5">
+      <c r="F1500" s="6"/>
+      <c r="G1500" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1500" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1500" s="6">
         <v>2026</v>
       </c>
     </row>
     <row r="1501" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1501" s="5" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B1501" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1501" s="22" t="s">
-        <v>1042</v>
-      </c>
-      <c r="D1501" s="15">
-        <v>85000</v>
-      </c>
-      <c r="E1501" s="5">
-        <v>9100</v>
-      </c>
-      <c r="F1501" s="5"/>
-      <c r="G1501" s="5" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1501" s="5" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1501" s="5">
+      <c r="A1501" s="6" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B1501" s="6" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C1501" s="19" t="s">
+        <v>1740</v>
+      </c>
+      <c r="D1501" s="7">
+        <v>40780</v>
+      </c>
+      <c r="E1501" s="6">
+        <v>5900</v>
+      </c>
+      <c r="F1501" s="6"/>
+      <c r="G1501" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1501" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1501" s="6">
         <v>2026</v>
       </c>
     </row>
     <row r="1502" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1502" s="5" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B1502" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1502" s="22" t="s">
-        <v>1043</v>
-      </c>
-      <c r="D1502" s="15">
-        <v>109000</v>
-      </c>
-      <c r="E1502" s="5">
-        <v>10900</v>
-      </c>
-      <c r="F1502" s="5"/>
-      <c r="G1502" s="5" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1502" s="5" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I1502" s="5">
+      <c r="A1502" s="6" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B1502" s="6" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C1502" s="19" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D1502" s="7">
+        <v>45580</v>
+      </c>
+      <c r="E1502" s="6">
+        <v>6600</v>
+      </c>
+      <c r="F1502" s="6"/>
+      <c r="G1502" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1502" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1502" s="6">
         <v>2026</v>
       </c>
     </row>
@@ -46970,13 +46985,13 @@
         <v>207</v>
       </c>
       <c r="C1503" s="22" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="D1503" s="15">
-        <v>112000</v>
+        <v>56000</v>
       </c>
       <c r="E1503" s="5">
-        <v>11900</v>
+        <v>5900</v>
       </c>
       <c r="F1503" s="5"/>
       <c r="G1503" s="5" t="s">
@@ -46997,13 +47012,13 @@
         <v>207</v>
       </c>
       <c r="C1504" s="22" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="D1504" s="15">
-        <v>140000</v>
+        <v>66000</v>
       </c>
       <c r="E1504" s="5">
-        <v>14000</v>
+        <v>7000</v>
       </c>
       <c r="F1504" s="5"/>
       <c r="G1504" s="5" t="s">
@@ -47024,13 +47039,13 @@
         <v>207</v>
       </c>
       <c r="C1505" s="22" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="D1505" s="15">
-        <v>154000</v>
+        <v>85000</v>
       </c>
       <c r="E1505" s="5">
-        <v>15400</v>
+        <v>9100</v>
       </c>
       <c r="F1505" s="5"/>
       <c r="G1505" s="5" t="s">
@@ -47044,110 +47059,110 @@
       </c>
     </row>
     <row r="1506" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1506" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1506" s="6" t="s">
+      <c r="A1506" s="5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B1506" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C1506" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="D1506" s="7">
-        <v>700000</v>
-      </c>
-      <c r="E1506" s="6">
-        <v>70000</v>
-      </c>
-      <c r="F1506" s="6"/>
-      <c r="G1506" s="6" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1506" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="I1506" s="6">
+      <c r="C1506" s="22" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D1506" s="15">
+        <v>109000</v>
+      </c>
+      <c r="E1506" s="5">
+        <v>10900</v>
+      </c>
+      <c r="F1506" s="5"/>
+      <c r="G1506" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1506" s="5" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1506" s="5">
         <v>2026</v>
       </c>
     </row>
     <row r="1507" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1507" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1507" s="6" t="s">
+      <c r="A1507" s="5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B1507" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C1507" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="D1507" s="7">
-        <v>490000</v>
-      </c>
-      <c r="E1507" s="6">
-        <v>49000</v>
-      </c>
-      <c r="F1507" s="6"/>
-      <c r="G1507" s="6" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1507" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="I1507" s="6">
+      <c r="C1507" s="22" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D1507" s="15">
+        <v>112000</v>
+      </c>
+      <c r="E1507" s="5">
+        <v>11900</v>
+      </c>
+      <c r="F1507" s="5"/>
+      <c r="G1507" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1507" s="5" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1507" s="5">
         <v>2026</v>
       </c>
     </row>
     <row r="1508" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1508" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1508" s="6" t="s">
+      <c r="A1508" s="5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B1508" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C1508" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="D1508" s="7">
-        <v>378000</v>
-      </c>
-      <c r="E1508" s="6">
-        <v>37800</v>
-      </c>
-      <c r="F1508" s="6"/>
-      <c r="G1508" s="6" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1508" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="I1508" s="6">
+      <c r="C1508" s="22" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D1508" s="15">
+        <v>140000</v>
+      </c>
+      <c r="E1508" s="5">
+        <v>14000</v>
+      </c>
+      <c r="F1508" s="5"/>
+      <c r="G1508" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1508" s="5" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1508" s="5">
         <v>2026</v>
       </c>
     </row>
     <row r="1509" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1509" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1509" s="6" t="s">
+      <c r="A1509" s="5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B1509" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C1509" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D1509" s="7">
-        <v>280000</v>
-      </c>
-      <c r="E1509" s="6">
-        <v>28000</v>
-      </c>
-      <c r="F1509" s="6"/>
-      <c r="G1509" s="6" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1509" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="I1509" s="6">
+      <c r="C1509" s="22" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D1509" s="15">
+        <v>154000</v>
+      </c>
+      <c r="E1509" s="5">
+        <v>15400</v>
+      </c>
+      <c r="F1509" s="5"/>
+      <c r="G1509" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1509" s="5" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1509" s="5">
         <v>2026</v>
       </c>
     </row>
@@ -47159,13 +47174,13 @@
         <v>207</v>
       </c>
       <c r="C1510" s="19" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D1510" s="7">
-        <v>252000</v>
+        <v>700000</v>
       </c>
       <c r="E1510" s="6">
-        <v>25200</v>
+        <v>70000</v>
       </c>
       <c r="F1510" s="6"/>
       <c r="G1510" s="6" t="s">
@@ -47186,13 +47201,13 @@
         <v>207</v>
       </c>
       <c r="C1511" s="19" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D1511" s="7">
-        <v>224000</v>
+        <v>490000</v>
       </c>
       <c r="E1511" s="6">
-        <v>22400</v>
+        <v>49000</v>
       </c>
       <c r="F1511" s="6"/>
       <c r="G1511" s="6" t="s">
@@ -47213,13 +47228,13 @@
         <v>207</v>
       </c>
       <c r="C1512" s="19" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D1512" s="7">
-        <v>217000</v>
+        <v>378000</v>
       </c>
       <c r="E1512" s="6">
-        <v>21700</v>
+        <v>37800</v>
       </c>
       <c r="F1512" s="6"/>
       <c r="G1512" s="6" t="s">
@@ -47240,13 +47255,13 @@
         <v>207</v>
       </c>
       <c r="C1513" s="19" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D1513" s="7">
-        <v>204000</v>
+        <v>280000</v>
       </c>
       <c r="E1513" s="6">
-        <v>20400</v>
+        <v>28000</v>
       </c>
       <c r="F1513" s="6"/>
       <c r="G1513" s="6" t="s">
@@ -47267,13 +47282,13 @@
         <v>207</v>
       </c>
       <c r="C1514" s="19" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D1514" s="7">
-        <v>189000</v>
+        <v>252000</v>
       </c>
       <c r="E1514" s="6">
-        <v>18900</v>
+        <v>25200</v>
       </c>
       <c r="F1514" s="6"/>
       <c r="G1514" s="6" t="s">
@@ -47294,13 +47309,13 @@
         <v>207</v>
       </c>
       <c r="C1515" s="19" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D1515" s="7">
-        <v>175000</v>
+        <v>224000</v>
       </c>
       <c r="E1515" s="6">
-        <v>17500</v>
+        <v>22400</v>
       </c>
       <c r="F1515" s="6"/>
       <c r="G1515" s="6" t="s">
@@ -47321,13 +47336,13 @@
         <v>207</v>
       </c>
       <c r="C1516" s="19" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D1516" s="7">
-        <v>154000</v>
+        <v>217000</v>
       </c>
       <c r="E1516" s="6">
-        <v>15400</v>
+        <v>21700</v>
       </c>
       <c r="F1516" s="6"/>
       <c r="G1516" s="6" t="s">
@@ -47348,13 +47363,13 @@
         <v>207</v>
       </c>
       <c r="C1517" s="19" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D1517" s="7">
-        <v>140000</v>
+        <v>204000</v>
       </c>
       <c r="E1517" s="6">
-        <v>14000</v>
+        <v>20400</v>
       </c>
       <c r="F1517" s="6"/>
       <c r="G1517" s="6" t="s">
@@ -47375,13 +47390,13 @@
         <v>207</v>
       </c>
       <c r="C1518" s="19" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D1518" s="7">
-        <v>133000</v>
+        <v>189000</v>
       </c>
       <c r="E1518" s="6">
-        <v>13300</v>
+        <v>18900</v>
       </c>
       <c r="F1518" s="6"/>
       <c r="G1518" s="6" t="s">
@@ -47402,13 +47417,13 @@
         <v>207</v>
       </c>
       <c r="C1519" s="19" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D1519" s="7">
-        <v>123000</v>
+        <v>175000</v>
       </c>
       <c r="E1519" s="6">
-        <v>12300</v>
+        <v>17500</v>
       </c>
       <c r="F1519" s="6"/>
       <c r="G1519" s="6" t="s">
@@ -47429,13 +47444,13 @@
         <v>207</v>
       </c>
       <c r="C1520" s="19" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D1520" s="7">
-        <v>116000</v>
+        <v>154000</v>
       </c>
       <c r="E1520" s="6">
-        <v>11600</v>
+        <v>15400</v>
       </c>
       <c r="F1520" s="6"/>
       <c r="G1520" s="6" t="s">
@@ -47456,13 +47471,13 @@
         <v>207</v>
       </c>
       <c r="C1521" s="19" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D1521" s="7">
-        <v>102000</v>
+        <v>140000</v>
       </c>
       <c r="E1521" s="6">
-        <v>10200</v>
+        <v>14000</v>
       </c>
       <c r="F1521" s="6"/>
       <c r="G1521" s="6" t="s">
@@ -47483,13 +47498,13 @@
         <v>207</v>
       </c>
       <c r="C1522" s="19" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D1522" s="7">
-        <v>97000</v>
+        <v>133000</v>
       </c>
       <c r="E1522" s="6">
-        <v>9700</v>
+        <v>13300</v>
       </c>
       <c r="F1522" s="6"/>
       <c r="G1522" s="6" t="s">
@@ -47510,13 +47525,13 @@
         <v>207</v>
       </c>
       <c r="C1523" s="19" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D1523" s="7">
-        <v>74000</v>
+        <v>123000</v>
       </c>
       <c r="E1523" s="6">
-        <v>7400</v>
+        <v>12300</v>
       </c>
       <c r="F1523" s="6"/>
       <c r="G1523" s="6" t="s">
@@ -47537,13 +47552,13 @@
         <v>207</v>
       </c>
       <c r="C1524" s="19" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D1524" s="7">
-        <v>71000</v>
+        <v>116000</v>
       </c>
       <c r="E1524" s="6">
-        <v>7100</v>
+        <v>11600</v>
       </c>
       <c r="F1524" s="6"/>
       <c r="G1524" s="6" t="s">
@@ -47564,13 +47579,13 @@
         <v>207</v>
       </c>
       <c r="C1525" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D1525" s="7">
-        <v>63000</v>
+        <v>102000</v>
       </c>
       <c r="E1525" s="6">
-        <v>6300</v>
+        <v>10200</v>
       </c>
       <c r="F1525" s="6"/>
       <c r="G1525" s="6" t="s">
@@ -47591,13 +47606,13 @@
         <v>207</v>
       </c>
       <c r="C1526" s="19" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D1526" s="7">
-        <v>56000</v>
+        <v>97000</v>
       </c>
       <c r="E1526" s="6">
-        <v>5600</v>
+        <v>9700</v>
       </c>
       <c r="F1526" s="6"/>
       <c r="G1526" s="6" t="s">
@@ -47612,19 +47627,19 @@
     </row>
     <row r="1527" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1527" s="6" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1527" s="6" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1527" s="19" t="s">
-        <v>629</v>
+        <v>201</v>
       </c>
       <c r="D1527" s="7">
-        <v>5400</v>
+        <v>74000</v>
       </c>
       <c r="E1527" s="6">
-        <v>800</v>
+        <v>7400</v>
       </c>
       <c r="F1527" s="6"/>
       <c r="G1527" s="6" t="s">
@@ -47639,19 +47654,19 @@
     </row>
     <row r="1528" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1528" s="6" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1528" s="6" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1528" s="19" t="s">
-        <v>630</v>
+        <v>202</v>
       </c>
       <c r="D1528" s="7">
-        <v>26200</v>
+        <v>71000</v>
       </c>
       <c r="E1528" s="6">
-        <v>4100</v>
+        <v>7100</v>
       </c>
       <c r="F1528" s="6"/>
       <c r="G1528" s="6" t="s">
@@ -47666,19 +47681,19 @@
     </row>
     <row r="1529" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1529" s="6" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1529" s="6" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1529" s="19" t="s">
-        <v>631</v>
+        <v>203</v>
       </c>
       <c r="D1529" s="7">
-        <v>27200</v>
+        <v>63000</v>
       </c>
       <c r="E1529" s="6">
-        <v>4200</v>
+        <v>6300</v>
       </c>
       <c r="F1529" s="6"/>
       <c r="G1529" s="6" t="s">
@@ -47693,19 +47708,19 @@
     </row>
     <row r="1530" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1530" s="6" t="s">
-        <v>728</v>
+        <v>170</v>
       </c>
       <c r="B1530" s="6" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="C1530" s="19" t="s">
-        <v>632</v>
+        <v>204</v>
       </c>
       <c r="D1530" s="7">
-        <v>20700</v>
+        <v>56000</v>
       </c>
       <c r="E1530" s="6">
-        <v>3200</v>
+        <v>5600</v>
       </c>
       <c r="F1530" s="6"/>
       <c r="G1530" s="6" t="s">
@@ -47726,13 +47741,13 @@
         <v>447</v>
       </c>
       <c r="C1531" s="19" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="D1531" s="7">
-        <v>9900</v>
+        <v>5400</v>
       </c>
       <c r="E1531" s="6">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="F1531" s="6"/>
       <c r="G1531" s="6" t="s">
@@ -47753,13 +47768,13 @@
         <v>447</v>
       </c>
       <c r="C1532" s="19" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="D1532" s="7">
-        <v>10200</v>
+        <v>26200</v>
       </c>
       <c r="E1532" s="6">
-        <v>1600</v>
+        <v>4100</v>
       </c>
       <c r="F1532" s="6"/>
       <c r="G1532" s="6" t="s">
@@ -47780,13 +47795,13 @@
         <v>447</v>
       </c>
       <c r="C1533" s="19" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="D1533" s="7">
-        <v>14300</v>
+        <v>27200</v>
       </c>
       <c r="E1533" s="6">
-        <v>2200</v>
+        <v>4200</v>
       </c>
       <c r="F1533" s="6"/>
       <c r="G1533" s="6" t="s">
@@ -47807,13 +47822,13 @@
         <v>447</v>
       </c>
       <c r="C1534" s="19" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="D1534" s="7">
-        <v>8500</v>
+        <v>20700</v>
       </c>
       <c r="E1534" s="6">
-        <v>1300</v>
+        <v>3200</v>
       </c>
       <c r="F1534" s="6"/>
       <c r="G1534" s="6" t="s">
@@ -47834,10 +47849,10 @@
         <v>447</v>
       </c>
       <c r="C1535" s="19" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="D1535" s="7">
-        <v>9400</v>
+        <v>9900</v>
       </c>
       <c r="E1535" s="6">
         <v>1500</v>
@@ -47861,13 +47876,13 @@
         <v>447</v>
       </c>
       <c r="C1536" s="19" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="D1536" s="7">
-        <v>7900</v>
+        <v>10200</v>
       </c>
       <c r="E1536" s="6">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="F1536" s="6"/>
       <c r="G1536" s="6" t="s">
@@ -47888,13 +47903,13 @@
         <v>447</v>
       </c>
       <c r="C1537" s="19" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="D1537" s="7">
-        <v>36900</v>
+        <v>14300</v>
       </c>
       <c r="E1537" s="6">
-        <v>5700</v>
+        <v>2200</v>
       </c>
       <c r="F1537" s="6"/>
       <c r="G1537" s="6" t="s">
@@ -47915,13 +47930,13 @@
         <v>447</v>
       </c>
       <c r="C1538" s="19" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="D1538" s="7">
-        <v>26600</v>
+        <v>8500</v>
       </c>
       <c r="E1538" s="6">
-        <v>4100</v>
+        <v>1300</v>
       </c>
       <c r="F1538" s="6"/>
       <c r="G1538" s="6" t="s">
@@ -47942,13 +47957,13 @@
         <v>447</v>
       </c>
       <c r="C1539" s="19" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="D1539" s="7">
-        <v>40200</v>
+        <v>9400</v>
       </c>
       <c r="E1539" s="6">
-        <v>6200</v>
+        <v>1500</v>
       </c>
       <c r="F1539" s="6"/>
       <c r="G1539" s="6" t="s">
@@ -47969,13 +47984,13 @@
         <v>447</v>
       </c>
       <c r="C1540" s="19" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="D1540" s="7">
-        <v>8400</v>
+        <v>7900</v>
       </c>
       <c r="E1540" s="6">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F1540" s="6"/>
       <c r="G1540" s="6" t="s">
@@ -47996,13 +48011,13 @@
         <v>447</v>
       </c>
       <c r="C1541" s="19" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="D1541" s="7">
-        <v>8300</v>
+        <v>36900</v>
       </c>
       <c r="E1541" s="6">
-        <v>1300</v>
+        <v>5700</v>
       </c>
       <c r="F1541" s="6"/>
       <c r="G1541" s="6" t="s">
@@ -48023,13 +48038,13 @@
         <v>447</v>
       </c>
       <c r="C1542" s="19" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="D1542" s="7">
-        <v>8000</v>
+        <v>26600</v>
       </c>
       <c r="E1542" s="6">
-        <v>1200</v>
+        <v>4100</v>
       </c>
       <c r="F1542" s="6"/>
       <c r="G1542" s="6" t="s">
@@ -48050,13 +48065,13 @@
         <v>447</v>
       </c>
       <c r="C1543" s="19" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="D1543" s="7">
-        <v>18300</v>
+        <v>40200</v>
       </c>
       <c r="E1543" s="6">
-        <v>2800</v>
+        <v>6200</v>
       </c>
       <c r="F1543" s="6"/>
       <c r="G1543" s="6" t="s">
@@ -48077,13 +48092,13 @@
         <v>447</v>
       </c>
       <c r="C1544" s="19" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="D1544" s="7">
-        <v>15500</v>
+        <v>8400</v>
       </c>
       <c r="E1544" s="6">
-        <v>2400</v>
+        <v>1300</v>
       </c>
       <c r="F1544" s="6"/>
       <c r="G1544" s="6" t="s">
@@ -48104,13 +48119,13 @@
         <v>447</v>
       </c>
       <c r="C1545" s="19" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="D1545" s="7">
-        <v>18300</v>
+        <v>8300</v>
       </c>
       <c r="E1545" s="6">
-        <v>2800</v>
+        <v>1300</v>
       </c>
       <c r="F1545" s="6"/>
       <c r="G1545" s="6" t="s">
@@ -48131,13 +48146,13 @@
         <v>447</v>
       </c>
       <c r="C1546" s="19" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="D1546" s="7">
-        <v>20600</v>
+        <v>8000</v>
       </c>
       <c r="E1546" s="6">
-        <v>3200</v>
+        <v>1200</v>
       </c>
       <c r="F1546" s="6"/>
       <c r="G1546" s="6" t="s">
@@ -48158,13 +48173,13 @@
         <v>447</v>
       </c>
       <c r="C1547" s="19" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="D1547" s="7">
-        <v>19391</v>
+        <v>18300</v>
       </c>
       <c r="E1547" s="6">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="F1547" s="6"/>
       <c r="G1547" s="6" t="s">
@@ -48185,13 +48200,13 @@
         <v>447</v>
       </c>
       <c r="C1548" s="19" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="D1548" s="7">
-        <v>19391</v>
+        <v>15500</v>
       </c>
       <c r="E1548" s="6">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="F1548" s="6"/>
       <c r="G1548" s="6" t="s">
@@ -48212,13 +48227,13 @@
         <v>447</v>
       </c>
       <c r="C1549" s="19" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="D1549" s="7">
-        <v>7700</v>
+        <v>18300</v>
       </c>
       <c r="E1549" s="6">
-        <v>1200</v>
+        <v>2800</v>
       </c>
       <c r="F1549" s="6"/>
       <c r="G1549" s="6" t="s">
@@ -48239,13 +48254,13 @@
         <v>447</v>
       </c>
       <c r="C1550" s="19" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="D1550" s="7">
-        <v>10300</v>
+        <v>20600</v>
       </c>
       <c r="E1550" s="6">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="F1550" s="6"/>
       <c r="G1550" s="6" t="s">
@@ -48266,13 +48281,13 @@
         <v>447</v>
       </c>
       <c r="C1551" s="19" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D1551" s="7">
-        <v>9700</v>
+        <v>19391</v>
       </c>
       <c r="E1551" s="6">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="F1551" s="6"/>
       <c r="G1551" s="6" t="s">
@@ -48293,13 +48308,13 @@
         <v>447</v>
       </c>
       <c r="C1552" s="19" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="D1552" s="7">
-        <v>9068</v>
+        <v>19391</v>
       </c>
       <c r="E1552" s="6">
-        <v>1400</v>
+        <v>3000</v>
       </c>
       <c r="F1552" s="6"/>
       <c r="G1552" s="6" t="s">
@@ -48320,13 +48335,13 @@
         <v>447</v>
       </c>
       <c r="C1553" s="19" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="D1553" s="7">
-        <v>8200</v>
+        <v>7700</v>
       </c>
       <c r="E1553" s="6">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F1553" s="6"/>
       <c r="G1553" s="6" t="s">
@@ -48347,13 +48362,13 @@
         <v>447</v>
       </c>
       <c r="C1554" s="19" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D1554" s="7">
-        <v>11400</v>
+        <v>10300</v>
       </c>
       <c r="E1554" s="6">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="F1554" s="6"/>
       <c r="G1554" s="6" t="s">
@@ -48374,13 +48389,13 @@
         <v>447</v>
       </c>
       <c r="C1555" s="19" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="D1555" s="7">
-        <v>10000</v>
+        <v>9700</v>
       </c>
       <c r="E1555" s="6">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="F1555" s="6"/>
       <c r="G1555" s="6" t="s">
@@ -48401,13 +48416,13 @@
         <v>447</v>
       </c>
       <c r="C1556" s="19" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="D1556" s="7">
-        <v>8510</v>
+        <v>9068</v>
       </c>
       <c r="E1556" s="6">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="F1556" s="6"/>
       <c r="G1556" s="6" t="s">
@@ -48428,7 +48443,7 @@
         <v>447</v>
       </c>
       <c r="C1557" s="19" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="D1557" s="7">
         <v>8200</v>
@@ -48455,13 +48470,13 @@
         <v>447</v>
       </c>
       <c r="C1558" s="19" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="D1558" s="7">
-        <v>8000</v>
+        <v>11400</v>
       </c>
       <c r="E1558" s="6">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="F1558" s="6"/>
       <c r="G1558" s="6" t="s">
@@ -48482,13 +48497,13 @@
         <v>447</v>
       </c>
       <c r="C1559" s="19" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="D1559" s="7">
-        <v>6929</v>
+        <v>10000</v>
       </c>
       <c r="E1559" s="6">
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="F1559" s="6"/>
       <c r="G1559" s="6" t="s">
@@ -48509,13 +48524,13 @@
         <v>447</v>
       </c>
       <c r="C1560" s="19" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="D1560" s="7">
-        <v>16400</v>
+        <v>8510</v>
       </c>
       <c r="E1560" s="6">
-        <v>2500</v>
+        <v>1300</v>
       </c>
       <c r="F1560" s="6"/>
       <c r="G1560" s="6" t="s">
@@ -48536,13 +48551,13 @@
         <v>447</v>
       </c>
       <c r="C1561" s="19" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="D1561" s="7">
-        <v>14800</v>
+        <v>8200</v>
       </c>
       <c r="E1561" s="6">
-        <v>2300</v>
+        <v>1300</v>
       </c>
       <c r="F1561" s="6"/>
       <c r="G1561" s="6" t="s">
@@ -48563,13 +48578,13 @@
         <v>447</v>
       </c>
       <c r="C1562" s="19" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="D1562" s="7">
-        <v>14800</v>
+        <v>8000</v>
       </c>
       <c r="E1562" s="6">
-        <v>2300</v>
+        <v>1200</v>
       </c>
       <c r="F1562" s="6"/>
       <c r="G1562" s="6" t="s">
@@ -48590,13 +48605,13 @@
         <v>447</v>
       </c>
       <c r="C1563" s="19" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="D1563" s="7">
-        <v>9000</v>
+        <v>6929</v>
       </c>
       <c r="E1563" s="6">
-        <v>1400</v>
+        <v>1100</v>
       </c>
       <c r="F1563" s="6"/>
       <c r="G1563" s="6" t="s">
@@ -48617,13 +48632,13 @@
         <v>447</v>
       </c>
       <c r="C1564" s="19" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="D1564" s="7">
-        <v>34900</v>
+        <v>16400</v>
       </c>
       <c r="E1564" s="6">
-        <v>5400</v>
+        <v>2500</v>
       </c>
       <c r="F1564" s="6"/>
       <c r="G1564" s="6" t="s">
@@ -48644,13 +48659,13 @@
         <v>447</v>
       </c>
       <c r="C1565" s="19" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="D1565" s="7">
-        <v>4000</v>
+        <v>14800</v>
       </c>
       <c r="E1565" s="6">
-        <v>600</v>
+        <v>2300</v>
       </c>
       <c r="F1565" s="6"/>
       <c r="G1565" s="6" t="s">
@@ -48671,13 +48686,13 @@
         <v>447</v>
       </c>
       <c r="C1566" s="19" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="D1566" s="7">
-        <v>4200</v>
+        <v>14800</v>
       </c>
       <c r="E1566" s="6">
-        <v>700</v>
+        <v>2300</v>
       </c>
       <c r="F1566" s="6"/>
       <c r="G1566" s="6" t="s">
@@ -48698,13 +48713,13 @@
         <v>447</v>
       </c>
       <c r="C1567" s="19" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="D1567" s="7">
-        <v>8300</v>
+        <v>9000</v>
       </c>
       <c r="E1567" s="6">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="F1567" s="6"/>
       <c r="G1567" s="6" t="s">
@@ -48725,13 +48740,13 @@
         <v>447</v>
       </c>
       <c r="C1568" s="19" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="D1568" s="7">
-        <v>7900</v>
+        <v>34900</v>
       </c>
       <c r="E1568" s="6">
-        <v>1200</v>
+        <v>5400</v>
       </c>
       <c r="F1568" s="6"/>
       <c r="G1568" s="6" t="s">
@@ -48752,13 +48767,13 @@
         <v>447</v>
       </c>
       <c r="C1569" s="19" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="D1569" s="7">
-        <v>7900</v>
+        <v>4000</v>
       </c>
       <c r="E1569" s="6">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="F1569" s="6"/>
       <c r="G1569" s="6" t="s">
@@ -48779,13 +48794,13 @@
         <v>447</v>
       </c>
       <c r="C1570" s="19" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="D1570" s="7">
-        <v>9900</v>
+        <v>4200</v>
       </c>
       <c r="E1570" s="6">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="F1570" s="6"/>
       <c r="G1570" s="6" t="s">
@@ -48806,13 +48821,13 @@
         <v>447</v>
       </c>
       <c r="C1571" s="19" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="D1571" s="7">
-        <v>12600</v>
+        <v>8300</v>
       </c>
       <c r="E1571" s="6">
-        <v>2000</v>
+        <v>1300</v>
       </c>
       <c r="F1571" s="6"/>
       <c r="G1571" s="6" t="s">
@@ -48833,13 +48848,13 @@
         <v>447</v>
       </c>
       <c r="C1572" s="19" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="D1572" s="7">
-        <v>33200</v>
+        <v>7900</v>
       </c>
       <c r="E1572" s="6">
-        <v>5100</v>
+        <v>1200</v>
       </c>
       <c r="F1572" s="6"/>
       <c r="G1572" s="6" t="s">
@@ -48860,13 +48875,13 @@
         <v>447</v>
       </c>
       <c r="C1573" s="19" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="D1573" s="7">
-        <v>27600</v>
+        <v>7900</v>
       </c>
       <c r="E1573" s="6">
-        <v>4300</v>
+        <v>1200</v>
       </c>
       <c r="F1573" s="6"/>
       <c r="G1573" s="6" t="s">
@@ -48887,13 +48902,13 @@
         <v>447</v>
       </c>
       <c r="C1574" s="19" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="D1574" s="7">
-        <v>29400</v>
+        <v>9900</v>
       </c>
       <c r="E1574" s="6">
-        <v>4600</v>
+        <v>1500</v>
       </c>
       <c r="F1574" s="6"/>
       <c r="G1574" s="6" t="s">
@@ -48914,13 +48929,13 @@
         <v>447</v>
       </c>
       <c r="C1575" s="19" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="D1575" s="7">
-        <v>25800</v>
+        <v>12600</v>
       </c>
       <c r="E1575" s="6">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="F1575" s="6"/>
       <c r="G1575" s="6" t="s">
@@ -48941,13 +48956,13 @@
         <v>447</v>
       </c>
       <c r="C1576" s="19" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="D1576" s="7">
-        <v>19391</v>
+        <v>33200</v>
       </c>
       <c r="E1576" s="6">
-        <v>3000</v>
+        <v>5100</v>
       </c>
       <c r="F1576" s="6"/>
       <c r="G1576" s="6" t="s">
@@ -48968,13 +48983,13 @@
         <v>447</v>
       </c>
       <c r="C1577" s="19" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="D1577" s="7">
-        <v>19391</v>
+        <v>27600</v>
       </c>
       <c r="E1577" s="6">
-        <v>3000</v>
+        <v>4300</v>
       </c>
       <c r="F1577" s="6"/>
       <c r="G1577" s="6" t="s">
@@ -48995,13 +49010,13 @@
         <v>447</v>
       </c>
       <c r="C1578" s="19" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="D1578" s="7">
-        <v>21100</v>
+        <v>29400</v>
       </c>
       <c r="E1578" s="6">
-        <v>3300</v>
+        <v>4600</v>
       </c>
       <c r="F1578" s="6"/>
       <c r="G1578" s="6" t="s">
@@ -49022,13 +49037,13 @@
         <v>447</v>
       </c>
       <c r="C1579" s="19" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="D1579" s="7">
-        <v>7500</v>
+        <v>25800</v>
       </c>
       <c r="E1579" s="6">
-        <v>1200</v>
+        <v>4000</v>
       </c>
       <c r="F1579" s="6"/>
       <c r="G1579" s="6" t="s">
@@ -49049,13 +49064,13 @@
         <v>447</v>
       </c>
       <c r="C1580" s="19" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="D1580" s="7">
-        <v>8500</v>
+        <v>19391</v>
       </c>
       <c r="E1580" s="6">
-        <v>1300</v>
+        <v>3000</v>
       </c>
       <c r="F1580" s="6"/>
       <c r="G1580" s="6" t="s">
@@ -49076,13 +49091,13 @@
         <v>447</v>
       </c>
       <c r="C1581" s="19" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="D1581" s="7">
-        <v>4300</v>
+        <v>19391</v>
       </c>
       <c r="E1581" s="6">
-        <v>700</v>
+        <v>3000</v>
       </c>
       <c r="F1581" s="6"/>
       <c r="G1581" s="6" t="s">
@@ -49103,13 +49118,13 @@
         <v>447</v>
       </c>
       <c r="C1582" s="19" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="D1582" s="7">
-        <v>8800</v>
+        <v>21100</v>
       </c>
       <c r="E1582" s="6">
-        <v>1400</v>
+        <v>3300</v>
       </c>
       <c r="F1582" s="6"/>
       <c r="G1582" s="6" t="s">
@@ -49130,13 +49145,13 @@
         <v>447</v>
       </c>
       <c r="C1583" s="19" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="D1583" s="7">
-        <v>8800</v>
+        <v>7500</v>
       </c>
       <c r="E1583" s="6">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="F1583" s="6"/>
       <c r="G1583" s="6" t="s">
@@ -49157,13 +49172,13 @@
         <v>447</v>
       </c>
       <c r="C1584" s="19" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="D1584" s="7">
-        <v>7900</v>
+        <v>8500</v>
       </c>
       <c r="E1584" s="6">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="F1584" s="6"/>
       <c r="G1584" s="6" t="s">
@@ -49184,13 +49199,13 @@
         <v>447</v>
       </c>
       <c r="C1585" s="19" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="D1585" s="7">
-        <v>32900</v>
+        <v>4300</v>
       </c>
       <c r="E1585" s="6">
-        <v>5100</v>
+        <v>700</v>
       </c>
       <c r="F1585" s="6"/>
       <c r="G1585" s="6" t="s">
@@ -49211,13 +49226,13 @@
         <v>447</v>
       </c>
       <c r="C1586" s="19" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="D1586" s="7">
-        <v>7700</v>
+        <v>8800</v>
       </c>
       <c r="E1586" s="6">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="F1586" s="6"/>
       <c r="G1586" s="6" t="s">
@@ -49238,13 +49253,13 @@
         <v>447</v>
       </c>
       <c r="C1587" s="19" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="D1587" s="7">
-        <v>21300</v>
+        <v>8800</v>
       </c>
       <c r="E1587" s="6">
-        <v>3300</v>
+        <v>1400</v>
       </c>
       <c r="F1587" s="6"/>
       <c r="G1587" s="6" t="s">
@@ -49265,13 +49280,13 @@
         <v>447</v>
       </c>
       <c r="C1588" s="19" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D1588" s="7">
-        <v>16300</v>
+        <v>7900</v>
       </c>
       <c r="E1588" s="6">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="F1588" s="6"/>
       <c r="G1588" s="6" t="s">
@@ -49292,13 +49307,13 @@
         <v>447</v>
       </c>
       <c r="C1589" s="19" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="D1589" s="7">
-        <v>12200</v>
+        <v>32900</v>
       </c>
       <c r="E1589" s="6">
-        <v>1900</v>
+        <v>5100</v>
       </c>
       <c r="F1589" s="6"/>
       <c r="G1589" s="6" t="s">
@@ -49319,13 +49334,13 @@
         <v>447</v>
       </c>
       <c r="C1590" s="19" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="D1590" s="7">
-        <v>9400</v>
+        <v>7700</v>
       </c>
       <c r="E1590" s="6">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="F1590" s="6"/>
       <c r="G1590" s="6" t="s">
@@ -49346,13 +49361,13 @@
         <v>447</v>
       </c>
       <c r="C1591" s="19" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="D1591" s="7">
-        <v>10300</v>
+        <v>21300</v>
       </c>
       <c r="E1591" s="6">
-        <v>1600</v>
+        <v>3300</v>
       </c>
       <c r="F1591" s="6"/>
       <c r="G1591" s="6" t="s">
@@ -49373,13 +49388,13 @@
         <v>447</v>
       </c>
       <c r="C1592" s="19" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D1592" s="7">
-        <v>14300</v>
+        <v>16300</v>
       </c>
       <c r="E1592" s="6">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="F1592" s="6"/>
       <c r="G1592" s="6" t="s">
@@ -49400,13 +49415,13 @@
         <v>447</v>
       </c>
       <c r="C1593" s="19" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="D1593" s="7">
-        <v>8510</v>
+        <v>12200</v>
       </c>
       <c r="E1593" s="6">
-        <v>1300</v>
+        <v>1900</v>
       </c>
       <c r="F1593" s="6"/>
       <c r="G1593" s="6" t="s">
@@ -49427,10 +49442,10 @@
         <v>447</v>
       </c>
       <c r="C1594" s="19" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="D1594" s="7">
-        <v>9600</v>
+        <v>9400</v>
       </c>
       <c r="E1594" s="6">
         <v>1500</v>
@@ -49454,13 +49469,13 @@
         <v>447</v>
       </c>
       <c r="C1595" s="19" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="D1595" s="7">
-        <v>9400</v>
+        <v>10300</v>
       </c>
       <c r="E1595" s="6">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="F1595" s="6"/>
       <c r="G1595" s="6" t="s">
@@ -49481,13 +49496,13 @@
         <v>447</v>
       </c>
       <c r="C1596" s="19" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="D1596" s="7">
-        <v>7700</v>
+        <v>14300</v>
       </c>
       <c r="E1596" s="6">
-        <v>1200</v>
+        <v>2200</v>
       </c>
       <c r="F1596" s="6"/>
       <c r="G1596" s="6" t="s">
@@ -49508,13 +49523,13 @@
         <v>447</v>
       </c>
       <c r="C1597" s="19" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D1597" s="7">
-        <v>5900</v>
+        <v>8510</v>
       </c>
       <c r="E1597" s="6">
-        <v>900</v>
+        <v>1300</v>
       </c>
       <c r="F1597" s="6"/>
       <c r="G1597" s="6" t="s">
@@ -49535,13 +49550,13 @@
         <v>447</v>
       </c>
       <c r="C1598" s="19" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="D1598" s="7">
-        <v>5900</v>
+        <v>9600</v>
       </c>
       <c r="E1598" s="6">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="F1598" s="6"/>
       <c r="G1598" s="6" t="s">
@@ -49562,13 +49577,13 @@
         <v>447</v>
       </c>
       <c r="C1599" s="19" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="D1599" s="7">
-        <v>7952</v>
+        <v>9400</v>
       </c>
       <c r="E1599" s="6">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="F1599" s="6"/>
       <c r="G1599" s="6" t="s">
@@ -49589,13 +49604,13 @@
         <v>447</v>
       </c>
       <c r="C1600" s="19" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="D1600" s="7">
-        <v>44035</v>
+        <v>7700</v>
       </c>
       <c r="E1600" s="6">
-        <v>6800</v>
+        <v>1200</v>
       </c>
       <c r="F1600" s="6"/>
       <c r="G1600" s="6" t="s">
@@ -49616,13 +49631,13 @@
         <v>447</v>
       </c>
       <c r="C1601" s="19" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="D1601" s="7">
-        <v>8045</v>
+        <v>5900</v>
       </c>
       <c r="E1601" s="6">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="F1601" s="6"/>
       <c r="G1601" s="6" t="s">
@@ -49643,13 +49658,13 @@
         <v>447</v>
       </c>
       <c r="C1602" s="19" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="D1602" s="7">
-        <v>15857</v>
+        <v>5900</v>
       </c>
       <c r="E1602" s="6">
-        <v>2500</v>
+        <v>900</v>
       </c>
       <c r="F1602" s="6"/>
       <c r="G1602" s="6" t="s">
@@ -49670,13 +49685,13 @@
         <v>447</v>
       </c>
       <c r="C1603" s="19" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="D1603" s="7">
-        <v>16415</v>
+        <v>7952</v>
       </c>
       <c r="E1603" s="6">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="F1603" s="6"/>
       <c r="G1603" s="6" t="s">
@@ -49697,13 +49712,13 @@
         <v>447</v>
       </c>
       <c r="C1604" s="19" t="s">
-        <v>675</v>
+        <v>702</v>
       </c>
       <c r="D1604" s="7">
-        <v>27854</v>
+        <v>44035</v>
       </c>
       <c r="E1604" s="6">
-        <v>3900</v>
+        <v>6800</v>
       </c>
       <c r="F1604" s="6"/>
       <c r="G1604" s="6" t="s">
@@ -49724,13 +49739,13 @@
         <v>447</v>
       </c>
       <c r="C1605" s="19" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="D1605" s="7">
-        <v>6929</v>
+        <v>8045</v>
       </c>
       <c r="E1605" s="6">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="F1605" s="6"/>
       <c r="G1605" s="6" t="s">
@@ -49751,13 +49766,13 @@
         <v>447</v>
       </c>
       <c r="C1606" s="19" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="D1606" s="7">
-        <v>7855</v>
+        <v>15857</v>
       </c>
       <c r="E1606" s="6">
-        <v>1100</v>
+        <v>2500</v>
       </c>
       <c r="F1606" s="6"/>
       <c r="G1606" s="6" t="s">
@@ -49778,13 +49793,13 @@
         <v>447</v>
       </c>
       <c r="C1607" s="19" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="D1607" s="7">
-        <v>21158</v>
+        <v>16415</v>
       </c>
       <c r="E1607" s="6">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="F1607" s="6"/>
       <c r="G1607" s="6" t="s">
@@ -49805,13 +49820,13 @@
         <v>447</v>
       </c>
       <c r="C1608" s="19" t="s">
-        <v>709</v>
+        <v>675</v>
       </c>
       <c r="D1608" s="7">
-        <v>19949</v>
+        <v>27854</v>
       </c>
       <c r="E1608" s="6">
-        <v>2800</v>
+        <v>3900</v>
       </c>
       <c r="F1608" s="6"/>
       <c r="G1608" s="6" t="s">
@@ -49832,13 +49847,13 @@
         <v>447</v>
       </c>
       <c r="C1609" s="19" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="D1609" s="7">
-        <v>9626</v>
+        <v>6929</v>
       </c>
       <c r="E1609" s="6">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="F1609" s="6"/>
       <c r="G1609" s="6" t="s">
@@ -49859,13 +49874,13 @@
         <v>447</v>
       </c>
       <c r="C1610" s="19" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="D1610" s="7">
-        <v>9719</v>
+        <v>7855</v>
       </c>
       <c r="E1610" s="6">
-        <v>1400</v>
+        <v>1100</v>
       </c>
       <c r="F1610" s="6"/>
       <c r="G1610" s="6" t="s">
@@ -49886,13 +49901,13 @@
         <v>447</v>
       </c>
       <c r="C1611" s="19" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="D1611" s="7">
-        <v>12974</v>
+        <v>21158</v>
       </c>
       <c r="E1611" s="6">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="F1611" s="6"/>
       <c r="G1611" s="6" t="s">
@@ -49913,13 +49928,13 @@
         <v>447</v>
       </c>
       <c r="C1612" s="19" t="s">
-        <v>1467</v>
+        <v>709</v>
       </c>
       <c r="D1612" s="7">
-        <v>21344</v>
+        <v>19949</v>
       </c>
       <c r="E1612" s="6">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="F1612" s="6"/>
       <c r="G1612" s="6" t="s">
@@ -49940,13 +49955,13 @@
         <v>447</v>
       </c>
       <c r="C1613" s="19" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="D1613" s="7">
-        <v>14276</v>
+        <v>9626</v>
       </c>
       <c r="E1613" s="6">
-        <v>2000</v>
+        <v>1300</v>
       </c>
       <c r="F1613" s="6"/>
       <c r="G1613" s="6" t="s">
@@ -49967,13 +49982,13 @@
         <v>447</v>
       </c>
       <c r="C1614" s="19" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="D1614" s="7">
-        <v>14276</v>
+        <v>9719</v>
       </c>
       <c r="E1614" s="6">
-        <v>2000</v>
+        <v>1400</v>
       </c>
       <c r="F1614" s="6"/>
       <c r="G1614" s="6" t="s">
@@ -49994,13 +50009,13 @@
         <v>447</v>
       </c>
       <c r="C1615" s="19" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="D1615" s="7">
-        <v>15950</v>
+        <v>12974</v>
       </c>
       <c r="E1615" s="6">
-        <v>2200</v>
+        <v>1800</v>
       </c>
       <c r="F1615" s="6"/>
       <c r="G1615" s="6" t="s">
@@ -50021,13 +50036,13 @@
         <v>447</v>
       </c>
       <c r="C1616" s="19" t="s">
-        <v>716</v>
+        <v>1467</v>
       </c>
       <c r="D1616" s="7">
-        <v>28970</v>
+        <v>21344</v>
       </c>
       <c r="E1616" s="6">
-        <v>4100</v>
+        <v>3000</v>
       </c>
       <c r="F1616" s="6"/>
       <c r="G1616" s="6" t="s">
@@ -50042,19 +50057,19 @@
     </row>
     <row r="1617" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1617" s="6" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1617" s="6" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1617" s="19" t="s">
-        <v>1061</v>
+        <v>713</v>
       </c>
       <c r="D1617" s="7">
-        <v>41000</v>
+        <v>14276</v>
       </c>
       <c r="E1617" s="6">
-        <v>4100</v>
+        <v>2000</v>
       </c>
       <c r="F1617" s="6"/>
       <c r="G1617" s="6" t="s">
@@ -50069,19 +50084,19 @@
     </row>
     <row r="1618" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1618" s="6" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1618" s="6" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1618" s="19" t="s">
-        <v>1062</v>
+        <v>714</v>
       </c>
       <c r="D1618" s="7">
-        <v>55000</v>
+        <v>14276</v>
       </c>
       <c r="E1618" s="6">
-        <v>5500</v>
+        <v>2000</v>
       </c>
       <c r="F1618" s="6"/>
       <c r="G1618" s="6" t="s">
@@ -50096,19 +50111,19 @@
     </row>
     <row r="1619" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1619" s="6" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1619" s="6" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1619" s="19" t="s">
-        <v>1063</v>
+        <v>715</v>
       </c>
       <c r="D1619" s="7">
-        <v>45000</v>
+        <v>15950</v>
       </c>
       <c r="E1619" s="6">
-        <v>4500</v>
+        <v>2200</v>
       </c>
       <c r="F1619" s="6"/>
       <c r="G1619" s="6" t="s">
@@ -50123,19 +50138,19 @@
     </row>
     <row r="1620" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1620" s="6" t="s">
-        <v>1080</v>
+        <v>728</v>
       </c>
       <c r="B1620" s="6" t="s">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="C1620" s="19" t="s">
-        <v>1064</v>
+        <v>716</v>
       </c>
       <c r="D1620" s="7">
-        <v>63000</v>
+        <v>28970</v>
       </c>
       <c r="E1620" s="6">
-        <v>6300</v>
+        <v>4100</v>
       </c>
       <c r="F1620" s="6"/>
       <c r="G1620" s="6" t="s">
@@ -50156,13 +50171,13 @@
         <v>207</v>
       </c>
       <c r="C1621" s="19" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="D1621" s="7">
-        <v>60000</v>
+        <v>41000</v>
       </c>
       <c r="E1621" s="6">
-        <v>6000</v>
+        <v>4100</v>
       </c>
       <c r="F1621" s="6"/>
       <c r="G1621" s="6" t="s">
@@ -50183,13 +50198,13 @@
         <v>207</v>
       </c>
       <c r="C1622" s="19" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="D1622" s="7">
-        <v>42000</v>
+        <v>55000</v>
       </c>
       <c r="E1622" s="6">
-        <v>4200</v>
+        <v>5500</v>
       </c>
       <c r="F1622" s="6"/>
       <c r="G1622" s="6" t="s">
@@ -50210,13 +50225,13 @@
         <v>207</v>
       </c>
       <c r="C1623" s="19" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="D1623" s="7">
-        <v>64000</v>
+        <v>45000</v>
       </c>
       <c r="E1623" s="6">
-        <v>6400</v>
+        <v>4500</v>
       </c>
       <c r="F1623" s="6"/>
       <c r="G1623" s="6" t="s">
@@ -50237,13 +50252,13 @@
         <v>207</v>
       </c>
       <c r="C1624" s="19" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="D1624" s="7">
-        <v>78000</v>
+        <v>63000</v>
       </c>
       <c r="E1624" s="6">
-        <v>7800</v>
+        <v>6300</v>
       </c>
       <c r="F1624" s="6"/>
       <c r="G1624" s="6" t="s">
@@ -50264,13 +50279,13 @@
         <v>207</v>
       </c>
       <c r="C1625" s="19" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="D1625" s="7">
-        <v>83000</v>
+        <v>60000</v>
       </c>
       <c r="E1625" s="6">
-        <v>8300</v>
+        <v>6000</v>
       </c>
       <c r="F1625" s="6"/>
       <c r="G1625" s="6" t="s">
@@ -50291,13 +50306,13 @@
         <v>207</v>
       </c>
       <c r="C1626" s="19" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="D1626" s="7">
-        <v>106000</v>
+        <v>42000</v>
       </c>
       <c r="E1626" s="6">
-        <v>10600</v>
+        <v>4200</v>
       </c>
       <c r="F1626" s="6"/>
       <c r="G1626" s="6" t="s">
@@ -50318,13 +50333,13 @@
         <v>207</v>
       </c>
       <c r="C1627" s="19" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="D1627" s="7">
-        <v>81000</v>
+        <v>64000</v>
       </c>
       <c r="E1627" s="6">
-        <v>8100</v>
+        <v>6400</v>
       </c>
       <c r="F1627" s="6"/>
       <c r="G1627" s="6" t="s">
@@ -50345,13 +50360,13 @@
         <v>207</v>
       </c>
       <c r="C1628" s="19" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="D1628" s="7">
-        <v>84000</v>
+        <v>78000</v>
       </c>
       <c r="E1628" s="6">
-        <v>8400</v>
+        <v>7800</v>
       </c>
       <c r="F1628" s="6"/>
       <c r="G1628" s="6" t="s">
@@ -50372,13 +50387,13 @@
         <v>207</v>
       </c>
       <c r="C1629" s="19" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="D1629" s="7">
-        <v>120000</v>
+        <v>83000</v>
       </c>
       <c r="E1629" s="6">
-        <v>12000</v>
+        <v>8300</v>
       </c>
       <c r="F1629" s="6"/>
       <c r="G1629" s="6" t="s">
@@ -50399,13 +50414,13 @@
         <v>207</v>
       </c>
       <c r="C1630" s="19" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="D1630" s="7">
-        <v>113000</v>
+        <v>106000</v>
       </c>
       <c r="E1630" s="6">
-        <v>11300</v>
+        <v>10600</v>
       </c>
       <c r="F1630" s="6"/>
       <c r="G1630" s="6" t="s">
@@ -50426,13 +50441,13 @@
         <v>207</v>
       </c>
       <c r="C1631" s="19" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="D1631" s="7">
-        <v>141000</v>
+        <v>81000</v>
       </c>
       <c r="E1631" s="6">
-        <v>14100</v>
+        <v>8100</v>
       </c>
       <c r="F1631" s="6"/>
       <c r="G1631" s="6" t="s">
@@ -50453,13 +50468,13 @@
         <v>207</v>
       </c>
       <c r="C1632" s="19" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="D1632" s="7">
-        <v>141000</v>
+        <v>84000</v>
       </c>
       <c r="E1632" s="6">
-        <v>14100</v>
+        <v>8400</v>
       </c>
       <c r="F1632" s="6"/>
       <c r="G1632" s="6" t="s">
@@ -50480,13 +50495,13 @@
         <v>207</v>
       </c>
       <c r="C1633" s="19" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="D1633" s="7">
-        <v>169000</v>
+        <v>120000</v>
       </c>
       <c r="E1633" s="6">
-        <v>16900</v>
+        <v>12000</v>
       </c>
       <c r="F1633" s="6"/>
       <c r="G1633" s="6" t="s">
@@ -50504,16 +50519,16 @@
         <v>1080</v>
       </c>
       <c r="B1634" s="6" t="s">
-        <v>401</v>
+        <v>207</v>
       </c>
       <c r="C1634" s="19" t="s">
-        <v>1249</v>
+        <v>1074</v>
       </c>
       <c r="D1634" s="7">
-        <v>47240</v>
+        <v>113000</v>
       </c>
       <c r="E1634" s="6">
-        <v>6400</v>
+        <v>11300</v>
       </c>
       <c r="F1634" s="6"/>
       <c r="G1634" s="6" t="s">
@@ -50531,16 +50546,16 @@
         <v>1080</v>
       </c>
       <c r="B1635" s="6" t="s">
-        <v>401</v>
+        <v>207</v>
       </c>
       <c r="C1635" s="19" t="s">
-        <v>1250</v>
+        <v>1075</v>
       </c>
       <c r="D1635" s="7">
-        <v>71600</v>
+        <v>141000</v>
       </c>
       <c r="E1635" s="6">
-        <v>9700</v>
+        <v>14100</v>
       </c>
       <c r="F1635" s="6"/>
       <c r="G1635" s="6" t="s">
@@ -50558,16 +50573,16 @@
         <v>1080</v>
       </c>
       <c r="B1636" s="6" t="s">
-        <v>401</v>
+        <v>207</v>
       </c>
       <c r="C1636" s="19" t="s">
-        <v>1251</v>
+        <v>1076</v>
       </c>
       <c r="D1636" s="7">
-        <v>87720</v>
+        <v>141000</v>
       </c>
       <c r="E1636" s="6">
-        <v>11800</v>
+        <v>14100</v>
       </c>
       <c r="F1636" s="6"/>
       <c r="G1636" s="6" t="s">
@@ -50585,16 +50600,16 @@
         <v>1080</v>
       </c>
       <c r="B1637" s="6" t="s">
-        <v>401</v>
+        <v>207</v>
       </c>
       <c r="C1637" s="19" t="s">
-        <v>1252</v>
+        <v>1077</v>
       </c>
       <c r="D1637" s="7">
-        <v>124360</v>
+        <v>169000</v>
       </c>
       <c r="E1637" s="6">
-        <v>16800</v>
+        <v>16900</v>
       </c>
       <c r="F1637" s="6"/>
       <c r="G1637" s="6" t="s">
@@ -50615,13 +50630,13 @@
         <v>401</v>
       </c>
       <c r="C1638" s="19" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
       <c r="D1638" s="7">
-        <v>178440</v>
+        <v>47240</v>
       </c>
       <c r="E1638" s="6">
-        <v>24100</v>
+        <v>6400</v>
       </c>
       <c r="F1638" s="6"/>
       <c r="G1638" s="6" t="s">
@@ -50642,13 +50657,13 @@
         <v>401</v>
       </c>
       <c r="C1639" s="19" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="D1639" s="7">
-        <v>258920</v>
+        <v>71600</v>
       </c>
       <c r="E1639" s="6">
-        <v>35000</v>
+        <v>9700</v>
       </c>
       <c r="F1639" s="6"/>
       <c r="G1639" s="6" t="s">
@@ -50669,13 +50684,13 @@
         <v>401</v>
       </c>
       <c r="C1640" s="19" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="D1640" s="7">
-        <v>236130</v>
+        <v>87720</v>
       </c>
       <c r="E1640" s="6">
-        <v>31900</v>
+        <v>11800</v>
       </c>
       <c r="F1640" s="6"/>
       <c r="G1640" s="6" t="s">
@@ -50696,13 +50711,13 @@
         <v>401</v>
       </c>
       <c r="C1641" s="19" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="D1641" s="7">
-        <v>329950</v>
+        <v>124360</v>
       </c>
       <c r="E1641" s="6">
-        <v>44500</v>
+        <v>16800</v>
       </c>
       <c r="F1641" s="6"/>
       <c r="G1641" s="6" t="s">
@@ -50717,27 +50732,26 @@
     </row>
     <row r="1642" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1642" s="6" t="s">
-        <v>1438</v>
+        <v>1080</v>
       </c>
       <c r="B1642" s="6" t="s">
-        <v>1442</v>
+        <v>401</v>
       </c>
       <c r="C1642" s="19" t="s">
-        <v>1680</v>
+        <v>1253</v>
       </c>
       <c r="D1642" s="7">
-        <f>E1642*10</f>
-        <v>256000</v>
+        <v>178440</v>
       </c>
       <c r="E1642" s="6">
-        <v>25600</v>
+        <v>24100</v>
       </c>
       <c r="F1642" s="6"/>
       <c r="G1642" s="6" t="s">
-        <v>1690</v>
+        <v>1459</v>
       </c>
       <c r="H1642" s="6" t="s">
-        <v>1455</v>
+        <v>206</v>
       </c>
       <c r="I1642" s="6">
         <v>2026</v>
@@ -50745,27 +50759,26 @@
     </row>
     <row r="1643" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1643" s="6" t="s">
-        <v>1438</v>
+        <v>1080</v>
       </c>
       <c r="B1643" s="6" t="s">
-        <v>1442</v>
+        <v>401</v>
       </c>
       <c r="C1643" s="19" t="s">
-        <v>1681</v>
+        <v>1254</v>
       </c>
       <c r="D1643" s="7">
-        <f t="shared" ref="D1643:D1652" si="0">E1643*10</f>
-        <v>324000</v>
+        <v>258920</v>
       </c>
       <c r="E1643" s="6">
-        <v>32400</v>
+        <v>35000</v>
       </c>
       <c r="F1643" s="6"/>
       <c r="G1643" s="6" t="s">
-        <v>1691</v>
+        <v>1459</v>
       </c>
       <c r="H1643" s="6" t="s">
-        <v>1455</v>
+        <v>206</v>
       </c>
       <c r="I1643" s="6">
         <v>2026</v>
@@ -50773,27 +50786,26 @@
     </row>
     <row r="1644" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1644" s="6" t="s">
-        <v>1438</v>
+        <v>1080</v>
       </c>
       <c r="B1644" s="6" t="s">
-        <v>1442</v>
+        <v>401</v>
       </c>
       <c r="C1644" s="19" t="s">
-        <v>1682</v>
+        <v>1255</v>
       </c>
       <c r="D1644" s="7">
-        <f t="shared" si="0"/>
-        <v>404000</v>
+        <v>236130</v>
       </c>
       <c r="E1644" s="6">
-        <v>40400</v>
+        <v>31900</v>
       </c>
       <c r="F1644" s="6"/>
       <c r="G1644" s="6" t="s">
-        <v>1692</v>
+        <v>1459</v>
       </c>
       <c r="H1644" s="6" t="s">
-        <v>1455</v>
+        <v>206</v>
       </c>
       <c r="I1644" s="6">
         <v>2026</v>
@@ -50801,27 +50813,26 @@
     </row>
     <row r="1645" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1645" s="6" t="s">
-        <v>1438</v>
+        <v>1080</v>
       </c>
       <c r="B1645" s="6" t="s">
-        <v>1442</v>
+        <v>401</v>
       </c>
       <c r="C1645" s="19" t="s">
-        <v>1683</v>
+        <v>1256</v>
       </c>
       <c r="D1645" s="7">
-        <f t="shared" si="0"/>
-        <v>297000</v>
+        <v>329950</v>
       </c>
       <c r="E1645" s="6">
-        <v>29700</v>
+        <v>44500</v>
       </c>
       <c r="F1645" s="6"/>
       <c r="G1645" s="6" t="s">
-        <v>1693</v>
+        <v>1459</v>
       </c>
       <c r="H1645" s="6" t="s">
-        <v>1455</v>
+        <v>206</v>
       </c>
       <c r="I1645" s="6">
         <v>2026</v>
@@ -50835,18 +50846,18 @@
         <v>1442</v>
       </c>
       <c r="C1646" s="19" t="s">
-        <v>1684</v>
+        <v>1680</v>
       </c>
       <c r="D1646" s="7">
-        <f t="shared" si="0"/>
-        <v>310000</v>
+        <f>E1646*10</f>
+        <v>256000</v>
       </c>
       <c r="E1646" s="6">
-        <v>31000</v>
+        <v>25600</v>
       </c>
       <c r="F1646" s="6"/>
       <c r="G1646" s="6" t="s">
-        <v>1694</v>
+        <v>1690</v>
       </c>
       <c r="H1646" s="6" t="s">
         <v>1455</v>
@@ -50863,18 +50874,18 @@
         <v>1442</v>
       </c>
       <c r="C1647" s="19" t="s">
-        <v>1685</v>
+        <v>1681</v>
       </c>
       <c r="D1647" s="7">
-        <f t="shared" si="0"/>
-        <v>337000</v>
+        <f t="shared" ref="D1647:D1656" si="0">E1647*10</f>
+        <v>324000</v>
       </c>
       <c r="E1647" s="6">
-        <v>33700</v>
+        <v>32400</v>
       </c>
       <c r="F1647" s="6"/>
       <c r="G1647" s="6" t="s">
-        <v>1695</v>
+        <v>1691</v>
       </c>
       <c r="H1647" s="6" t="s">
         <v>1455</v>
@@ -50891,18 +50902,18 @@
         <v>1442</v>
       </c>
       <c r="C1648" s="19" t="s">
-        <v>1686</v>
+        <v>1682</v>
       </c>
       <c r="D1648" s="7">
         <f t="shared" si="0"/>
-        <v>351000</v>
+        <v>404000</v>
       </c>
       <c r="E1648" s="6">
-        <v>35100</v>
+        <v>40400</v>
       </c>
       <c r="F1648" s="6"/>
       <c r="G1648" s="6" t="s">
-        <v>1695</v>
+        <v>1692</v>
       </c>
       <c r="H1648" s="6" t="s">
         <v>1455</v>
@@ -50919,18 +50930,18 @@
         <v>1442</v>
       </c>
       <c r="C1649" s="19" t="s">
-        <v>1687</v>
+        <v>1683</v>
       </c>
       <c r="D1649" s="7">
         <f t="shared" si="0"/>
-        <v>378000</v>
+        <v>297000</v>
       </c>
       <c r="E1649" s="6">
-        <v>37800</v>
+        <v>29700</v>
       </c>
       <c r="F1649" s="6"/>
       <c r="G1649" s="6" t="s">
-        <v>1696</v>
+        <v>1693</v>
       </c>
       <c r="H1649" s="6" t="s">
         <v>1455</v>
@@ -50947,18 +50958,18 @@
         <v>1442</v>
       </c>
       <c r="C1650" s="19" t="s">
-        <v>1688</v>
+        <v>1684</v>
       </c>
       <c r="D1650" s="7">
         <f t="shared" si="0"/>
-        <v>526000</v>
+        <v>310000</v>
       </c>
       <c r="E1650" s="6">
-        <v>52600</v>
+        <v>31000</v>
       </c>
       <c r="F1650" s="6"/>
       <c r="G1650" s="6" t="s">
-        <v>1697</v>
+        <v>1694</v>
       </c>
       <c r="H1650" s="6" t="s">
         <v>1455</v>
@@ -50975,18 +50986,18 @@
         <v>1442</v>
       </c>
       <c r="C1651" s="19" t="s">
-        <v>1689</v>
+        <v>1685</v>
       </c>
       <c r="D1651" s="7">
         <f t="shared" si="0"/>
-        <v>742000</v>
+        <v>337000</v>
       </c>
       <c r="E1651" s="6">
-        <v>74200</v>
+        <v>33700</v>
       </c>
       <c r="F1651" s="6"/>
       <c r="G1651" s="6" t="s">
-        <v>1698</v>
+        <v>1695</v>
       </c>
       <c r="H1651" s="6" t="s">
         <v>1455</v>
@@ -50997,24 +51008,24 @@
     </row>
     <row r="1652" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1652" s="6" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B1652" s="6" t="s">
         <v>1442</v>
       </c>
       <c r="C1652" s="19" t="s">
-        <v>1440</v>
+        <v>1686</v>
       </c>
       <c r="D1652" s="7">
         <f t="shared" si="0"/>
-        <v>567000</v>
+        <v>351000</v>
       </c>
       <c r="E1652" s="6">
-        <v>56700</v>
+        <v>35100</v>
       </c>
       <c r="F1652" s="6"/>
       <c r="G1652" s="6" t="s">
-        <v>1459</v>
+        <v>1695</v>
       </c>
       <c r="H1652" s="6" t="s">
         <v>1455</v>
@@ -51025,23 +51036,24 @@
     </row>
     <row r="1653" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1653" s="6" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="B1653" s="6" t="s">
         <v>1442</v>
       </c>
       <c r="C1653" s="19" t="s">
-        <v>1443</v>
+        <v>1687</v>
       </c>
       <c r="D1653" s="7">
-        <v>250000</v>
+        <f t="shared" si="0"/>
+        <v>378000</v>
       </c>
       <c r="E1653" s="6">
-        <v>25000</v>
+        <v>37800</v>
       </c>
       <c r="F1653" s="6"/>
       <c r="G1653" s="6" t="s">
-        <v>1459</v>
+        <v>1696</v>
       </c>
       <c r="H1653" s="6" t="s">
         <v>1455</v>
@@ -51052,23 +51064,24 @@
     </row>
     <row r="1654" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1654" s="6" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="B1654" s="6" t="s">
         <v>1442</v>
       </c>
       <c r="C1654" s="19" t="s">
-        <v>1444</v>
+        <v>1688</v>
       </c>
       <c r="D1654" s="7">
-        <v>236000</v>
+        <f t="shared" si="0"/>
+        <v>526000</v>
       </c>
       <c r="E1654" s="6">
-        <v>23600</v>
+        <v>52600</v>
       </c>
       <c r="F1654" s="6"/>
       <c r="G1654" s="6" t="s">
-        <v>1459</v>
+        <v>1697</v>
       </c>
       <c r="H1654" s="6" t="s">
         <v>1455</v>
@@ -51079,23 +51092,24 @@
     </row>
     <row r="1655" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1655" s="6" t="s">
-        <v>1445</v>
+        <v>1438</v>
       </c>
       <c r="B1655" s="6" t="s">
         <v>1442</v>
       </c>
       <c r="C1655" s="19" t="s">
-        <v>1446</v>
+        <v>1689</v>
       </c>
       <c r="D1655" s="7">
-        <v>312000</v>
+        <f t="shared" si="0"/>
+        <v>742000</v>
       </c>
       <c r="E1655" s="6">
-        <v>31200</v>
+        <v>74200</v>
       </c>
       <c r="F1655" s="6"/>
       <c r="G1655" s="6" t="s">
-        <v>1459</v>
+        <v>1698</v>
       </c>
       <c r="H1655" s="6" t="s">
         <v>1455</v>
@@ -51106,19 +51120,20 @@
     </row>
     <row r="1656" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1656" s="6" t="s">
-        <v>1445</v>
+        <v>1439</v>
       </c>
       <c r="B1656" s="6" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="C1656" s="19" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="D1656" s="7">
-        <v>156000</v>
+        <f t="shared" si="0"/>
+        <v>567000</v>
       </c>
       <c r="E1656" s="6">
-        <v>15600</v>
+        <v>56700</v>
       </c>
       <c r="F1656" s="6"/>
       <c r="G1656" s="6" t="s">
@@ -51133,19 +51148,19 @@
     </row>
     <row r="1657" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1657" s="6" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="B1657" s="6" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="C1657" s="19" t="s">
-        <v>1450</v>
+        <v>1443</v>
       </c>
       <c r="D1657" s="7">
-        <v>153000</v>
+        <v>250000</v>
       </c>
       <c r="E1657" s="6">
-        <v>15300</v>
+        <v>25000</v>
       </c>
       <c r="F1657" s="6"/>
       <c r="G1657" s="6" t="s">
@@ -51160,19 +51175,19 @@
     </row>
     <row r="1658" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1658" s="6" t="s">
-        <v>1451</v>
+        <v>1441</v>
       </c>
       <c r="B1658" s="6" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="C1658" s="19" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="D1658" s="7">
-        <v>153000</v>
+        <v>236000</v>
       </c>
       <c r="E1658" s="6">
-        <v>15300</v>
+        <v>23600</v>
       </c>
       <c r="F1658" s="6"/>
       <c r="G1658" s="6" t="s">
@@ -51187,19 +51202,19 @@
     </row>
     <row r="1659" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1659" s="6" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="B1659" s="6" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="C1659" s="19" t="s">
-        <v>1454</v>
+        <v>1446</v>
       </c>
       <c r="D1659" s="7">
-        <v>153000</v>
+        <v>312000</v>
       </c>
       <c r="E1659" s="6">
-        <v>15300</v>
+        <v>31200</v>
       </c>
       <c r="F1659" s="6"/>
       <c r="G1659" s="6" t="s">
@@ -51212,9 +51227,117 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="1660" spans="1:9" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="1660" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1660" s="6" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B1660" s="6" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C1660" s="19" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D1660" s="7">
+        <v>156000</v>
+      </c>
+      <c r="E1660" s="6">
+        <v>15600</v>
+      </c>
+      <c r="F1660" s="6"/>
+      <c r="G1660" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1660" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1660" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1661" s="6" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B1661" s="6" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C1661" s="19" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D1661" s="7">
+        <v>153000</v>
+      </c>
+      <c r="E1661" s="6">
+        <v>15300</v>
+      </c>
+      <c r="F1661" s="6"/>
+      <c r="G1661" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1661" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1661" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1662" s="6" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B1662" s="6" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C1662" s="19" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D1662" s="7">
+        <v>153000</v>
+      </c>
+      <c r="E1662" s="6">
+        <v>15300</v>
+      </c>
+      <c r="F1662" s="6"/>
+      <c r="G1662" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1662" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1662" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:9" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1663" s="6" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B1663" s="6" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C1663" s="19" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1663" s="7">
+        <v>153000</v>
+      </c>
+      <c r="E1663" s="6">
+        <v>15300</v>
+      </c>
+      <c r="F1663" s="6"/>
+      <c r="G1663" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1663" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1663" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:9" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:I1659" xr:uid="{B6FE0007-86B3-4D5F-9CBC-37B22BC3E091}"/>
+  <autoFilter ref="A1:I1663" xr:uid="{B6FE0007-86B3-4D5F-9CBC-37B22BC3E091}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/rates.xlsx
+++ b/rates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS COM\Dropbox\Rates Portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D87086BB-035D-4CC2-AB6B-3FC4FB1AFFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B290CC-88DF-437D-8F05-EDB751B5CEEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32894,10 +32894,10 @@
         <v>171</v>
       </c>
       <c r="D981" s="7">
-        <v>59000</v>
+        <v>56000</v>
       </c>
       <c r="E981" s="6">
-        <v>5900</v>
+        <v>5600</v>
       </c>
       <c r="F981" s="6"/>
       <c r="G981" s="6" t="s">
@@ -32921,10 +32921,10 @@
         <v>172</v>
       </c>
       <c r="D982" s="7">
-        <v>70000</v>
+        <v>66000</v>
       </c>
       <c r="E982" s="6">
-        <v>7000</v>
+        <v>6600</v>
       </c>
       <c r="F982" s="6"/>
       <c r="G982" s="6" t="s">
@@ -33191,10 +33191,10 @@
         <v>182</v>
       </c>
       <c r="D992" s="7">
-        <v>97000</v>
+        <v>91000</v>
       </c>
       <c r="E992" s="6">
-        <v>9700</v>
+        <v>9100</v>
       </c>
       <c r="F992" s="6"/>
       <c r="G992" s="6" t="s">
@@ -33218,10 +33218,10 @@
         <v>183</v>
       </c>
       <c r="D993" s="7">
-        <v>126000</v>
+        <v>122000</v>
       </c>
       <c r="E993" s="6">
-        <v>12600</v>
+        <v>12200</v>
       </c>
       <c r="F993" s="6"/>
       <c r="G993" s="6" t="s">
@@ -46991,7 +46991,7 @@
         <v>56000</v>
       </c>
       <c r="E1503" s="5">
-        <v>5900</v>
+        <v>5600</v>
       </c>
       <c r="F1503" s="5"/>
       <c r="G1503" s="5" t="s">
@@ -47018,7 +47018,7 @@
         <v>66000</v>
       </c>
       <c r="E1504" s="5">
-        <v>7000</v>
+        <v>6600</v>
       </c>
       <c r="F1504" s="5"/>
       <c r="G1504" s="5" t="s">
@@ -47045,7 +47045,7 @@
         <v>85000</v>
       </c>
       <c r="E1505" s="5">
-        <v>9100</v>
+        <v>8500</v>
       </c>
       <c r="F1505" s="5"/>
       <c r="G1505" s="5" t="s">

--- a/rates.xlsx
+++ b/rates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS COM\Dropbox\Rates Portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF21B4B9-F2F7-4A87-BC8F-A4BE053393BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3751C42-3866-41A3-8AFB-97034D4FF159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9947,7 +9947,7 @@
         <v>275</v>
       </c>
       <c r="D143" s="6">
-        <v>79111</v>
+        <v>72474</v>
       </c>
       <c r="E143" s="6">
         <v>11100</v>
